--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C6AA564-5593-4E21-8C75-66EE1999B8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D69055F-5D74-4241-89BB-E4EA3FEDA017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Inversionistas 26" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base Inversionistas 26'!$A$4:$Y$371</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gastos 26'!$A$4:$T$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gastos 26'!$A$4:$W$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="582">
   <si>
     <t>NO.</t>
   </si>
@@ -2000,7 +2000,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2047,9 +2047,6 @@
     <xf numFmtId="44" fontId="18" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2075,9 +2072,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="4" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2099,10 +2093,10 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="20" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2450,24 +2444,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="H1" s="43"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="3" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="H3" s="43"/>
-      <c r="J3" s="42">
+      <c r="H3" s="42"/>
+      <c r="J3" s="61">
         <v>2026</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="S3" s="42"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="61"/>
+      <c r="S3" s="61"/>
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -2563,10 +2557,10 @@
       <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="43">
         <v>2059000</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I5" s="3" t="s">
@@ -2624,10 +2618,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="44">
+      <c r="G6" s="43">
         <v>100000</v>
       </c>
-      <c r="H6" s="45"/>
+      <c r="H6" s="44"/>
       <c r="I6" s="3" t="s">
         <v>24</v>
       </c>
@@ -2685,10 +2679,10 @@
         <v>29</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="46">
+      <c r="G7" s="45">
         <v>200000</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="46" t="s">
         <v>573</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -2748,10 +2742,10 @@
         <v>29</v>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="46">
+      <c r="G8" s="45">
         <v>100000</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="46" t="s">
         <v>573</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -2815,10 +2809,10 @@
         <v>29</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="46">
+      <c r="G9" s="45">
         <v>2000000</v>
       </c>
-      <c r="H9" s="47" t="s">
+      <c r="H9" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -2882,10 +2876,10 @@
         <v>31</v>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="46">
+      <c r="G10" s="45">
         <v>1100000</v>
       </c>
-      <c r="H10" s="47" t="s">
+      <c r="H10" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -2949,10 +2943,10 @@
         <v>33</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="44">
+      <c r="G11" s="43">
         <v>1600000</v>
       </c>
-      <c r="H11" s="45"/>
+      <c r="H11" s="44"/>
       <c r="I11" s="3" t="s">
         <v>24</v>
       </c>
@@ -3008,10 +3002,10 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="44">
+      <c r="G12" s="43">
         <v>1000000</v>
       </c>
-      <c r="H12" s="45"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="3" t="s">
         <v>24</v>
       </c>
@@ -3069,10 +3063,10 @@
         <v>29</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="44">
+      <c r="G13" s="43">
         <v>580000</v>
       </c>
-      <c r="H13" s="45"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="3" t="s">
         <v>24</v>
       </c>
@@ -3128,10 +3122,10 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="44">
-        <v>0</v>
-      </c>
-      <c r="H14" s="45" t="s">
+      <c r="G14" s="43">
+        <v>0</v>
+      </c>
+      <c r="H14" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -3193,10 +3187,10 @@
       <c r="F15" s="8">
         <v>3</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G15" s="45">
         <v>1600000</v>
       </c>
-      <c r="H15" s="47" t="s">
+      <c r="H15" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I15" s="3" t="s">
@@ -3254,10 +3248,10 @@
       <c r="D16" s="8"/>
       <c r="E16" s="2"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="46">
+      <c r="G16" s="45">
         <v>1500000</v>
       </c>
-      <c r="H16" s="47" t="s">
+      <c r="H16" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -3319,10 +3313,10 @@
         <v>41</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>2820000</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -3386,10 +3380,10 @@
         <v>29</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <v>1000000</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -3451,10 +3445,10 @@
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="43">
         <v>6219000</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I19" s="3" t="s">
@@ -3516,10 +3510,10 @@
       <c r="F20" s="8">
         <v>1</v>
       </c>
-      <c r="G20" s="46">
+      <c r="G20" s="45">
         <v>4800000</v>
       </c>
-      <c r="H20" s="47" t="s">
+      <c r="H20" s="46" t="s">
         <v>573</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -3583,10 +3577,10 @@
         <v>46</v>
       </c>
       <c r="F21" s="8"/>
-      <c r="G21" s="46">
+      <c r="G21" s="45">
         <v>5200000</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H21" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I21" s="3" t="s">
@@ -3646,10 +3640,10 @@
         <v>29</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="44">
+      <c r="G22" s="43">
         <v>100000</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I22" s="3" t="s">
@@ -3715,10 +3709,10 @@
       <c r="F23" s="2">
         <v>3</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="43">
         <v>22900000</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I23" s="3" t="s">
@@ -3778,10 +3772,10 @@
         <v>41</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="44">
+      <c r="G24" s="43">
         <v>800000</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -3843,10 +3837,10 @@
       <c r="F25" s="8">
         <v>1</v>
       </c>
-      <c r="G25" s="46">
+      <c r="G25" s="45">
         <v>1200000</v>
       </c>
-      <c r="H25" s="47" t="s">
+      <c r="H25" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I25" s="3" t="s">
@@ -3904,10 +3898,10 @@
       <c r="D26" s="9"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="44">
+      <c r="G26" s="43">
         <v>200000</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I26" s="3" t="s">
@@ -3965,10 +3959,10 @@
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="44">
+      <c r="G27" s="43">
         <v>2400000</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I27" s="3" t="s">
@@ -4030,10 +4024,10 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="44">
+      <c r="G28" s="43">
         <v>4400000</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -4095,10 +4089,10 @@
       <c r="F29" s="2">
         <v>1</v>
       </c>
-      <c r="G29" s="44">
+      <c r="G29" s="43">
         <v>240000</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I29" s="3" t="s">
@@ -4164,10 +4158,10 @@
       <c r="F30" s="8">
         <v>1</v>
       </c>
-      <c r="G30" s="46">
+      <c r="G30" s="45">
         <v>1000000</v>
       </c>
-      <c r="H30" s="47" t="s">
+      <c r="H30" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -4227,10 +4221,10 @@
         <v>29</v>
       </c>
       <c r="F31" s="2"/>
-      <c r="G31" s="44">
+      <c r="G31" s="43">
         <v>100000</v>
       </c>
-      <c r="H31" s="45" t="s">
+      <c r="H31" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -4296,10 +4290,10 @@
       <c r="F32" s="8">
         <v>1</v>
       </c>
-      <c r="G32" s="46">
+      <c r="G32" s="45">
         <v>10045000</v>
       </c>
-      <c r="H32" s="47" t="s">
+      <c r="H32" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I32" s="3" t="s">
@@ -4359,10 +4353,10 @@
         <v>29</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="G33" s="44">
+      <c r="G33" s="43">
         <v>450000</v>
       </c>
-      <c r="H33" s="44" t="s">
+      <c r="H33" s="43" t="s">
         <v>573</v>
       </c>
       <c r="I33" s="3" t="s">
@@ -4422,10 +4416,10 @@
       <c r="F34" s="2">
         <v>1</v>
       </c>
-      <c r="G34" s="46">
-        <v>0</v>
-      </c>
-      <c r="H34" s="45" t="s">
+      <c r="G34" s="45">
+        <v>0</v>
+      </c>
+      <c r="H34" s="44" t="s">
         <v>575</v>
       </c>
       <c r="I34" s="3" t="s">
@@ -4485,10 +4479,10 @@
         <v>29</v>
       </c>
       <c r="F35" s="2"/>
-      <c r="G35" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H35" s="45" t="s">
+      <c r="G35" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H35" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I35" s="3" t="s">
@@ -4554,10 +4548,10 @@
       <c r="F36" s="8">
         <v>2</v>
       </c>
-      <c r="G36" s="46">
+      <c r="G36" s="45">
         <v>21600000</v>
       </c>
-      <c r="H36" s="47" t="s">
+      <c r="H36" s="46" t="s">
         <v>576</v>
       </c>
       <c r="I36" s="3" t="s">
@@ -4617,10 +4611,10 @@
         <v>29</v>
       </c>
       <c r="F37" s="2"/>
-      <c r="G37" s="44">
+      <c r="G37" s="43">
         <v>2200000</v>
       </c>
-      <c r="H37" s="44" t="s">
+      <c r="H37" s="43" t="s">
         <v>573</v>
       </c>
       <c r="I37" s="3" t="s">
@@ -4686,10 +4680,10 @@
       <c r="F38" s="8">
         <v>1</v>
       </c>
-      <c r="G38" s="46">
+      <c r="G38" s="45">
         <v>800000</v>
       </c>
-      <c r="H38" s="47" t="s">
+      <c r="H38" s="46" t="s">
         <v>575</v>
       </c>
       <c r="I38" s="3" t="s">
@@ -4747,10 +4741,10 @@
       <c r="D39" s="8"/>
       <c r="E39" s="2"/>
       <c r="F39" s="8"/>
-      <c r="G39" s="46">
+      <c r="G39" s="45">
         <v>1200000</v>
       </c>
-      <c r="H39" s="47" t="s">
+      <c r="H39" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I39" s="3" t="s">
@@ -4814,10 +4808,10 @@
         <v>69</v>
       </c>
       <c r="F40" s="8"/>
-      <c r="G40" s="46">
+      <c r="G40" s="45">
         <v>4400000</v>
       </c>
-      <c r="H40" s="47" t="s">
+      <c r="H40" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I40" s="3" t="s">
@@ -4881,10 +4875,10 @@
         <v>69</v>
       </c>
       <c r="F41" s="2"/>
-      <c r="G41" s="46">
+      <c r="G41" s="45">
         <v>6000000</v>
       </c>
-      <c r="H41" s="45" t="s">
+      <c r="H41" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I41" s="3" t="s">
@@ -4948,10 +4942,10 @@
         <v>72</v>
       </c>
       <c r="F42" s="2"/>
-      <c r="G42" s="46">
+      <c r="G42" s="45">
         <v>4400000</v>
       </c>
-      <c r="H42" s="45" t="s">
+      <c r="H42" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -5011,10 +5005,10 @@
         <v>74</v>
       </c>
       <c r="F43" s="8"/>
-      <c r="G43" s="46">
+      <c r="G43" s="45">
         <v>6522000</v>
       </c>
-      <c r="H43" s="47" t="s">
+      <c r="H43" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -5078,10 +5072,10 @@
         <v>76</v>
       </c>
       <c r="F44" s="8"/>
-      <c r="G44" s="46">
+      <c r="G44" s="45">
         <v>20208000</v>
       </c>
-      <c r="H44" s="47" t="s">
+      <c r="H44" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I44" s="3" t="s">
@@ -5141,10 +5135,10 @@
         <v>555</v>
       </c>
       <c r="F45" s="8"/>
-      <c r="G45" s="46">
+      <c r="G45" s="45">
         <v>600000</v>
       </c>
-      <c r="H45" s="47" t="s">
+      <c r="H45" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I45" s="3" t="s">
@@ -5208,10 +5202,10 @@
         <v>473</v>
       </c>
       <c r="F46" s="2"/>
-      <c r="G46" s="44">
+      <c r="G46" s="43">
         <v>19725000</v>
       </c>
-      <c r="H46" s="45"/>
+      <c r="H46" s="44"/>
       <c r="I46" s="3" t="s">
         <v>24</v>
       </c>
@@ -5271,10 +5265,10 @@
       <c r="F47" s="2">
         <v>1</v>
       </c>
-      <c r="G47" s="44">
+      <c r="G47" s="43">
         <v>4095000</v>
       </c>
-      <c r="H47" s="45" t="s">
+      <c r="H47" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I47" s="3" t="s">
@@ -5336,10 +5330,10 @@
       <c r="F48" s="2">
         <v>1</v>
       </c>
-      <c r="G48" s="44">
+      <c r="G48" s="43">
         <v>12937600</v>
       </c>
-      <c r="H48" s="45" t="s">
+      <c r="H48" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I48" s="3" t="s">
@@ -5405,10 +5399,10 @@
       <c r="F49" s="8">
         <v>1</v>
       </c>
-      <c r="G49" s="46">
+      <c r="G49" s="45">
         <v>16940000</v>
       </c>
-      <c r="H49" s="47" t="s">
+      <c r="H49" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I49" s="3" t="s">
@@ -5468,10 +5462,10 @@
         <v>556</v>
       </c>
       <c r="F50" s="8"/>
-      <c r="G50" s="46">
+      <c r="G50" s="45">
         <v>2700000</v>
       </c>
-      <c r="H50" s="47" t="s">
+      <c r="H50" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I50" s="3" t="s">
@@ -5535,10 +5529,10 @@
         <v>29</v>
       </c>
       <c r="F51" s="2"/>
-      <c r="G51" s="46">
+      <c r="G51" s="45">
         <v>16800000</v>
       </c>
-      <c r="H51" s="45" t="s">
+      <c r="H51" s="44" t="s">
         <v>577</v>
       </c>
       <c r="I51" s="3" t="s">
@@ -5598,10 +5592,10 @@
         <v>87</v>
       </c>
       <c r="F52" s="8"/>
-      <c r="G52" s="46">
+      <c r="G52" s="45">
         <v>220000</v>
       </c>
-      <c r="H52" s="47" t="s">
+      <c r="H52" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I52" s="3" t="s">
@@ -5661,10 +5655,10 @@
         <v>31</v>
       </c>
       <c r="F53" s="2"/>
-      <c r="G53" s="46">
+      <c r="G53" s="45">
         <v>13600000</v>
       </c>
-      <c r="H53" s="45" t="s">
+      <c r="H53" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I53" s="3" t="s">
@@ -5724,10 +5718,10 @@
         <v>90</v>
       </c>
       <c r="F54" s="8"/>
-      <c r="G54" s="46">
+      <c r="G54" s="45">
         <v>3050000</v>
       </c>
-      <c r="H54" s="47" t="s">
+      <c r="H54" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I54" s="3" t="s">
@@ -5791,10 +5785,10 @@
         <v>92</v>
       </c>
       <c r="F55" s="8"/>
-      <c r="G55" s="46">
+      <c r="G55" s="45">
         <v>9745000</v>
       </c>
-      <c r="H55" s="47" t="s">
+      <c r="H55" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I55" s="3" t="s">
@@ -5854,10 +5848,10 @@
         <v>94</v>
       </c>
       <c r="F56" s="2"/>
-      <c r="G56" s="44">
+      <c r="G56" s="43">
         <v>1600000</v>
       </c>
-      <c r="H56" s="45" t="s">
+      <c r="H56" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I56" s="3" t="s">
@@ -5919,10 +5913,10 @@
       <c r="F57" s="8">
         <v>1</v>
       </c>
-      <c r="G57" s="46">
+      <c r="G57" s="45">
         <v>2285000</v>
       </c>
-      <c r="H57" s="47" t="s">
+      <c r="H57" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I57" s="3" t="s">
@@ -5982,10 +5976,10 @@
         <v>23</v>
       </c>
       <c r="F58" s="8"/>
-      <c r="G58" s="46">
+      <c r="G58" s="45">
         <v>2800000</v>
       </c>
-      <c r="H58" s="47" t="s">
+      <c r="H58" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I58" s="3" t="s">
@@ -6045,10 +6039,10 @@
         <v>99</v>
       </c>
       <c r="F59" s="8"/>
-      <c r="G59" s="46">
+      <c r="G59" s="45">
         <v>9200000</v>
       </c>
-      <c r="H59" s="47" t="s">
+      <c r="H59" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I59" s="3" t="s">
@@ -6110,10 +6104,10 @@
         <v>102</v>
       </c>
       <c r="F60" s="2"/>
-      <c r="G60" s="44">
+      <c r="G60" s="43">
         <v>11200000</v>
       </c>
-      <c r="H60" s="45" t="s">
+      <c r="H60" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I60" s="3" t="s">
@@ -6175,10 +6169,10 @@
       <c r="F61" s="2">
         <v>2</v>
       </c>
-      <c r="G61" s="46">
+      <c r="G61" s="45">
         <v>14800000</v>
       </c>
-      <c r="H61" s="45" t="s">
+      <c r="H61" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I61" s="3" t="s">
@@ -6242,10 +6236,10 @@
         <v>106</v>
       </c>
       <c r="F62" s="2"/>
-      <c r="G62" s="44">
+      <c r="G62" s="43">
         <v>2400000</v>
       </c>
-      <c r="H62" s="45" t="s">
+      <c r="H62" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I62" s="3" t="s">
@@ -6305,10 +6299,10 @@
         <v>108</v>
       </c>
       <c r="F63" s="8"/>
-      <c r="G63" s="46">
+      <c r="G63" s="45">
         <v>440000</v>
       </c>
-      <c r="H63" s="47" t="s">
+      <c r="H63" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I63" s="3" t="s">
@@ -6368,10 +6362,10 @@
         <v>110</v>
       </c>
       <c r="F64" s="2"/>
-      <c r="G64" s="46">
+      <c r="G64" s="45">
         <v>1250000</v>
       </c>
-      <c r="H64" s="45" t="s">
+      <c r="H64" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I64" s="3" t="s">
@@ -6431,10 +6425,10 @@
         <v>112</v>
       </c>
       <c r="F65" s="8"/>
-      <c r="G65" s="46">
+      <c r="G65" s="45">
         <v>1400000</v>
       </c>
-      <c r="H65" s="47" t="s">
+      <c r="H65" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I65" s="3" t="s">
@@ -6494,10 +6488,10 @@
         <v>114</v>
       </c>
       <c r="F66" s="8"/>
-      <c r="G66" s="46">
+      <c r="G66" s="45">
         <v>9524000</v>
       </c>
-      <c r="H66" s="47" t="s">
+      <c r="H66" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I66" s="3" t="s">
@@ -6561,10 +6555,10 @@
         <v>117</v>
       </c>
       <c r="F67" s="8"/>
-      <c r="G67" s="46">
+      <c r="G67" s="45">
         <v>7266250</v>
       </c>
-      <c r="H67" s="47" t="s">
+      <c r="H67" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I67" s="3" t="s">
@@ -6624,10 +6618,10 @@
         <v>119</v>
       </c>
       <c r="F68" s="8"/>
-      <c r="G68" s="46">
+      <c r="G68" s="45">
         <v>3645000</v>
       </c>
-      <c r="H68" s="47" t="s">
+      <c r="H68" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I68" s="3" t="s">
@@ -6687,10 +6681,10 @@
         <v>121</v>
       </c>
       <c r="F69" s="8"/>
-      <c r="G69" s="46">
+      <c r="G69" s="45">
         <v>5704059</v>
       </c>
-      <c r="H69" s="47" t="s">
+      <c r="H69" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I69" s="3" t="s">
@@ -6754,10 +6748,10 @@
         <v>123</v>
       </c>
       <c r="F70" s="2"/>
-      <c r="G70" s="44">
+      <c r="G70" s="43">
         <v>18700000</v>
       </c>
-      <c r="H70" s="45" t="s">
+      <c r="H70" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I70" s="3" t="s">
@@ -6819,10 +6813,10 @@
         <v>160</v>
       </c>
       <c r="F71" s="2"/>
-      <c r="G71" s="44">
+      <c r="G71" s="43">
         <v>62180000</v>
       </c>
-      <c r="H71" s="45" t="s">
+      <c r="H71" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I71" s="3" t="s">
@@ -6882,10 +6876,10 @@
         <v>126</v>
       </c>
       <c r="F72" s="2"/>
-      <c r="G72" s="44">
+      <c r="G72" s="43">
         <v>2110000</v>
       </c>
-      <c r="H72" s="45" t="s">
+      <c r="H72" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I72" s="3" t="s">
@@ -6945,10 +6939,10 @@
         <v>557</v>
       </c>
       <c r="F73" s="8"/>
-      <c r="G73" s="46">
+      <c r="G73" s="45">
         <v>7580000</v>
       </c>
-      <c r="H73" s="47" t="s">
+      <c r="H73" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I73" s="3" t="s">
@@ -7008,10 +7002,10 @@
         <v>129</v>
       </c>
       <c r="F74" s="2"/>
-      <c r="G74" s="44">
+      <c r="G74" s="43">
         <v>2800000</v>
       </c>
-      <c r="H74" s="45" t="s">
+      <c r="H74" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I74" s="3" t="s">
@@ -7071,10 +7065,10 @@
         <v>131</v>
       </c>
       <c r="F75" s="2"/>
-      <c r="G75" s="44">
+      <c r="G75" s="43">
         <v>3600000</v>
       </c>
-      <c r="H75" s="45"/>
+      <c r="H75" s="44"/>
       <c r="I75" s="3" t="s">
         <v>24</v>
       </c>
@@ -7132,10 +7126,10 @@
         <v>133</v>
       </c>
       <c r="F76" s="2"/>
-      <c r="G76" s="44">
+      <c r="G76" s="43">
         <v>12090000</v>
       </c>
-      <c r="H76" s="45"/>
+      <c r="H76" s="44"/>
       <c r="I76" s="3" t="s">
         <v>24</v>
       </c>
@@ -7197,10 +7191,10 @@
         <v>56</v>
       </c>
       <c r="F77" s="2"/>
-      <c r="G77" s="44">
+      <c r="G77" s="43">
         <v>8200000</v>
       </c>
-      <c r="H77" s="45"/>
+      <c r="H77" s="44"/>
       <c r="I77" s="3" t="s">
         <v>24</v>
       </c>
@@ -7260,10 +7254,10 @@
       <c r="F78" s="2">
         <v>1</v>
       </c>
-      <c r="G78" s="44">
+      <c r="G78" s="43">
         <v>14000000</v>
       </c>
-      <c r="H78" s="45" t="s">
+      <c r="H78" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I78" s="3" t="s">
@@ -7323,10 +7317,10 @@
         <v>29</v>
       </c>
       <c r="F79" s="2"/>
-      <c r="G79" s="44">
+      <c r="G79" s="43">
         <v>200000</v>
       </c>
-      <c r="H79" s="45" t="s">
+      <c r="H79" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I79" s="3" t="s">
@@ -7388,10 +7382,10 @@
       <c r="F80" s="2">
         <v>1</v>
       </c>
-      <c r="G80" s="44">
+      <c r="G80" s="43">
         <v>50000</v>
       </c>
-      <c r="H80" s="45" t="s">
+      <c r="H80" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I80" s="3" t="s">
@@ -7451,10 +7445,10 @@
         <v>29</v>
       </c>
       <c r="F81" s="8"/>
-      <c r="G81" s="46">
+      <c r="G81" s="45">
         <v>1762000</v>
       </c>
-      <c r="H81" s="47" t="s">
+      <c r="H81" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I81" s="3" t="s">
@@ -7514,10 +7508,10 @@
         <v>23</v>
       </c>
       <c r="F82" s="8"/>
-      <c r="G82" s="46">
+      <c r="G82" s="45">
         <v>800000</v>
       </c>
-      <c r="H82" s="47" t="s">
+      <c r="H82" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I82" s="3" t="s">
@@ -7581,10 +7575,10 @@
         <v>56</v>
       </c>
       <c r="F83" s="8"/>
-      <c r="G83" s="46">
+      <c r="G83" s="45">
         <v>6000000</v>
       </c>
-      <c r="H83" s="47" t="s">
+      <c r="H83" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I83" s="3" t="s">
@@ -7648,10 +7642,10 @@
         <v>143</v>
       </c>
       <c r="F84" s="2"/>
-      <c r="G84" s="44">
+      <c r="G84" s="43">
         <v>4240000</v>
       </c>
-      <c r="H84" s="45" t="s">
+      <c r="H84" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I84" s="3" t="s">
@@ -7713,10 +7707,10 @@
         <v>99</v>
       </c>
       <c r="F85" s="8"/>
-      <c r="G85" s="46">
+      <c r="G85" s="45">
         <v>1300000</v>
       </c>
-      <c r="H85" s="47" t="s">
+      <c r="H85" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I85" s="3" t="s">
@@ -7776,10 +7770,10 @@
         <v>23</v>
       </c>
       <c r="F86" s="2"/>
-      <c r="G86" s="44">
+      <c r="G86" s="43">
         <v>420000</v>
       </c>
-      <c r="H86" s="45" t="s">
+      <c r="H86" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I86" s="3" t="s">
@@ -7843,10 +7837,10 @@
         <v>147</v>
       </c>
       <c r="F87" s="2"/>
-      <c r="G87" s="44">
+      <c r="G87" s="43">
         <v>2000000</v>
       </c>
-      <c r="H87" s="45" t="s">
+      <c r="H87" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I87" s="3" t="s">
@@ -7904,10 +7898,10 @@
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
-      <c r="G88" s="44">
+      <c r="G88" s="43">
         <v>4000000</v>
       </c>
-      <c r="H88" s="44"/>
+      <c r="H88" s="43"/>
       <c r="I88" s="3" t="s">
         <v>24</v>
       </c>
@@ -7971,10 +7965,10 @@
       <c r="F89" s="8">
         <v>2</v>
       </c>
-      <c r="G89" s="46">
+      <c r="G89" s="45">
         <v>4300000</v>
       </c>
-      <c r="H89" s="47" t="s">
+      <c r="H89" s="46" t="s">
         <v>575</v>
       </c>
       <c r="I89" s="3" t="s">
@@ -8034,10 +8028,10 @@
       <c r="D90" s="8"/>
       <c r="E90" s="2"/>
       <c r="F90" s="8"/>
-      <c r="G90" s="46">
+      <c r="G90" s="45">
         <v>3600000</v>
       </c>
-      <c r="H90" s="47" t="s">
+      <c r="H90" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I90" s="3" t="s">
@@ -8095,10 +8089,10 @@
       <c r="D91" s="8"/>
       <c r="E91" s="2"/>
       <c r="F91" s="8"/>
-      <c r="G91" s="46">
-        <v>400000</v>
-      </c>
-      <c r="H91" s="47" t="s">
+      <c r="G91" s="45">
+        <v>400000</v>
+      </c>
+      <c r="H91" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I91" s="3" t="s">
@@ -8156,10 +8150,10 @@
       <c r="D92" s="8"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="46">
+      <c r="G92" s="45">
         <v>860000</v>
       </c>
-      <c r="H92" s="45" t="s">
+      <c r="H92" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I92" s="3" t="s">
@@ -8221,10 +8215,10 @@
         <v>147</v>
       </c>
       <c r="F93" s="2"/>
-      <c r="G93" s="44">
+      <c r="G93" s="43">
         <v>4140000</v>
       </c>
-      <c r="H93" s="45" t="s">
+      <c r="H93" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I93" s="3" t="s">
@@ -8284,10 +8278,10 @@
       <c r="F94" s="2">
         <v>1</v>
       </c>
-      <c r="G94" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H94" s="45" t="s">
+      <c r="G94" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H94" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I94" s="3" t="s">
@@ -8345,10 +8339,10 @@
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
-      <c r="G95" s="44">
+      <c r="G95" s="43">
         <v>1600000</v>
       </c>
-      <c r="H95" s="45" t="s">
+      <c r="H95" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I95" s="3" t="s">
@@ -8414,10 +8408,10 @@
       <c r="F96" s="2">
         <v>1</v>
       </c>
-      <c r="G96" s="44">
+      <c r="G96" s="43">
         <v>1600000</v>
       </c>
-      <c r="H96" s="45" t="s">
+      <c r="H96" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I96" s="3" t="s">
@@ -8481,10 +8475,10 @@
         <v>31</v>
       </c>
       <c r="F97" s="2"/>
-      <c r="G97" s="46">
+      <c r="G97" s="45">
         <v>1200000</v>
       </c>
-      <c r="H97" s="45" t="s">
+      <c r="H97" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I97" s="3" t="s">
@@ -8542,10 +8536,10 @@
       <c r="D98" s="8"/>
       <c r="E98" s="2"/>
       <c r="F98" s="8"/>
-      <c r="G98" s="46">
-        <v>400000</v>
-      </c>
-      <c r="H98" s="47"/>
+      <c r="G98" s="45">
+        <v>400000</v>
+      </c>
+      <c r="H98" s="46"/>
       <c r="I98" s="3" t="s">
         <v>24</v>
       </c>
@@ -8607,10 +8601,10 @@
         <v>160</v>
       </c>
       <c r="F99" s="8"/>
-      <c r="G99" s="46">
+      <c r="G99" s="45">
         <v>8000000</v>
       </c>
-      <c r="H99" s="47" t="s">
+      <c r="H99" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I99" s="3" t="s">
@@ -8668,10 +8662,10 @@
       <c r="D100" s="8"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
-      <c r="G100" s="46">
+      <c r="G100" s="45">
         <v>10000000</v>
       </c>
-      <c r="H100" s="45" t="s">
+      <c r="H100" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I100" s="3" t="s">
@@ -8729,10 +8723,10 @@
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
-      <c r="G101" s="44">
+      <c r="G101" s="43">
         <v>800000</v>
       </c>
-      <c r="H101" s="44" t="s">
+      <c r="H101" s="43" t="s">
         <v>572</v>
       </c>
       <c r="I101" s="3" t="s">
@@ -8792,10 +8786,10 @@
       <c r="F102" s="2">
         <v>3</v>
       </c>
-      <c r="G102" s="44">
-        <v>0</v>
-      </c>
-      <c r="H102" s="45" t="s">
+      <c r="G102" s="43">
+        <v>0</v>
+      </c>
+      <c r="H102" s="44" t="s">
         <v>575</v>
       </c>
       <c r="I102" s="3" t="s">
@@ -8855,10 +8849,10 @@
         <v>473</v>
       </c>
       <c r="F103" s="2"/>
-      <c r="G103" s="44">
+      <c r="G103" s="43">
         <v>800000</v>
       </c>
-      <c r="H103" s="45" t="s">
+      <c r="H103" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I103" s="3" t="s">
@@ -8922,10 +8916,10 @@
         <v>106</v>
       </c>
       <c r="F104" s="2"/>
-      <c r="G104" s="44">
+      <c r="G104" s="43">
         <v>4000000</v>
       </c>
-      <c r="H104" s="45" t="s">
+      <c r="H104" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I104" s="3" t="s">
@@ -8987,10 +8981,10 @@
       <c r="F105" s="2">
         <v>2</v>
       </c>
-      <c r="G105" s="44">
+      <c r="G105" s="43">
         <v>12800000</v>
       </c>
-      <c r="H105" s="45" t="s">
+      <c r="H105" s="44" t="s">
         <v>578</v>
       </c>
       <c r="I105" s="3" t="s">
@@ -9050,10 +9044,10 @@
         <v>29</v>
       </c>
       <c r="F106" s="2"/>
-      <c r="G106" s="44">
+      <c r="G106" s="43">
         <v>200000</v>
       </c>
-      <c r="H106" s="45"/>
+      <c r="H106" s="44"/>
       <c r="I106" s="3" t="s">
         <v>24</v>
       </c>
@@ -9111,10 +9105,10 @@
         <v>29</v>
       </c>
       <c r="F107" s="2"/>
-      <c r="G107" s="44">
+      <c r="G107" s="43">
         <v>200000</v>
       </c>
-      <c r="H107" s="45" t="s">
+      <c r="H107" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I107" s="3" t="s">
@@ -9176,10 +9170,10 @@
       <c r="F108" s="2">
         <v>2</v>
       </c>
-      <c r="G108" s="46">
+      <c r="G108" s="45">
         <v>2800000</v>
       </c>
-      <c r="H108" s="45" t="s">
+      <c r="H108" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I108" s="3" t="s">
@@ -9239,10 +9233,10 @@
         <v>23</v>
       </c>
       <c r="F109" s="2"/>
-      <c r="G109" s="44">
+      <c r="G109" s="43">
         <v>500000</v>
       </c>
-      <c r="H109" s="45" t="s">
+      <c r="H109" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I109" s="3" t="s">
@@ -9306,10 +9300,10 @@
         <v>106</v>
       </c>
       <c r="F110" s="2"/>
-      <c r="G110" s="44">
+      <c r="G110" s="43">
         <v>800000</v>
       </c>
-      <c r="H110" s="45"/>
+      <c r="H110" s="44"/>
       <c r="I110" s="3" t="s">
         <v>24</v>
       </c>
@@ -9371,10 +9365,10 @@
         <v>174</v>
       </c>
       <c r="F111" s="2"/>
-      <c r="G111" s="44">
+      <c r="G111" s="43">
         <v>12000000</v>
       </c>
-      <c r="H111" s="45" t="s">
+      <c r="H111" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I111" s="3" t="s">
@@ -9432,10 +9426,10 @@
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
-      <c r="G112" s="44">
+      <c r="G112" s="43">
         <v>4800000</v>
       </c>
-      <c r="H112" s="45" t="s">
+      <c r="H112" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I112" s="3" t="s">
@@ -9499,10 +9493,10 @@
         <v>147</v>
       </c>
       <c r="F113" s="8"/>
-      <c r="G113" s="46">
+      <c r="G113" s="45">
         <v>2400000</v>
       </c>
-      <c r="H113" s="47" t="s">
+      <c r="H113" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I113" s="3" t="s">
@@ -9566,10 +9560,10 @@
         <v>179</v>
       </c>
       <c r="F114" s="2"/>
-      <c r="G114" s="44">
+      <c r="G114" s="43">
         <v>2390000</v>
       </c>
-      <c r="H114" s="45" t="s">
+      <c r="H114" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I114" s="3" t="s">
@@ -9629,10 +9623,10 @@
         <v>29</v>
       </c>
       <c r="F115" s="2"/>
-      <c r="G115" s="44">
+      <c r="G115" s="43">
         <v>3700000</v>
       </c>
-      <c r="H115" s="45" t="s">
+      <c r="H115" s="44" t="s">
         <v>579</v>
       </c>
       <c r="I115" s="3" t="s">
@@ -9690,10 +9684,10 @@
       <c r="D116" s="8"/>
       <c r="E116" s="2"/>
       <c r="F116" s="8"/>
-      <c r="G116" s="46">
+      <c r="G116" s="45">
         <v>1200000</v>
       </c>
-      <c r="H116" s="47"/>
+      <c r="H116" s="46"/>
       <c r="I116" s="3" t="s">
         <v>24</v>
       </c>
@@ -9755,10 +9749,10 @@
         <v>76</v>
       </c>
       <c r="F117" s="8"/>
-      <c r="G117" s="46">
+      <c r="G117" s="45">
         <v>1800000</v>
       </c>
-      <c r="H117" s="47" t="s">
+      <c r="H117" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I117" s="3" t="s">
@@ -9818,10 +9812,10 @@
         <v>29</v>
       </c>
       <c r="F118" s="8"/>
-      <c r="G118" s="46">
+      <c r="G118" s="45">
         <v>100000</v>
       </c>
-      <c r="H118" s="47" t="s">
+      <c r="H118" s="46" t="s">
         <v>573</v>
       </c>
       <c r="I118" s="3" t="s">
@@ -9881,10 +9875,10 @@
         <v>29</v>
       </c>
       <c r="F119" s="2"/>
-      <c r="G119" s="46">
-        <v>400000</v>
-      </c>
-      <c r="H119" s="45" t="s">
+      <c r="G119" s="45">
+        <v>400000</v>
+      </c>
+      <c r="H119" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I119" s="3" t="s">
@@ -9948,10 +9942,10 @@
         <v>186</v>
       </c>
       <c r="F120" s="2"/>
-      <c r="G120" s="44">
+      <c r="G120" s="43">
         <v>4000000</v>
       </c>
-      <c r="H120" s="45" t="s">
+      <c r="H120" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I120" s="3" t="s">
@@ -10013,10 +10007,10 @@
       <c r="F121" s="2">
         <v>1</v>
       </c>
-      <c r="G121" s="46">
+      <c r="G121" s="45">
         <v>10670000</v>
       </c>
-      <c r="H121" s="45" t="s">
+      <c r="H121" s="44" t="s">
         <v>573</v>
       </c>
       <c r="I121" s="3" t="s">
@@ -10078,10 +10072,10 @@
         <v>554</v>
       </c>
       <c r="F122" s="2"/>
-      <c r="G122" s="44">
+      <c r="G122" s="43">
         <v>1200000</v>
       </c>
-      <c r="H122" s="45" t="s">
+      <c r="H122" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I122" s="3" t="s">
@@ -10143,10 +10137,10 @@
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
-      <c r="G123" s="44">
+      <c r="G123" s="43">
         <v>1200000</v>
       </c>
-      <c r="H123" s="45"/>
+      <c r="H123" s="44"/>
       <c r="I123" s="3" t="s">
         <v>24</v>
       </c>
@@ -10202,10 +10196,10 @@
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
-      <c r="G124" s="44">
+      <c r="G124" s="43">
         <v>200000</v>
       </c>
-      <c r="H124" s="45"/>
+      <c r="H124" s="44"/>
       <c r="I124" s="3" t="s">
         <v>24</v>
       </c>
@@ -10261,10 +10255,10 @@
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
-      <c r="G125" s="44">
+      <c r="G125" s="43">
         <v>850000</v>
       </c>
-      <c r="H125" s="45" t="s">
+      <c r="H125" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I125" s="3" t="s">
@@ -10328,10 +10322,10 @@
         <v>92</v>
       </c>
       <c r="F126" s="8"/>
-      <c r="G126" s="46">
+      <c r="G126" s="45">
         <v>1600000</v>
       </c>
-      <c r="H126" s="47" t="s">
+      <c r="H126" s="46" t="s">
         <v>574</v>
       </c>
       <c r="I126" s="3" t="s">
@@ -10389,10 +10383,10 @@
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
-      <c r="G127" s="44">
+      <c r="G127" s="43">
         <v>3900000</v>
       </c>
-      <c r="H127" s="45" t="s">
+      <c r="H127" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I127" s="3" t="s">
@@ -10450,10 +10444,10 @@
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
-      <c r="G128" s="44">
+      <c r="G128" s="43">
         <v>800000</v>
       </c>
-      <c r="H128" s="44"/>
+      <c r="H128" s="43"/>
       <c r="I128" s="3" t="s">
         <v>24</v>
       </c>
@@ -10517,10 +10511,10 @@
       <c r="F129" s="8">
         <v>1</v>
       </c>
-      <c r="G129" s="46">
-        <v>400000</v>
-      </c>
-      <c r="H129" s="47" t="s">
+      <c r="G129" s="45">
+        <v>400000</v>
+      </c>
+      <c r="H129" s="46" t="s">
         <v>575</v>
       </c>
       <c r="I129" s="3" t="s">
@@ -10584,10 +10578,10 @@
         <v>56</v>
       </c>
       <c r="F130" s="2"/>
-      <c r="G130" s="44">
+      <c r="G130" s="43">
         <v>3200000</v>
       </c>
-      <c r="H130" s="44" t="s">
+      <c r="H130" s="43" t="s">
         <v>572</v>
       </c>
       <c r="I130" s="3" t="s">
@@ -10647,10 +10641,10 @@
       <c r="F131" s="2">
         <v>1</v>
       </c>
-      <c r="G131" s="44">
-        <v>0</v>
-      </c>
-      <c r="H131" s="45" t="s">
+      <c r="G131" s="43">
+        <v>0</v>
+      </c>
+      <c r="H131" s="44" t="s">
         <v>575</v>
       </c>
       <c r="I131" s="3" t="s">
@@ -10712,10 +10706,10 @@
         <v>29</v>
       </c>
       <c r="F132" s="2"/>
-      <c r="G132" s="44">
+      <c r="G132" s="43">
         <v>2800000</v>
       </c>
-      <c r="H132" s="45"/>
+      <c r="H132" s="44"/>
       <c r="I132" s="3" t="s">
         <v>24</v>
       </c>
@@ -10773,10 +10767,10 @@
         <v>29</v>
       </c>
       <c r="F133" s="8"/>
-      <c r="G133" s="46">
-        <v>400000</v>
-      </c>
-      <c r="H133" s="47"/>
+      <c r="G133" s="45">
+        <v>400000</v>
+      </c>
+      <c r="H133" s="46"/>
       <c r="I133" s="3" t="s">
         <v>24</v>
       </c>
@@ -10832,10 +10826,10 @@
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
-      <c r="G134" s="44">
+      <c r="G134" s="43">
         <v>100000</v>
       </c>
-      <c r="H134" s="45" t="s">
+      <c r="H134" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I134" s="3" t="s">
@@ -10895,10 +10889,10 @@
         <v>29</v>
       </c>
       <c r="F135" s="8"/>
-      <c r="G135" s="46">
+      <c r="G135" s="45">
         <v>5600000</v>
       </c>
-      <c r="H135" s="47"/>
+      <c r="H135" s="46"/>
       <c r="I135" s="3" t="s">
         <v>24</v>
       </c>
@@ -10956,10 +10950,10 @@
         <v>29</v>
       </c>
       <c r="F136" s="2"/>
-      <c r="G136" s="44">
+      <c r="G136" s="43">
         <v>100000</v>
       </c>
-      <c r="H136" s="45" t="s">
+      <c r="H136" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I136" s="3" t="s">
@@ -11025,10 +11019,10 @@
       <c r="F137" s="2">
         <v>2</v>
       </c>
-      <c r="G137" s="44">
+      <c r="G137" s="43">
         <v>11300000</v>
       </c>
-      <c r="H137" s="44" t="s">
+      <c r="H137" s="43" t="s">
         <v>572</v>
       </c>
       <c r="I137" s="3" t="s">
@@ -11088,10 +11082,10 @@
       <c r="F138" s="2">
         <v>1</v>
       </c>
-      <c r="G138" s="44">
-        <v>0</v>
-      </c>
-      <c r="H138" s="45" t="s">
+      <c r="G138" s="43">
+        <v>0</v>
+      </c>
+      <c r="H138" s="44" t="s">
         <v>575</v>
       </c>
       <c r="I138" s="3" t="s">
@@ -11155,10 +11149,10 @@
         <v>207</v>
       </c>
       <c r="F139" s="8"/>
-      <c r="G139" s="46">
+      <c r="G139" s="45">
         <v>4000000</v>
       </c>
-      <c r="H139" s="47" t="s">
+      <c r="H139" s="46" t="s">
         <v>572</v>
       </c>
       <c r="I139" s="3" t="s">
@@ -11216,10 +11210,10 @@
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
-      <c r="G140" s="44">
+      <c r="G140" s="43">
         <v>3000000</v>
       </c>
-      <c r="H140" s="45" t="s">
+      <c r="H140" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I140" s="3" t="s">
@@ -11277,10 +11271,10 @@
       <c r="D141" s="8"/>
       <c r="E141" s="2"/>
       <c r="F141" s="8"/>
-      <c r="G141" s="46">
+      <c r="G141" s="45">
         <v>260000</v>
       </c>
-      <c r="H141" s="47"/>
+      <c r="H141" s="46"/>
       <c r="I141" s="3" t="s">
         <v>24</v>
       </c>
@@ -11338,10 +11332,10 @@
         <v>29</v>
       </c>
       <c r="F142" s="2"/>
-      <c r="G142" s="44">
+      <c r="G142" s="43">
         <v>3600000</v>
       </c>
-      <c r="H142" s="45" t="s">
+      <c r="H142" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I142" s="3" t="s">
@@ -11403,10 +11397,10 @@
         <v>104</v>
       </c>
       <c r="F143" s="2"/>
-      <c r="G143" s="46">
+      <c r="G143" s="45">
         <v>1400000</v>
       </c>
-      <c r="H143" s="45"/>
+      <c r="H143" s="44"/>
       <c r="I143" s="3" t="s">
         <v>24</v>
       </c>
@@ -11462,10 +11456,10 @@
       <c r="D144" s="8"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
-      <c r="G144" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H144" s="45" t="s">
+      <c r="G144" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H144" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I144" s="3" t="s">
@@ -11523,10 +11517,10 @@
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
-      <c r="G145" s="44">
+      <c r="G145" s="43">
         <v>1200000</v>
       </c>
-      <c r="H145" s="45"/>
+      <c r="H145" s="44"/>
       <c r="I145" s="3" t="s">
         <v>24</v>
       </c>
@@ -11584,10 +11578,10 @@
         <v>215</v>
       </c>
       <c r="F146" s="2"/>
-      <c r="G146" s="44">
+      <c r="G146" s="43">
         <v>500000</v>
       </c>
-      <c r="H146" s="45"/>
+      <c r="H146" s="44"/>
       <c r="I146" s="3" t="s">
         <v>24</v>
       </c>
@@ -11645,10 +11639,10 @@
       <c r="F147" s="2">
         <v>1</v>
       </c>
-      <c r="G147" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H147" s="45" t="s">
+      <c r="G147" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H147" s="44" t="s">
         <v>574</v>
       </c>
       <c r="I147" s="3" t="s">
@@ -11708,10 +11702,10 @@
         <v>29</v>
       </c>
       <c r="F148" s="2"/>
-      <c r="G148" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H148" s="45"/>
+      <c r="G148" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H148" s="44"/>
       <c r="I148" s="3" t="s">
         <v>24</v>
       </c>
@@ -11773,10 +11767,10 @@
         <v>219</v>
       </c>
       <c r="F149" s="2"/>
-      <c r="G149" s="44">
+      <c r="G149" s="43">
         <v>1600000</v>
       </c>
-      <c r="H149" s="45"/>
+      <c r="H149" s="44"/>
       <c r="I149" s="3" t="s">
         <v>24</v>
       </c>
@@ -11832,10 +11826,10 @@
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
-      <c r="G150" s="44">
+      <c r="G150" s="43">
         <v>3200000</v>
       </c>
-      <c r="H150" s="45"/>
+      <c r="H150" s="44"/>
       <c r="I150" s="3" t="s">
         <v>24</v>
       </c>
@@ -11891,10 +11885,10 @@
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="44">
+      <c r="G151" s="43">
         <v>3200000</v>
       </c>
-      <c r="H151" s="45"/>
+      <c r="H151" s="44"/>
       <c r="I151" s="3" t="s">
         <v>24</v>
       </c>
@@ -11950,10 +11944,10 @@
       <c r="D152" s="8"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
-      <c r="G152" s="44">
+      <c r="G152" s="43">
         <v>200000</v>
       </c>
-      <c r="H152" s="45"/>
+      <c r="H152" s="44"/>
       <c r="I152" s="3" t="s">
         <v>24</v>
       </c>
@@ -12009,10 +12003,10 @@
       <c r="D153" s="8"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
-      <c r="G153" s="44">
+      <c r="G153" s="43">
         <v>800000</v>
       </c>
-      <c r="H153" s="45"/>
+      <c r="H153" s="44"/>
       <c r="I153" s="3" t="s">
         <v>24</v>
       </c>
@@ -12074,10 +12068,10 @@
         <v>554</v>
       </c>
       <c r="F154" s="2"/>
-      <c r="G154" s="44">
+      <c r="G154" s="43">
         <v>2490000</v>
       </c>
-      <c r="H154" s="45"/>
+      <c r="H154" s="44"/>
       <c r="I154" s="3" t="s">
         <v>24</v>
       </c>
@@ -12135,10 +12129,10 @@
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
-      <c r="G155" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H155" s="45"/>
+      <c r="G155" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H155" s="44"/>
       <c r="I155" s="3" t="s">
         <v>24</v>
       </c>
@@ -12200,10 +12194,10 @@
         <v>92</v>
       </c>
       <c r="F156" s="2"/>
-      <c r="G156" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H156" s="45"/>
+      <c r="G156" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H156" s="44"/>
       <c r="I156" s="3" t="s">
         <v>24</v>
       </c>
@@ -12265,10 +12259,10 @@
         <v>106</v>
       </c>
       <c r="F157" s="2"/>
-      <c r="G157" s="44">
+      <c r="G157" s="43">
         <v>1600000</v>
       </c>
-      <c r="H157" s="45"/>
+      <c r="H157" s="44"/>
       <c r="I157" s="3" t="s">
         <v>24</v>
       </c>
@@ -12330,10 +12324,10 @@
         <v>106</v>
       </c>
       <c r="F158" s="2"/>
-      <c r="G158" s="44">
+      <c r="G158" s="43">
         <v>1600000</v>
       </c>
-      <c r="H158" s="45"/>
+      <c r="H158" s="44"/>
       <c r="I158" s="3" t="s">
         <v>24</v>
       </c>
@@ -12393,10 +12387,10 @@
         <v>29</v>
       </c>
       <c r="F159" s="2"/>
-      <c r="G159" s="44">
+      <c r="G159" s="43">
         <v>840000</v>
       </c>
-      <c r="H159" s="45"/>
+      <c r="H159" s="44"/>
       <c r="I159" s="3" t="s">
         <v>24</v>
       </c>
@@ -12452,10 +12446,10 @@
       <c r="D160" s="8"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="44">
+      <c r="G160" s="43">
         <v>460000</v>
       </c>
-      <c r="H160" s="45"/>
+      <c r="H160" s="44"/>
       <c r="I160" s="3" t="s">
         <v>24</v>
       </c>
@@ -12515,10 +12509,10 @@
         <v>179</v>
       </c>
       <c r="F161" s="2"/>
-      <c r="G161" s="44">
+      <c r="G161" s="43">
         <v>250000</v>
       </c>
-      <c r="H161" s="45"/>
+      <c r="H161" s="44"/>
       <c r="I161" s="3" t="s">
         <v>24</v>
       </c>
@@ -12576,10 +12570,10 @@
       <c r="D162" s="8"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H162" s="45"/>
+      <c r="G162" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H162" s="44"/>
       <c r="I162" s="3" t="s">
         <v>24</v>
       </c>
@@ -12641,10 +12635,10 @@
         <v>106</v>
       </c>
       <c r="F163" s="2"/>
-      <c r="G163" s="44">
+      <c r="G163" s="43">
         <v>2400000</v>
       </c>
-      <c r="H163" s="45"/>
+      <c r="H163" s="44"/>
       <c r="I163" s="3" t="s">
         <v>24</v>
       </c>
@@ -12706,10 +12700,10 @@
         <v>69</v>
       </c>
       <c r="F164" s="2"/>
-      <c r="G164" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H164" s="45"/>
+      <c r="G164" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H164" s="44"/>
       <c r="I164" s="3" t="s">
         <v>24</v>
       </c>
@@ -12765,10 +12759,10 @@
       <c r="D165" s="8"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
-      <c r="G165" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H165" s="45"/>
+      <c r="G165" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H165" s="44"/>
       <c r="I165" s="3" t="s">
         <v>24</v>
       </c>
@@ -13076,10 +13070,10 @@
         <v>56</v>
       </c>
       <c r="F170" s="2"/>
-      <c r="G170" s="44">
+      <c r="G170" s="43">
         <v>800000</v>
       </c>
-      <c r="H170" s="45"/>
+      <c r="H170" s="44"/>
       <c r="I170" s="3" t="s">
         <v>24</v>
       </c>
@@ -13135,10 +13129,10 @@
       <c r="D171" s="8"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
-      <c r="G171" s="44">
+      <c r="G171" s="43">
         <v>950000</v>
       </c>
-      <c r="H171" s="45"/>
+      <c r="H171" s="44"/>
       <c r="I171" s="3" t="s">
         <v>24</v>
       </c>
@@ -13200,10 +13194,10 @@
         <v>56</v>
       </c>
       <c r="F172" s="2"/>
-      <c r="G172" s="44">
+      <c r="G172" s="43">
         <v>2400000</v>
       </c>
-      <c r="H172" s="45"/>
+      <c r="H172" s="44"/>
       <c r="I172" s="3" t="s">
         <v>24</v>
       </c>
@@ -13261,10 +13255,10 @@
         <v>473</v>
       </c>
       <c r="F173" s="2"/>
-      <c r="G173" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H173" s="45"/>
+      <c r="G173" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H173" s="44"/>
       <c r="I173" s="3" t="s">
         <v>24</v>
       </c>
@@ -13322,10 +13316,10 @@
         <v>559</v>
       </c>
       <c r="F174" s="2"/>
-      <c r="G174" s="44">
+      <c r="G174" s="43">
         <v>3600000</v>
       </c>
-      <c r="H174" s="45"/>
+      <c r="H174" s="44"/>
       <c r="I174" s="3" t="s">
         <v>24</v>
       </c>
@@ -13383,10 +13377,10 @@
       <c r="D175" s="8"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
-      <c r="G175" s="44">
+      <c r="G175" s="43">
         <v>1200000</v>
       </c>
-      <c r="H175" s="45"/>
+      <c r="H175" s="44"/>
       <c r="I175" s="3" t="s">
         <v>24</v>
       </c>
@@ -13444,10 +13438,10 @@
       <c r="D176" s="8"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
-      <c r="G176" s="44">
+      <c r="G176" s="43">
         <v>1200000</v>
       </c>
-      <c r="H176" s="45"/>
+      <c r="H176" s="44"/>
       <c r="I176" s="3" t="s">
         <v>24</v>
       </c>
@@ -13509,10 +13503,10 @@
         <v>72</v>
       </c>
       <c r="F177" s="2"/>
-      <c r="G177" s="44">
+      <c r="G177" s="43">
         <v>1200000</v>
       </c>
-      <c r="H177" s="45"/>
+      <c r="H177" s="44"/>
       <c r="I177" s="3" t="s">
         <v>24</v>
       </c>
@@ -13574,10 +13568,10 @@
         <v>249</v>
       </c>
       <c r="F178" s="2"/>
-      <c r="G178" s="44">
+      <c r="G178" s="43">
         <v>2000000</v>
       </c>
-      <c r="H178" s="45"/>
+      <c r="H178" s="44"/>
       <c r="I178" s="3" t="s">
         <v>24</v>
       </c>
@@ -13639,10 +13633,10 @@
         <v>106</v>
       </c>
       <c r="F179" s="2"/>
-      <c r="G179" s="44">
+      <c r="G179" s="43">
         <v>1600000</v>
       </c>
-      <c r="H179" s="45"/>
+      <c r="H179" s="44"/>
       <c r="I179" s="3" t="s">
         <v>24</v>
       </c>
@@ -13704,10 +13698,10 @@
         <v>69</v>
       </c>
       <c r="F180" s="2"/>
-      <c r="G180" s="44">
+      <c r="G180" s="43">
         <v>2000000</v>
       </c>
-      <c r="H180" s="45"/>
+      <c r="H180" s="44"/>
       <c r="I180" s="3" t="s">
         <v>24</v>
       </c>
@@ -13765,10 +13759,10 @@
       <c r="D181" s="8"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
-      <c r="G181" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H181" s="45"/>
+      <c r="G181" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H181" s="44"/>
       <c r="I181" s="3" t="s">
         <v>24</v>
       </c>
@@ -13830,10 +13824,10 @@
         <v>147</v>
       </c>
       <c r="F182" s="2"/>
-      <c r="G182" s="44">
+      <c r="G182" s="43">
         <v>2000000</v>
       </c>
-      <c r="H182" s="45"/>
+      <c r="H182" s="44"/>
       <c r="I182" s="3" t="s">
         <v>24</v>
       </c>
@@ -13889,10 +13883,10 @@
       <c r="D183" s="8"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
-      <c r="G183" s="44">
+      <c r="G183" s="43">
         <v>2000000</v>
       </c>
-      <c r="H183" s="45"/>
+      <c r="H183" s="44"/>
       <c r="I183" s="3" t="s">
         <v>24</v>
       </c>
@@ -13948,10 +13942,10 @@
       <c r="D184" s="8"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
-      <c r="G184" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H184" s="45"/>
+      <c r="G184" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H184" s="44"/>
       <c r="I184" s="3" t="s">
         <v>24</v>
       </c>
@@ -14009,10 +14003,10 @@
         <v>29</v>
       </c>
       <c r="F185" s="2"/>
-      <c r="G185" s="44">
+      <c r="G185" s="43">
         <v>1400000</v>
       </c>
-      <c r="H185" s="45"/>
+      <c r="H185" s="44"/>
       <c r="I185" s="3" t="s">
         <v>24</v>
       </c>
@@ -14068,10 +14062,10 @@
       <c r="D186" s="8"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
-      <c r="G186" s="44">
+      <c r="G186" s="43">
         <v>600000</v>
       </c>
-      <c r="H186" s="45"/>
+      <c r="H186" s="44"/>
       <c r="I186" s="3" t="s">
         <v>24</v>
       </c>
@@ -14133,10 +14127,10 @@
         <v>560</v>
       </c>
       <c r="F187" s="2"/>
-      <c r="G187" s="44">
+      <c r="G187" s="43">
         <v>2000000</v>
       </c>
-      <c r="H187" s="45"/>
+      <c r="H187" s="44"/>
       <c r="I187" s="3" t="s">
         <v>24</v>
       </c>
@@ -14192,10 +14186,10 @@
       <c r="D188" s="8"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
-      <c r="G188" s="44">
+      <c r="G188" s="43">
         <v>70000</v>
       </c>
-      <c r="H188" s="45"/>
+      <c r="H188" s="44"/>
       <c r="I188" s="3" t="s">
         <v>24</v>
       </c>
@@ -14253,10 +14247,10 @@
       <c r="D189" s="8"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
-      <c r="G189" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H189" s="45"/>
+      <c r="G189" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H189" s="44"/>
       <c r="I189" s="3" t="s">
         <v>24</v>
       </c>
@@ -14318,10 +14312,10 @@
         <v>263</v>
       </c>
       <c r="F190" s="2"/>
-      <c r="G190" s="44">
+      <c r="G190" s="43">
         <v>1600000</v>
       </c>
-      <c r="H190" s="45"/>
+      <c r="H190" s="44"/>
       <c r="I190" s="3" t="s">
         <v>24</v>
       </c>
@@ -14383,10 +14377,10 @@
         <v>147</v>
       </c>
       <c r="F191" s="2"/>
-      <c r="G191" s="44">
+      <c r="G191" s="43">
         <v>800000</v>
       </c>
-      <c r="H191" s="45"/>
+      <c r="H191" s="44"/>
       <c r="I191" s="3" t="s">
         <v>24</v>
       </c>
@@ -14442,10 +14436,10 @@
       <c r="D192" s="8"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
-      <c r="G192" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H192" s="45"/>
+      <c r="G192" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H192" s="44"/>
       <c r="I192" s="3" t="s">
         <v>24</v>
       </c>
@@ -14507,10 +14501,10 @@
         <v>56</v>
       </c>
       <c r="F193" s="2"/>
-      <c r="G193" s="44">
+      <c r="G193" s="43">
         <v>1200000</v>
       </c>
-      <c r="H193" s="45"/>
+      <c r="H193" s="44"/>
       <c r="I193" s="3" t="s">
         <v>24</v>
       </c>
@@ -14572,10 +14566,10 @@
         <v>106</v>
       </c>
       <c r="F194" s="2"/>
-      <c r="G194" s="44">
+      <c r="G194" s="43">
         <v>3200000</v>
       </c>
-      <c r="H194" s="45"/>
+      <c r="H194" s="44"/>
       <c r="I194" s="3" t="s">
         <v>24</v>
       </c>
@@ -14631,10 +14625,10 @@
       <c r="D195" s="8"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
-      <c r="G195" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H195" s="45"/>
+      <c r="G195" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H195" s="44"/>
       <c r="I195" s="3" t="s">
         <v>24</v>
       </c>
@@ -14694,10 +14688,10 @@
         <v>270</v>
       </c>
       <c r="F196" s="2"/>
-      <c r="G196" s="44">
+      <c r="G196" s="43">
         <v>1600000</v>
       </c>
-      <c r="H196" s="45"/>
+      <c r="H196" s="44"/>
       <c r="I196" s="3" t="s">
         <v>24</v>
       </c>
@@ -14755,10 +14749,10 @@
         <v>29</v>
       </c>
       <c r="F197" s="2"/>
-      <c r="G197" s="44">
+      <c r="G197" s="43">
         <v>1600000</v>
       </c>
-      <c r="H197" s="45"/>
+      <c r="H197" s="44"/>
       <c r="I197" s="3" t="s">
         <v>24</v>
       </c>
@@ -14820,10 +14814,10 @@
         <v>66</v>
       </c>
       <c r="F198" s="2"/>
-      <c r="G198" s="44">
+      <c r="G198" s="43">
         <v>1600000</v>
       </c>
-      <c r="H198" s="45"/>
+      <c r="H198" s="44"/>
       <c r="I198" s="3" t="s">
         <v>24</v>
       </c>
@@ -14885,10 +14879,10 @@
         <v>69</v>
       </c>
       <c r="F199" s="2"/>
-      <c r="G199" s="44">
+      <c r="G199" s="43">
         <v>800000</v>
       </c>
-      <c r="H199" s="45"/>
+      <c r="H199" s="44"/>
       <c r="I199" s="3" t="s">
         <v>24</v>
       </c>
@@ -14950,10 +14944,10 @@
         <v>66</v>
       </c>
       <c r="F200" s="2"/>
-      <c r="G200" s="44">
+      <c r="G200" s="43">
         <v>1200000</v>
       </c>
-      <c r="H200" s="45"/>
+      <c r="H200" s="44"/>
       <c r="I200" s="3" t="s">
         <v>24</v>
       </c>
@@ -15011,10 +15005,10 @@
         <v>378</v>
       </c>
       <c r="F201" s="2"/>
-      <c r="G201" s="44">
+      <c r="G201" s="43">
         <v>100000</v>
       </c>
-      <c r="H201" s="45"/>
+      <c r="H201" s="44"/>
       <c r="I201" s="3" t="s">
         <v>24</v>
       </c>
@@ -15070,10 +15064,10 @@
       <c r="D202" s="8"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
-      <c r="G202" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H202" s="45"/>
+      <c r="G202" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H202" s="44"/>
       <c r="I202" s="3" t="s">
         <v>24</v>
       </c>
@@ -15135,10 +15129,10 @@
         <v>278</v>
       </c>
       <c r="F203" s="2"/>
-      <c r="G203" s="44">
+      <c r="G203" s="43">
         <v>1200000</v>
       </c>
-      <c r="H203" s="45"/>
+      <c r="H203" s="44"/>
       <c r="I203" s="3" t="s">
         <v>24</v>
       </c>
@@ -15198,10 +15192,10 @@
       </c>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
-      <c r="G204" s="44">
+      <c r="G204" s="43">
         <v>800000</v>
       </c>
-      <c r="H204" s="45"/>
+      <c r="H204" s="44"/>
       <c r="I204" s="3" t="s">
         <v>24</v>
       </c>
@@ -15257,10 +15251,10 @@
       <c r="D205" s="8"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
-      <c r="G205" s="44">
+      <c r="G205" s="43">
         <v>1130000</v>
       </c>
-      <c r="H205" s="45"/>
+      <c r="H205" s="44"/>
       <c r="I205" s="3" t="s">
         <v>24</v>
       </c>
@@ -15318,10 +15312,10 @@
         <v>270</v>
       </c>
       <c r="F206" s="2"/>
-      <c r="G206" s="44">
+      <c r="G206" s="43">
         <v>460000</v>
       </c>
-      <c r="H206" s="45"/>
+      <c r="H206" s="44"/>
       <c r="I206" s="3" t="s">
         <v>24</v>
       </c>
@@ -15383,10 +15377,10 @@
         <v>41</v>
       </c>
       <c r="F207" s="2"/>
-      <c r="G207" s="44">
+      <c r="G207" s="43">
         <v>800000</v>
       </c>
-      <c r="H207" s="45"/>
+      <c r="H207" s="44"/>
       <c r="I207" s="3" t="s">
         <v>24</v>
       </c>
@@ -15442,10 +15436,10 @@
       <c r="D208" s="8"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
-      <c r="G208" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H208" s="45"/>
+      <c r="G208" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H208" s="44"/>
       <c r="I208" s="3" t="s">
         <v>24</v>
       </c>
@@ -15507,10 +15501,10 @@
         <v>147</v>
       </c>
       <c r="F209" s="2"/>
-      <c r="G209" s="44">
+      <c r="G209" s="43">
         <v>1600000</v>
       </c>
-      <c r="H209" s="45"/>
+      <c r="H209" s="44"/>
       <c r="I209" s="3" t="s">
         <v>24</v>
       </c>
@@ -15572,10 +15566,10 @@
         <v>287</v>
       </c>
       <c r="F210" s="2"/>
-      <c r="G210" s="44">
+      <c r="G210" s="43">
         <v>800000</v>
       </c>
-      <c r="H210" s="45" t="s">
+      <c r="H210" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I210" s="3" t="s">
@@ -15639,10 +15633,10 @@
         <v>289</v>
       </c>
       <c r="F211" s="2"/>
-      <c r="G211" s="44">
+      <c r="G211" s="43">
         <v>800000</v>
       </c>
-      <c r="H211" s="45"/>
+      <c r="H211" s="44"/>
       <c r="I211" s="3" t="s">
         <v>24</v>
       </c>
@@ -15704,10 +15698,10 @@
         <v>289</v>
       </c>
       <c r="F212" s="2"/>
-      <c r="G212" s="44">
+      <c r="G212" s="43">
         <v>1000000</v>
       </c>
-      <c r="H212" s="45"/>
+      <c r="H212" s="44"/>
       <c r="I212" s="3" t="s">
         <v>24</v>
       </c>
@@ -15769,10 +15763,10 @@
         <v>554</v>
       </c>
       <c r="F213" s="2"/>
-      <c r="G213" s="44">
+      <c r="G213" s="43">
         <v>800000</v>
       </c>
-      <c r="H213" s="45"/>
+      <c r="H213" s="44"/>
       <c r="I213" s="3" t="s">
         <v>24</v>
       </c>
@@ -15834,10 +15828,10 @@
         <v>29</v>
       </c>
       <c r="F214" s="2"/>
-      <c r="G214" s="44">
+      <c r="G214" s="43">
         <v>1200000</v>
       </c>
-      <c r="H214" s="45"/>
+      <c r="H214" s="44"/>
       <c r="I214" s="3" t="s">
         <v>24</v>
       </c>
@@ -15899,10 +15893,10 @@
         <v>56</v>
       </c>
       <c r="F215" s="2"/>
-      <c r="G215" s="44">
+      <c r="G215" s="43">
         <v>800000</v>
       </c>
-      <c r="H215" s="45"/>
+      <c r="H215" s="44"/>
       <c r="I215" s="3" t="s">
         <v>24</v>
       </c>
@@ -15964,10 +15958,10 @@
         <v>554</v>
       </c>
       <c r="F216" s="2"/>
-      <c r="G216" s="44">
+      <c r="G216" s="43">
         <v>800000</v>
       </c>
-      <c r="H216" s="45"/>
+      <c r="H216" s="44"/>
       <c r="I216" s="3" t="s">
         <v>24</v>
       </c>
@@ -16029,10 +16023,10 @@
         <v>106</v>
       </c>
       <c r="F217" s="2"/>
-      <c r="G217" s="44">
+      <c r="G217" s="43">
         <v>1200000</v>
       </c>
-      <c r="H217" s="45"/>
+      <c r="H217" s="44"/>
       <c r="I217" s="3" t="s">
         <v>24</v>
       </c>
@@ -16094,10 +16088,10 @@
         <v>56</v>
       </c>
       <c r="F218" s="2"/>
-      <c r="G218" s="44">
+      <c r="G218" s="43">
         <v>800000</v>
       </c>
-      <c r="H218" s="45"/>
+      <c r="H218" s="44"/>
       <c r="I218" s="3" t="s">
         <v>24</v>
       </c>
@@ -16159,10 +16153,10 @@
         <v>299</v>
       </c>
       <c r="F219" s="2"/>
-      <c r="G219" s="44">
+      <c r="G219" s="43">
         <v>500000</v>
       </c>
-      <c r="H219" s="45"/>
+      <c r="H219" s="44"/>
       <c r="I219" s="3" t="s">
         <v>24</v>
       </c>
@@ -16224,10 +16218,10 @@
         <v>301</v>
       </c>
       <c r="F220" s="2"/>
-      <c r="G220" s="44">
+      <c r="G220" s="43">
         <v>800000</v>
       </c>
-      <c r="H220" s="45"/>
+      <c r="H220" s="44"/>
       <c r="I220" s="3" t="s">
         <v>24</v>
       </c>
@@ -16289,10 +16283,10 @@
         <v>561</v>
       </c>
       <c r="F221" s="2"/>
-      <c r="G221" s="44">
+      <c r="G221" s="43">
         <v>40000</v>
       </c>
-      <c r="H221" s="45"/>
+      <c r="H221" s="44"/>
       <c r="I221" s="3" t="s">
         <v>24</v>
       </c>
@@ -16354,10 +16348,10 @@
         <v>304</v>
       </c>
       <c r="F222" s="2"/>
-      <c r="G222" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H222" s="45"/>
+      <c r="G222" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H222" s="44"/>
       <c r="I222" s="3" t="s">
         <v>24</v>
       </c>
@@ -16419,10 +16413,10 @@
         <v>56</v>
       </c>
       <c r="F223" s="2"/>
-      <c r="G223" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H223" s="45"/>
+      <c r="G223" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H223" s="44"/>
       <c r="I223" s="3" t="s">
         <v>24</v>
       </c>
@@ -16484,10 +16478,10 @@
         <v>56</v>
       </c>
       <c r="F224" s="2"/>
-      <c r="G224" s="44">
+      <c r="G224" s="43">
         <v>800000</v>
       </c>
-      <c r="H224" s="45"/>
+      <c r="H224" s="44"/>
       <c r="I224" s="3" t="s">
         <v>24</v>
       </c>
@@ -16549,10 +16543,10 @@
         <v>309</v>
       </c>
       <c r="F225" s="2"/>
-      <c r="G225" s="44">
+      <c r="G225" s="43">
         <v>800000</v>
       </c>
-      <c r="H225" s="45"/>
+      <c r="H225" s="44"/>
       <c r="I225" s="3" t="s">
         <v>24</v>
       </c>
@@ -16614,10 +16608,10 @@
         <v>309</v>
       </c>
       <c r="F226" s="2"/>
-      <c r="G226" s="44">
+      <c r="G226" s="43">
         <v>800000</v>
       </c>
-      <c r="H226" s="45"/>
+      <c r="H226" s="44"/>
       <c r="I226" s="3" t="s">
         <v>24</v>
       </c>
@@ -16679,10 +16673,10 @@
         <v>309</v>
       </c>
       <c r="F227" s="2"/>
-      <c r="G227" s="44">
+      <c r="G227" s="43">
         <v>1200000</v>
       </c>
-      <c r="H227" s="45"/>
+      <c r="H227" s="44"/>
       <c r="I227" s="3" t="s">
         <v>24</v>
       </c>
@@ -16744,10 +16738,10 @@
         <v>309</v>
       </c>
       <c r="F228" s="2"/>
-      <c r="G228" s="44">
+      <c r="G228" s="43">
         <v>800000</v>
       </c>
-      <c r="H228" s="45"/>
+      <c r="H228" s="44"/>
       <c r="I228" s="3" t="s">
         <v>24</v>
       </c>
@@ -16809,10 +16803,10 @@
         <v>309</v>
       </c>
       <c r="F229" s="2"/>
-      <c r="G229" s="44">
+      <c r="G229" s="43">
         <v>800000</v>
       </c>
-      <c r="H229" s="45"/>
+      <c r="H229" s="44"/>
       <c r="I229" s="3" t="s">
         <v>24</v>
       </c>
@@ -16874,10 +16868,10 @@
         <v>320</v>
       </c>
       <c r="F230" s="2"/>
-      <c r="G230" s="44">
+      <c r="G230" s="43">
         <v>800000</v>
       </c>
-      <c r="H230" s="45"/>
+      <c r="H230" s="44"/>
       <c r="I230" s="3" t="s">
         <v>24</v>
       </c>
@@ -16939,10 +16933,10 @@
         <v>323</v>
       </c>
       <c r="F231" s="2"/>
-      <c r="G231" s="44">
+      <c r="G231" s="43">
         <v>800000</v>
       </c>
-      <c r="H231" s="45"/>
+      <c r="H231" s="44"/>
       <c r="I231" s="3" t="s">
         <v>24</v>
       </c>
@@ -17004,10 +16998,10 @@
         <v>326</v>
       </c>
       <c r="F232" s="2"/>
-      <c r="G232" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H232" s="45"/>
+      <c r="G232" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H232" s="44"/>
       <c r="I232" s="3" t="s">
         <v>24</v>
       </c>
@@ -17069,10 +17063,10 @@
         <v>326</v>
       </c>
       <c r="F233" s="2"/>
-      <c r="G233" s="44">
+      <c r="G233" s="43">
         <v>800000</v>
       </c>
-      <c r="H233" s="45"/>
+      <c r="H233" s="44"/>
       <c r="I233" s="3" t="s">
         <v>24</v>
       </c>
@@ -17134,10 +17128,10 @@
         <v>331</v>
       </c>
       <c r="F234" s="2"/>
-      <c r="G234" s="44">
+      <c r="G234" s="43">
         <v>800000</v>
       </c>
-      <c r="H234" s="45"/>
+      <c r="H234" s="44"/>
       <c r="I234" s="3" t="s">
         <v>24</v>
       </c>
@@ -17199,10 +17193,10 @@
         <v>334</v>
       </c>
       <c r="F235" s="2"/>
-      <c r="G235" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H235" s="45"/>
+      <c r="G235" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H235" s="44"/>
       <c r="I235" s="3" t="s">
         <v>24</v>
       </c>
@@ -17264,10 +17258,10 @@
         <v>331</v>
       </c>
       <c r="F236" s="2"/>
-      <c r="G236" s="44">
+      <c r="G236" s="43">
         <v>800000</v>
       </c>
-      <c r="H236" s="45"/>
+      <c r="H236" s="44"/>
       <c r="I236" s="3" t="s">
         <v>24</v>
       </c>
@@ -17329,10 +17323,10 @@
         <v>558</v>
       </c>
       <c r="F237" s="2"/>
-      <c r="G237" s="44">
+      <c r="G237" s="43">
         <v>800000</v>
       </c>
-      <c r="H237" s="45"/>
+      <c r="H237" s="44"/>
       <c r="I237" s="3" t="s">
         <v>24</v>
       </c>
@@ -17394,10 +17388,10 @@
         <v>339</v>
       </c>
       <c r="F238" s="2"/>
-      <c r="G238" s="44">
+      <c r="G238" s="43">
         <v>800000</v>
       </c>
-      <c r="H238" s="45"/>
+      <c r="H238" s="44"/>
       <c r="I238" s="3" t="s">
         <v>24</v>
       </c>
@@ -17457,10 +17451,10 @@
       </c>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
-      <c r="G239" s="44">
+      <c r="G239" s="43">
         <v>800000</v>
       </c>
-      <c r="H239" s="45"/>
+      <c r="H239" s="44"/>
       <c r="I239" s="3" t="s">
         <v>24</v>
       </c>
@@ -17522,10 +17516,10 @@
         <v>342</v>
       </c>
       <c r="F240" s="2"/>
-      <c r="G240" s="44">
+      <c r="G240" s="43">
         <v>800000</v>
       </c>
-      <c r="H240" s="45"/>
+      <c r="H240" s="44"/>
       <c r="I240" s="3" t="s">
         <v>24</v>
       </c>
@@ -17587,10 +17581,10 @@
         <v>344</v>
       </c>
       <c r="F241" s="2"/>
-      <c r="G241" s="44">
+      <c r="G241" s="43">
         <v>800000</v>
       </c>
-      <c r="H241" s="45"/>
+      <c r="H241" s="44"/>
       <c r="I241" s="3" t="s">
         <v>24</v>
       </c>
@@ -17652,10 +17646,10 @@
         <v>558</v>
       </c>
       <c r="F242" s="2"/>
-      <c r="G242" s="44">
+      <c r="G242" s="43">
         <v>800000</v>
       </c>
-      <c r="H242" s="45"/>
+      <c r="H242" s="44"/>
       <c r="I242" s="3" t="s">
         <v>24</v>
       </c>
@@ -17717,10 +17711,10 @@
         <v>562</v>
       </c>
       <c r="F243" s="2"/>
-      <c r="G243" s="44">
+      <c r="G243" s="43">
         <v>800000</v>
       </c>
-      <c r="H243" s="45"/>
+      <c r="H243" s="44"/>
       <c r="I243" s="3" t="s">
         <v>24</v>
       </c>
@@ -17782,10 +17776,10 @@
         <v>558</v>
       </c>
       <c r="F244" s="2"/>
-      <c r="G244" s="44">
+      <c r="G244" s="43">
         <v>800000</v>
       </c>
-      <c r="H244" s="45"/>
+      <c r="H244" s="44"/>
       <c r="I244" s="3" t="s">
         <v>24</v>
       </c>
@@ -17847,10 +17841,10 @@
         <v>558</v>
       </c>
       <c r="F245" s="2"/>
-      <c r="G245" s="44">
+      <c r="G245" s="43">
         <v>800000</v>
       </c>
-      <c r="H245" s="45"/>
+      <c r="H245" s="44"/>
       <c r="I245" s="3" t="s">
         <v>24</v>
       </c>
@@ -17912,10 +17906,10 @@
         <v>339</v>
       </c>
       <c r="F246" s="2"/>
-      <c r="G246" s="44">
+      <c r="G246" s="43">
         <v>800000</v>
       </c>
-      <c r="H246" s="45"/>
+      <c r="H246" s="44"/>
       <c r="I246" s="3" t="s">
         <v>24</v>
       </c>
@@ -17977,10 +17971,10 @@
         <v>339</v>
       </c>
       <c r="F247" s="2"/>
-      <c r="G247" s="44">
+      <c r="G247" s="43">
         <v>800000</v>
       </c>
-      <c r="H247" s="45"/>
+      <c r="H247" s="44"/>
       <c r="I247" s="3" t="s">
         <v>24</v>
       </c>
@@ -18042,10 +18036,10 @@
         <v>558</v>
       </c>
       <c r="F248" s="2"/>
-      <c r="G248" s="44">
+      <c r="G248" s="43">
         <v>800000</v>
       </c>
-      <c r="H248" s="45"/>
+      <c r="H248" s="44"/>
       <c r="I248" s="3" t="s">
         <v>24</v>
       </c>
@@ -18107,10 +18101,10 @@
         <v>558</v>
       </c>
       <c r="F249" s="2"/>
-      <c r="G249" s="44">
+      <c r="G249" s="43">
         <v>800000</v>
       </c>
-      <c r="H249" s="45"/>
+      <c r="H249" s="44"/>
       <c r="I249" s="3" t="s">
         <v>24</v>
       </c>
@@ -18172,10 +18166,10 @@
         <v>344</v>
       </c>
       <c r="F250" s="2"/>
-      <c r="G250" s="44">
+      <c r="G250" s="43">
         <v>800000</v>
       </c>
-      <c r="H250" s="45"/>
+      <c r="H250" s="44"/>
       <c r="I250" s="3" t="s">
         <v>24</v>
       </c>
@@ -18237,10 +18231,10 @@
         <v>558</v>
       </c>
       <c r="F251" s="2"/>
-      <c r="G251" s="44">
+      <c r="G251" s="43">
         <v>800000</v>
       </c>
-      <c r="H251" s="45"/>
+      <c r="H251" s="44"/>
       <c r="I251" s="3" t="s">
         <v>24</v>
       </c>
@@ -18302,10 +18296,10 @@
         <v>342</v>
       </c>
       <c r="F252" s="2"/>
-      <c r="G252" s="44">
+      <c r="G252" s="43">
         <v>800000</v>
       </c>
-      <c r="H252" s="45"/>
+      <c r="H252" s="44"/>
       <c r="I252" s="3" t="s">
         <v>24</v>
       </c>
@@ -18367,10 +18361,10 @@
         <v>342</v>
       </c>
       <c r="F253" s="2"/>
-      <c r="G253" s="44">
+      <c r="G253" s="43">
         <v>800000</v>
       </c>
-      <c r="H253" s="45"/>
+      <c r="H253" s="44"/>
       <c r="I253" s="3" t="s">
         <v>24</v>
       </c>
@@ -18430,10 +18424,10 @@
         <v>278</v>
       </c>
       <c r="F254" s="2"/>
-      <c r="G254" s="44">
+      <c r="G254" s="43">
         <v>200000</v>
       </c>
-      <c r="H254" s="45"/>
+      <c r="H254" s="44"/>
       <c r="I254" s="3" t="s">
         <v>24</v>
       </c>
@@ -18495,10 +18489,10 @@
         <v>56</v>
       </c>
       <c r="F255" s="2"/>
-      <c r="G255" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H255" s="45"/>
+      <c r="G255" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H255" s="44"/>
       <c r="I255" s="3" t="s">
         <v>24</v>
       </c>
@@ -18560,10 +18554,10 @@
         <v>360</v>
       </c>
       <c r="F256" s="2"/>
-      <c r="G256" s="44">
+      <c r="G256" s="43">
         <v>850000</v>
       </c>
-      <c r="H256" s="45"/>
+      <c r="H256" s="44"/>
       <c r="I256" s="3" t="s">
         <v>24</v>
       </c>
@@ -18625,10 +18619,10 @@
         <v>287</v>
       </c>
       <c r="F257" s="2"/>
-      <c r="G257" s="44">
+      <c r="G257" s="43">
         <v>800000</v>
       </c>
-      <c r="H257" s="45" t="s">
+      <c r="H257" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I257" s="3" t="s">
@@ -18692,10 +18686,10 @@
         <v>287</v>
       </c>
       <c r="F258" s="2"/>
-      <c r="G258" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H258" s="45" t="s">
+      <c r="G258" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H258" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I258" s="3" t="s">
@@ -18759,10 +18753,10 @@
         <v>364</v>
       </c>
       <c r="F259" s="2"/>
-      <c r="G259" s="44">
+      <c r="G259" s="43">
         <v>800000</v>
       </c>
-      <c r="H259" s="45"/>
+      <c r="H259" s="44"/>
       <c r="I259" s="3" t="s">
         <v>24</v>
       </c>
@@ -18824,10 +18818,10 @@
         <v>133</v>
       </c>
       <c r="F260" s="2"/>
-      <c r="G260" s="44">
+      <c r="G260" s="43">
         <v>800000</v>
       </c>
-      <c r="H260" s="45"/>
+      <c r="H260" s="44"/>
       <c r="I260" s="3" t="s">
         <v>24</v>
       </c>
@@ -18889,10 +18883,10 @@
         <v>133</v>
       </c>
       <c r="F261" s="2"/>
-      <c r="G261" s="44">
+      <c r="G261" s="43">
         <v>800000</v>
       </c>
-      <c r="H261" s="45"/>
+      <c r="H261" s="44"/>
       <c r="I261" s="3" t="s">
         <v>24</v>
       </c>
@@ -18954,10 +18948,10 @@
         <v>133</v>
       </c>
       <c r="F262" s="2"/>
-      <c r="G262" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H262" s="45"/>
+      <c r="G262" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H262" s="44"/>
       <c r="I262" s="3" t="s">
         <v>24</v>
       </c>
@@ -19019,10 +19013,10 @@
         <v>66</v>
       </c>
       <c r="F263" s="2"/>
-      <c r="G263" s="44">
+      <c r="G263" s="43">
         <v>800000</v>
       </c>
-      <c r="H263" s="45"/>
+      <c r="H263" s="44"/>
       <c r="I263" s="3" t="s">
         <v>24</v>
       </c>
@@ -19084,10 +19078,10 @@
         <v>66</v>
       </c>
       <c r="F264" s="2"/>
-      <c r="G264" s="44">
+      <c r="G264" s="43">
         <v>800000</v>
       </c>
-      <c r="H264" s="45"/>
+      <c r="H264" s="44"/>
       <c r="I264" s="3" t="s">
         <v>24</v>
       </c>
@@ -19149,10 +19143,10 @@
         <v>66</v>
       </c>
       <c r="F265" s="2"/>
-      <c r="G265" s="44">
+      <c r="G265" s="43">
         <v>800000</v>
       </c>
-      <c r="H265" s="45"/>
+      <c r="H265" s="44"/>
       <c r="I265" s="3" t="s">
         <v>24</v>
       </c>
@@ -19212,10 +19206,10 @@
         <v>41</v>
       </c>
       <c r="F266" s="2"/>
-      <c r="G266" s="44">
+      <c r="G266" s="43">
         <v>800000</v>
       </c>
-      <c r="H266" s="45"/>
+      <c r="H266" s="44"/>
       <c r="I266" s="3" t="s">
         <v>24</v>
       </c>
@@ -19277,10 +19271,10 @@
         <v>106</v>
       </c>
       <c r="F267" s="2"/>
-      <c r="G267" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H267" s="45"/>
+      <c r="G267" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H267" s="44"/>
       <c r="I267" s="3" t="s">
         <v>24</v>
       </c>
@@ -19338,10 +19332,10 @@
         <v>405</v>
       </c>
       <c r="F268" s="2"/>
-      <c r="G268" s="44">
+      <c r="G268" s="43">
         <v>200000</v>
       </c>
-      <c r="H268" s="45"/>
+      <c r="H268" s="44"/>
       <c r="I268" s="3" t="s">
         <v>24</v>
       </c>
@@ -19401,10 +19395,10 @@
         <v>378</v>
       </c>
       <c r="F269" s="2"/>
-      <c r="G269" s="44">
+      <c r="G269" s="43">
         <v>50000</v>
       </c>
-      <c r="H269" s="45"/>
+      <c r="H269" s="44"/>
       <c r="I269" s="3" t="s">
         <v>24</v>
       </c>
@@ -19466,10 +19460,10 @@
         <v>378</v>
       </c>
       <c r="F270" s="2"/>
-      <c r="G270" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H270" s="45"/>
+      <c r="G270" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H270" s="44"/>
       <c r="I270" s="3" t="s">
         <v>24</v>
       </c>
@@ -19531,10 +19525,10 @@
         <v>382</v>
       </c>
       <c r="F271" s="2"/>
-      <c r="G271" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H271" s="45"/>
+      <c r="G271" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H271" s="44"/>
       <c r="I271" s="3" t="s">
         <v>24</v>
       </c>
@@ -19594,10 +19588,10 @@
         <v>41</v>
       </c>
       <c r="F272" s="2"/>
-      <c r="G272" s="44">
+      <c r="G272" s="43">
         <v>1400000</v>
       </c>
-      <c r="H272" s="45"/>
+      <c r="H272" s="44"/>
       <c r="I272" s="3" t="s">
         <v>24</v>
       </c>
@@ -19659,10 +19653,10 @@
         <v>147</v>
       </c>
       <c r="F273" s="2"/>
-      <c r="G273" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H273" s="45"/>
+      <c r="G273" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H273" s="44"/>
       <c r="I273" s="3" t="s">
         <v>24</v>
       </c>
@@ -19722,10 +19716,10 @@
         <v>133</v>
       </c>
       <c r="F274" s="2"/>
-      <c r="G274" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H274" s="45"/>
+      <c r="G274" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H274" s="44"/>
       <c r="I274" s="3" t="s">
         <v>24</v>
       </c>
@@ -19787,10 +19781,10 @@
         <v>66</v>
       </c>
       <c r="F275" s="2"/>
-      <c r="G275" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H275" s="45"/>
+      <c r="G275" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H275" s="44"/>
       <c r="I275" s="3" t="s">
         <v>24</v>
       </c>
@@ -19852,10 +19846,10 @@
         <v>364</v>
       </c>
       <c r="F276" s="2"/>
-      <c r="G276" s="44">
+      <c r="G276" s="43">
         <v>80000</v>
       </c>
-      <c r="H276" s="45"/>
+      <c r="H276" s="44"/>
       <c r="I276" s="3" t="s">
         <v>24</v>
       </c>
@@ -19917,10 +19911,10 @@
         <v>389</v>
       </c>
       <c r="F277" s="2"/>
-      <c r="G277" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H277" s="45"/>
+      <c r="G277" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H277" s="44"/>
       <c r="I277" s="3" t="s">
         <v>24</v>
       </c>
@@ -19980,10 +19974,10 @@
         <v>41</v>
       </c>
       <c r="F278" s="2"/>
-      <c r="G278" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H278" s="45"/>
+      <c r="G278" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H278" s="44"/>
       <c r="I278" s="3" t="s">
         <v>24</v>
       </c>
@@ -20043,10 +20037,10 @@
         <v>249</v>
       </c>
       <c r="F279" s="2"/>
-      <c r="G279" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H279" s="45"/>
+      <c r="G279" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H279" s="44"/>
       <c r="I279" s="3" t="s">
         <v>24</v>
       </c>
@@ -20104,10 +20098,10 @@
         <v>278</v>
       </c>
       <c r="F280" s="2"/>
-      <c r="G280" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H280" s="45"/>
+      <c r="G280" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H280" s="44"/>
       <c r="I280" s="3" t="s">
         <v>24</v>
       </c>
@@ -20165,10 +20159,10 @@
         <v>41</v>
       </c>
       <c r="F281" s="2"/>
-      <c r="G281" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H281" s="45"/>
+      <c r="G281" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H281" s="44"/>
       <c r="I281" s="3" t="s">
         <v>24</v>
       </c>
@@ -20226,8 +20220,8 @@
         <v>395</v>
       </c>
       <c r="F282" s="2"/>
-      <c r="G282" s="44"/>
-      <c r="H282" s="45"/>
+      <c r="G282" s="43"/>
+      <c r="H282" s="44"/>
       <c r="I282" s="3" t="s">
         <v>24</v>
       </c>
@@ -20289,8 +20283,8 @@
         <v>278</v>
       </c>
       <c r="F283" s="2"/>
-      <c r="G283" s="44"/>
-      <c r="H283" s="45"/>
+      <c r="G283" s="43"/>
+      <c r="H283" s="44"/>
       <c r="I283" s="3" t="s">
         <v>24</v>
       </c>
@@ -20348,8 +20342,8 @@
         <v>29</v>
       </c>
       <c r="F284" s="2"/>
-      <c r="G284" s="44"/>
-      <c r="H284" s="45"/>
+      <c r="G284" s="43"/>
+      <c r="H284" s="44"/>
       <c r="I284" s="3" t="s">
         <v>24</v>
       </c>
@@ -20407,8 +20401,8 @@
         <v>29</v>
       </c>
       <c r="F285" s="2"/>
-      <c r="G285" s="44"/>
-      <c r="H285" s="45"/>
+      <c r="G285" s="43"/>
+      <c r="H285" s="44"/>
       <c r="I285" s="3" t="s">
         <v>24</v>
       </c>
@@ -20468,10 +20462,10 @@
         <v>41</v>
       </c>
       <c r="F286" s="2"/>
-      <c r="G286" s="44">
-        <v>400000</v>
-      </c>
-      <c r="H286" s="45"/>
+      <c r="G286" s="43">
+        <v>400000</v>
+      </c>
+      <c r="H286" s="44"/>
       <c r="I286" s="3" t="s">
         <v>24</v>
       </c>
@@ -20531,8 +20525,8 @@
         <v>382</v>
       </c>
       <c r="F287" s="2"/>
-      <c r="G287" s="44"/>
-      <c r="H287" s="45"/>
+      <c r="G287" s="43"/>
+      <c r="H287" s="44"/>
       <c r="I287" s="3" t="s">
         <v>24</v>
       </c>
@@ -20592,8 +20586,8 @@
         <v>41</v>
       </c>
       <c r="F288" s="2"/>
-      <c r="G288" s="44"/>
-      <c r="H288" s="45"/>
+      <c r="G288" s="43"/>
+      <c r="H288" s="44"/>
       <c r="I288" s="3" t="s">
         <v>24</v>
       </c>
@@ -20653,8 +20647,8 @@
         <v>147</v>
       </c>
       <c r="F289" s="2"/>
-      <c r="G289" s="44"/>
-      <c r="H289" s="45"/>
+      <c r="G289" s="43"/>
+      <c r="H289" s="44"/>
       <c r="I289" s="3" t="s">
         <v>24</v>
       </c>
@@ -20714,8 +20708,8 @@
         <v>29</v>
       </c>
       <c r="F290" s="2"/>
-      <c r="G290" s="44"/>
-      <c r="H290" s="45"/>
+      <c r="G290" s="43"/>
+      <c r="H290" s="44"/>
       <c r="I290" s="3" t="s">
         <v>24</v>
       </c>
@@ -20777,8 +20771,8 @@
         <v>405</v>
       </c>
       <c r="F291" s="2"/>
-      <c r="G291" s="44"/>
-      <c r="H291" s="45"/>
+      <c r="G291" s="43"/>
+      <c r="H291" s="44"/>
       <c r="I291" s="3" t="s">
         <v>24</v>
       </c>
@@ -20838,8 +20832,8 @@
         <v>563</v>
       </c>
       <c r="F292" s="2"/>
-      <c r="G292" s="44"/>
-      <c r="H292" s="45" t="s">
+      <c r="G292" s="43"/>
+      <c r="H292" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I292" s="3" t="s">
@@ -20901,8 +20895,8 @@
         <v>563</v>
       </c>
       <c r="F293" s="2"/>
-      <c r="G293" s="44"/>
-      <c r="H293" s="45" t="s">
+      <c r="G293" s="43"/>
+      <c r="H293" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I293" s="3" t="s">
@@ -20964,8 +20958,8 @@
         <v>41</v>
       </c>
       <c r="F294" s="2"/>
-      <c r="G294" s="44"/>
-      <c r="H294" s="45"/>
+      <c r="G294" s="43"/>
+      <c r="H294" s="44"/>
       <c r="I294" s="3" t="s">
         <v>24</v>
       </c>
@@ -21023,8 +21017,8 @@
         <v>412</v>
       </c>
       <c r="F295" s="2"/>
-      <c r="G295" s="44"/>
-      <c r="H295" s="45"/>
+      <c r="G295" s="43"/>
+      <c r="H295" s="44"/>
       <c r="I295" s="3" t="s">
         <v>24</v>
       </c>
@@ -21086,8 +21080,8 @@
         <v>414</v>
       </c>
       <c r="F296" s="2"/>
-      <c r="G296" s="44"/>
-      <c r="H296" s="45"/>
+      <c r="G296" s="43"/>
+      <c r="H296" s="44"/>
       <c r="I296" s="3" t="s">
         <v>24</v>
       </c>
@@ -21149,8 +21143,8 @@
         <v>414</v>
       </c>
       <c r="F297" s="2"/>
-      <c r="G297" s="44"/>
-      <c r="H297" s="45"/>
+      <c r="G297" s="43"/>
+      <c r="H297" s="44"/>
       <c r="I297" s="3" t="s">
         <v>24</v>
       </c>
@@ -21208,8 +21202,8 @@
         <v>29</v>
       </c>
       <c r="F298" s="2"/>
-      <c r="G298" s="44"/>
-      <c r="H298" s="45"/>
+      <c r="G298" s="43"/>
+      <c r="H298" s="44"/>
       <c r="I298" s="3" t="s">
         <v>24</v>
       </c>
@@ -21267,8 +21261,8 @@
         <v>360</v>
       </c>
       <c r="F299" s="2"/>
-      <c r="G299" s="44"/>
-      <c r="H299" s="45"/>
+      <c r="G299" s="43"/>
+      <c r="H299" s="44"/>
       <c r="I299" s="3" t="s">
         <v>24</v>
       </c>
@@ -21326,8 +21320,8 @@
         <v>29</v>
       </c>
       <c r="F300" s="2"/>
-      <c r="G300" s="44"/>
-      <c r="H300" s="45"/>
+      <c r="G300" s="43"/>
+      <c r="H300" s="44"/>
       <c r="I300" s="3" t="s">
         <v>24</v>
       </c>
@@ -21385,8 +21379,8 @@
         <v>419</v>
       </c>
       <c r="F301" s="2"/>
-      <c r="G301" s="44"/>
-      <c r="H301" s="45"/>
+      <c r="G301" s="43"/>
+      <c r="H301" s="44"/>
       <c r="I301" s="3" t="s">
         <v>24</v>
       </c>
@@ -21446,8 +21440,8 @@
         <v>249</v>
       </c>
       <c r="F302" s="2"/>
-      <c r="G302" s="44"/>
-      <c r="H302" s="45"/>
+      <c r="G302" s="43"/>
+      <c r="H302" s="44"/>
       <c r="I302" s="3" t="s">
         <v>24</v>
       </c>
@@ -21509,8 +21503,8 @@
         <v>289</v>
       </c>
       <c r="F303" s="2"/>
-      <c r="G303" s="44"/>
-      <c r="H303" s="45"/>
+      <c r="G303" s="43"/>
+      <c r="H303" s="44"/>
       <c r="I303" s="3" t="s">
         <v>24</v>
       </c>
@@ -21572,8 +21566,8 @@
         <v>29</v>
       </c>
       <c r="F304" s="2"/>
-      <c r="G304" s="44"/>
-      <c r="H304" s="45"/>
+      <c r="G304" s="43"/>
+      <c r="H304" s="44"/>
       <c r="I304" s="3" t="s">
         <v>24</v>
       </c>
@@ -21633,8 +21627,8 @@
         <v>473</v>
       </c>
       <c r="F305" s="2"/>
-      <c r="G305" s="44"/>
-      <c r="H305" s="45"/>
+      <c r="G305" s="43"/>
+      <c r="H305" s="44"/>
       <c r="I305" s="3" t="s">
         <v>24</v>
       </c>
@@ -21696,8 +21690,8 @@
         <v>69</v>
       </c>
       <c r="F306" s="2"/>
-      <c r="G306" s="44"/>
-      <c r="H306" s="45"/>
+      <c r="G306" s="43"/>
+      <c r="H306" s="44"/>
       <c r="I306" s="3" t="s">
         <v>24</v>
       </c>
@@ -21759,8 +21753,8 @@
         <v>147</v>
       </c>
       <c r="F307" s="2"/>
-      <c r="G307" s="44"/>
-      <c r="H307" s="45"/>
+      <c r="G307" s="43"/>
+      <c r="H307" s="44"/>
       <c r="I307" s="3" t="s">
         <v>24</v>
       </c>
@@ -21822,8 +21816,8 @@
         <v>427</v>
       </c>
       <c r="F308" s="2"/>
-      <c r="G308" s="44"/>
-      <c r="H308" s="45"/>
+      <c r="G308" s="43"/>
+      <c r="H308" s="44"/>
       <c r="I308" s="3" t="s">
         <v>24</v>
       </c>
@@ -21881,8 +21875,8 @@
         <v>59</v>
       </c>
       <c r="F309" s="2"/>
-      <c r="G309" s="44"/>
-      <c r="H309" s="45"/>
+      <c r="G309" s="43"/>
+      <c r="H309" s="44"/>
       <c r="I309" s="3" t="s">
         <v>24</v>
       </c>
@@ -21942,8 +21936,8 @@
         <v>431</v>
       </c>
       <c r="F310" s="2"/>
-      <c r="G310" s="44"/>
-      <c r="H310" s="45" t="s">
+      <c r="G310" s="43"/>
+      <c r="H310" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I310" s="3" t="s">
@@ -22005,8 +21999,8 @@
         <v>431</v>
       </c>
       <c r="F311" s="2"/>
-      <c r="G311" s="44"/>
-      <c r="H311" s="45" t="s">
+      <c r="G311" s="43"/>
+      <c r="H311" s="44" t="s">
         <v>572</v>
       </c>
       <c r="I311" s="3" t="s">
@@ -22066,8 +22060,8 @@
         <v>160</v>
       </c>
       <c r="F312" s="2"/>
-      <c r="G312" s="44"/>
-      <c r="H312" s="45"/>
+      <c r="G312" s="43"/>
+      <c r="H312" s="44"/>
       <c r="I312" s="3" t="s">
         <v>24</v>
       </c>
@@ -22125,8 +22119,8 @@
         <v>29</v>
       </c>
       <c r="F313" s="2"/>
-      <c r="G313" s="44"/>
-      <c r="H313" s="45"/>
+      <c r="G313" s="43"/>
+      <c r="H313" s="44"/>
       <c r="I313" s="3" t="s">
         <v>24</v>
       </c>
@@ -22184,8 +22178,8 @@
         <v>41</v>
       </c>
       <c r="F314" s="2"/>
-      <c r="G314" s="44"/>
-      <c r="H314" s="45"/>
+      <c r="G314" s="43"/>
+      <c r="H314" s="44"/>
       <c r="I314" s="3" t="s">
         <v>24</v>
       </c>
@@ -22243,8 +22237,8 @@
         <v>56</v>
       </c>
       <c r="F315" s="2"/>
-      <c r="G315" s="44"/>
-      <c r="H315" s="45"/>
+      <c r="G315" s="43"/>
+      <c r="H315" s="44"/>
       <c r="I315" s="3" t="s">
         <v>24</v>
       </c>
@@ -22306,8 +22300,8 @@
         <v>66</v>
       </c>
       <c r="F316" s="2"/>
-      <c r="G316" s="44"/>
-      <c r="H316" s="45"/>
+      <c r="G316" s="43"/>
+      <c r="H316" s="44"/>
       <c r="I316" s="3" t="s">
         <v>24</v>
       </c>
@@ -22365,8 +22359,8 @@
         <v>147</v>
       </c>
       <c r="F317" s="2"/>
-      <c r="G317" s="44"/>
-      <c r="H317" s="45"/>
+      <c r="G317" s="43"/>
+      <c r="H317" s="44"/>
       <c r="I317" s="3" t="s">
         <v>24</v>
       </c>
@@ -22424,8 +22418,8 @@
         <v>147</v>
       </c>
       <c r="F318" s="2"/>
-      <c r="G318" s="44"/>
-      <c r="H318" s="45"/>
+      <c r="G318" s="43"/>
+      <c r="H318" s="44"/>
       <c r="I318" s="3" t="s">
         <v>24</v>
       </c>
@@ -22483,8 +22477,8 @@
         <v>147</v>
       </c>
       <c r="F319" s="2"/>
-      <c r="G319" s="44"/>
-      <c r="H319" s="45"/>
+      <c r="G319" s="43"/>
+      <c r="H319" s="44"/>
       <c r="I319" s="3" t="s">
         <v>24</v>
       </c>
@@ -22546,8 +22540,8 @@
         <v>364</v>
       </c>
       <c r="F320" s="2"/>
-      <c r="G320" s="44"/>
-      <c r="H320" s="45"/>
+      <c r="G320" s="43"/>
+      <c r="H320" s="44"/>
       <c r="I320" s="3" t="s">
         <v>24</v>
       </c>
@@ -22605,8 +22599,8 @@
         <v>72</v>
       </c>
       <c r="F321" s="2"/>
-      <c r="G321" s="44"/>
-      <c r="H321" s="45"/>
+      <c r="G321" s="43"/>
+      <c r="H321" s="44"/>
       <c r="I321" s="3" t="s">
         <v>24</v>
       </c>
@@ -22666,8 +22660,8 @@
         <v>382</v>
       </c>
       <c r="F322" s="2"/>
-      <c r="G322" s="44"/>
-      <c r="H322" s="45"/>
+      <c r="G322" s="43"/>
+      <c r="H322" s="44"/>
       <c r="I322" s="3" t="s">
         <v>24</v>
       </c>
@@ -22725,8 +22719,8 @@
         <v>29</v>
       </c>
       <c r="F323" s="2"/>
-      <c r="G323" s="44"/>
-      <c r="H323" s="45"/>
+      <c r="G323" s="43"/>
+      <c r="H323" s="44"/>
       <c r="I323" s="3" t="s">
         <v>24</v>
       </c>
@@ -22784,8 +22778,8 @@
         <v>447</v>
       </c>
       <c r="F324" s="2"/>
-      <c r="G324" s="44"/>
-      <c r="H324" s="45"/>
+      <c r="G324" s="43"/>
+      <c r="H324" s="44"/>
       <c r="I324" s="3" t="s">
         <v>24</v>
       </c>
@@ -22843,8 +22837,8 @@
         <v>287</v>
       </c>
       <c r="F325" s="2"/>
-      <c r="G325" s="44"/>
-      <c r="H325" s="45"/>
+      <c r="G325" s="43"/>
+      <c r="H325" s="44"/>
       <c r="I325" s="3" t="s">
         <v>24</v>
       </c>
@@ -22906,8 +22900,8 @@
         <v>147</v>
       </c>
       <c r="F326" s="2"/>
-      <c r="G326" s="44"/>
-      <c r="H326" s="45"/>
+      <c r="G326" s="43"/>
+      <c r="H326" s="44"/>
       <c r="I326" s="3" t="s">
         <v>24</v>
       </c>
@@ -22969,8 +22963,8 @@
         <v>278</v>
       </c>
       <c r="F327" s="2"/>
-      <c r="G327" s="44"/>
-      <c r="H327" s="45"/>
+      <c r="G327" s="43"/>
+      <c r="H327" s="44"/>
       <c r="I327" s="3" t="s">
         <v>24</v>
       </c>
@@ -23032,8 +23026,8 @@
         <v>147</v>
       </c>
       <c r="F328" s="2"/>
-      <c r="G328" s="44"/>
-      <c r="H328" s="45"/>
+      <c r="G328" s="43"/>
+      <c r="H328" s="44"/>
       <c r="I328" s="3" t="s">
         <v>24</v>
       </c>
@@ -23093,8 +23087,8 @@
         <v>554</v>
       </c>
       <c r="F329" s="2"/>
-      <c r="G329" s="44"/>
-      <c r="H329" s="45"/>
+      <c r="G329" s="43"/>
+      <c r="H329" s="44"/>
       <c r="I329" s="3" t="s">
         <v>24</v>
       </c>
@@ -23154,8 +23148,8 @@
         <v>554</v>
       </c>
       <c r="F330" s="2"/>
-      <c r="G330" s="44"/>
-      <c r="H330" s="45"/>
+      <c r="G330" s="43"/>
+      <c r="H330" s="44"/>
       <c r="I330" s="3" t="s">
         <v>24</v>
       </c>
@@ -23215,8 +23209,8 @@
         <v>554</v>
       </c>
       <c r="F331" s="2"/>
-      <c r="G331" s="44"/>
-      <c r="H331" s="45"/>
+      <c r="G331" s="43"/>
+      <c r="H331" s="44"/>
       <c r="I331" s="3" t="s">
         <v>24</v>
       </c>
@@ -23276,8 +23270,8 @@
         <v>554</v>
       </c>
       <c r="F332" s="2"/>
-      <c r="G332" s="44"/>
-      <c r="H332" s="45"/>
+      <c r="G332" s="43"/>
+      <c r="H332" s="44"/>
       <c r="I332" s="3" t="s">
         <v>24</v>
       </c>
@@ -23337,8 +23331,8 @@
         <v>554</v>
       </c>
       <c r="F333" s="2"/>
-      <c r="G333" s="44"/>
-      <c r="H333" s="45"/>
+      <c r="G333" s="43"/>
+      <c r="H333" s="44"/>
       <c r="I333" s="3" t="s">
         <v>24</v>
       </c>
@@ -23400,8 +23394,8 @@
         <v>29</v>
       </c>
       <c r="F334" s="2"/>
-      <c r="G334" s="44"/>
-      <c r="H334" s="45"/>
+      <c r="G334" s="43"/>
+      <c r="H334" s="44"/>
       <c r="I334" s="3" t="s">
         <v>24</v>
       </c>
@@ -23461,8 +23455,8 @@
       </c>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
-      <c r="G335" s="44"/>
-      <c r="H335" s="45"/>
+      <c r="G335" s="43"/>
+      <c r="H335" s="44"/>
       <c r="I335" s="3" t="s">
         <v>24</v>
       </c>
@@ -23520,8 +23514,8 @@
         <v>460</v>
       </c>
       <c r="F336" s="2"/>
-      <c r="G336" s="44"/>
-      <c r="H336" s="45"/>
+      <c r="G336" s="43"/>
+      <c r="H336" s="44"/>
       <c r="I336" s="3" t="s">
         <v>24</v>
       </c>
@@ -23583,8 +23577,8 @@
         <v>66</v>
       </c>
       <c r="F337" s="2"/>
-      <c r="G337" s="44"/>
-      <c r="H337" s="45"/>
+      <c r="G337" s="43"/>
+      <c r="H337" s="44"/>
       <c r="I337" s="3" t="s">
         <v>24</v>
       </c>
@@ -23644,8 +23638,8 @@
         <v>289</v>
       </c>
       <c r="F338" s="2"/>
-      <c r="G338" s="44"/>
-      <c r="H338" s="45"/>
+      <c r="G338" s="43"/>
+      <c r="H338" s="44"/>
       <c r="I338" s="3" t="s">
         <v>24</v>
       </c>
@@ -23707,8 +23701,8 @@
         <v>29</v>
       </c>
       <c r="F339" s="2"/>
-      <c r="G339" s="44"/>
-      <c r="H339" s="45"/>
+      <c r="G339" s="43"/>
+      <c r="H339" s="44"/>
       <c r="I339" s="3" t="s">
         <v>24</v>
       </c>
@@ -23770,8 +23764,8 @@
         <v>465</v>
       </c>
       <c r="F340" s="2"/>
-      <c r="G340" s="44"/>
-      <c r="H340" s="45"/>
+      <c r="G340" s="43"/>
+      <c r="H340" s="44"/>
       <c r="I340" s="3" t="s">
         <v>24</v>
       </c>
@@ -23833,8 +23827,8 @@
         <v>467</v>
       </c>
       <c r="F341" s="2"/>
-      <c r="G341" s="44"/>
-      <c r="H341" s="45"/>
+      <c r="G341" s="43"/>
+      <c r="H341" s="44"/>
       <c r="I341" s="3" t="s">
         <v>24</v>
       </c>
@@ -23896,8 +23890,8 @@
         <v>554</v>
       </c>
       <c r="F342" s="2"/>
-      <c r="G342" s="44"/>
-      <c r="H342" s="45"/>
+      <c r="G342" s="43"/>
+      <c r="H342" s="44"/>
       <c r="I342" s="3" t="s">
         <v>24</v>
       </c>
@@ -23953,8 +23947,8 @@
       <c r="D343" s="8"/>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
-      <c r="G343" s="44"/>
-      <c r="H343" s="45"/>
+      <c r="G343" s="43"/>
+      <c r="H343" s="44"/>
       <c r="I343" s="3" t="s">
         <v>24</v>
       </c>
@@ -24012,8 +24006,8 @@
         <v>72</v>
       </c>
       <c r="F344" s="2"/>
-      <c r="G344" s="44"/>
-      <c r="H344" s="45"/>
+      <c r="G344" s="43"/>
+      <c r="H344" s="44"/>
       <c r="I344" s="3" t="s">
         <v>24</v>
       </c>
@@ -24075,8 +24069,8 @@
         <v>278</v>
       </c>
       <c r="F345" s="2"/>
-      <c r="G345" s="44"/>
-      <c r="H345" s="45"/>
+      <c r="G345" s="43"/>
+      <c r="H345" s="44"/>
       <c r="I345" s="3" t="s">
         <v>24</v>
       </c>
@@ -24138,8 +24132,8 @@
         <v>473</v>
       </c>
       <c r="F346" s="2"/>
-      <c r="G346" s="44"/>
-      <c r="H346" s="45"/>
+      <c r="G346" s="43"/>
+      <c r="H346" s="44"/>
       <c r="I346" s="3" t="s">
         <v>24</v>
       </c>
@@ -24199,8 +24193,8 @@
         <v>382</v>
       </c>
       <c r="F347" s="2"/>
-      <c r="G347" s="44"/>
-      <c r="H347" s="45"/>
+      <c r="G347" s="43"/>
+      <c r="H347" s="44"/>
       <c r="I347" s="3" t="s">
         <v>24</v>
       </c>
@@ -24262,8 +24256,8 @@
         <v>301</v>
       </c>
       <c r="F348" s="2"/>
-      <c r="G348" s="44"/>
-      <c r="H348" s="45"/>
+      <c r="G348" s="43"/>
+      <c r="H348" s="44"/>
       <c r="I348" s="3" t="s">
         <v>24</v>
       </c>
@@ -24321,8 +24315,8 @@
         <v>395</v>
       </c>
       <c r="F349" s="2"/>
-      <c r="G349" s="44"/>
-      <c r="H349" s="45"/>
+      <c r="G349" s="43"/>
+      <c r="H349" s="44"/>
       <c r="I349" s="3" t="s">
         <v>24</v>
       </c>
@@ -24380,8 +24374,8 @@
         <v>556</v>
       </c>
       <c r="F350" s="2"/>
-      <c r="G350" s="44"/>
-      <c r="H350" s="45"/>
+      <c r="G350" s="43"/>
+      <c r="H350" s="44"/>
       <c r="I350" s="3" t="s">
         <v>24</v>
       </c>
@@ -24441,8 +24435,8 @@
         <v>382</v>
       </c>
       <c r="F351" s="2"/>
-      <c r="G351" s="44"/>
-      <c r="H351" s="45"/>
+      <c r="G351" s="43"/>
+      <c r="H351" s="44"/>
       <c r="I351" s="3" t="s">
         <v>24</v>
       </c>
@@ -24500,8 +24494,8 @@
         <v>41</v>
       </c>
       <c r="F352" s="2"/>
-      <c r="G352" s="44"/>
-      <c r="H352" s="45"/>
+      <c r="G352" s="43"/>
+      <c r="H352" s="44"/>
       <c r="I352" s="3" t="s">
         <v>24</v>
       </c>
@@ -24559,8 +24553,8 @@
         <v>566</v>
       </c>
       <c r="F353" s="2"/>
-      <c r="G353" s="44"/>
-      <c r="H353" s="45"/>
+      <c r="G353" s="43"/>
+      <c r="H353" s="44"/>
       <c r="I353" s="3" t="s">
         <v>24</v>
       </c>
@@ -24616,8 +24610,8 @@
       <c r="D354" s="8"/>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
-      <c r="G354" s="44"/>
-      <c r="H354" s="45"/>
+      <c r="G354" s="43"/>
+      <c r="H354" s="44"/>
       <c r="I354" s="3" t="s">
         <v>24</v>
       </c>
@@ -24673,8 +24667,8 @@
       <c r="D355" s="8"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
-      <c r="G355" s="44"/>
-      <c r="H355" s="45"/>
+      <c r="G355" s="43"/>
+      <c r="H355" s="44"/>
       <c r="I355" s="3" t="s">
         <v>24</v>
       </c>
@@ -24728,8 +24722,8 @@
       <c r="D356" s="8"/>
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
-      <c r="G356" s="44"/>
-      <c r="H356" s="45"/>
+      <c r="G356" s="43"/>
+      <c r="H356" s="44"/>
       <c r="I356" s="3" t="s">
         <v>24</v>
       </c>
@@ -24783,8 +24777,8 @@
       <c r="D357" s="8"/>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
-      <c r="G357" s="44"/>
-      <c r="H357" s="45"/>
+      <c r="G357" s="43"/>
+      <c r="H357" s="44"/>
       <c r="I357" s="3" t="s">
         <v>24</v>
       </c>
@@ -24838,8 +24832,8 @@
       <c r="D358" s="8"/>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
-      <c r="G358" s="44"/>
-      <c r="H358" s="45"/>
+      <c r="G358" s="43"/>
+      <c r="H358" s="44"/>
       <c r="I358" s="3" t="s">
         <v>24</v>
       </c>
@@ -24893,8 +24887,8 @@
       <c r="D359" s="8"/>
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
-      <c r="G359" s="44"/>
-      <c r="H359" s="45"/>
+      <c r="G359" s="43"/>
+      <c r="H359" s="44"/>
       <c r="I359" s="3" t="s">
         <v>24</v>
       </c>
@@ -24948,8 +24942,8 @@
       <c r="D360" s="8"/>
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
-      <c r="G360" s="44"/>
-      <c r="H360" s="45"/>
+      <c r="G360" s="43"/>
+      <c r="H360" s="44"/>
       <c r="I360" s="3" t="s">
         <v>24</v>
       </c>
@@ -25003,8 +24997,8 @@
       <c r="D361" s="8"/>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
-      <c r="G361" s="44"/>
-      <c r="H361" s="45"/>
+      <c r="G361" s="43"/>
+      <c r="H361" s="44"/>
       <c r="I361" s="3" t="s">
         <v>24</v>
       </c>
@@ -25058,8 +25052,8 @@
       <c r="D362" s="8"/>
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
-      <c r="G362" s="44"/>
-      <c r="H362" s="45"/>
+      <c r="G362" s="43"/>
+      <c r="H362" s="44"/>
       <c r="I362" s="3" t="s">
         <v>24</v>
       </c>
@@ -25113,8 +25107,8 @@
       <c r="D363" s="8"/>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
-      <c r="G363" s="44"/>
-      <c r="H363" s="45"/>
+      <c r="G363" s="43"/>
+      <c r="H363" s="44"/>
       <c r="I363" s="3" t="s">
         <v>24</v>
       </c>
@@ -25168,8 +25162,8 @@
       <c r="D364" s="8"/>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
-      <c r="G364" s="44"/>
-      <c r="H364" s="45"/>
+      <c r="G364" s="43"/>
+      <c r="H364" s="44"/>
       <c r="I364" s="3" t="s">
         <v>24</v>
       </c>
@@ -25223,8 +25217,8 @@
       <c r="D365" s="8"/>
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
-      <c r="G365" s="44"/>
-      <c r="H365" s="45"/>
+      <c r="G365" s="43"/>
+      <c r="H365" s="44"/>
       <c r="I365" s="3" t="s">
         <v>24</v>
       </c>
@@ -25278,8 +25272,8 @@
       <c r="D366" s="8"/>
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
-      <c r="G366" s="44"/>
-      <c r="H366" s="45"/>
+      <c r="G366" s="43"/>
+      <c r="H366" s="44"/>
       <c r="I366" s="3" t="s">
         <v>24</v>
       </c>
@@ -25333,8 +25327,8 @@
       <c r="D367" s="8"/>
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
-      <c r="G367" s="44"/>
-      <c r="H367" s="45"/>
+      <c r="G367" s="43"/>
+      <c r="H367" s="44"/>
       <c r="I367" s="3" t="s">
         <v>24</v>
       </c>
@@ -25388,8 +25382,8 @@
       <c r="D368" s="8"/>
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
-      <c r="G368" s="44"/>
-      <c r="H368" s="45"/>
+      <c r="G368" s="43"/>
+      <c r="H368" s="44"/>
       <c r="I368" s="3" t="s">
         <v>24</v>
       </c>
@@ -25443,8 +25437,8 @@
       <c r="D369" s="8"/>
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
-      <c r="G369" s="44"/>
-      <c r="H369" s="45"/>
+      <c r="G369" s="43"/>
+      <c r="H369" s="44"/>
       <c r="I369" s="3" t="s">
         <v>24</v>
       </c>
@@ -25498,8 +25492,8 @@
       <c r="D370" s="8"/>
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
-      <c r="G370" s="44"/>
-      <c r="H370" s="45"/>
+      <c r="G370" s="43"/>
+      <c r="H370" s="44"/>
       <c r="I370" s="3" t="s">
         <v>24</v>
       </c>
@@ -25544,27 +25538,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:25" s="48" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B371" s="49"/>
-      <c r="C371" s="49"/>
-      <c r="D371" s="49"/>
-      <c r="E371" s="49"/>
-      <c r="F371" s="49"/>
-      <c r="G371" s="50"/>
-      <c r="H371" s="51"/>
-      <c r="I371" s="52"/>
-      <c r="J371" s="53"/>
-      <c r="K371" s="53"/>
-      <c r="L371" s="53"/>
-      <c r="M371" s="53"/>
-      <c r="N371" s="53"/>
-      <c r="O371" s="53"/>
-      <c r="P371" s="53"/>
-      <c r="Q371" s="53"/>
-      <c r="R371" s="53"/>
-      <c r="S371" s="53"/>
-      <c r="T371" s="53"/>
-      <c r="U371" s="53"/>
+    <row r="371" spans="1:25" s="47" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B371" s="48"/>
+      <c r="C371" s="48"/>
+      <c r="D371" s="48"/>
+      <c r="E371" s="48"/>
+      <c r="F371" s="48"/>
+      <c r="G371" s="49"/>
+      <c r="H371" s="50"/>
+      <c r="I371" s="51"/>
+      <c r="J371" s="52"/>
+      <c r="K371" s="52"/>
+      <c r="L371" s="52"/>
+      <c r="M371" s="52"/>
+      <c r="N371" s="52"/>
+      <c r="O371" s="52"/>
+      <c r="P371" s="52"/>
+      <c r="Q371" s="52"/>
+      <c r="R371" s="52"/>
+      <c r="S371" s="52"/>
+      <c r="T371" s="52"/>
+      <c r="U371" s="52"/>
     </row>
     <row r="372" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A372" s="13"/>
@@ -25629,10 +25623,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="I1" s="43"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="I3" s="43"/>
+      <c r="I3" s="42"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -25719,10 +25713,10 @@
       <c r="E5" s="8"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="54" t="s">
-        <v>24</v>
+      <c r="H5" s="43"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -25753,8 +25747,8 @@
       <c r="E6" s="8"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="45"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="44"/>
       <c r="J6" s="19" t="s">
         <v>37</v>
       </c>
@@ -25789,10 +25783,10 @@
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
-      <c r="H7" s="55">
+      <c r="H7" s="53">
         <v>-12000000</v>
       </c>
-      <c r="I7" s="56"/>
+      <c r="I7" s="54"/>
       <c r="J7" s="19" t="s">
         <v>37</v>
       </c>
@@ -25825,10 +25819,10 @@
       <c r="E8" s="20"/>
       <c r="F8" s="20"/>
       <c r="G8" s="20"/>
-      <c r="H8" s="55">
+      <c r="H8" s="53">
         <v>-5231807</v>
       </c>
-      <c r="I8" s="56" t="s">
+      <c r="I8" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J8" s="19" t="s">
@@ -25863,10 +25857,10 @@
       <c r="E9" s="20"/>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
-      <c r="H9" s="55">
+      <c r="H9" s="53">
         <v>-3500000</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="54" t="s">
         <v>580</v>
       </c>
       <c r="J9" s="19" t="s">
@@ -25901,10 +25895,10 @@
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
-      <c r="H10" s="55">
-        <v>0</v>
-      </c>
-      <c r="I10" s="56" t="s">
+      <c r="H10" s="53">
+        <v>0</v>
+      </c>
+      <c r="I10" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J10" s="19" t="s">
@@ -25939,10 +25933,10 @@
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="55">
+      <c r="H11" s="53">
         <v>-20000000</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="I11" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J11" s="19" t="s">
@@ -25977,8 +25971,8 @@
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="56"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="54"/>
       <c r="J12" s="19" t="s">
         <v>37</v>
       </c>
@@ -26011,10 +26005,10 @@
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
-      <c r="H13" s="55">
-        <v>0</v>
-      </c>
-      <c r="I13" s="56" t="s">
+      <c r="H13" s="53">
+        <v>0</v>
+      </c>
+      <c r="I13" s="54" t="s">
         <v>581</v>
       </c>
       <c r="J13" s="19" t="s">
@@ -26049,10 +26043,10 @@
       <c r="E14" s="20"/>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="55">
-        <v>0</v>
-      </c>
-      <c r="I14" s="56"/>
+      <c r="H14" s="53">
+        <v>0</v>
+      </c>
+      <c r="I14" s="54"/>
       <c r="J14" s="19" t="s">
         <v>37</v>
       </c>
@@ -26085,10 +26079,10 @@
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
-      <c r="H15" s="55">
+      <c r="H15" s="53">
         <v>-6700000</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J15" s="19" t="s">
@@ -26123,8 +26117,8 @@
       <c r="E16" s="20"/>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="56"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="54"/>
       <c r="J16" s="19" t="s">
         <v>37</v>
       </c>
@@ -26157,10 +26151,10 @@
       <c r="E17" s="20"/>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
-      <c r="H17" s="55">
+      <c r="H17" s="53">
         <v>-12300000</v>
       </c>
-      <c r="I17" s="56"/>
+      <c r="I17" s="54"/>
       <c r="J17" s="19" t="s">
         <v>37</v>
       </c>
@@ -26193,8 +26187,8 @@
       <c r="E18" s="20"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="54"/>
       <c r="J18" s="19" t="s">
         <v>37</v>
       </c>
@@ -26227,10 +26221,10 @@
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
       <c r="G19" s="20"/>
-      <c r="H19" s="55">
+      <c r="H19" s="53">
         <v>-400000</v>
       </c>
-      <c r="I19" s="56" t="s">
+      <c r="I19" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J19" s="19" t="s">
@@ -26265,10 +26259,10 @@
       <c r="E20" s="20"/>
       <c r="F20" s="20"/>
       <c r="G20" s="20"/>
-      <c r="H20" s="55">
-        <v>0</v>
-      </c>
-      <c r="I20" s="56" t="s">
+      <c r="H20" s="53">
+        <v>0</v>
+      </c>
+      <c r="I20" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J20" s="19" t="s">
@@ -26303,8 +26297,8 @@
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
       <c r="G21" s="20"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="56" t="s">
+      <c r="H21" s="53"/>
+      <c r="I21" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J21" s="19" t="s">
@@ -26339,10 +26333,10 @@
       <c r="E22" s="20"/>
       <c r="F22" s="20"/>
       <c r="G22" s="20"/>
-      <c r="H22" s="55">
+      <c r="H22" s="53">
         <v>-6413915</v>
       </c>
-      <c r="I22" s="56"/>
+      <c r="I22" s="54"/>
       <c r="J22" s="19" t="s">
         <v>37</v>
       </c>
@@ -26375,10 +26369,10 @@
       <c r="E23" s="20"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="55">
-        <v>0</v>
-      </c>
-      <c r="I23" s="56" t="s">
+      <c r="H23" s="53">
+        <v>0</v>
+      </c>
+      <c r="I23" s="54" t="s">
         <v>573</v>
       </c>
       <c r="J23" s="19" t="s">
@@ -26413,8 +26407,8 @@
       <c r="E24" s="20"/>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="56" t="s">
+      <c r="H24" s="53"/>
+      <c r="I24" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J24" s="19" t="s">
@@ -26449,10 +26443,10 @@
       <c r="E25" s="20"/>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
-      <c r="H25" s="55">
-        <v>0</v>
-      </c>
-      <c r="I25" s="56" t="s">
+      <c r="H25" s="53">
+        <v>0</v>
+      </c>
+      <c r="I25" s="54" t="s">
         <v>572</v>
       </c>
       <c r="J25" s="19" t="s">
@@ -26487,8 +26481,8 @@
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="56"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="54"/>
       <c r="J26" s="19" t="s">
         <v>37</v>
       </c>
@@ -26521,8 +26515,8 @@
       <c r="E27" s="20"/>
       <c r="F27" s="20"/>
       <c r="G27" s="20"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="56"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="54"/>
       <c r="J27" s="19" t="s">
         <v>37</v>
       </c>
@@ -26555,8 +26549,8 @@
       <c r="E28" s="20"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="56"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="54"/>
       <c r="J28" s="19" t="s">
         <v>37</v>
       </c>
@@ -26589,8 +26583,8 @@
       <c r="E29" s="20"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="56"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="54"/>
       <c r="J29" s="19" t="s">
         <v>37</v>
       </c>
@@ -26623,8 +26617,8 @@
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="56"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="54"/>
       <c r="J30" s="19" t="s">
         <v>37</v>
       </c>
@@ -26657,8 +26651,8 @@
       <c r="E31" s="20"/>
       <c r="F31" s="20"/>
       <c r="G31" s="20"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="56"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="54"/>
       <c r="J31" s="19" t="s">
         <v>37</v>
       </c>
@@ -26691,8 +26685,8 @@
       <c r="E32" s="20"/>
       <c r="F32" s="20"/>
       <c r="G32" s="20"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="56"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="54"/>
       <c r="J32" s="19" t="s">
         <v>37</v>
       </c>
@@ -26725,8 +26719,8 @@
       <c r="E33" s="20"/>
       <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="56"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="54"/>
       <c r="J33" s="19" t="s">
         <v>37</v>
       </c>
@@ -26759,8 +26753,8 @@
       <c r="E34" s="20"/>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
-      <c r="H34" s="55"/>
-      <c r="I34" s="56"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="54"/>
       <c r="J34" s="19" t="s">
         <v>37</v>
       </c>
@@ -26793,8 +26787,8 @@
       <c r="E35" s="20"/>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
-      <c r="H35" s="55"/>
-      <c r="I35" s="56"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="54"/>
       <c r="J35" s="19" t="s">
         <v>37</v>
       </c>
@@ -26827,8 +26821,8 @@
       <c r="E36" s="20"/>
       <c r="F36" s="20"/>
       <c r="G36" s="20"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="56"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="54"/>
       <c r="J36" s="19" t="s">
         <v>37</v>
       </c>
@@ -26861,8 +26855,8 @@
       <c r="E37" s="20"/>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="56"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="54"/>
       <c r="J37" s="19" t="s">
         <v>37</v>
       </c>
@@ -26895,8 +26889,8 @@
       <c r="E38" s="20"/>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="56"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="54"/>
       <c r="J38" s="19" t="s">
         <v>37</v>
       </c>
@@ -26929,8 +26923,8 @@
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="56"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="54"/>
       <c r="J39" s="19" t="s">
         <v>37</v>
       </c>
@@ -26963,8 +26957,8 @@
       <c r="E40" s="20"/>
       <c r="F40" s="20"/>
       <c r="G40" s="20"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="56"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="54"/>
       <c r="J40" s="19" t="s">
         <v>37</v>
       </c>
@@ -26997,8 +26991,8 @@
       <c r="E41" s="20"/>
       <c r="F41" s="20"/>
       <c r="G41" s="20"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="56"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="54"/>
       <c r="J41" s="19" t="s">
         <v>37</v>
       </c>
@@ -27031,8 +27025,8 @@
       <c r="E42" s="20"/>
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="56"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="54"/>
       <c r="J42" s="19" t="s">
         <v>37</v>
       </c>
@@ -27065,8 +27059,8 @@
       <c r="E43" s="20"/>
       <c r="F43" s="20"/>
       <c r="G43" s="20"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="56"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="54"/>
       <c r="J43" s="19" t="s">
         <v>37</v>
       </c>
@@ -27099,8 +27093,8 @@
       <c r="E44" s="20"/>
       <c r="F44" s="20"/>
       <c r="G44" s="20"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="56"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="54"/>
       <c r="J44" s="19" t="s">
         <v>37</v>
       </c>
@@ -27133,8 +27127,8 @@
       <c r="E45" s="20"/>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="56"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="54"/>
       <c r="J45" s="19" t="s">
         <v>37</v>
       </c>
@@ -27167,8 +27161,8 @@
       <c r="E46" s="20"/>
       <c r="F46" s="20"/>
       <c r="G46" s="20"/>
-      <c r="H46" s="55"/>
-      <c r="I46" s="56"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="54"/>
       <c r="J46" s="19" t="s">
         <v>37</v>
       </c>
@@ -27201,8 +27195,8 @@
       <c r="E47" s="20"/>
       <c r="F47" s="20"/>
       <c r="G47" s="20"/>
-      <c r="H47" s="55"/>
-      <c r="I47" s="56"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="54"/>
       <c r="J47" s="19" t="s">
         <v>37</v>
       </c>
@@ -27235,8 +27229,8 @@
       <c r="E48" s="20"/>
       <c r="F48" s="20"/>
       <c r="G48" s="20"/>
-      <c r="H48" s="55"/>
-      <c r="I48" s="56"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="54"/>
       <c r="J48" s="19" t="s">
         <v>37</v>
       </c>
@@ -27269,8 +27263,8 @@
       <c r="E49" s="20"/>
       <c r="F49" s="20"/>
       <c r="G49" s="20"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="56"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="54"/>
       <c r="J49" s="19" t="s">
         <v>37</v>
       </c>
@@ -27303,8 +27297,8 @@
       <c r="E50" s="20"/>
       <c r="F50" s="20"/>
       <c r="G50" s="20"/>
-      <c r="H50" s="55"/>
-      <c r="I50" s="56"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="54"/>
       <c r="J50" s="19" t="s">
         <v>37</v>
       </c>
@@ -27337,8 +27331,8 @@
       <c r="E51" s="21"/>
       <c r="F51" s="22"/>
       <c r="G51" s="22"/>
-      <c r="H51" s="57"/>
-      <c r="I51" s="58"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="56"/>
       <c r="J51" s="19" t="s">
         <v>37</v>
       </c>
@@ -27371,8 +27365,8 @@
       <c r="E52" s="21"/>
       <c r="F52" s="22"/>
       <c r="G52" s="22"/>
-      <c r="H52" s="57"/>
-      <c r="I52" s="58"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="56"/>
       <c r="J52" s="19" t="s">
         <v>37</v>
       </c>
@@ -27405,8 +27399,8 @@
       <c r="E53" s="21"/>
       <c r="F53" s="22"/>
       <c r="G53" s="22"/>
-      <c r="H53" s="57"/>
-      <c r="I53" s="58"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="56"/>
       <c r="J53" s="19" t="s">
         <v>37</v>
       </c>
@@ -27439,8 +27433,8 @@
       <c r="E54" s="21"/>
       <c r="F54" s="22"/>
       <c r="G54" s="22"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="58"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="56"/>
       <c r="J54" s="19" t="s">
         <v>37</v>
       </c>
@@ -27472,8 +27466,8 @@
       <c r="E55" s="21"/>
       <c r="F55" s="22"/>
       <c r="G55" s="22"/>
-      <c r="H55" s="57"/>
-      <c r="I55" s="58"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="56"/>
       <c r="J55" s="19" t="s">
         <v>37</v>
       </c>
@@ -27505,8 +27499,8 @@
       <c r="E56" s="21"/>
       <c r="F56" s="22"/>
       <c r="G56" s="22"/>
-      <c r="H56" s="57"/>
-      <c r="I56" s="58"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="56"/>
       <c r="J56" s="19" t="s">
         <v>37</v>
       </c>
@@ -27538,8 +27532,8 @@
       <c r="E57" s="21"/>
       <c r="F57" s="22"/>
       <c r="G57" s="22"/>
-      <c r="H57" s="57"/>
-      <c r="I57" s="58"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="56"/>
       <c r="J57" s="19" t="s">
         <v>37</v>
       </c>
@@ -27571,8 +27565,8 @@
       <c r="E58" s="21"/>
       <c r="F58" s="22"/>
       <c r="G58" s="22"/>
-      <c r="H58" s="57"/>
-      <c r="I58" s="58"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="56"/>
       <c r="J58" s="19" t="s">
         <v>37</v>
       </c>
@@ -27606,8 +27600,8 @@
       <c r="E59" s="21"/>
       <c r="F59" s="22"/>
       <c r="G59" s="22"/>
-      <c r="H59" s="57"/>
-      <c r="I59" s="58"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="56"/>
       <c r="J59" s="19" t="s">
         <v>37</v>
       </c>
@@ -27639,9 +27633,9 @@
       <c r="E60" s="24"/>
       <c r="F60" s="24"/>
       <c r="G60" s="24"/>
-      <c r="H60" s="59"/>
-      <c r="I60" s="60"/>
-      <c r="J60" s="61" t="s">
+      <c r="H60" s="57"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K60" s="25"/>
@@ -27672,9 +27666,9 @@
       <c r="E61" s="30"/>
       <c r="F61" s="24"/>
       <c r="G61" s="24"/>
-      <c r="H61" s="59"/>
-      <c r="I61" s="60"/>
-      <c r="J61" s="61" t="s">
+      <c r="H61" s="57"/>
+      <c r="I61" s="58"/>
+      <c r="J61" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K61" s="25"/>
@@ -27705,9 +27699,9 @@
       <c r="E62" s="30"/>
       <c r="F62" s="24"/>
       <c r="G62" s="24"/>
-      <c r="H62" s="59"/>
-      <c r="I62" s="60"/>
-      <c r="J62" s="61" t="s">
+      <c r="H62" s="57"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K62" s="11"/>
@@ -27738,9 +27732,9 @@
       <c r="E63" s="30"/>
       <c r="F63" s="24"/>
       <c r="G63" s="24"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="60"/>
-      <c r="J63" s="61" t="s">
+      <c r="H63" s="57"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K63" s="11">
@@ -27773,9 +27767,9 @@
       <c r="E64" s="30"/>
       <c r="F64" s="24"/>
       <c r="G64" s="24"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="60"/>
-      <c r="J64" s="61" t="s">
+      <c r="H64" s="57"/>
+      <c r="I64" s="58"/>
+      <c r="J64" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K64" s="11">
@@ -27808,9 +27802,9 @@
       <c r="E65" s="30"/>
       <c r="F65" s="24"/>
       <c r="G65" s="24"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="60"/>
-      <c r="J65" s="61" t="s">
+      <c r="H65" s="57"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K65" s="11">
@@ -27843,9 +27837,11 @@
       <c r="E66" s="30"/>
       <c r="F66" s="24"/>
       <c r="G66" s="24"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="60"/>
-      <c r="J66" s="61"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="58"/>
+      <c r="J66" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K66" s="11"/>
       <c r="L66" s="11">
         <v>-4568732</v>
@@ -27876,9 +27872,11 @@
       <c r="E67" s="30"/>
       <c r="F67" s="24"/>
       <c r="G67" s="24"/>
-      <c r="H67" s="59"/>
-      <c r="I67" s="60"/>
-      <c r="J67" s="61"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="58"/>
+      <c r="J67" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K67" s="11"/>
       <c r="L67" s="11">
         <v>-6176000</v>
@@ -27909,9 +27907,11 @@
       <c r="E68" s="30"/>
       <c r="F68" s="24"/>
       <c r="G68" s="24"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="60"/>
-      <c r="J68" s="61"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="58"/>
+      <c r="J68" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K68" s="11"/>
       <c r="L68" s="11">
         <v>-60897000</v>
@@ -27942,9 +27942,11 @@
       <c r="E69" s="30"/>
       <c r="F69" s="24"/>
       <c r="G69" s="24"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="61"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="58"/>
+      <c r="J69" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K69" s="11"/>
       <c r="L69" s="11">
         <v>-19035649</v>
@@ -27975,9 +27977,11 @@
       <c r="E70" s="30"/>
       <c r="F70" s="24"/>
       <c r="G70" s="24"/>
-      <c r="H70" s="59"/>
-      <c r="I70" s="60"/>
-      <c r="J70" s="61"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K70" s="11"/>
       <c r="L70" s="11" t="s">
         <v>543</v>
@@ -28008,9 +28012,11 @@
       <c r="E71" s="30"/>
       <c r="F71" s="24"/>
       <c r="G71" s="24"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="61"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="58"/>
+      <c r="J71" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K71" s="11"/>
       <c r="L71" s="11">
         <v>0</v>
@@ -28043,9 +28049,11 @@
       <c r="E72" s="30"/>
       <c r="F72" s="24"/>
       <c r="G72" s="24"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="60"/>
-      <c r="J72" s="61"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="58"/>
+      <c r="J72" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K72" s="11"/>
       <c r="L72" s="11"/>
       <c r="M72" s="11">
@@ -28076,9 +28084,11 @@
       <c r="E73" s="21"/>
       <c r="F73" s="22"/>
       <c r="G73" s="22"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="58"/>
-      <c r="J73" s="19"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K73" s="11"/>
       <c r="L73" s="11"/>
       <c r="M73" s="11">
@@ -28109,9 +28119,11 @@
       <c r="E74" s="21"/>
       <c r="F74" s="22"/>
       <c r="G74" s="22"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="58"/>
-      <c r="J74" s="19"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K74" s="11"/>
       <c r="L74" s="11"/>
       <c r="M74" s="11">
@@ -28142,9 +28154,11 @@
       <c r="E75" s="21"/>
       <c r="F75" s="22"/>
       <c r="G75" s="22"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="58"/>
-      <c r="J75" s="19"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K75" s="11"/>
       <c r="L75" s="11"/>
       <c r="M75" s="11">
@@ -28175,9 +28189,11 @@
       <c r="E76" s="21"/>
       <c r="F76" s="22"/>
       <c r="G76" s="22"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="58"/>
-      <c r="J76" s="62"/>
+      <c r="H76" s="55"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K76" s="11"/>
       <c r="L76" s="31"/>
       <c r="M76" s="11">
@@ -28210,7 +28226,7 @@
       <c r="G77" s="23"/>
       <c r="H77" s="23"/>
       <c r="I77" s="23"/>
-      <c r="J77" s="23" t="s">
+      <c r="J77" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K77" s="11"/>
@@ -28245,7 +28261,7 @@
       <c r="G78" s="23"/>
       <c r="H78" s="23"/>
       <c r="I78" s="23"/>
-      <c r="J78" s="23" t="s">
+      <c r="J78" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K78" s="11"/>
@@ -28280,7 +28296,7 @@
       <c r="G79" s="23"/>
       <c r="H79" s="23"/>
       <c r="I79" s="23"/>
-      <c r="J79" s="23" t="s">
+      <c r="J79" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K79" s="11"/>
@@ -28315,7 +28331,7 @@
       <c r="G80" s="23"/>
       <c r="H80" s="23"/>
       <c r="I80" s="23"/>
-      <c r="J80" s="23" t="s">
+      <c r="J80" s="59" t="s">
         <v>37</v>
       </c>
       <c r="K80" s="11"/>
@@ -28350,7 +28366,9 @@
       <c r="G81" s="23"/>
       <c r="H81" s="23"/>
       <c r="I81" s="23"/>
-      <c r="J81" s="23"/>
+      <c r="J81" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K81" s="11"/>
       <c r="L81" s="11"/>
       <c r="M81" s="11"/>
@@ -28383,7 +28401,9 @@
       <c r="G82" s="23"/>
       <c r="H82" s="23"/>
       <c r="I82" s="23"/>
-      <c r="J82" s="23"/>
+      <c r="J82" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K82" s="11"/>
       <c r="L82" s="11"/>
       <c r="M82" s="11"/>
@@ -28416,7 +28436,9 @@
       <c r="G83" s="23"/>
       <c r="H83" s="23"/>
       <c r="I83" s="23"/>
-      <c r="J83" s="23"/>
+      <c r="J83" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K83" s="11"/>
       <c r="L83" s="11"/>
       <c r="M83" s="11"/>
@@ -28449,7 +28471,9 @@
       <c r="G84" s="23"/>
       <c r="H84" s="23"/>
       <c r="I84" s="23"/>
-      <c r="J84" s="23"/>
+      <c r="J84" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K84" s="11"/>
       <c r="L84" s="11"/>
       <c r="M84" s="11"/>
@@ -28482,7 +28506,9 @@
       <c r="G85" s="23"/>
       <c r="H85" s="23"/>
       <c r="I85" s="23"/>
-      <c r="J85" s="23"/>
+      <c r="J85" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K85" s="11"/>
       <c r="L85" s="11"/>
       <c r="M85" s="11"/>
@@ -28515,7 +28541,9 @@
       <c r="G86" s="23"/>
       <c r="H86" s="23"/>
       <c r="I86" s="23"/>
-      <c r="J86" s="23"/>
+      <c r="J86" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
       <c r="M86" s="11"/>
@@ -28548,7 +28576,9 @@
       <c r="G87" s="23"/>
       <c r="H87" s="23"/>
       <c r="I87" s="23"/>
-      <c r="J87" s="23"/>
+      <c r="J87" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K87" s="11"/>
       <c r="L87" s="11"/>
       <c r="M87" s="11"/>
@@ -28581,7 +28611,9 @@
       <c r="G88" s="23"/>
       <c r="H88" s="23"/>
       <c r="I88" s="23"/>
-      <c r="J88" s="23"/>
+      <c r="J88" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K88" s="11"/>
       <c r="L88" s="11"/>
       <c r="M88" s="11"/>
@@ -28614,7 +28646,9 @@
       <c r="G89" s="23"/>
       <c r="H89" s="23"/>
       <c r="I89" s="23"/>
-      <c r="J89" s="23"/>
+      <c r="J89" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K89" s="11"/>
       <c r="L89" s="11"/>
       <c r="M89" s="11"/>
@@ -28647,7 +28681,9 @@
       <c r="G90" s="23"/>
       <c r="H90" s="23"/>
       <c r="I90" s="23"/>
-      <c r="J90" s="23"/>
+      <c r="J90" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
       <c r="M90" s="11"/>
@@ -28680,7 +28716,9 @@
       <c r="G91" s="23"/>
       <c r="H91" s="23"/>
       <c r="I91" s="23"/>
-      <c r="J91" s="23"/>
+      <c r="J91" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K91" s="11"/>
       <c r="L91" s="11"/>
       <c r="M91" s="11"/>
@@ -28713,7 +28751,9 @@
       <c r="G92" s="23"/>
       <c r="H92" s="23"/>
       <c r="I92" s="23"/>
-      <c r="J92" s="23"/>
+      <c r="J92" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K92" s="11"/>
       <c r="L92" s="11"/>
       <c r="M92" s="11"/>
@@ -28858,27 +28898,27 @@
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" s="13"/>
-      <c r="C98" s="49"/>
-      <c r="D98" s="49"/>
-      <c r="E98" s="49"/>
-      <c r="F98" s="49"/>
-      <c r="G98" s="49"/>
-      <c r="H98" s="50"/>
-      <c r="I98" s="51"/>
-      <c r="J98" s="52"/>
-      <c r="K98" s="53"/>
-      <c r="L98" s="53"/>
-      <c r="M98" s="53"/>
-      <c r="N98" s="53"/>
-      <c r="O98" s="53"/>
-      <c r="P98" s="53"/>
-      <c r="Q98" s="63"/>
-      <c r="R98" s="63"/>
-      <c r="S98" s="63"/>
-      <c r="T98" s="53"/>
-      <c r="U98" s="53"/>
-      <c r="V98" s="53"/>
-      <c r="W98" s="53"/>
+      <c r="C98" s="48"/>
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="49"/>
+      <c r="I98" s="50"/>
+      <c r="J98" s="51"/>
+      <c r="K98" s="52"/>
+      <c r="L98" s="52"/>
+      <c r="M98" s="52"/>
+      <c r="N98" s="52"/>
+      <c r="O98" s="52"/>
+      <c r="P98" s="52"/>
+      <c r="Q98" s="60"/>
+      <c r="R98" s="60"/>
+      <c r="S98" s="60"/>
+      <c r="T98" s="52"/>
+      <c r="U98" s="52"/>
+      <c r="V98" s="52"/>
+      <c r="W98" s="52"/>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
@@ -28904,6 +28944,7 @@
       <c r="U99" s="14"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:W92" xr:uid="{350831E6-0A7A-43D6-B07E-CBF373153DD9}"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="286" scale="80" orientation="landscape" r:id="rId1"/>
 </worksheet>

--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D69055F-5D74-4241-89BB-E4EA3FEDA017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325A3A25-9D15-428F-8623-3FFC074EF735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="584">
   <si>
     <t>NO.</t>
   </si>
@@ -1703,15 +1703,9 @@
     <t>VUELOS PANAMA JULIO SANCHEZ</t>
   </si>
   <si>
-    <t>PUERTO COLOMBIA</t>
-  </si>
-  <si>
     <t>Bolivar</t>
   </si>
   <si>
-    <t>DOS QUEBRADAS</t>
-  </si>
-  <si>
     <t>Villa del Rosario</t>
   </si>
   <si>
@@ -1727,12 +1721,6 @@
     <t>ANTIOQUIA</t>
   </si>
   <si>
-    <t>SANTA LUCIA</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>YENNY VELANDIA</t>
   </si>
   <si>
@@ -1742,9 +1730,6 @@
     <t>EL BANCO</t>
   </si>
   <si>
-    <t>CUOTAS NO REPORTADAS</t>
-  </si>
-  <si>
     <t>ABRIL</t>
   </si>
   <si>
@@ -1785,6 +1770,27 @@
   </si>
   <si>
     <t>BCOL CTE</t>
+  </si>
+  <si>
+    <t>NO REPORTADA</t>
+  </si>
+  <si>
+    <t>PTO. COLOM</t>
+  </si>
+  <si>
+    <t>Dosquebradas</t>
+  </si>
+  <si>
+    <t>Valledupar</t>
+  </si>
+  <si>
+    <t>NOTA CONCILIATORIA CONSIG NO REPORTADAS MAY</t>
+  </si>
+  <si>
+    <t>NOTA CONCILIATORIA CONSIG NO REPORTADAS JUN</t>
+  </si>
+  <si>
+    <t>IG. EN CHIQUINQUIRA</t>
   </si>
 </sst>
 </file>
@@ -2480,13 +2486,13 @@
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>5</v>
@@ -2501,7 +2507,7 @@
         <v>8</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>10</v>
@@ -2561,7 +2567,7 @@
         <v>2059000</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>24</v>
@@ -2616,7 +2622,9 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="43">
         <v>100000</v>
@@ -2683,7 +2691,7 @@
         <v>200000</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>24</v>
@@ -2746,7 +2754,7 @@
         <v>100000</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>24</v>
@@ -2813,7 +2821,7 @@
         <v>2000000</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>24</v>
@@ -2880,7 +2888,7 @@
         <v>1100000</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>24</v>
@@ -3000,7 +3008,9 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="43">
         <v>1000000</v>
@@ -3120,16 +3130,18 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="43">
         <v>0</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J14" s="4">
         <v>0</v>
@@ -3182,7 +3194,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F15" s="8">
         <v>3</v>
@@ -3191,7 +3203,7 @@
         <v>1600000</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>24</v>
@@ -3246,13 +3258,15 @@
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F16" s="8"/>
       <c r="G16" s="45">
         <v>1500000</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>24</v>
@@ -3317,7 +3331,7 @@
         <v>2820000</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>24</v>
@@ -3384,7 +3398,7 @@
         <v>1000000</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>24</v>
@@ -3449,7 +3463,7 @@
         <v>6219000</v>
       </c>
       <c r="H19" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>24</v>
@@ -3514,7 +3528,7 @@
         <v>4800000</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>24</v>
@@ -3581,7 +3595,7 @@
         <v>5200000</v>
       </c>
       <c r="H21" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>24</v>
@@ -3637,14 +3651,14 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>577</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="43">
         <v>100000</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>24</v>
@@ -3713,7 +3727,7 @@
         <v>22900000</v>
       </c>
       <c r="H23" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>24</v>
@@ -3776,7 +3790,7 @@
         <v>800000</v>
       </c>
       <c r="H24" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>24</v>
@@ -3832,7 +3846,7 @@
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="2" t="s">
-        <v>382</v>
+        <v>99</v>
       </c>
       <c r="F25" s="8">
         <v>1</v>
@@ -3841,7 +3855,7 @@
         <v>1200000</v>
       </c>
       <c r="H25" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>24</v>
@@ -3896,13 +3910,15 @@
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F26" s="2"/>
       <c r="G26" s="43">
         <v>200000</v>
       </c>
       <c r="H26" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>24</v>
@@ -3957,13 +3973,15 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F27" s="2"/>
       <c r="G27" s="43">
         <v>2400000</v>
       </c>
       <c r="H27" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>24</v>
@@ -4028,7 +4046,7 @@
         <v>4400000</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>24</v>
@@ -4093,7 +4111,7 @@
         <v>240000</v>
       </c>
       <c r="H29" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>24</v>
@@ -4162,7 +4180,7 @@
         <v>1000000</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>24</v>
@@ -4225,7 +4243,7 @@
         <v>100000</v>
       </c>
       <c r="H31" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>24</v>
@@ -4294,7 +4312,7 @@
         <v>10045000</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>24</v>
@@ -4357,7 +4375,7 @@
         <v>450000</v>
       </c>
       <c r="H33" s="43" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>24</v>
@@ -4412,7 +4430,9 @@
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F34" s="2">
         <v>1</v>
       </c>
@@ -4420,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>24</v>
@@ -4483,7 +4503,7 @@
         <v>400000</v>
       </c>
       <c r="H35" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>24</v>
@@ -4552,7 +4572,7 @@
         <v>21600000</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>24</v>
@@ -4615,7 +4635,7 @@
         <v>2200000</v>
       </c>
       <c r="H37" s="43" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>24</v>
@@ -4684,7 +4704,7 @@
         <v>800000</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>24</v>
@@ -4739,13 +4759,15 @@
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F39" s="8"/>
       <c r="G39" s="45">
         <v>1200000</v>
       </c>
       <c r="H39" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>24</v>
@@ -4812,7 +4834,7 @@
         <v>4400000</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>24</v>
@@ -4879,7 +4901,7 @@
         <v>6000000</v>
       </c>
       <c r="H41" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>24</v>
@@ -4946,7 +4968,7 @@
         <v>4400000</v>
       </c>
       <c r="H42" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>24</v>
@@ -5009,7 +5031,7 @@
         <v>6522000</v>
       </c>
       <c r="H43" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>24</v>
@@ -5076,7 +5098,7 @@
         <v>20208000</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>24</v>
@@ -5132,14 +5154,14 @@
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
       <c r="E45" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="45">
         <v>600000</v>
       </c>
       <c r="H45" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>24</v>
@@ -5269,7 +5291,7 @@
         <v>4095000</v>
       </c>
       <c r="H47" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>24</v>
@@ -5334,7 +5356,7 @@
         <v>12937600</v>
       </c>
       <c r="H48" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>24</v>
@@ -5403,7 +5425,7 @@
         <v>16940000</v>
       </c>
       <c r="H49" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>24</v>
@@ -5459,14 +5481,14 @@
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="2" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="45">
         <v>2700000</v>
       </c>
       <c r="H50" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>24</v>
@@ -5487,7 +5509,7 @@
         <v>120000</v>
       </c>
       <c r="O50" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
@@ -5497,19 +5519,19 @@
       <c r="U50" s="4"/>
       <c r="V50" s="5">
         <f t="shared" si="3"/>
-        <v>350000</v>
+        <v>600000</v>
       </c>
       <c r="W50" s="6">
         <f t="shared" si="0"/>
-        <v>0.875</v>
+        <v>1.5</v>
       </c>
       <c r="X50" s="6">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y50" s="6">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
@@ -5533,7 +5555,7 @@
         <v>16800000</v>
       </c>
       <c r="H51" s="44" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>24</v>
@@ -5596,7 +5618,7 @@
         <v>220000</v>
       </c>
       <c r="H52" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>24</v>
@@ -5659,7 +5681,7 @@
         <v>13600000</v>
       </c>
       <c r="H53" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>24</v>
@@ -5722,7 +5744,7 @@
         <v>3050000</v>
       </c>
       <c r="H54" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>24</v>
@@ -5789,7 +5811,7 @@
         <v>9745000</v>
       </c>
       <c r="H55" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>24</v>
@@ -5852,7 +5874,7 @@
         <v>1600000</v>
       </c>
       <c r="H56" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>24</v>
@@ -5917,7 +5939,7 @@
         <v>2285000</v>
       </c>
       <c r="H57" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>24</v>
@@ -5980,7 +6002,7 @@
         <v>2800000</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>24</v>
@@ -6043,7 +6065,7 @@
         <v>9200000</v>
       </c>
       <c r="H59" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>24</v>
@@ -6108,7 +6130,7 @@
         <v>11200000</v>
       </c>
       <c r="H60" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>24</v>
@@ -6129,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="O60" s="4">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
@@ -6139,19 +6161,19 @@
       <c r="U60" s="4"/>
       <c r="V60" s="5">
         <f t="shared" si="3"/>
-        <v>4800000</v>
+        <v>5600000</v>
       </c>
       <c r="W60" s="6">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X60" s="6">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y60" s="6">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
@@ -6173,7 +6195,7 @@
         <v>14800000</v>
       </c>
       <c r="H61" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>24</v>
@@ -6240,7 +6262,7 @@
         <v>2400000</v>
       </c>
       <c r="H62" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>24</v>
@@ -6303,7 +6325,7 @@
         <v>440000</v>
       </c>
       <c r="H63" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>24</v>
@@ -6366,7 +6388,7 @@
         <v>1250000</v>
       </c>
       <c r="H64" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>24</v>
@@ -6429,7 +6451,7 @@
         <v>1400000</v>
       </c>
       <c r="H65" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>24</v>
@@ -6492,7 +6514,7 @@
         <v>9524000</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>24</v>
@@ -6559,7 +6581,7 @@
         <v>7266250</v>
       </c>
       <c r="H67" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>24</v>
@@ -6622,7 +6644,7 @@
         <v>3645000</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>24</v>
@@ -6685,7 +6707,7 @@
         <v>5704059</v>
       </c>
       <c r="H69" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>24</v>
@@ -6752,7 +6774,7 @@
         <v>18700000</v>
       </c>
       <c r="H70" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>24</v>
@@ -6810,14 +6832,14 @@
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2" t="s">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="43">
         <v>62180000</v>
       </c>
       <c r="H71" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>24</v>
@@ -6880,7 +6902,7 @@
         <v>2110000</v>
       </c>
       <c r="H72" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>24</v>
@@ -6936,14 +6958,14 @@
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="45">
         <v>7580000</v>
       </c>
       <c r="H73" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>24</v>
@@ -6964,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
@@ -6974,19 +6996,19 @@
       <c r="U73" s="4"/>
       <c r="V73" s="5">
         <f t="shared" si="7"/>
-        <v>2400000</v>
+        <v>2800000</v>
       </c>
       <c r="W73" s="6">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X73" s="6">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y73" s="6">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
@@ -7006,7 +7028,7 @@
         <v>2800000</v>
       </c>
       <c r="H74" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>24</v>
@@ -7249,7 +7271,7 @@
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F78" s="2">
         <v>1</v>
@@ -7258,7 +7280,7 @@
         <v>14000000</v>
       </c>
       <c r="H78" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>24</v>
@@ -7279,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="O78" s="4">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
@@ -7289,19 +7311,19 @@
       <c r="U78" s="4"/>
       <c r="V78" s="5">
         <f t="shared" si="7"/>
-        <v>7200000</v>
+        <v>15200000</v>
       </c>
       <c r="W78" s="6">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="X78" s="6">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y78" s="6">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
@@ -7321,7 +7343,7 @@
         <v>200000</v>
       </c>
       <c r="H79" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>24</v>
@@ -7386,7 +7408,7 @@
         <v>50000</v>
       </c>
       <c r="H80" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>24</v>
@@ -7449,7 +7471,7 @@
         <v>1762000</v>
       </c>
       <c r="H81" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>24</v>
@@ -7512,7 +7534,7 @@
         <v>800000</v>
       </c>
       <c r="H82" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>24</v>
@@ -7579,7 +7601,7 @@
         <v>6000000</v>
       </c>
       <c r="H83" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>24</v>
@@ -7646,7 +7668,7 @@
         <v>4240000</v>
       </c>
       <c r="H84" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>24</v>
@@ -7711,7 +7733,7 @@
         <v>1300000</v>
       </c>
       <c r="H85" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>24</v>
@@ -7774,7 +7796,7 @@
         <v>420000</v>
       </c>
       <c r="H86" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>24</v>
@@ -7841,7 +7863,7 @@
         <v>2000000</v>
       </c>
       <c r="H87" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>24</v>
@@ -7896,7 +7918,9 @@
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="E88" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F88" s="2"/>
       <c r="G88" s="43">
         <v>4000000</v>
@@ -7969,7 +7993,7 @@
         <v>4300000</v>
       </c>
       <c r="H89" s="46" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>24</v>
@@ -8026,13 +8050,15 @@
         <v>91249777</v>
       </c>
       <c r="D90" s="8"/>
-      <c r="E90" s="2"/>
+      <c r="E90" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F90" s="8"/>
       <c r="G90" s="45">
         <v>3600000</v>
       </c>
       <c r="H90" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>24</v>
@@ -8087,13 +8113,15 @@
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
-      <c r="E91" s="2"/>
+      <c r="E91" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F91" s="8"/>
       <c r="G91" s="45">
         <v>400000</v>
       </c>
       <c r="H91" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>24</v>
@@ -8148,13 +8176,15 @@
       </c>
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
-      <c r="E92" s="2"/>
+      <c r="E92" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F92" s="2"/>
       <c r="G92" s="45">
         <v>860000</v>
       </c>
       <c r="H92" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>24</v>
@@ -8212,14 +8242,14 @@
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="43">
         <v>4140000</v>
       </c>
       <c r="H93" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>24</v>
@@ -8274,7 +8304,9 @@
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="E94" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F94" s="2">
         <v>1</v>
       </c>
@@ -8282,7 +8314,7 @@
         <v>400000</v>
       </c>
       <c r="H94" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>24</v>
@@ -8337,13 +8369,15 @@
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="E95" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F95" s="2"/>
       <c r="G95" s="43">
         <v>1600000</v>
       </c>
       <c r="H95" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>24</v>
@@ -8412,7 +8446,7 @@
         <v>1600000</v>
       </c>
       <c r="H96" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>24</v>
@@ -8479,7 +8513,7 @@
         <v>1200000</v>
       </c>
       <c r="H97" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>24</v>
@@ -8534,7 +8568,9 @@
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
-      <c r="E98" s="2"/>
+      <c r="E98" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F98" s="8"/>
       <c r="G98" s="45">
         <v>400000</v>
@@ -8605,7 +8641,7 @@
         <v>8000000</v>
       </c>
       <c r="H99" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>24</v>
@@ -8626,7 +8662,7 @@
         <v>2400000</v>
       </c>
       <c r="O99" s="4">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
@@ -8636,19 +8672,19 @@
       <c r="U99" s="4"/>
       <c r="V99" s="5">
         <f t="shared" si="7"/>
-        <v>7200000</v>
+        <v>9600000</v>
       </c>
       <c r="W99" s="6">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="X99" s="6">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y99" s="6">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.25">
@@ -8660,13 +8696,15 @@
       </c>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
-      <c r="E100" s="2"/>
+      <c r="E100" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F100" s="2"/>
       <c r="G100" s="45">
         <v>10000000</v>
       </c>
       <c r="H100" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>24</v>
@@ -8721,13 +8759,15 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
+      <c r="E101" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F101" s="2"/>
       <c r="G101" s="43">
         <v>800000</v>
       </c>
       <c r="H101" s="43" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>24</v>
@@ -8782,7 +8822,9 @@
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+      <c r="E102" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F102" s="2">
         <v>3</v>
       </c>
@@ -8790,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="44" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>24</v>
@@ -8853,7 +8895,7 @@
         <v>800000</v>
       </c>
       <c r="H103" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>24</v>
@@ -8920,7 +8962,7 @@
         <v>4000000</v>
       </c>
       <c r="H104" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>24</v>
@@ -8985,7 +9027,7 @@
         <v>12800000</v>
       </c>
       <c r="H105" s="44" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>24</v>
@@ -9109,7 +9151,7 @@
         <v>200000</v>
       </c>
       <c r="H107" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>24</v>
@@ -9174,7 +9216,7 @@
         <v>2800000</v>
       </c>
       <c r="H108" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>24</v>
@@ -9237,7 +9279,7 @@
         <v>500000</v>
       </c>
       <c r="H109" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I109" s="3" t="s">
         <v>24</v>
@@ -9369,7 +9411,7 @@
         <v>12000000</v>
       </c>
       <c r="H111" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>24</v>
@@ -9424,13 +9466,15 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
+      <c r="E112" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F112" s="2"/>
       <c r="G112" s="43">
         <v>4800000</v>
       </c>
       <c r="H112" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>24</v>
@@ -9497,7 +9541,7 @@
         <v>2400000</v>
       </c>
       <c r="H113" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>24</v>
@@ -9564,7 +9608,7 @@
         <v>2390000</v>
       </c>
       <c r="H114" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>24</v>
@@ -9627,7 +9671,7 @@
         <v>3700000</v>
       </c>
       <c r="H115" s="44" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>24</v>
@@ -9682,7 +9726,9 @@
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
-      <c r="E116" s="2"/>
+      <c r="E116" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F116" s="8"/>
       <c r="G116" s="45">
         <v>1200000</v>
@@ -9753,7 +9799,7 @@
         <v>1800000</v>
       </c>
       <c r="H117" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>24</v>
@@ -9816,7 +9862,7 @@
         <v>100000</v>
       </c>
       <c r="H118" s="46" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>24</v>
@@ -9879,7 +9925,7 @@
         <v>400000</v>
       </c>
       <c r="H119" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>24</v>
@@ -9946,7 +9992,7 @@
         <v>4000000</v>
       </c>
       <c r="H120" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>24</v>
@@ -10011,7 +10057,7 @@
         <v>10670000</v>
       </c>
       <c r="H121" s="44" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>24</v>
@@ -10069,14 +10115,14 @@
       </c>
       <c r="D122" s="2"/>
       <c r="E122" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="43">
         <v>1200000</v>
       </c>
       <c r="H122" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I122" s="3" t="s">
         <v>24</v>
@@ -10135,7 +10181,9 @@
       <c r="D123" s="8">
         <v>3215254487</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F123" s="2"/>
       <c r="G123" s="43">
         <v>1200000</v>
@@ -10194,7 +10242,9 @@
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
+      <c r="E124" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F124" s="2"/>
       <c r="G124" s="43">
         <v>200000</v>
@@ -10253,13 +10303,15 @@
       </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
+      <c r="E125" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F125" s="2"/>
       <c r="G125" s="43">
         <v>850000</v>
       </c>
       <c r="H125" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>24</v>
@@ -10326,7 +10378,7 @@
         <v>1600000</v>
       </c>
       <c r="H126" s="46" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>24</v>
@@ -10381,13 +10433,15 @@
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
+      <c r="E127" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F127" s="2"/>
       <c r="G127" s="43">
         <v>3900000</v>
       </c>
       <c r="H127" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>24</v>
@@ -10442,7 +10496,9 @@
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="E128" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F128" s="2"/>
       <c r="G128" s="43">
         <v>800000</v>
@@ -10515,7 +10571,7 @@
         <v>400000</v>
       </c>
       <c r="H129" s="46" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>24</v>
@@ -10582,7 +10638,7 @@
         <v>3200000</v>
       </c>
       <c r="H130" s="43" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>24</v>
@@ -10637,7 +10693,9 @@
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
-      <c r="E131" s="2"/>
+      <c r="E131" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F131" s="2">
         <v>1</v>
       </c>
@@ -10645,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="44" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>24</v>
@@ -10824,13 +10882,15 @@
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
+      <c r="E134" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F134" s="2"/>
       <c r="G134" s="43">
         <v>100000</v>
       </c>
       <c r="H134" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>24</v>
@@ -10954,7 +11014,7 @@
         <v>100000</v>
       </c>
       <c r="H136" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>24</v>
@@ -11023,7 +11083,7 @@
         <v>11300000</v>
       </c>
       <c r="H137" s="43" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>24</v>
@@ -11078,7 +11138,9 @@
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
+      <c r="E138" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F138" s="2">
         <v>1</v>
       </c>
@@ -11086,7 +11148,7 @@
         <v>0</v>
       </c>
       <c r="H138" s="44" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>24</v>
@@ -11153,7 +11215,7 @@
         <v>4000000</v>
       </c>
       <c r="H139" s="46" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>24</v>
@@ -11208,13 +11270,15 @@
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
+      <c r="E140" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F140" s="2"/>
       <c r="G140" s="43">
         <v>3000000</v>
       </c>
       <c r="H140" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I140" s="3" t="s">
         <v>24</v>
@@ -11269,7 +11333,9 @@
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
-      <c r="E141" s="2"/>
+      <c r="E141" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F141" s="8"/>
       <c r="G141" s="45">
         <v>260000</v>
@@ -11336,7 +11402,7 @@
         <v>3600000</v>
       </c>
       <c r="H142" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I142" s="3" t="s">
         <v>24</v>
@@ -11357,7 +11423,7 @@
         <v>1200000</v>
       </c>
       <c r="O142" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P142" s="4"/>
       <c r="Q142" s="4"/>
@@ -11367,19 +11433,19 @@
       <c r="U142" s="4"/>
       <c r="V142" s="5">
         <f t="shared" si="11"/>
-        <v>2400000</v>
+        <v>2800000</v>
       </c>
       <c r="W142" s="6">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X142" s="6">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y142" s="6">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.25">
@@ -11454,13 +11520,15 @@
       </c>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
-      <c r="E144" s="2"/>
+      <c r="E144" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F144" s="2"/>
       <c r="G144" s="43">
         <v>400000</v>
       </c>
       <c r="H144" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I144" s="3" t="s">
         <v>24</v>
@@ -11515,7 +11583,9 @@
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="E145" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F145" s="2"/>
       <c r="G145" s="43">
         <v>1200000</v>
@@ -11635,7 +11705,9 @@
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="E147" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F147" s="2">
         <v>1</v>
       </c>
@@ -11643,7 +11715,7 @@
         <v>400000</v>
       </c>
       <c r="H147" s="44" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="I147" s="3" t="s">
         <v>24</v>
@@ -11824,7 +11896,9 @@
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
+      <c r="E150" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F150" s="2"/>
       <c r="G150" s="43">
         <v>3200000</v>
@@ -11883,7 +11957,9 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
+      <c r="E151" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F151" s="2"/>
       <c r="G151" s="43">
         <v>3200000</v>
@@ -11942,7 +12018,9 @@
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
-      <c r="E152" s="2"/>
+      <c r="E152" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F152" s="2"/>
       <c r="G152" s="43">
         <v>200000</v>
@@ -12001,7 +12079,9 @@
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
-      <c r="E153" s="2"/>
+      <c r="E153" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F153" s="2"/>
       <c r="G153" s="43">
         <v>800000</v>
@@ -12065,7 +12145,7 @@
         <v>3008202508</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="43">
@@ -12127,7 +12207,9 @@
         <v>1067594389</v>
       </c>
       <c r="D155" s="2"/>
-      <c r="E155" s="2"/>
+      <c r="E155" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F155" s="2"/>
       <c r="G155" s="43">
         <v>400000</v>
@@ -12444,7 +12526,9 @@
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="8"/>
-      <c r="E160" s="2"/>
+      <c r="E160" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F160" s="2"/>
       <c r="G160" s="43">
         <v>460000</v>
@@ -12568,7 +12652,9 @@
         <v>39105075</v>
       </c>
       <c r="D162" s="8"/>
-      <c r="E162" s="2"/>
+      <c r="E162" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F162" s="2"/>
       <c r="G162" s="43">
         <v>400000</v>
@@ -12757,7 +12843,9 @@
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
-      <c r="E165" s="2"/>
+      <c r="E165" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F165" s="2"/>
       <c r="G165" s="43">
         <v>400000</v>
@@ -12883,7 +12971,9 @@
         <v>109042290</v>
       </c>
       <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
+      <c r="E167" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2">
         <v>100000</v>
@@ -12944,7 +13034,9 @@
         <v>10937503</v>
       </c>
       <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
+      <c r="E168" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2">
         <v>100000</v>
@@ -13005,7 +13097,9 @@
         <v>60442867</v>
       </c>
       <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
+      <c r="E169" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F169" s="2"/>
       <c r="G169" s="2">
         <v>900000</v>
@@ -13127,7 +13221,9 @@
       </c>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
-      <c r="E171" s="2"/>
+      <c r="E171" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F171" s="2"/>
       <c r="G171" s="43">
         <v>950000</v>
@@ -13313,7 +13409,7 @@
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c r="E174" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="43">
@@ -13375,7 +13471,9 @@
         <v>79772077</v>
       </c>
       <c r="D175" s="8"/>
-      <c r="E175" s="2"/>
+      <c r="E175" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F175" s="2"/>
       <c r="G175" s="43">
         <v>1200000</v>
@@ -13436,7 +13534,9 @@
         <v>1093775115</v>
       </c>
       <c r="D176" s="8"/>
-      <c r="E176" s="2"/>
+      <c r="E176" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F176" s="2"/>
       <c r="G176" s="43">
         <v>1200000</v>
@@ -13757,7 +13857,9 @@
         <v>1128051565</v>
       </c>
       <c r="D181" s="8"/>
-      <c r="E181" s="2"/>
+      <c r="E181" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F181" s="2"/>
       <c r="G181" s="43">
         <v>400000</v>
@@ -13881,7 +13983,9 @@
       </c>
       <c r="C183" s="8"/>
       <c r="D183" s="8"/>
-      <c r="E183" s="2"/>
+      <c r="E183" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F183" s="2"/>
       <c r="G183" s="43">
         <v>2000000</v>
@@ -13940,7 +14044,9 @@
       </c>
       <c r="C184" s="8"/>
       <c r="D184" s="8"/>
-      <c r="E184" s="2"/>
+      <c r="E184" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F184" s="2"/>
       <c r="G184" s="43">
         <v>400000</v>
@@ -14060,7 +14166,9 @@
       </c>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
-      <c r="E186" s="2"/>
+      <c r="E186" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F186" s="2"/>
       <c r="G186" s="43">
         <v>600000</v>
@@ -14124,7 +14232,7 @@
         <v>3187333883</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="43">
@@ -14184,7 +14292,9 @@
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="8"/>
-      <c r="E188" s="2"/>
+      <c r="E188" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F188" s="2"/>
       <c r="G188" s="43">
         <v>70000</v>
@@ -14209,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="O188" s="4">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="P188" s="11"/>
       <c r="Q188" s="10"/>
@@ -14219,19 +14329,19 @@
       <c r="U188" s="4"/>
       <c r="V188" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="W188" s="6">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X188" s="6">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y188" s="6">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:25" x14ac:dyDescent="0.25">
@@ -14245,7 +14355,9 @@
         <v>49741498</v>
       </c>
       <c r="D189" s="8"/>
-      <c r="E189" s="2"/>
+      <c r="E189" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F189" s="2"/>
       <c r="G189" s="43">
         <v>400000</v>
@@ -14434,7 +14546,9 @@
       </c>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
-      <c r="E192" s="2"/>
+      <c r="E192" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F192" s="2"/>
       <c r="G192" s="43">
         <v>400000</v>
@@ -14623,7 +14737,9 @@
       </c>
       <c r="C195" s="8"/>
       <c r="D195" s="8"/>
-      <c r="E195" s="2"/>
+      <c r="E195" s="2" t="s">
+        <v>473</v>
+      </c>
       <c r="F195" s="2"/>
       <c r="G195" s="43">
         <v>400000</v>
@@ -15002,7 +15118,7 @@
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
       <c r="E201" s="2" t="s">
-        <v>378</v>
+        <v>577</v>
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="43">
@@ -15062,7 +15178,9 @@
       </c>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
-      <c r="E202" s="2"/>
+      <c r="E202" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F202" s="2"/>
       <c r="G202" s="43">
         <v>400000</v>
@@ -15190,7 +15308,9 @@
       <c r="D204" s="8">
         <v>3158769403</v>
       </c>
-      <c r="E204" s="2"/>
+      <c r="E204" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F204" s="2"/>
       <c r="G204" s="43">
         <v>800000</v>
@@ -15249,7 +15369,9 @@
       </c>
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
-      <c r="E205" s="2"/>
+      <c r="E205" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F205" s="2"/>
       <c r="G205" s="43">
         <v>1130000</v>
@@ -15434,7 +15556,9 @@
       </c>
       <c r="C208" s="8"/>
       <c r="D208" s="8"/>
-      <c r="E208" s="2"/>
+      <c r="E208" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F208" s="2"/>
       <c r="G208" s="43">
         <v>400000</v>
@@ -15570,7 +15694,7 @@
         <v>800000</v>
       </c>
       <c r="H210" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I210" s="3" t="s">
         <v>24</v>
@@ -15760,7 +15884,7 @@
         <v>3042425180</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="43">
@@ -15955,7 +16079,7 @@
         <v>3015184734</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="43">
@@ -16280,7 +16404,7 @@
         <v>3108936691</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="43">
@@ -17320,7 +17444,7 @@
         <v>3107315557</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="43">
@@ -17449,7 +17573,9 @@
       <c r="D239" s="8">
         <v>3205707487</v>
       </c>
-      <c r="E239" s="2"/>
+      <c r="E239" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F239" s="2"/>
       <c r="G239" s="43">
         <v>800000</v>
@@ -17643,7 +17769,7 @@
         <v>3135513063</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="43">
@@ -17708,7 +17834,7 @@
         <v>3215857733</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>562</v>
+        <v>339</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="43">
@@ -17773,7 +17899,7 @@
         <v>3186436044</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="43">
@@ -17838,7 +17964,7 @@
         <v>3205294049</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="43">
@@ -18033,7 +18159,7 @@
         <v>3217473284</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="43">
@@ -18098,7 +18224,7 @@
         <v>3205025275</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="43">
@@ -18228,7 +18354,7 @@
         <v>3205172305</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="43">
@@ -18623,7 +18749,7 @@
         <v>800000</v>
       </c>
       <c r="H257" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I257" s="3" t="s">
         <v>24</v>
@@ -18690,7 +18816,7 @@
         <v>400000</v>
       </c>
       <c r="H258" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I258" s="3" t="s">
         <v>24</v>
@@ -20829,12 +20955,12 @@
         <v>407</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="43"/>
       <c r="H292" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I292" s="3" t="s">
         <v>24</v>
@@ -20855,7 +20981,7 @@
         <v>0</v>
       </c>
       <c r="O292" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P292" s="11"/>
       <c r="Q292" s="11"/>
@@ -20865,19 +20991,19 @@
       <c r="U292" s="4"/>
       <c r="V292" s="5">
         <f t="shared" si="20"/>
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="W292" s="6">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X292" s="6">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y292" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:25" x14ac:dyDescent="0.25">
@@ -20892,12 +21018,12 @@
         <v>409</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="43"/>
       <c r="H293" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I293" s="3" t="s">
         <v>24</v>
@@ -20918,7 +21044,7 @@
         <v>0</v>
       </c>
       <c r="O293" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P293" s="11"/>
       <c r="Q293" s="11"/>
@@ -20928,19 +21054,19 @@
       <c r="U293" s="4"/>
       <c r="V293" s="5">
         <f t="shared" si="20"/>
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="W293" s="6">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X293" s="6">
         <f t="shared" si="17"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y293" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:25" x14ac:dyDescent="0.25">
@@ -21938,7 +22064,7 @@
       <c r="F310" s="2"/>
       <c r="G310" s="43"/>
       <c r="H310" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I310" s="3" t="s">
         <v>24</v>
@@ -21959,7 +22085,7 @@
         <v>0</v>
       </c>
       <c r="O310" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P310" s="11"/>
       <c r="Q310" s="11"/>
@@ -21969,19 +22095,19 @@
       <c r="U310" s="4"/>
       <c r="V310" s="5">
         <f t="shared" si="19"/>
-        <v>1200000</v>
+        <v>1600000</v>
       </c>
       <c r="W310" s="6">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X310" s="6">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y310" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="311" spans="1:25" x14ac:dyDescent="0.25">
@@ -22001,7 +22127,7 @@
       <c r="F311" s="2"/>
       <c r="G311" s="43"/>
       <c r="H311" s="44" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="I311" s="3" t="s">
         <v>24</v>
@@ -22022,7 +22148,7 @@
         <v>0</v>
       </c>
       <c r="O311" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P311" s="11"/>
       <c r="Q311" s="11"/>
@@ -22032,19 +22158,19 @@
       <c r="U311" s="4"/>
       <c r="V311" s="5">
         <f t="shared" si="19"/>
-        <v>1200000</v>
+        <v>1600000</v>
       </c>
       <c r="W311" s="6">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X311" s="6">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y311" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="312" spans="1:25" x14ac:dyDescent="0.25">
@@ -23084,7 +23210,7 @@
       </c>
       <c r="D329" s="8"/>
       <c r="E329" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="43"/>
@@ -23145,7 +23271,7 @@
       </c>
       <c r="D330" s="8"/>
       <c r="E330" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="43"/>
@@ -23206,7 +23332,7 @@
       </c>
       <c r="D331" s="8"/>
       <c r="E331" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F331" s="2"/>
       <c r="G331" s="43"/>
@@ -23267,7 +23393,7 @@
       </c>
       <c r="D332" s="8"/>
       <c r="E332" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F332" s="2"/>
       <c r="G332" s="43"/>
@@ -23328,7 +23454,7 @@
       </c>
       <c r="D333" s="8"/>
       <c r="E333" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F333" s="2"/>
       <c r="G333" s="43"/>
@@ -23453,7 +23579,9 @@
       <c r="D335" s="8">
         <v>3135768027</v>
       </c>
-      <c r="E335" s="2"/>
+      <c r="E335" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F335" s="2"/>
       <c r="G335" s="43"/>
       <c r="H335" s="44"/>
@@ -23476,7 +23604,7 @@
         <v>400000</v>
       </c>
       <c r="O335" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P335" s="11"/>
       <c r="Q335" s="11"/>
@@ -23486,19 +23614,19 @@
       <c r="U335" s="4"/>
       <c r="V335" s="5">
         <f t="shared" si="24"/>
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="W335" s="6">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X335" s="6">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y335" s="6">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336" spans="1:25" x14ac:dyDescent="0.25">
@@ -23785,7 +23913,7 @@
         <v>400000</v>
       </c>
       <c r="O340" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P340" s="11"/>
       <c r="Q340" s="11"/>
@@ -23795,19 +23923,19 @@
       <c r="U340" s="4"/>
       <c r="V340" s="5">
         <f t="shared" si="24"/>
-        <v>800000</v>
+        <v>1200000</v>
       </c>
       <c r="W340" s="6">
         <f t="shared" si="21"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X340" s="6">
         <f t="shared" si="22"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y340" s="6">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="341" spans="1:25" x14ac:dyDescent="0.25">
@@ -23830,7 +23958,7 @@
       <c r="G341" s="43"/>
       <c r="H341" s="44"/>
       <c r="I341" s="3" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="J341" s="4">
         <v>0</v>
@@ -23887,7 +24015,7 @@
         <v>3006140088</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="43"/>
@@ -23945,7 +24073,9 @@
       </c>
       <c r="C343" s="8"/>
       <c r="D343" s="8"/>
-      <c r="E343" s="2"/>
+      <c r="E343" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F343" s="2"/>
       <c r="G343" s="43"/>
       <c r="H343" s="44"/>
@@ -24371,7 +24501,7 @@
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="2" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="43"/>
@@ -24486,7 +24616,7 @@
         <v>350</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C352" s="8"/>
       <c r="D352" s="8"/>
@@ -24545,12 +24675,12 @@
         <v>351</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C353" s="8"/>
       <c r="D353" s="8"/>
       <c r="E353" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="43"/>
@@ -24604,11 +24734,13 @@
         <v>352</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="C354" s="8"/>
       <c r="D354" s="8"/>
-      <c r="E354" s="2"/>
+      <c r="E354" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F354" s="2"/>
       <c r="G354" s="43"/>
       <c r="H354" s="44"/>
@@ -24661,11 +24793,13 @@
         <v>353</v>
       </c>
       <c r="B355" s="8" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="C355" s="8"/>
       <c r="D355" s="8"/>
-      <c r="E355" s="2"/>
+      <c r="E355" s="2" t="s">
+        <v>577</v>
+      </c>
       <c r="F355" s="2"/>
       <c r="G355" s="43"/>
       <c r="H355" s="44"/>
@@ -24717,10 +24851,14 @@
       <c r="A356" s="2">
         <v>354</v>
       </c>
-      <c r="B356" s="8"/>
+      <c r="B356" s="8" t="s">
+        <v>583</v>
+      </c>
       <c r="C356" s="8"/>
       <c r="D356" s="8"/>
-      <c r="E356" s="2"/>
+      <c r="E356" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="F356" s="2"/>
       <c r="G356" s="43"/>
       <c r="H356" s="44"/>
@@ -24743,7 +24881,7 @@
         <v>0</v>
       </c>
       <c r="O356" s="4">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="P356" s="11"/>
       <c r="Q356" s="11"/>
@@ -24753,19 +24891,19 @@
       <c r="U356" s="4"/>
       <c r="V356" s="5">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="W356" s="6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="X356" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y356" s="6">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="357" spans="1:25" x14ac:dyDescent="0.25">
@@ -25648,13 +25786,13 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>5</v>
@@ -25823,7 +25961,7 @@
         <v>-5231807</v>
       </c>
       <c r="I8" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>37</v>
@@ -25861,7 +25999,7 @@
         <v>-3500000</v>
       </c>
       <c r="I9" s="54" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>37</v>
@@ -25899,7 +26037,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J10" s="19" t="s">
         <v>37</v>
@@ -25937,7 +26075,7 @@
         <v>-20000000</v>
       </c>
       <c r="I11" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>37</v>
@@ -26009,7 +26147,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="54" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="J13" s="19" t="s">
         <v>37</v>
@@ -26083,7 +26221,7 @@
         <v>-6700000</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>37</v>
@@ -26225,7 +26363,7 @@
         <v>-400000</v>
       </c>
       <c r="I19" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J19" s="19" t="s">
         <v>37</v>
@@ -26263,7 +26401,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>37</v>
@@ -26299,7 +26437,7 @@
       <c r="G21" s="20"/>
       <c r="H21" s="53"/>
       <c r="I21" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>37</v>
@@ -26373,7 +26511,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="54" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="J23" s="19" t="s">
         <v>37</v>
@@ -26409,7 +26547,7 @@
       <c r="G24" s="20"/>
       <c r="H24" s="53"/>
       <c r="I24" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>37</v>
@@ -26447,7 +26585,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="54" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="J25" s="19" t="s">
         <v>37</v>
@@ -28771,22 +28909,32 @@
       <c r="W92" s="11"/>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A93" s="22"/>
-      <c r="B93" s="22"/>
-      <c r="C93" s="23"/>
+      <c r="A93" s="22">
+        <v>89</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>515</v>
+      </c>
       <c r="D93" s="23"/>
       <c r="E93" s="23"/>
       <c r="F93" s="23"/>
       <c r="G93" s="23"/>
       <c r="H93" s="23"/>
       <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
+      <c r="J93" s="59" t="s">
+        <v>37</v>
+      </c>
       <c r="K93" s="11"/>
       <c r="L93" s="11"/>
       <c r="M93" s="11"/>
       <c r="N93" s="11"/>
       <c r="O93" s="11"/>
-      <c r="P93" s="11"/>
+      <c r="P93" s="11">
+        <v>-3475000</v>
+      </c>
       <c r="Q93" s="11"/>
       <c r="R93" s="34"/>
       <c r="S93" s="35"/>

--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F91B1A-2845-41EC-9A89-5F23ED819830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA52D3B2-7233-414F-A47D-AE9E18E9BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
@@ -2474,10 +2474,10 @@
     <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="8" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
     <col min="10" max="10" width="18.5703125" customWidth="1"/>
     <col min="11" max="11" width="19.5703125" customWidth="1"/>
     <col min="12" max="12" width="16.42578125" customWidth="1"/>
@@ -2631,7 +2631,7 @@
       <c r="O5" s="4">
         <v>0</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="4">
         <v>0</v>
       </c>
       <c r="Q5" s="4"/>
@@ -2696,7 +2696,7 @@
       <c r="O6" s="4">
         <v>0</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="4">
         <v>0</v>
       </c>
       <c r="Q6" s="4"/>
@@ -2761,7 +2761,7 @@
       <c r="O7" s="4">
         <v>0</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="4">
         <v>0</v>
       </c>
       <c r="Q7" s="4"/>
@@ -2826,7 +2826,7 @@
       <c r="O8" s="4">
         <v>0</v>
       </c>
-      <c r="P8" s="10">
+      <c r="P8" s="4">
         <v>0</v>
       </c>
       <c r="Q8" s="4"/>
@@ -2895,7 +2895,7 @@
       <c r="O9" s="4">
         <v>0</v>
       </c>
-      <c r="P9" s="10">
+      <c r="P9" s="4">
         <v>0</v>
       </c>
       <c r="Q9" s="4"/>
@@ -2962,7 +2962,7 @@
       <c r="O10" s="4">
         <v>400000</v>
       </c>
-      <c r="P10" s="10">
+      <c r="P10" s="4">
         <v>0</v>
       </c>
       <c r="Q10" s="4"/>
@@ -3029,7 +3029,7 @@
       <c r="O11" s="4">
         <v>800000</v>
       </c>
-      <c r="P11" s="10">
+      <c r="P11" s="4">
         <v>0</v>
       </c>
       <c r="Q11" s="4"/>
@@ -3092,7 +3092,7 @@
       <c r="O12" s="4">
         <v>0</v>
       </c>
-      <c r="P12" s="10">
+      <c r="P12" s="4">
         <v>0</v>
       </c>
       <c r="Q12" s="4"/>
@@ -3157,7 +3157,7 @@
       <c r="O13" s="4">
         <v>0</v>
       </c>
-      <c r="P13" s="10">
+      <c r="P13" s="4">
         <v>0</v>
       </c>
       <c r="Q13" s="4"/>
@@ -3224,7 +3224,7 @@
       <c r="O14" s="4">
         <v>0</v>
       </c>
-      <c r="P14" s="10">
+      <c r="P14" s="4">
         <v>0</v>
       </c>
       <c r="Q14" s="4"/>
@@ -3289,7 +3289,7 @@
       <c r="O15" s="4">
         <v>1200000</v>
       </c>
-      <c r="P15" s="10">
+      <c r="P15" s="4">
         <v>1600000</v>
       </c>
       <c r="Q15" s="4"/>
@@ -3354,7 +3354,7 @@
       <c r="O16" s="4">
         <v>0</v>
       </c>
-      <c r="P16" s="10">
+      <c r="P16" s="4">
         <v>0</v>
       </c>
       <c r="Q16" s="4"/>
@@ -3421,7 +3421,7 @@
       <c r="O17" s="4">
         <v>400000</v>
       </c>
-      <c r="P17" s="10">
+      <c r="P17" s="4">
         <v>0</v>
       </c>
       <c r="Q17" s="4"/>
@@ -3492,7 +3492,7 @@
       <c r="O18" s="4">
         <v>0</v>
       </c>
-      <c r="P18" s="10">
+      <c r="P18" s="4">
         <v>0</v>
       </c>
       <c r="Q18" s="4"/>
@@ -3559,7 +3559,7 @@
       <c r="O19" s="4">
         <v>600000</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P19" s="4">
         <v>0</v>
       </c>
       <c r="Q19" s="4"/>
@@ -3624,7 +3624,7 @@
       <c r="O20" s="4">
         <v>0</v>
       </c>
-      <c r="P20" s="10">
+      <c r="P20" s="4">
         <v>0</v>
       </c>
       <c r="Q20" s="4"/>
@@ -3693,7 +3693,7 @@
       <c r="O21" s="4">
         <v>0</v>
       </c>
-      <c r="P21" s="10">
+      <c r="P21" s="4">
         <v>600000</v>
       </c>
       <c r="Q21" s="4"/>
@@ -3760,7 +3760,7 @@
       <c r="O22" s="4">
         <v>0</v>
       </c>
-      <c r="P22" s="10">
+      <c r="P22" s="4">
         <v>0</v>
       </c>
       <c r="Q22" s="4"/>
@@ -3829,7 +3829,7 @@
       <c r="O23" s="4">
         <v>4000000</v>
       </c>
-      <c r="P23" s="10">
+      <c r="P23" s="4">
         <v>0</v>
       </c>
       <c r="Q23" s="4"/>
@@ -3896,7 +3896,7 @@
       <c r="O24" s="4">
         <v>0</v>
       </c>
-      <c r="P24" s="10">
+      <c r="P24" s="4">
         <v>0</v>
       </c>
       <c r="Q24" s="4"/>
@@ -3961,7 +3961,7 @@
       <c r="O25" s="4">
         <v>400000</v>
       </c>
-      <c r="P25" s="10">
+      <c r="P25" s="4">
         <v>0</v>
       </c>
       <c r="Q25" s="4"/>
@@ -4026,7 +4026,7 @@
       <c r="O26" s="4">
         <v>0</v>
       </c>
-      <c r="P26" s="10">
+      <c r="P26" s="4">
         <v>0</v>
       </c>
       <c r="Q26" s="4"/>
@@ -4093,7 +4093,7 @@
       <c r="O27" s="4">
         <v>0</v>
       </c>
-      <c r="P27" s="10">
+      <c r="P27" s="4">
         <v>0</v>
       </c>
       <c r="Q27" s="4"/>
@@ -4160,7 +4160,7 @@
       <c r="O28" s="4">
         <v>400000</v>
       </c>
-      <c r="P28" s="10">
+      <c r="P28" s="4">
         <v>0</v>
       </c>
       <c r="Q28" s="4"/>
@@ -4227,7 +4227,7 @@
       <c r="O29" s="4">
         <v>0</v>
       </c>
-      <c r="P29" s="10">
+      <c r="P29" s="4">
         <v>0</v>
       </c>
       <c r="Q29" s="4"/>
@@ -4296,7 +4296,7 @@
       <c r="O30" s="4">
         <v>0</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P30" s="4">
         <v>0</v>
       </c>
       <c r="Q30" s="4"/>
@@ -4363,7 +4363,7 @@
       <c r="O31" s="4">
         <v>0</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P31" s="4">
         <v>0</v>
       </c>
       <c r="Q31" s="4"/>
@@ -4432,7 +4432,7 @@
       <c r="O32" s="4">
         <v>1200000</v>
       </c>
-      <c r="P32" s="10">
+      <c r="P32" s="4">
         <v>0</v>
       </c>
       <c r="Q32" s="4"/>
@@ -4499,7 +4499,7 @@
       <c r="O33" s="4">
         <v>0</v>
       </c>
-      <c r="P33" s="10">
+      <c r="P33" s="4">
         <v>0</v>
       </c>
       <c r="Q33" s="4"/>
@@ -4564,7 +4564,7 @@
       <c r="O34" s="4">
         <v>0</v>
       </c>
-      <c r="P34" s="10">
+      <c r="P34" s="4">
         <v>0</v>
       </c>
       <c r="Q34" s="4"/>
@@ -4631,7 +4631,7 @@
       <c r="O35" s="4">
         <v>0</v>
       </c>
-      <c r="P35" s="10">
+      <c r="P35" s="4">
         <v>0</v>
       </c>
       <c r="Q35" s="4"/>
@@ -4700,7 +4700,7 @@
       <c r="O36" s="4">
         <v>3600000</v>
       </c>
-      <c r="P36" s="10">
+      <c r="P36" s="4">
         <v>0</v>
       </c>
       <c r="Q36" s="4"/>
@@ -4767,7 +4767,7 @@
       <c r="O37" s="4">
         <v>400000</v>
       </c>
-      <c r="P37" s="10">
+      <c r="P37" s="4">
         <v>400000</v>
       </c>
       <c r="Q37" s="4"/>
@@ -4836,7 +4836,7 @@
       <c r="O38" s="4">
         <v>0</v>
       </c>
-      <c r="P38" s="10">
+      <c r="P38" s="4">
         <v>400000</v>
       </c>
       <c r="Q38" s="4"/>
@@ -4901,7 +4901,7 @@
       <c r="O39" s="4">
         <v>0</v>
       </c>
-      <c r="P39" s="10">
+      <c r="P39" s="4">
         <v>0</v>
       </c>
       <c r="Q39" s="4"/>
@@ -4970,7 +4970,7 @@
       <c r="O40" s="4">
         <v>1600000</v>
       </c>
-      <c r="P40" s="10">
+      <c r="P40" s="4">
         <v>1600000</v>
       </c>
       <c r="Q40" s="4"/>
@@ -5039,7 +5039,7 @@
       <c r="O41" s="4">
         <v>800000</v>
       </c>
-      <c r="P41" s="10">
+      <c r="P41" s="4">
         <v>800000</v>
       </c>
       <c r="Q41" s="4"/>
@@ -5108,7 +5108,7 @@
       <c r="O42" s="4">
         <v>0</v>
       </c>
-      <c r="P42" s="10">
+      <c r="P42" s="4">
         <v>0</v>
       </c>
       <c r="Q42" s="4"/>
@@ -5173,7 +5173,7 @@
       <c r="O43" s="4">
         <v>0</v>
       </c>
-      <c r="P43" s="10">
+      <c r="P43" s="4">
         <v>0</v>
       </c>
       <c r="Q43" s="4"/>
@@ -5242,7 +5242,7 @@
       <c r="O44" s="4">
         <v>1430000</v>
       </c>
-      <c r="P44" s="10">
+      <c r="P44" s="4">
         <v>0</v>
       </c>
       <c r="Q44" s="4"/>
@@ -5305,7 +5305,7 @@
       <c r="O45" s="4">
         <v>0</v>
       </c>
-      <c r="P45" s="10">
+      <c r="P45" s="4">
         <v>0</v>
       </c>
       <c r="Q45" s="4"/>
@@ -5376,7 +5376,7 @@
       <c r="O46" s="4">
         <v>0</v>
       </c>
-      <c r="P46" s="10">
+      <c r="P46" s="4">
         <v>0</v>
       </c>
       <c r="Q46" s="4"/>
@@ -5443,7 +5443,7 @@
       <c r="O47" s="4">
         <v>0</v>
       </c>
-      <c r="P47" s="10">
+      <c r="P47" s="4">
         <v>0</v>
       </c>
       <c r="Q47" s="4"/>
@@ -5510,7 +5510,7 @@
       <c r="O48" s="4">
         <v>0</v>
       </c>
-      <c r="P48" s="10">
+      <c r="P48" s="4">
         <v>0</v>
       </c>
       <c r="Q48" s="4"/>
@@ -5579,7 +5579,7 @@
       <c r="O49" s="4">
         <v>800000</v>
       </c>
-      <c r="P49" s="10">
+      <c r="P49" s="4">
         <v>0</v>
       </c>
       <c r="Q49" s="4"/>
@@ -5644,7 +5644,7 @@
       <c r="O50" s="4">
         <v>250000</v>
       </c>
-      <c r="P50" s="10">
+      <c r="P50" s="4">
         <v>270000</v>
       </c>
       <c r="Q50" s="4"/>
@@ -5713,7 +5713,7 @@
       <c r="O51" s="4">
         <v>800000</v>
       </c>
-      <c r="P51" s="10">
+      <c r="P51" s="4">
         <v>0</v>
       </c>
       <c r="Q51" s="4"/>
@@ -5778,7 +5778,7 @@
       <c r="O52" s="4">
         <v>0</v>
       </c>
-      <c r="P52" s="10">
+      <c r="P52" s="4">
         <v>800000</v>
       </c>
       <c r="Q52" s="4"/>
@@ -5843,7 +5843,7 @@
       <c r="O53" s="4">
         <v>1500000</v>
       </c>
-      <c r="P53" s="10">
+      <c r="P53" s="4">
         <v>0</v>
       </c>
       <c r="Q53" s="4"/>
@@ -5908,7 +5908,7 @@
       <c r="O54" s="4">
         <v>0</v>
       </c>
-      <c r="P54" s="10">
+      <c r="P54" s="4">
         <v>0</v>
       </c>
       <c r="Q54" s="4"/>
@@ -5977,7 +5977,7 @@
       <c r="O55" s="4">
         <v>1200000</v>
       </c>
-      <c r="P55" s="10">
+      <c r="P55" s="4">
         <v>0</v>
       </c>
       <c r="Q55" s="4"/>
@@ -6044,7 +6044,7 @@
       <c r="O56" s="4">
         <v>0</v>
       </c>
-      <c r="P56" s="10">
+      <c r="P56" s="4">
         <v>0</v>
       </c>
       <c r="Q56" s="4"/>
@@ -6109,7 +6109,7 @@
       <c r="O57" s="4">
         <v>0</v>
       </c>
-      <c r="P57" s="10">
+      <c r="P57" s="4">
         <v>0</v>
       </c>
       <c r="Q57" s="4"/>
@@ -6174,7 +6174,7 @@
       <c r="O58" s="4">
         <v>0</v>
       </c>
-      <c r="P58" s="10">
+      <c r="P58" s="4">
         <v>0</v>
       </c>
       <c r="Q58" s="4"/>
@@ -6239,7 +6239,7 @@
       <c r="O59" s="4">
         <v>600000</v>
       </c>
-      <c r="P59" s="10">
+      <c r="P59" s="4">
         <v>0</v>
       </c>
       <c r="Q59" s="4"/>
@@ -6308,7 +6308,7 @@
       <c r="O60" s="4">
         <v>800000</v>
       </c>
-      <c r="P60" s="10">
+      <c r="P60" s="4">
         <v>1200000</v>
       </c>
       <c r="Q60" s="4"/>
@@ -6373,7 +6373,7 @@
       <c r="O61" s="4">
         <v>1600000</v>
       </c>
-      <c r="P61" s="10">
+      <c r="P61" s="4">
         <v>0</v>
       </c>
       <c r="Q61" s="4"/>
@@ -6442,7 +6442,7 @@
       <c r="O62" s="4">
         <v>400000</v>
       </c>
-      <c r="P62" s="10">
+      <c r="P62" s="4">
         <v>0</v>
       </c>
       <c r="Q62" s="4"/>
@@ -6507,7 +6507,7 @@
       <c r="O63" s="4">
         <v>0</v>
       </c>
-      <c r="P63" s="10">
+      <c r="P63" s="4">
         <v>0</v>
       </c>
       <c r="Q63" s="4"/>
@@ -6572,7 +6572,7 @@
       <c r="O64" s="4">
         <v>0</v>
       </c>
-      <c r="P64" s="10">
+      <c r="P64" s="4">
         <v>0</v>
       </c>
       <c r="Q64" s="4"/>
@@ -6637,7 +6637,7 @@
       <c r="O65" s="4">
         <v>0</v>
       </c>
-      <c r="P65" s="10">
+      <c r="P65" s="4">
         <v>0</v>
       </c>
       <c r="Q65" s="4"/>
@@ -6702,7 +6702,7 @@
       <c r="O66" s="4">
         <v>1600000</v>
       </c>
-      <c r="P66" s="10">
+      <c r="P66" s="4">
         <v>1600000</v>
       </c>
       <c r="Q66" s="4"/>
@@ -6771,7 +6771,7 @@
       <c r="O67" s="4">
         <v>2070000</v>
       </c>
-      <c r="P67" s="10">
+      <c r="P67" s="4">
         <v>2100000</v>
       </c>
       <c r="Q67" s="4"/>
@@ -6836,7 +6836,7 @@
       <c r="O68" s="4">
         <v>0</v>
       </c>
-      <c r="P68" s="10">
+      <c r="P68" s="4">
         <v>0</v>
       </c>
       <c r="Q68" s="4"/>
@@ -6901,7 +6901,7 @@
       <c r="O69" s="4">
         <v>0</v>
       </c>
-      <c r="P69" s="10">
+      <c r="P69" s="4">
         <v>0</v>
       </c>
       <c r="Q69" s="4"/>
@@ -6970,7 +6970,7 @@
       <c r="O70" s="4">
         <v>5060000</v>
       </c>
-      <c r="P70" s="10">
+      <c r="P70" s="4">
         <v>0</v>
       </c>
       <c r="Q70" s="4"/>
@@ -7037,7 +7037,7 @@
       <c r="O71" s="4">
         <v>10214000</v>
       </c>
-      <c r="P71" s="10">
+      <c r="P71" s="4">
         <v>0</v>
       </c>
       <c r="Q71" s="4"/>
@@ -7102,7 +7102,7 @@
       <c r="O72" s="4">
         <v>0</v>
       </c>
-      <c r="P72" s="10">
+      <c r="P72" s="4">
         <v>0</v>
       </c>
       <c r="Q72" s="4"/>
@@ -7167,7 +7167,7 @@
       <c r="O73" s="4">
         <v>400000</v>
       </c>
-      <c r="P73" s="10">
+      <c r="P73" s="4">
         <v>0</v>
       </c>
       <c r="Q73" s="4"/>
@@ -7230,7 +7230,7 @@
       <c r="O74" s="4">
         <v>0</v>
       </c>
-      <c r="P74" s="10">
+      <c r="P74" s="4">
         <v>800000</v>
       </c>
       <c r="Q74" s="4"/>
@@ -7293,7 +7293,7 @@
       <c r="O75" s="4">
         <v>0</v>
       </c>
-      <c r="P75" s="10">
+      <c r="P75" s="4">
         <v>800000</v>
       </c>
       <c r="Q75" s="4"/>
@@ -7356,7 +7356,7 @@
       <c r="O76" s="4">
         <v>2400000</v>
       </c>
-      <c r="P76" s="10">
+      <c r="P76" s="4">
         <v>0</v>
       </c>
       <c r="Q76" s="4"/>
@@ -7427,7 +7427,7 @@
       <c r="O77" s="4">
         <v>800000</v>
       </c>
-      <c r="P77" s="10">
+      <c r="P77" s="4">
         <v>800000</v>
       </c>
       <c r="Q77" s="4"/>
@@ -7492,7 +7492,7 @@
       <c r="O78" s="4">
         <v>8000000</v>
       </c>
-      <c r="P78" s="10">
+      <c r="P78" s="4">
         <v>0</v>
       </c>
       <c r="Q78" s="4"/>
@@ -7559,7 +7559,7 @@
       <c r="O79" s="4">
         <v>0</v>
       </c>
-      <c r="P79" s="10">
+      <c r="P79" s="4">
         <v>0</v>
       </c>
       <c r="Q79" s="4"/>
@@ -7624,7 +7624,7 @@
       <c r="O80" s="4">
         <v>0</v>
       </c>
-      <c r="P80" s="10">
+      <c r="P80" s="4">
         <v>0</v>
       </c>
       <c r="Q80" s="4"/>
@@ -7689,7 +7689,7 @@
       <c r="O81" s="4">
         <v>0</v>
       </c>
-      <c r="P81" s="10">
+      <c r="P81" s="4">
         <v>0</v>
       </c>
       <c r="Q81" s="4"/>
@@ -7754,7 +7754,7 @@
       <c r="O82" s="4">
         <v>0</v>
       </c>
-      <c r="P82" s="10">
+      <c r="P82" s="4">
         <v>0</v>
       </c>
       <c r="Q82" s="4"/>
@@ -7823,7 +7823,7 @@
       <c r="O83" s="4">
         <v>1200000</v>
       </c>
-      <c r="P83" s="10">
+      <c r="P83" s="4">
         <v>0</v>
       </c>
       <c r="Q83" s="4"/>
@@ -7892,7 +7892,7 @@
       <c r="O84" s="4">
         <v>300000</v>
       </c>
-      <c r="P84" s="10">
+      <c r="P84" s="4">
         <v>400000</v>
       </c>
       <c r="Q84" s="4"/>
@@ -7959,7 +7959,7 @@
       <c r="O85" s="4">
         <v>400000</v>
       </c>
-      <c r="P85" s="10">
+      <c r="P85" s="4">
         <v>400000</v>
       </c>
       <c r="Q85" s="4"/>
@@ -8024,7 +8024,7 @@
       <c r="O86" s="4">
         <v>0</v>
       </c>
-      <c r="P86" s="10">
+      <c r="P86" s="4">
         <v>0</v>
       </c>
       <c r="Q86" s="4"/>
@@ -8091,7 +8091,7 @@
       <c r="O87" s="4">
         <v>0</v>
       </c>
-      <c r="P87" s="10">
+      <c r="P87" s="4">
         <v>0</v>
       </c>
       <c r="Q87" s="4"/>
@@ -8158,7 +8158,7 @@
       <c r="O88" s="4">
         <v>0</v>
       </c>
-      <c r="P88" s="10">
+      <c r="P88" s="4">
         <v>0</v>
       </c>
       <c r="Q88" s="4"/>
@@ -8227,7 +8227,7 @@
       <c r="O89" s="4">
         <v>0</v>
       </c>
-      <c r="P89" s="10">
+      <c r="P89" s="4">
         <v>0</v>
       </c>
       <c r="Q89" s="4"/>
@@ -8294,7 +8294,7 @@
       <c r="O90" s="4">
         <v>0</v>
       </c>
-      <c r="P90" s="10">
+      <c r="P90" s="4">
         <v>0</v>
       </c>
       <c r="Q90" s="4"/>
@@ -8359,7 +8359,7 @@
       <c r="O91" s="4">
         <v>0</v>
       </c>
-      <c r="P91" s="10">
+      <c r="P91" s="4">
         <v>0</v>
       </c>
       <c r="Q91" s="4"/>
@@ -8424,7 +8424,7 @@
       <c r="O92" s="4">
         <v>0</v>
       </c>
-      <c r="P92" s="10">
+      <c r="P92" s="4">
         <v>0</v>
       </c>
       <c r="Q92" s="4"/>
@@ -8493,7 +8493,7 @@
       <c r="O93" s="4">
         <v>400000</v>
       </c>
-      <c r="P93" s="10">
+      <c r="P93" s="4">
         <v>0</v>
       </c>
       <c r="Q93" s="4"/>
@@ -8558,7 +8558,7 @@
       <c r="O94" s="4">
         <v>0</v>
       </c>
-      <c r="P94" s="10">
+      <c r="P94" s="4">
         <v>0</v>
       </c>
       <c r="Q94" s="4"/>
@@ -8625,7 +8625,7 @@
       <c r="O95" s="4">
         <v>0</v>
       </c>
-      <c r="P95" s="10">
+      <c r="P95" s="4">
         <v>0</v>
       </c>
       <c r="Q95" s="4"/>
@@ -8694,7 +8694,7 @@
       <c r="O96" s="4">
         <v>0</v>
       </c>
-      <c r="P96" s="10">
+      <c r="P96" s="4">
         <v>0</v>
       </c>
       <c r="Q96" s="4"/>
@@ -8761,7 +8761,7 @@
       <c r="O97" s="4">
         <v>400000</v>
       </c>
-      <c r="P97" s="10">
+      <c r="P97" s="4">
         <v>0</v>
       </c>
       <c r="Q97" s="4"/>
@@ -8826,7 +8826,7 @@
       <c r="O98" s="4">
         <v>0</v>
       </c>
-      <c r="P98" s="10">
+      <c r="P98" s="4">
         <v>400000</v>
       </c>
       <c r="Q98" s="4"/>
@@ -8895,7 +8895,7 @@
       <c r="O99" s="4">
         <v>2400000</v>
       </c>
-      <c r="P99" s="10">
+      <c r="P99" s="4">
         <v>0</v>
       </c>
       <c r="Q99" s="4"/>
@@ -8960,7 +8960,7 @@
       <c r="O100" s="4">
         <v>0</v>
       </c>
-      <c r="P100" s="10">
+      <c r="P100" s="4">
         <v>0</v>
       </c>
       <c r="Q100" s="4"/>
@@ -9027,7 +9027,7 @@
       <c r="O101" s="4">
         <v>0</v>
       </c>
-      <c r="P101" s="10">
+      <c r="P101" s="4">
         <v>0</v>
       </c>
       <c r="Q101" s="4"/>
@@ -9092,7 +9092,7 @@
       <c r="O102" s="4">
         <v>0</v>
       </c>
-      <c r="P102" s="10">
+      <c r="P102" s="4">
         <v>0</v>
       </c>
       <c r="Q102" s="4"/>
@@ -9157,7 +9157,7 @@
       <c r="O103" s="4">
         <v>0</v>
       </c>
-      <c r="P103" s="10">
+      <c r="P103" s="4">
         <v>0</v>
       </c>
       <c r="Q103" s="4"/>
@@ -9228,7 +9228,7 @@
       <c r="O104" s="4">
         <v>0</v>
       </c>
-      <c r="P104" s="10">
+      <c r="P104" s="4">
         <v>0</v>
       </c>
       <c r="Q104" s="4"/>
@@ -9291,7 +9291,7 @@
       <c r="O105" s="4">
         <v>800000</v>
       </c>
-      <c r="P105" s="10">
+      <c r="P105" s="4">
         <v>0</v>
       </c>
       <c r="Q105" s="4"/>
@@ -9356,7 +9356,7 @@
       <c r="O106" s="4">
         <v>0</v>
       </c>
-      <c r="P106" s="10">
+      <c r="P106" s="4">
         <v>0</v>
       </c>
       <c r="Q106" s="4"/>
@@ -9423,7 +9423,7 @@
       <c r="O107" s="4">
         <v>0</v>
       </c>
-      <c r="P107" s="10">
+      <c r="P107" s="4">
         <v>0</v>
       </c>
       <c r="Q107" s="4"/>
@@ -9488,7 +9488,7 @@
       <c r="O108" s="4">
         <v>0</v>
       </c>
-      <c r="P108" s="10">
+      <c r="P108" s="4">
         <v>0</v>
       </c>
       <c r="Q108" s="4"/>
@@ -9551,7 +9551,7 @@
       <c r="O109" s="4">
         <v>0</v>
       </c>
-      <c r="P109" s="10">
+      <c r="P109" s="4">
         <v>0</v>
       </c>
       <c r="Q109" s="4"/>
@@ -9620,7 +9620,7 @@
       <c r="O110" s="4">
         <v>800000</v>
       </c>
-      <c r="P110" s="10">
+      <c r="P110" s="4">
         <v>0</v>
       </c>
       <c r="Q110" s="4"/>
@@ -9689,7 +9689,7 @@
       <c r="O111" s="4">
         <v>2000000</v>
       </c>
-      <c r="P111" s="10">
+      <c r="P111" s="4">
         <v>2000000</v>
       </c>
       <c r="Q111" s="4"/>
@@ -9754,7 +9754,7 @@
       <c r="O112" s="4">
         <v>0</v>
       </c>
-      <c r="P112" s="10">
+      <c r="P112" s="4">
         <v>0</v>
       </c>
       <c r="Q112" s="4"/>
@@ -9823,7 +9823,7 @@
       <c r="O113" s="4">
         <v>400000</v>
       </c>
-      <c r="P113" s="10">
+      <c r="P113" s="4">
         <v>0</v>
       </c>
       <c r="Q113" s="4"/>
@@ -9892,7 +9892,7 @@
       <c r="O114" s="4">
         <v>400000</v>
       </c>
-      <c r="P114" s="10">
+      <c r="P114" s="4">
         <v>0</v>
       </c>
       <c r="Q114" s="4"/>
@@ -9955,7 +9955,7 @@
       <c r="O115" s="4">
         <v>800000</v>
       </c>
-      <c r="P115" s="10">
+      <c r="P115" s="4">
         <v>400000</v>
       </c>
       <c r="Q115" s="4"/>
@@ -10020,7 +10020,7 @@
       <c r="O116" s="4">
         <v>0</v>
       </c>
-      <c r="P116" s="10">
+      <c r="P116" s="4">
         <v>0</v>
       </c>
       <c r="Q116" s="4"/>
@@ -10089,7 +10089,7 @@
       <c r="O117" s="4">
         <v>0</v>
       </c>
-      <c r="P117" s="10">
+      <c r="P117" s="4">
         <v>0</v>
       </c>
       <c r="Q117" s="4"/>
@@ -10154,7 +10154,7 @@
       <c r="O118" s="4">
         <v>0</v>
       </c>
-      <c r="P118" s="10">
+      <c r="P118" s="4">
         <v>0</v>
       </c>
       <c r="Q118" s="4"/>
@@ -10219,7 +10219,7 @@
       <c r="O119" s="4">
         <v>0</v>
       </c>
-      <c r="P119" s="10">
+      <c r="P119" s="4">
         <v>0</v>
       </c>
       <c r="Q119" s="4"/>
@@ -10290,7 +10290,7 @@
       <c r="O120" s="4">
         <v>400000</v>
       </c>
-      <c r="P120" s="10">
+      <c r="P120" s="4">
         <v>400000</v>
       </c>
       <c r="Q120" s="4"/>
@@ -10355,7 +10355,7 @@
       <c r="O121" s="4">
         <v>800000</v>
       </c>
-      <c r="P121" s="10">
+      <c r="P121" s="4">
         <v>0</v>
       </c>
       <c r="Q121" s="4"/>
@@ -10420,7 +10420,7 @@
       <c r="O122" s="4">
         <v>400000</v>
       </c>
-      <c r="P122" s="10">
+      <c r="P122" s="4">
         <v>100000</v>
       </c>
       <c r="Q122" s="4"/>
@@ -10487,7 +10487,7 @@
       <c r="O123" s="4">
         <v>0</v>
       </c>
-      <c r="P123" s="10">
+      <c r="P123" s="4">
         <v>0</v>
       </c>
       <c r="Q123" s="4"/>
@@ -10552,7 +10552,7 @@
       <c r="O124" s="4">
         <v>0</v>
       </c>
-      <c r="P124" s="10">
+      <c r="P124" s="4">
         <v>0</v>
       </c>
       <c r="Q124" s="4"/>
@@ -10617,7 +10617,7 @@
       <c r="O125" s="4">
         <v>0</v>
       </c>
-      <c r="P125" s="10">
+      <c r="P125" s="4">
         <v>0</v>
       </c>
       <c r="Q125" s="4"/>
@@ -10686,7 +10686,7 @@
       <c r="O126" s="4">
         <v>0</v>
       </c>
-      <c r="P126" s="10">
+      <c r="P126" s="4">
         <v>0</v>
       </c>
       <c r="Q126" s="4"/>
@@ -10749,7 +10749,7 @@
       <c r="O127" s="4">
         <v>0</v>
       </c>
-      <c r="P127" s="10">
+      <c r="P127" s="4">
         <v>0</v>
       </c>
       <c r="Q127" s="4"/>
@@ -10816,7 +10816,7 @@
       <c r="O128" s="4">
         <v>0</v>
       </c>
-      <c r="P128" s="10">
+      <c r="P128" s="4">
         <v>0</v>
       </c>
       <c r="Q128" s="4"/>
@@ -10885,7 +10885,7 @@
       <c r="O129" s="4">
         <v>400000</v>
       </c>
-      <c r="P129" s="10">
+      <c r="P129" s="4">
         <v>400000</v>
       </c>
       <c r="Q129" s="4"/>
@@ -10956,7 +10956,7 @@
       <c r="O130" s="4">
         <v>400000</v>
       </c>
-      <c r="P130" s="10">
+      <c r="P130" s="4">
         <v>400000</v>
       </c>
       <c r="Q130" s="4"/>
@@ -11019,7 +11019,7 @@
       <c r="O131" s="4">
         <v>0</v>
       </c>
-      <c r="P131" s="10">
+      <c r="P131" s="4">
         <v>0</v>
       </c>
       <c r="Q131" s="4"/>
@@ -11084,7 +11084,7 @@
       <c r="O132" s="4">
         <v>0</v>
       </c>
-      <c r="P132" s="10">
+      <c r="P132" s="4">
         <v>400000</v>
       </c>
       <c r="Q132" s="4"/>
@@ -11149,7 +11149,7 @@
       <c r="O133" s="4">
         <v>0</v>
       </c>
-      <c r="P133" s="10">
+      <c r="P133" s="4">
         <v>0</v>
       </c>
       <c r="Q133" s="4"/>
@@ -11212,7 +11212,7 @@
       <c r="O134" s="4">
         <v>0</v>
       </c>
-      <c r="P134" s="10">
+      <c r="P134" s="4">
         <v>0</v>
       </c>
       <c r="Q134" s="4"/>
@@ -11277,7 +11277,7 @@
       <c r="O135" s="4">
         <v>0</v>
       </c>
-      <c r="P135" s="10">
+      <c r="P135" s="4">
         <v>0</v>
       </c>
       <c r="Q135" s="4"/>
@@ -11344,7 +11344,7 @@
       <c r="O136" s="4">
         <v>0</v>
       </c>
-      <c r="P136" s="10">
+      <c r="P136" s="4">
         <v>0</v>
       </c>
       <c r="Q136" s="4"/>
@@ -11415,7 +11415,7 @@
       <c r="O137" s="4">
         <v>400000</v>
       </c>
-      <c r="P137" s="10">
+      <c r="P137" s="4">
         <v>400000</v>
       </c>
       <c r="Q137" s="4"/>
@@ -11480,7 +11480,7 @@
       <c r="O138" s="4">
         <v>0</v>
       </c>
-      <c r="P138" s="10">
+      <c r="P138" s="4">
         <v>0</v>
       </c>
       <c r="Q138" s="4"/>
@@ -11549,7 +11549,7 @@
       <c r="O139" s="4">
         <v>800000</v>
       </c>
-      <c r="P139" s="10">
+      <c r="P139" s="4">
         <v>800000</v>
       </c>
       <c r="Q139" s="4"/>
@@ -11612,7 +11612,7 @@
       <c r="O140" s="4">
         <v>0</v>
       </c>
-      <c r="P140" s="10">
+      <c r="P140" s="4">
         <v>0</v>
       </c>
       <c r="Q140" s="4"/>
@@ -11677,7 +11677,7 @@
       <c r="O141" s="4">
         <v>0</v>
       </c>
-      <c r="P141" s="10">
+      <c r="P141" s="4">
         <v>0</v>
       </c>
       <c r="Q141" s="4"/>
@@ -11740,7 +11740,7 @@
       <c r="O142" s="4">
         <v>400000</v>
       </c>
-      <c r="P142" s="10">
+      <c r="P142" s="4">
         <v>0</v>
       </c>
       <c r="Q142" s="4"/>
@@ -11807,7 +11807,7 @@
       <c r="O143" s="4">
         <v>0</v>
       </c>
-      <c r="P143" s="10">
+      <c r="P143" s="4">
         <v>0</v>
       </c>
       <c r="Q143" s="4"/>
@@ -11870,7 +11870,7 @@
       <c r="O144" s="4">
         <v>0</v>
       </c>
-      <c r="P144" s="10">
+      <c r="P144" s="4">
         <v>0</v>
       </c>
       <c r="Q144" s="4"/>
@@ -11933,7 +11933,7 @@
       <c r="O145" s="4">
         <v>0</v>
       </c>
-      <c r="P145" s="10">
+      <c r="P145" s="4">
         <v>0</v>
       </c>
       <c r="Q145" s="4"/>
@@ -12000,7 +12000,7 @@
       <c r="O146" s="4">
         <v>0</v>
       </c>
-      <c r="P146" s="10">
+      <c r="P146" s="4">
         <v>0</v>
       </c>
       <c r="Q146" s="4"/>
@@ -12063,7 +12063,7 @@
       <c r="O147" s="4">
         <v>0</v>
       </c>
-      <c r="P147" s="10">
+      <c r="P147" s="4">
         <v>0</v>
       </c>
       <c r="Q147" s="4"/>
@@ -12126,7 +12126,7 @@
       <c r="O148" s="4">
         <v>0</v>
       </c>
-      <c r="P148" s="10">
+      <c r="P148" s="4">
         <v>0</v>
       </c>
       <c r="Q148" s="4"/>
@@ -12193,7 +12193,7 @@
       <c r="O149" s="4">
         <v>0</v>
       </c>
-      <c r="P149" s="10">
+      <c r="P149" s="4">
         <v>400000</v>
       </c>
       <c r="Q149" s="4"/>
@@ -12256,7 +12256,7 @@
       <c r="O150" s="4">
         <v>0</v>
       </c>
-      <c r="P150" s="10">
+      <c r="P150" s="4">
         <v>0</v>
       </c>
       <c r="Q150" s="4"/>
@@ -12319,7 +12319,7 @@
       <c r="O151" s="4">
         <v>0</v>
       </c>
-      <c r="P151" s="10">
+      <c r="P151" s="4">
         <v>0</v>
       </c>
       <c r="Q151" s="4"/>
@@ -12382,7 +12382,7 @@
       <c r="O152" s="4">
         <v>0</v>
       </c>
-      <c r="P152" s="10">
+      <c r="P152" s="4">
         <v>0</v>
       </c>
       <c r="Q152" s="4"/>
@@ -12445,7 +12445,7 @@
       <c r="O153" s="4">
         <v>0</v>
       </c>
-      <c r="P153" s="10">
+      <c r="P153" s="4">
         <v>0</v>
       </c>
       <c r="Q153" s="4"/>
@@ -12512,7 +12512,7 @@
       <c r="O154" s="4">
         <v>100000</v>
       </c>
-      <c r="P154" s="10">
+      <c r="P154" s="4">
         <v>100000</v>
       </c>
       <c r="Q154" s="4"/>
@@ -12577,7 +12577,7 @@
       <c r="O155" s="4">
         <v>0</v>
       </c>
-      <c r="P155" s="10">
+      <c r="P155" s="4">
         <v>0</v>
       </c>
       <c r="Q155" s="4"/>
@@ -12644,7 +12644,7 @@
       <c r="O156" s="4">
         <v>0</v>
       </c>
-      <c r="P156" s="10">
+      <c r="P156" s="4">
         <v>0</v>
       </c>
       <c r="Q156" s="4"/>
@@ -12711,7 +12711,7 @@
       <c r="O157" s="4">
         <v>400000</v>
       </c>
-      <c r="P157" s="10">
+      <c r="P157" s="4">
         <v>0</v>
       </c>
       <c r="Q157" s="4"/>
@@ -12778,7 +12778,7 @@
       <c r="O158" s="4">
         <v>0</v>
       </c>
-      <c r="P158" s="10">
+      <c r="P158" s="4">
         <v>0</v>
       </c>
       <c r="Q158" s="4"/>
@@ -12843,7 +12843,7 @@
       <c r="O159" s="4">
         <v>140000</v>
       </c>
-      <c r="P159" s="10">
+      <c r="P159" s="4">
         <v>140000</v>
       </c>
       <c r="Q159" s="4"/>
@@ -12906,7 +12906,7 @@
       <c r="O160" s="4">
         <v>0</v>
       </c>
-      <c r="P160" s="10">
+      <c r="P160" s="4">
         <v>0</v>
       </c>
       <c r="Q160" s="4"/>
@@ -12971,7 +12971,7 @@
       <c r="O161" s="4">
         <v>0</v>
       </c>
-      <c r="P161" s="10">
+      <c r="P161" s="4">
         <v>0</v>
       </c>
       <c r="Q161" s="4"/>
@@ -13036,7 +13036,7 @@
       <c r="O162" s="4">
         <v>0</v>
       </c>
-      <c r="P162" s="10">
+      <c r="P162" s="4">
         <v>0</v>
       </c>
       <c r="Q162" s="4"/>
@@ -13103,7 +13103,7 @@
       <c r="O163" s="4">
         <v>800000</v>
       </c>
-      <c r="P163" s="10">
+      <c r="P163" s="4">
         <v>800000</v>
       </c>
       <c r="Q163" s="4"/>
@@ -13170,7 +13170,7 @@
       <c r="O164" s="4">
         <v>400000</v>
       </c>
-      <c r="P164" s="10">
+      <c r="P164" s="4">
         <v>0</v>
       </c>
       <c r="Q164" s="4"/>
@@ -13233,7 +13233,7 @@
       <c r="O165" s="4">
         <v>0</v>
       </c>
-      <c r="P165" s="10">
+      <c r="P165" s="4">
         <v>0</v>
       </c>
       <c r="Q165" s="4"/>
@@ -13300,7 +13300,7 @@
       <c r="O166" s="4">
         <v>400000</v>
       </c>
-      <c r="P166" s="10">
+      <c r="P166" s="4">
         <v>400000</v>
       </c>
       <c r="Q166" s="4"/>
@@ -13365,7 +13365,7 @@
       <c r="O167" s="4">
         <v>0</v>
       </c>
-      <c r="P167" s="10">
+      <c r="P167" s="4">
         <v>0</v>
       </c>
       <c r="Q167" s="4"/>
@@ -13430,7 +13430,7 @@
       <c r="O168" s="4">
         <v>0</v>
       </c>
-      <c r="P168" s="10">
+      <c r="P168" s="4">
         <v>0</v>
       </c>
       <c r="Q168" s="4"/>
@@ -13495,7 +13495,7 @@
       <c r="O169" s="4">
         <v>0</v>
       </c>
-      <c r="P169" s="10">
+      <c r="P169" s="4">
         <v>0</v>
       </c>
       <c r="Q169" s="4"/>
@@ -13560,7 +13560,7 @@
       <c r="O170" s="4">
         <v>0</v>
       </c>
-      <c r="P170" s="10">
+      <c r="P170" s="4">
         <v>0</v>
       </c>
       <c r="Q170" s="4"/>
@@ -13623,7 +13623,7 @@
       <c r="O171" s="4">
         <v>0</v>
       </c>
-      <c r="P171" s="10">
+      <c r="P171" s="4">
         <v>0</v>
       </c>
       <c r="Q171" s="4"/>
@@ -13690,7 +13690,7 @@
       <c r="O172" s="4">
         <v>2000000</v>
       </c>
-      <c r="P172" s="10">
+      <c r="P172" s="4">
         <v>0</v>
       </c>
       <c r="Q172" s="4"/>
@@ -13753,7 +13753,7 @@
       <c r="O173" s="4">
         <v>0</v>
       </c>
-      <c r="P173" s="10">
+      <c r="P173" s="4">
         <v>0</v>
       </c>
       <c r="Q173" s="4"/>
@@ -13816,7 +13816,7 @@
       <c r="O174" s="4">
         <v>800000</v>
       </c>
-      <c r="P174" s="10">
+      <c r="P174" s="4">
         <v>0</v>
       </c>
       <c r="Q174" s="4"/>
@@ -13881,7 +13881,7 @@
       <c r="O175" s="4">
         <v>0</v>
       </c>
-      <c r="P175" s="10">
+      <c r="P175" s="4">
         <v>0</v>
       </c>
       <c r="Q175" s="4"/>
@@ -13946,7 +13946,7 @@
       <c r="O176" s="4">
         <v>0</v>
       </c>
-      <c r="P176" s="10">
+      <c r="P176" s="4">
         <v>0</v>
       </c>
       <c r="Q176" s="4"/>
@@ -14013,7 +14013,7 @@
       <c r="O177" s="4">
         <v>400000</v>
       </c>
-      <c r="P177" s="10">
+      <c r="P177" s="4">
         <v>400000</v>
       </c>
       <c r="Q177" s="4"/>
@@ -14080,7 +14080,7 @@
       <c r="O178" s="4">
         <v>1400000</v>
       </c>
-      <c r="P178" s="10">
+      <c r="P178" s="4">
         <v>800000</v>
       </c>
       <c r="Q178" s="4"/>
@@ -14147,7 +14147,7 @@
       <c r="O179" s="4">
         <v>400000</v>
       </c>
-      <c r="P179" s="10">
+      <c r="P179" s="4">
         <v>400000</v>
       </c>
       <c r="Q179" s="4"/>
@@ -14214,7 +14214,7 @@
       <c r="O180" s="4">
         <v>800000</v>
       </c>
-      <c r="P180" s="10">
+      <c r="P180" s="4">
         <v>400000</v>
       </c>
       <c r="Q180" s="4"/>
@@ -14279,7 +14279,7 @@
       <c r="O181" s="4">
         <v>0</v>
       </c>
-      <c r="P181" s="10">
+      <c r="P181" s="4">
         <v>0</v>
       </c>
       <c r="Q181" s="4"/>
@@ -14346,7 +14346,7 @@
       <c r="O182" s="4">
         <v>0</v>
       </c>
-      <c r="P182" s="10">
+      <c r="P182" s="4">
         <v>400000</v>
       </c>
       <c r="Q182" s="4"/>
@@ -14409,7 +14409,7 @@
       <c r="O183" s="4">
         <v>0</v>
       </c>
-      <c r="P183" s="10">
+      <c r="P183" s="4">
         <v>0</v>
       </c>
       <c r="Q183" s="4"/>
@@ -14472,7 +14472,7 @@
       <c r="O184" s="4">
         <v>0</v>
       </c>
-      <c r="P184" s="10">
+      <c r="P184" s="4">
         <v>0</v>
       </c>
       <c r="Q184" s="4"/>
@@ -14535,7 +14535,7 @@
       <c r="O185" s="4">
         <v>0</v>
       </c>
-      <c r="P185" s="10">
+      <c r="P185" s="4">
         <v>0</v>
       </c>
       <c r="Q185" s="4"/>
@@ -14598,7 +14598,7 @@
       <c r="O186" s="4">
         <v>0</v>
       </c>
-      <c r="P186" s="10">
+      <c r="P186" s="4">
         <v>1300000</v>
       </c>
       <c r="Q186" s="4"/>
@@ -14665,7 +14665,7 @@
       <c r="O187" s="4">
         <v>400000</v>
       </c>
-      <c r="P187" s="10">
+      <c r="P187" s="4">
         <v>400000</v>
       </c>
       <c r="Q187" s="10"/>
@@ -14728,7 +14728,7 @@
       <c r="O188" s="4">
         <v>1000000</v>
       </c>
-      <c r="P188" s="10">
+      <c r="P188" s="4">
         <v>0</v>
       </c>
       <c r="Q188" s="10"/>
@@ -14793,7 +14793,7 @@
       <c r="O189" s="4">
         <v>0</v>
       </c>
-      <c r="P189" s="10">
+      <c r="P189" s="4">
         <v>0</v>
       </c>
       <c r="Q189" s="10"/>
@@ -14860,7 +14860,7 @@
       <c r="O190" s="4">
         <v>0</v>
       </c>
-      <c r="P190" s="10">
+      <c r="P190" s="4">
         <v>0</v>
       </c>
       <c r="Q190" s="10"/>
@@ -14927,7 +14927,7 @@
       <c r="O191" s="4">
         <v>0</v>
       </c>
-      <c r="P191" s="10">
+      <c r="P191" s="4">
         <v>0</v>
       </c>
       <c r="Q191" s="10"/>
@@ -14990,7 +14990,7 @@
       <c r="O192" s="4">
         <v>0</v>
       </c>
-      <c r="P192" s="10">
+      <c r="P192" s="4">
         <v>0</v>
       </c>
       <c r="Q192" s="10"/>
@@ -15057,7 +15057,7 @@
       <c r="O193" s="4">
         <v>0</v>
       </c>
-      <c r="P193" s="10">
+      <c r="P193" s="4">
         <v>0</v>
       </c>
       <c r="Q193" s="11"/>
@@ -15124,7 +15124,7 @@
       <c r="O194" s="4">
         <v>800000</v>
       </c>
-      <c r="P194" s="10">
+      <c r="P194" s="4">
         <v>800000</v>
       </c>
       <c r="Q194" s="11"/>
@@ -15187,7 +15187,7 @@
       <c r="O195" s="4">
         <v>0</v>
       </c>
-      <c r="P195" s="10">
+      <c r="P195" s="4">
         <v>0</v>
       </c>
       <c r="Q195" s="11"/>
@@ -15252,7 +15252,7 @@
       <c r="O196" s="4">
         <v>450000</v>
       </c>
-      <c r="P196" s="10">
+      <c r="P196" s="4">
         <v>0</v>
       </c>
       <c r="Q196" s="11"/>
@@ -15315,7 +15315,7 @@
       <c r="O197" s="4">
         <v>0</v>
       </c>
-      <c r="P197" s="10">
+      <c r="P197" s="4">
         <v>400000</v>
       </c>
       <c r="Q197" s="11"/>
@@ -15382,7 +15382,7 @@
       <c r="O198" s="4">
         <v>0</v>
       </c>
-      <c r="P198" s="10">
+      <c r="P198" s="4">
         <v>0</v>
       </c>
       <c r="Q198" s="11"/>
@@ -15449,7 +15449,7 @@
       <c r="O199" s="4">
         <v>0</v>
       </c>
-      <c r="P199" s="10">
+      <c r="P199" s="4">
         <v>0</v>
       </c>
       <c r="Q199" s="11"/>
@@ -15516,7 +15516,7 @@
       <c r="O200" s="4">
         <v>0</v>
       </c>
-      <c r="P200" s="10">
+      <c r="P200" s="4">
         <v>0</v>
       </c>
       <c r="Q200" s="11"/>
@@ -15579,7 +15579,7 @@
       <c r="O201" s="4">
         <v>500000</v>
       </c>
-      <c r="P201" s="10">
+      <c r="P201" s="4">
         <v>0</v>
       </c>
       <c r="Q201" s="11"/>
@@ -15642,7 +15642,7 @@
       <c r="O202" s="4">
         <v>0</v>
       </c>
-      <c r="P202" s="10">
+      <c r="P202" s="4">
         <v>0</v>
       </c>
       <c r="Q202" s="11"/>
@@ -15709,7 +15709,7 @@
       <c r="O203" s="4">
         <v>400000</v>
       </c>
-      <c r="P203" s="10">
+      <c r="P203" s="4">
         <v>0</v>
       </c>
       <c r="Q203" s="11"/>
@@ -15776,7 +15776,7 @@
       <c r="O204" s="4">
         <v>0</v>
       </c>
-      <c r="P204" s="10">
+      <c r="P204" s="4">
         <v>0</v>
       </c>
       <c r="Q204" s="11"/>
@@ -15839,7 +15839,7 @@
       <c r="O205" s="4">
         <v>0</v>
       </c>
-      <c r="P205" s="10">
+      <c r="P205" s="4">
         <v>0</v>
       </c>
       <c r="Q205" s="11"/>
@@ -15902,7 +15902,7 @@
       <c r="O206" s="4">
         <v>0</v>
       </c>
-      <c r="P206" s="10">
+      <c r="P206" s="4">
         <v>0</v>
       </c>
       <c r="Q206" s="11"/>
@@ -15969,7 +15969,7 @@
       <c r="O207" s="4">
         <v>1200000</v>
       </c>
-      <c r="P207" s="10">
+      <c r="P207" s="4">
         <v>0</v>
       </c>
       <c r="Q207" s="11"/>
@@ -16032,7 +16032,7 @@
       <c r="O208" s="4">
         <v>0</v>
       </c>
-      <c r="P208" s="10">
+      <c r="P208" s="4">
         <v>0</v>
       </c>
       <c r="Q208" s="11"/>
@@ -16101,7 +16101,7 @@
       <c r="O209" s="4">
         <v>0</v>
       </c>
-      <c r="P209" s="10">
+      <c r="P209" s="4">
         <v>0</v>
       </c>
       <c r="Q209" s="11"/>
@@ -16168,7 +16168,7 @@
       <c r="O210" s="4">
         <v>400000</v>
       </c>
-      <c r="P210" s="10">
+      <c r="P210" s="4">
         <v>0</v>
       </c>
       <c r="Q210" s="11"/>
@@ -16235,7 +16235,7 @@
       <c r="O211" s="4">
         <v>0</v>
       </c>
-      <c r="P211" s="10">
+      <c r="P211" s="4">
         <v>0</v>
       </c>
       <c r="Q211" s="11"/>
@@ -16302,7 +16302,7 @@
       <c r="O212" s="4">
         <v>0</v>
       </c>
-      <c r="P212" s="10">
+      <c r="P212" s="4">
         <v>0</v>
       </c>
       <c r="Q212" s="11"/>
@@ -16369,7 +16369,7 @@
       <c r="O213" s="4">
         <v>0</v>
       </c>
-      <c r="P213" s="10">
+      <c r="P213" s="4">
         <v>0</v>
       </c>
       <c r="Q213" s="11"/>
@@ -16436,7 +16436,7 @@
       <c r="O214" s="4">
         <v>0</v>
       </c>
-      <c r="P214" s="10">
+      <c r="P214" s="4">
         <v>0</v>
       </c>
       <c r="Q214" s="11"/>
@@ -16503,7 +16503,7 @@
       <c r="O215" s="4">
         <v>0</v>
       </c>
-      <c r="P215" s="10">
+      <c r="P215" s="4">
         <v>0</v>
       </c>
       <c r="Q215" s="11"/>
@@ -16570,7 +16570,7 @@
       <c r="O216" s="4">
         <v>0</v>
       </c>
-      <c r="P216" s="10">
+      <c r="P216" s="4">
         <v>0</v>
       </c>
       <c r="Q216" s="11"/>
@@ -16637,7 +16637,7 @@
       <c r="O217" s="4">
         <v>400000</v>
       </c>
-      <c r="P217" s="10">
+      <c r="P217" s="4">
         <v>400000</v>
       </c>
       <c r="Q217" s="11"/>
@@ -16704,7 +16704,7 @@
       <c r="O218" s="4">
         <v>400000</v>
       </c>
-      <c r="P218" s="10">
+      <c r="P218" s="4">
         <v>400000</v>
       </c>
       <c r="Q218" s="11"/>
@@ -16771,7 +16771,7 @@
       <c r="O219" s="4">
         <v>400000</v>
       </c>
-      <c r="P219" s="10">
+      <c r="P219" s="4">
         <v>400000</v>
       </c>
       <c r="Q219" s="11"/>
@@ -16838,7 +16838,7 @@
       <c r="O220" s="4">
         <v>0</v>
       </c>
-      <c r="P220" s="10">
+      <c r="P220" s="4">
         <v>0</v>
       </c>
       <c r="Q220" s="11"/>
@@ -16905,7 +16905,7 @@
       <c r="O221" s="4">
         <v>50000</v>
       </c>
-      <c r="P221" s="10">
+      <c r="P221" s="4">
         <v>30000</v>
       </c>
       <c r="Q221" s="11"/>
@@ -16972,7 +16972,7 @@
       <c r="O222" s="4">
         <v>0</v>
       </c>
-      <c r="P222" s="10">
+      <c r="P222" s="4">
         <v>0</v>
       </c>
       <c r="Q222" s="11"/>
@@ -17039,7 +17039,7 @@
       <c r="O223" s="4">
         <v>0</v>
       </c>
-      <c r="P223" s="10">
+      <c r="P223" s="4">
         <v>0</v>
       </c>
       <c r="Q223" s="11"/>
@@ -17106,7 +17106,7 @@
       <c r="O224" s="4">
         <v>0</v>
       </c>
-      <c r="P224" s="10">
+      <c r="P224" s="4">
         <v>400000</v>
       </c>
       <c r="Q224" s="11"/>
@@ -17173,7 +17173,7 @@
       <c r="O225" s="4">
         <v>0</v>
       </c>
-      <c r="P225" s="10">
+      <c r="P225" s="4">
         <v>0</v>
       </c>
       <c r="Q225" s="11"/>
@@ -17240,7 +17240,7 @@
       <c r="O226" s="4">
         <v>0</v>
       </c>
-      <c r="P226" s="10">
+      <c r="P226" s="4">
         <v>0</v>
       </c>
       <c r="Q226" s="11"/>
@@ -17307,7 +17307,7 @@
       <c r="O227" s="4">
         <v>0</v>
       </c>
-      <c r="P227" s="10">
+      <c r="P227" s="4">
         <v>0</v>
       </c>
       <c r="Q227" s="11"/>
@@ -17374,7 +17374,7 @@
       <c r="O228" s="4">
         <v>0</v>
       </c>
-      <c r="P228" s="10">
+      <c r="P228" s="4">
         <v>0</v>
       </c>
       <c r="Q228" s="11"/>
@@ -17441,7 +17441,7 @@
       <c r="O229" s="4">
         <v>0</v>
       </c>
-      <c r="P229" s="10">
+      <c r="P229" s="4">
         <v>0</v>
       </c>
       <c r="Q229" s="11"/>
@@ -17508,7 +17508,7 @@
       <c r="O230" s="4">
         <v>0</v>
       </c>
-      <c r="P230" s="10">
+      <c r="P230" s="4">
         <v>0</v>
       </c>
       <c r="Q230" s="11"/>
@@ -17575,7 +17575,7 @@
       <c r="O231" s="4">
         <v>0</v>
       </c>
-      <c r="P231" s="10">
+      <c r="P231" s="4">
         <v>0</v>
       </c>
       <c r="Q231" s="11"/>
@@ -17642,7 +17642,7 @@
       <c r="O232" s="4">
         <v>0</v>
       </c>
-      <c r="P232" s="10">
+      <c r="P232" s="4">
         <v>0</v>
       </c>
       <c r="Q232" s="11"/>
@@ -17709,7 +17709,7 @@
       <c r="O233" s="4">
         <v>0</v>
       </c>
-      <c r="P233" s="10">
+      <c r="P233" s="4">
         <v>0</v>
       </c>
       <c r="Q233" s="11"/>
@@ -17776,7 +17776,7 @@
       <c r="O234" s="4">
         <v>0</v>
       </c>
-      <c r="P234" s="10">
+      <c r="P234" s="4">
         <v>0</v>
       </c>
       <c r="Q234" s="11"/>
@@ -17843,7 +17843,7 @@
       <c r="O235" s="4">
         <v>0</v>
       </c>
-      <c r="P235" s="10">
+      <c r="P235" s="4">
         <v>0</v>
       </c>
       <c r="Q235" s="11"/>
@@ -17910,7 +17910,7 @@
       <c r="O236" s="4">
         <v>0</v>
       </c>
-      <c r="P236" s="10">
+      <c r="P236" s="4">
         <v>0</v>
       </c>
       <c r="Q236" s="11"/>
@@ -17977,7 +17977,7 @@
       <c r="O237" s="4">
         <v>0</v>
       </c>
-      <c r="P237" s="10">
+      <c r="P237" s="4">
         <v>0</v>
       </c>
       <c r="Q237" s="11"/>
@@ -18044,7 +18044,7 @@
       <c r="O238" s="4">
         <v>0</v>
       </c>
-      <c r="P238" s="10">
+      <c r="P238" s="4">
         <v>0</v>
       </c>
       <c r="Q238" s="11"/>
@@ -18111,7 +18111,7 @@
       <c r="O239" s="4">
         <v>0</v>
       </c>
-      <c r="P239" s="10">
+      <c r="P239" s="4">
         <v>0</v>
       </c>
       <c r="Q239" s="11"/>
@@ -18178,7 +18178,7 @@
       <c r="O240" s="4">
         <v>0</v>
       </c>
-      <c r="P240" s="10">
+      <c r="P240" s="4">
         <v>0</v>
       </c>
       <c r="Q240" s="11"/>
@@ -18245,7 +18245,7 @@
       <c r="O241" s="4">
         <v>0</v>
       </c>
-      <c r="P241" s="10">
+      <c r="P241" s="4">
         <v>0</v>
       </c>
       <c r="Q241" s="11"/>
@@ -18312,7 +18312,7 @@
       <c r="O242" s="4">
         <v>0</v>
       </c>
-      <c r="P242" s="10">
+      <c r="P242" s="4">
         <v>0</v>
       </c>
       <c r="Q242" s="11"/>
@@ -18379,7 +18379,7 @@
       <c r="O243" s="4">
         <v>0</v>
       </c>
-      <c r="P243" s="10">
+      <c r="P243" s="4">
         <v>0</v>
       </c>
       <c r="Q243" s="11"/>
@@ -18446,7 +18446,7 @@
       <c r="O244" s="4">
         <v>0</v>
       </c>
-      <c r="P244" s="10">
+      <c r="P244" s="4">
         <v>0</v>
       </c>
       <c r="Q244" s="11"/>
@@ -18513,7 +18513,7 @@
       <c r="O245" s="4">
         <v>0</v>
       </c>
-      <c r="P245" s="10">
+      <c r="P245" s="4">
         <v>0</v>
       </c>
       <c r="Q245" s="11"/>
@@ -18580,7 +18580,7 @@
       <c r="O246" s="4">
         <v>0</v>
       </c>
-      <c r="P246" s="10">
+      <c r="P246" s="4">
         <v>0</v>
       </c>
       <c r="Q246" s="11"/>
@@ -18647,7 +18647,7 @@
       <c r="O247" s="4">
         <v>0</v>
       </c>
-      <c r="P247" s="10">
+      <c r="P247" s="4">
         <v>0</v>
       </c>
       <c r="Q247" s="11"/>
@@ -18714,7 +18714,7 @@
       <c r="O248" s="4">
         <v>0</v>
       </c>
-      <c r="P248" s="10">
+      <c r="P248" s="4">
         <v>0</v>
       </c>
       <c r="Q248" s="11"/>
@@ -18781,7 +18781,7 @@
       <c r="O249" s="4">
         <v>0</v>
       </c>
-      <c r="P249" s="10">
+      <c r="P249" s="4">
         <v>0</v>
       </c>
       <c r="Q249" s="11"/>
@@ -18848,7 +18848,7 @@
       <c r="O250" s="4">
         <v>0</v>
       </c>
-      <c r="P250" s="10">
+      <c r="P250" s="4">
         <v>0</v>
       </c>
       <c r="Q250" s="11"/>
@@ -18915,7 +18915,7 @@
       <c r="O251" s="4">
         <v>0</v>
       </c>
-      <c r="P251" s="10">
+      <c r="P251" s="4">
         <v>0</v>
       </c>
       <c r="Q251" s="11"/>
@@ -18982,7 +18982,7 @@
       <c r="O252" s="4">
         <v>0</v>
       </c>
-      <c r="P252" s="10">
+      <c r="P252" s="4">
         <v>0</v>
       </c>
       <c r="Q252" s="11"/>
@@ -19049,7 +19049,7 @@
       <c r="O253" s="4">
         <v>0</v>
       </c>
-      <c r="P253" s="10">
+      <c r="P253" s="4">
         <v>0</v>
       </c>
       <c r="Q253" s="11"/>
@@ -19114,7 +19114,7 @@
       <c r="O254" s="4">
         <v>0</v>
       </c>
-      <c r="P254" s="10">
+      <c r="P254" s="4">
         <v>400000</v>
       </c>
       <c r="Q254" s="11"/>
@@ -19181,7 +19181,7 @@
       <c r="O255" s="4">
         <v>0</v>
       </c>
-      <c r="P255" s="10">
+      <c r="P255" s="4">
         <v>0</v>
       </c>
       <c r="Q255" s="11"/>
@@ -19250,7 +19250,7 @@
       <c r="O256" s="4">
         <v>450000</v>
       </c>
-      <c r="P256" s="10">
+      <c r="P256" s="4">
         <v>0</v>
       </c>
       <c r="Q256" s="11"/>
@@ -19319,7 +19319,7 @@
       <c r="O257" s="4">
         <v>400000</v>
       </c>
-      <c r="P257" s="10">
+      <c r="P257" s="4">
         <v>0</v>
       </c>
       <c r="Q257" s="11"/>
@@ -19386,7 +19386,7 @@
       <c r="O258" s="4">
         <v>0</v>
       </c>
-      <c r="P258" s="10">
+      <c r="P258" s="4">
         <v>0</v>
       </c>
       <c r="Q258" s="11"/>
@@ -19453,7 +19453,7 @@
       <c r="O259" s="4">
         <v>400000</v>
       </c>
-      <c r="P259" s="10">
+      <c r="P259" s="4">
         <v>0</v>
       </c>
       <c r="Q259" s="11"/>
@@ -19520,7 +19520,7 @@
       <c r="O260" s="4">
         <v>0</v>
       </c>
-      <c r="P260" s="10">
+      <c r="P260" s="4">
         <v>0</v>
       </c>
       <c r="Q260" s="11"/>
@@ -19587,7 +19587,7 @@
       <c r="O261" s="4">
         <v>0</v>
       </c>
-      <c r="P261" s="10">
+      <c r="P261" s="4">
         <v>0</v>
       </c>
       <c r="Q261" s="11"/>
@@ -19654,7 +19654,7 @@
       <c r="O262" s="4">
         <v>0</v>
       </c>
-      <c r="P262" s="10">
+      <c r="P262" s="4">
         <v>0</v>
       </c>
       <c r="Q262" s="11"/>
@@ -19721,7 +19721,7 @@
       <c r="O263" s="4">
         <v>0</v>
       </c>
-      <c r="P263" s="10">
+      <c r="P263" s="4">
         <v>0</v>
       </c>
       <c r="Q263" s="11"/>
@@ -19788,7 +19788,7 @@
       <c r="O264" s="4">
         <v>0</v>
       </c>
-      <c r="P264" s="10">
+      <c r="P264" s="4">
         <v>400000</v>
       </c>
       <c r="Q264" s="11"/>
@@ -19855,7 +19855,7 @@
       <c r="O265" s="4">
         <v>400000</v>
       </c>
-      <c r="P265" s="10">
+      <c r="P265" s="4">
         <v>400000</v>
       </c>
       <c r="Q265" s="11"/>
@@ -19920,7 +19920,7 @@
       <c r="O266" s="4">
         <v>0</v>
       </c>
-      <c r="P266" s="10">
+      <c r="P266" s="4">
         <v>0</v>
       </c>
       <c r="Q266" s="11"/>
@@ -19987,7 +19987,7 @@
       <c r="O267" s="4">
         <v>800000</v>
       </c>
-      <c r="P267" s="10">
+      <c r="P267" s="4">
         <v>800000</v>
       </c>
       <c r="Q267" s="11"/>
@@ -20050,7 +20050,7 @@
       <c r="O268" s="4">
         <v>0</v>
       </c>
-      <c r="P268" s="10">
+      <c r="P268" s="4">
         <v>0</v>
       </c>
       <c r="Q268" s="11"/>
@@ -20115,7 +20115,7 @@
       <c r="O269" s="4">
         <v>0</v>
       </c>
-      <c r="P269" s="10">
+      <c r="P269" s="4">
         <v>0</v>
       </c>
       <c r="Q269" s="11"/>
@@ -20182,7 +20182,7 @@
       <c r="O270" s="4">
         <v>400000</v>
       </c>
-      <c r="P270" s="10">
+      <c r="P270" s="4">
         <v>0</v>
       </c>
       <c r="Q270" s="11"/>
@@ -20249,7 +20249,7 @@
       <c r="O271" s="4">
         <v>0</v>
       </c>
-      <c r="P271" s="10">
+      <c r="P271" s="4">
         <v>0</v>
       </c>
       <c r="Q271" s="11"/>
@@ -20314,7 +20314,7 @@
       <c r="O272" s="4">
         <v>400000</v>
       </c>
-      <c r="P272" s="10">
+      <c r="P272" s="4">
         <v>0</v>
       </c>
       <c r="Q272" s="11"/>
@@ -20381,7 +20381,7 @@
       <c r="O273" s="4">
         <v>0</v>
       </c>
-      <c r="P273" s="10">
+      <c r="P273" s="4">
         <v>0</v>
       </c>
       <c r="Q273" s="11"/>
@@ -20446,7 +20446,7 @@
       <c r="O274" s="4">
         <v>0</v>
       </c>
-      <c r="P274" s="10">
+      <c r="P274" s="4">
         <v>0</v>
       </c>
       <c r="Q274" s="11"/>
@@ -20513,7 +20513,7 @@
       <c r="O275" s="4">
         <v>0</v>
       </c>
-      <c r="P275" s="10">
+      <c r="P275" s="4">
         <v>0</v>
       </c>
       <c r="Q275" s="11"/>
@@ -20580,7 +20580,7 @@
       <c r="O276" s="4">
         <v>200000</v>
       </c>
-      <c r="P276" s="10">
+      <c r="P276" s="4">
         <v>0</v>
       </c>
       <c r="Q276" s="11"/>
@@ -20647,7 +20647,7 @@
       <c r="O277" s="4">
         <v>150000</v>
       </c>
-      <c r="P277" s="10">
+      <c r="P277" s="4">
         <v>0</v>
       </c>
       <c r="Q277" s="11"/>
@@ -20712,7 +20712,7 @@
       <c r="O278" s="4">
         <v>0</v>
       </c>
-      <c r="P278" s="10">
+      <c r="P278" s="4">
         <v>0</v>
       </c>
       <c r="Q278" s="11"/>
@@ -20777,7 +20777,7 @@
       <c r="O279" s="4">
         <v>0</v>
       </c>
-      <c r="P279" s="10">
+      <c r="P279" s="4">
         <v>0</v>
       </c>
       <c r="Q279" s="11"/>
@@ -20840,7 +20840,7 @@
       <c r="O280" s="4">
         <v>0</v>
       </c>
-      <c r="P280" s="10">
+      <c r="P280" s="4">
         <v>0</v>
       </c>
       <c r="Q280" s="11"/>
@@ -20901,7 +20901,7 @@
       <c r="O281" s="4">
         <v>400000</v>
       </c>
-      <c r="P281" s="10">
+      <c r="P281" s="4">
         <v>0</v>
       </c>
       <c r="Q281" s="11"/>
@@ -20962,7 +20962,7 @@
       <c r="O282" s="4">
         <v>500000</v>
       </c>
-      <c r="P282" s="10">
+      <c r="P282" s="4">
         <v>0</v>
       </c>
       <c r="Q282" s="11"/>
@@ -21027,7 +21027,7 @@
       <c r="O283" s="4">
         <v>400000</v>
       </c>
-      <c r="P283" s="10">
+      <c r="P283" s="4">
         <v>400000</v>
       </c>
       <c r="Q283" s="11"/>
@@ -21088,7 +21088,7 @@
       <c r="O284" s="4">
         <v>0</v>
       </c>
-      <c r="P284" s="10">
+      <c r="P284" s="4">
         <v>0</v>
       </c>
       <c r="Q284" s="11"/>
@@ -21151,7 +21151,7 @@
       <c r="O285" s="4">
         <v>400000</v>
       </c>
-      <c r="P285" s="10">
+      <c r="P285" s="4">
         <v>0</v>
       </c>
       <c r="Q285" s="11"/>
@@ -21214,7 +21214,7 @@
       <c r="O286" s="4">
         <v>400000</v>
       </c>
-      <c r="P286" s="10">
+      <c r="P286" s="4">
         <v>0</v>
       </c>
       <c r="Q286" s="11"/>
@@ -21277,7 +21277,7 @@
       <c r="O287" s="4">
         <v>2000000</v>
       </c>
-      <c r="P287" s="10">
+      <c r="P287" s="4">
         <v>0</v>
       </c>
       <c r="Q287" s="11"/>
@@ -21340,7 +21340,7 @@
       <c r="O288" s="4">
         <v>400000</v>
       </c>
-      <c r="P288" s="10">
+      <c r="P288" s="4">
         <v>0</v>
       </c>
       <c r="Q288" s="11"/>
@@ -21403,7 +21403,7 @@
       <c r="O289" s="4">
         <v>400000</v>
       </c>
-      <c r="P289" s="10">
+      <c r="P289" s="4">
         <v>400000</v>
       </c>
       <c r="Q289" s="11"/>
@@ -21466,7 +21466,7 @@
       <c r="O290" s="4">
         <v>0</v>
       </c>
-      <c r="P290" s="10">
+      <c r="P290" s="4">
         <v>0</v>
       </c>
       <c r="Q290" s="11"/>
@@ -21533,7 +21533,7 @@
       <c r="O291" s="4">
         <v>200000</v>
       </c>
-      <c r="P291" s="10">
+      <c r="P291" s="4">
         <v>0</v>
       </c>
       <c r="Q291" s="11"/>
@@ -21598,7 +21598,7 @@
       <c r="O292" s="4">
         <v>400000</v>
       </c>
-      <c r="P292" s="10">
+      <c r="P292" s="4">
         <v>0</v>
       </c>
       <c r="Q292" s="11"/>
@@ -21661,7 +21661,7 @@
       <c r="O293" s="4">
         <v>400000</v>
       </c>
-      <c r="P293" s="10">
+      <c r="P293" s="4">
         <v>0</v>
       </c>
       <c r="Q293" s="11"/>
@@ -21724,7 +21724,7 @@
       <c r="O294" s="4">
         <v>0</v>
       </c>
-      <c r="P294" s="10">
+      <c r="P294" s="4">
         <v>0</v>
       </c>
       <c r="Q294" s="11"/>
@@ -21785,7 +21785,7 @@
       <c r="O295" s="4">
         <v>0</v>
       </c>
-      <c r="P295" s="10">
+      <c r="P295" s="4">
         <v>0</v>
       </c>
       <c r="Q295" s="11"/>
@@ -21850,7 +21850,7 @@
       <c r="O296" s="4">
         <v>0</v>
       </c>
-      <c r="P296" s="10">
+      <c r="P296" s="4">
         <v>0</v>
       </c>
       <c r="Q296" s="11"/>
@@ -21915,7 +21915,7 @@
       <c r="O297" s="4">
         <v>0</v>
       </c>
-      <c r="P297" s="10">
+      <c r="P297" s="4">
         <v>0</v>
       </c>
       <c r="Q297" s="11"/>
@@ -21976,7 +21976,7 @@
       <c r="O298" s="4">
         <v>0</v>
       </c>
-      <c r="P298" s="10">
+      <c r="P298" s="4">
         <v>0</v>
       </c>
       <c r="Q298" s="11"/>
@@ -22037,7 +22037,7 @@
       <c r="O299" s="4">
         <v>0</v>
       </c>
-      <c r="P299" s="10">
+      <c r="P299" s="4">
         <v>800000</v>
       </c>
       <c r="Q299" s="11"/>
@@ -22098,7 +22098,7 @@
       <c r="O300" s="4">
         <v>800000</v>
       </c>
-      <c r="P300" s="10">
+      <c r="P300" s="4">
         <v>0</v>
       </c>
       <c r="Q300" s="11"/>
@@ -22159,7 +22159,7 @@
       <c r="O301" s="4">
         <v>0</v>
       </c>
-      <c r="P301" s="10">
+      <c r="P301" s="4">
         <v>0</v>
       </c>
       <c r="Q301" s="11"/>
@@ -22222,7 +22222,7 @@
       <c r="O302" s="4">
         <v>50000</v>
       </c>
-      <c r="P302" s="10">
+      <c r="P302" s="4">
         <v>0</v>
       </c>
       <c r="Q302" s="11"/>
@@ -22287,7 +22287,7 @@
       <c r="O303" s="4">
         <v>0</v>
       </c>
-      <c r="P303" s="10">
+      <c r="P303" s="4">
         <v>0</v>
       </c>
       <c r="Q303" s="11"/>
@@ -22352,7 +22352,7 @@
       <c r="O304" s="4">
         <v>0</v>
       </c>
-      <c r="P304" s="10">
+      <c r="P304" s="4">
         <v>0</v>
       </c>
       <c r="Q304" s="11"/>
@@ -22415,7 +22415,7 @@
       <c r="O305" s="4">
         <v>0</v>
       </c>
-      <c r="P305" s="10">
+      <c r="P305" s="4">
         <v>0</v>
       </c>
       <c r="Q305" s="11"/>
@@ -22480,7 +22480,7 @@
       <c r="O306" s="4">
         <v>400000</v>
       </c>
-      <c r="P306" s="10">
+      <c r="P306" s="4">
         <v>0</v>
       </c>
       <c r="Q306" s="11"/>
@@ -22545,7 +22545,7 @@
       <c r="O307" s="4">
         <v>400000</v>
       </c>
-      <c r="P307" s="10">
+      <c r="P307" s="4">
         <v>400000</v>
       </c>
       <c r="Q307" s="11"/>
@@ -22610,7 +22610,7 @@
       <c r="O308" s="4">
         <v>0</v>
       </c>
-      <c r="P308" s="10">
+      <c r="P308" s="4">
         <v>400000</v>
       </c>
       <c r="Q308" s="11"/>
@@ -22673,7 +22673,7 @@
       <c r="O309" s="4">
         <v>795000</v>
       </c>
-      <c r="P309" s="10">
+      <c r="P309" s="4">
         <v>1120000</v>
       </c>
       <c r="Q309" s="11"/>
@@ -22738,7 +22738,7 @@
       <c r="O310" s="4">
         <v>400000</v>
       </c>
-      <c r="P310" s="10">
+      <c r="P310" s="4">
         <v>0</v>
       </c>
       <c r="Q310" s="11"/>
@@ -22801,7 +22801,7 @@
       <c r="O311" s="4">
         <v>400000</v>
       </c>
-      <c r="P311" s="10">
+      <c r="P311" s="4">
         <v>0</v>
       </c>
       <c r="Q311" s="11"/>
@@ -22862,7 +22862,7 @@
       <c r="O312" s="4">
         <v>0</v>
       </c>
-      <c r="P312" s="10">
+      <c r="P312" s="4">
         <v>0</v>
       </c>
       <c r="Q312" s="11"/>
@@ -22923,7 +22923,7 @@
       <c r="O313" s="4">
         <v>0</v>
       </c>
-      <c r="P313" s="10">
+      <c r="P313" s="4">
         <v>4800000</v>
       </c>
       <c r="Q313" s="11"/>
@@ -22984,7 +22984,7 @@
       <c r="O314" s="4">
         <v>400000</v>
       </c>
-      <c r="P314" s="10">
+      <c r="P314" s="4">
         <v>0</v>
       </c>
       <c r="Q314" s="11"/>
@@ -23045,7 +23045,7 @@
       <c r="O315" s="4">
         <v>0</v>
       </c>
-      <c r="P315" s="10">
+      <c r="P315" s="4">
         <v>0</v>
       </c>
       <c r="Q315" s="11"/>
@@ -23110,7 +23110,7 @@
       <c r="O316" s="4">
         <v>0</v>
       </c>
-      <c r="P316" s="10">
+      <c r="P316" s="4">
         <v>0</v>
       </c>
       <c r="Q316" s="11"/>
@@ -23171,7 +23171,7 @@
       <c r="O317" s="4">
         <v>0</v>
       </c>
-      <c r="P317" s="10">
+      <c r="P317" s="4">
         <v>0</v>
       </c>
       <c r="Q317" s="11"/>
@@ -23232,7 +23232,7 @@
       <c r="O318" s="4">
         <v>0</v>
       </c>
-      <c r="P318" s="10">
+      <c r="P318" s="4">
         <v>0</v>
       </c>
       <c r="Q318" s="11"/>
@@ -23293,7 +23293,7 @@
       <c r="O319" s="4">
         <v>0</v>
       </c>
-      <c r="P319" s="10">
+      <c r="P319" s="4">
         <v>0</v>
       </c>
       <c r="Q319" s="11"/>
@@ -23358,7 +23358,7 @@
       <c r="O320" s="4">
         <v>0</v>
       </c>
-      <c r="P320" s="10">
+      <c r="P320" s="4">
         <v>0</v>
       </c>
       <c r="Q320" s="11"/>
@@ -23419,7 +23419,7 @@
       <c r="O321" s="4">
         <v>0</v>
       </c>
-      <c r="P321" s="10">
+      <c r="P321" s="4">
         <v>0</v>
       </c>
       <c r="Q321" s="11"/>
@@ -23482,7 +23482,7 @@
       <c r="O322" s="4">
         <v>400000</v>
       </c>
-      <c r="P322" s="10">
+      <c r="P322" s="4">
         <v>0</v>
       </c>
       <c r="Q322" s="11"/>
@@ -23543,7 +23543,7 @@
       <c r="O323" s="4">
         <v>0</v>
       </c>
-      <c r="P323" s="10">
+      <c r="P323" s="4">
         <v>0</v>
       </c>
       <c r="Q323" s="11"/>
@@ -23604,7 +23604,7 @@
       <c r="O324" s="4">
         <v>0</v>
       </c>
-      <c r="P324" s="10">
+      <c r="P324" s="4">
         <v>0</v>
       </c>
       <c r="Q324" s="11"/>
@@ -23665,7 +23665,7 @@
       <c r="O325" s="4">
         <v>0</v>
       </c>
-      <c r="P325" s="10">
+      <c r="P325" s="4">
         <v>0</v>
       </c>
       <c r="Q325" s="11"/>
@@ -23730,7 +23730,7 @@
       <c r="O326" s="4">
         <v>0</v>
       </c>
-      <c r="P326" s="10">
+      <c r="P326" s="4">
         <v>0</v>
       </c>
       <c r="Q326" s="11"/>
@@ -23795,7 +23795,7 @@
       <c r="O327" s="4">
         <v>400000</v>
       </c>
-      <c r="P327" s="10">
+      <c r="P327" s="4">
         <v>0</v>
       </c>
       <c r="Q327" s="11"/>
@@ -23860,7 +23860,7 @@
       <c r="O328" s="4">
         <v>0</v>
       </c>
-      <c r="P328" s="10">
+      <c r="P328" s="4">
         <v>0</v>
       </c>
       <c r="Q328" s="11"/>
@@ -23923,7 +23923,7 @@
       <c r="O329" s="4">
         <v>400000</v>
       </c>
-      <c r="P329" s="10">
+      <c r="P329" s="4">
         <v>400000</v>
       </c>
       <c r="Q329" s="11"/>
@@ -23986,7 +23986,7 @@
       <c r="O330" s="4">
         <v>400000</v>
       </c>
-      <c r="P330" s="10">
+      <c r="P330" s="4">
         <v>400000</v>
       </c>
       <c r="Q330" s="11"/>
@@ -24049,7 +24049,7 @@
       <c r="O331" s="4">
         <v>100000</v>
       </c>
-      <c r="P331" s="10">
+      <c r="P331" s="4">
         <v>100000</v>
       </c>
       <c r="Q331" s="11"/>
@@ -24112,7 +24112,7 @@
       <c r="O332" s="4">
         <v>0</v>
       </c>
-      <c r="P332" s="10">
+      <c r="P332" s="4">
         <v>30000</v>
       </c>
       <c r="Q332" s="11"/>
@@ -24175,7 +24175,7 @@
       <c r="O333" s="4">
         <v>90000</v>
       </c>
-      <c r="P333" s="10">
+      <c r="P333" s="4">
         <v>50000</v>
       </c>
       <c r="Q333" s="11"/>
@@ -24240,7 +24240,7 @@
       <c r="O334" s="4">
         <v>0</v>
       </c>
-      <c r="P334" s="10">
+      <c r="P334" s="4">
         <v>0</v>
       </c>
       <c r="Q334" s="11"/>
@@ -24305,7 +24305,7 @@
       <c r="O335" s="4">
         <v>400000</v>
       </c>
-      <c r="P335" s="10">
+      <c r="P335" s="4">
         <v>0</v>
       </c>
       <c r="Q335" s="11"/>
@@ -24366,7 +24366,7 @@
       <c r="O336" s="4">
         <v>0</v>
       </c>
-      <c r="P336" s="10">
+      <c r="P336" s="4">
         <v>0</v>
       </c>
       <c r="Q336" s="11"/>
@@ -24431,7 +24431,7 @@
       <c r="O337" s="4">
         <v>0</v>
       </c>
-      <c r="P337" s="10">
+      <c r="P337" s="4">
         <v>0</v>
       </c>
       <c r="Q337" s="11"/>
@@ -24494,7 +24494,7 @@
       <c r="O338" s="4">
         <v>0</v>
       </c>
-      <c r="P338" s="10">
+      <c r="P338" s="4">
         <v>0</v>
       </c>
       <c r="Q338" s="11"/>
@@ -24559,7 +24559,7 @@
       <c r="O339" s="4">
         <v>0</v>
       </c>
-      <c r="P339" s="10">
+      <c r="P339" s="4">
         <v>0</v>
       </c>
       <c r="Q339" s="11"/>
@@ -24624,7 +24624,7 @@
       <c r="O340" s="4">
         <v>400000</v>
       </c>
-      <c r="P340" s="10">
+      <c r="P340" s="4">
         <v>0</v>
       </c>
       <c r="Q340" s="11"/>
@@ -24689,7 +24689,7 @@
       <c r="O341" s="4">
         <v>0</v>
       </c>
-      <c r="P341" s="10">
+      <c r="P341" s="4">
         <v>0</v>
       </c>
       <c r="Q341" s="11"/>
@@ -24754,7 +24754,7 @@
       <c r="O342" s="4">
         <v>0</v>
       </c>
-      <c r="P342" s="10">
+      <c r="P342" s="4">
         <v>0</v>
       </c>
       <c r="Q342" s="11"/>
@@ -24815,7 +24815,7 @@
       <c r="O343" s="4">
         <v>0</v>
       </c>
-      <c r="P343" s="10">
+      <c r="P343" s="4">
         <v>0</v>
       </c>
       <c r="Q343" s="11"/>
@@ -24876,7 +24876,7 @@
       <c r="O344" s="4">
         <v>400000</v>
       </c>
-      <c r="P344" s="10">
+      <c r="P344" s="4">
         <v>0</v>
       </c>
       <c r="Q344" s="11"/>
@@ -24941,7 +24941,7 @@
       <c r="O345" s="4">
         <v>0</v>
       </c>
-      <c r="P345" s="10">
+      <c r="P345" s="4">
         <v>0</v>
       </c>
       <c r="Q345" s="11"/>
@@ -25006,7 +25006,7 @@
       <c r="O346" s="4">
         <v>400000</v>
       </c>
-      <c r="P346" s="10">
+      <c r="P346" s="4">
         <v>0</v>
       </c>
       <c r="Q346" s="11"/>
@@ -25069,7 +25069,7 @@
       <c r="O347" s="4">
         <v>400000</v>
       </c>
-      <c r="P347" s="10">
+      <c r="P347" s="4">
         <v>0</v>
       </c>
       <c r="Q347" s="11"/>
@@ -25134,7 +25134,7 @@
       <c r="O348" s="4">
         <v>0</v>
       </c>
-      <c r="P348" s="10">
+      <c r="P348" s="4">
         <v>0</v>
       </c>
       <c r="Q348" s="11"/>
@@ -25195,7 +25195,7 @@
       <c r="O349" s="4">
         <v>800000</v>
       </c>
-      <c r="P349" s="10">
+      <c r="P349" s="4">
         <v>400000</v>
       </c>
       <c r="Q349" s="11"/>
@@ -25256,7 +25256,7 @@
       <c r="O350" s="4">
         <v>800000</v>
       </c>
-      <c r="P350" s="10">
+      <c r="P350" s="4">
         <v>0</v>
       </c>
       <c r="Q350" s="11"/>
@@ -25319,7 +25319,7 @@
       <c r="O351" s="4">
         <v>400000</v>
       </c>
-      <c r="P351" s="10">
+      <c r="P351" s="4">
         <v>0</v>
       </c>
       <c r="Q351" s="11"/>
@@ -25380,7 +25380,7 @@
       <c r="O352" s="4">
         <v>400000</v>
       </c>
-      <c r="P352" s="10">
+      <c r="P352" s="4">
         <v>0</v>
       </c>
       <c r="Q352" s="11"/>
@@ -25441,7 +25441,7 @@
       <c r="O353" s="4">
         <v>300000</v>
       </c>
-      <c r="P353" s="10">
+      <c r="P353" s="4">
         <v>0</v>
       </c>
       <c r="Q353" s="11"/>
@@ -25502,7 +25502,7 @@
       <c r="O354" s="4">
         <v>18359000</v>
       </c>
-      <c r="P354" s="10">
+      <c r="P354" s="4">
         <v>0</v>
       </c>
       <c r="Q354" s="11"/>
@@ -25563,7 +25563,7 @@
       <c r="O355" s="4">
         <v>8860000</v>
       </c>
-      <c r="P355" s="10">
+      <c r="P355" s="4">
         <v>0</v>
       </c>
       <c r="Q355" s="11"/>
@@ -25624,7 +25624,7 @@
       <c r="O356" s="4">
         <v>550000</v>
       </c>
-      <c r="P356" s="10">
+      <c r="P356" s="4">
         <v>0</v>
       </c>
       <c r="Q356" s="11"/>
@@ -25687,7 +25687,7 @@
       <c r="O357" s="4">
         <v>400000</v>
       </c>
-      <c r="P357" s="10">
+      <c r="P357" s="4">
         <v>0</v>
       </c>
       <c r="Q357" s="11"/>
@@ -25748,7 +25748,7 @@
       <c r="O358" s="4">
         <v>0</v>
       </c>
-      <c r="P358" s="11">
+      <c r="P358" s="4">
         <v>400000</v>
       </c>
       <c r="Q358" s="11"/>
@@ -25809,7 +25809,7 @@
       <c r="O359" s="4">
         <v>0</v>
       </c>
-      <c r="P359" s="11">
+      <c r="P359" s="4">
         <v>400000</v>
       </c>
       <c r="Q359" s="11"/>
@@ -25870,7 +25870,7 @@
       <c r="O360" s="4">
         <v>0</v>
       </c>
-      <c r="P360" s="11">
+      <c r="P360" s="4">
         <v>400000</v>
       </c>
       <c r="Q360" s="11"/>
@@ -25931,7 +25931,7 @@
       <c r="O361" s="4">
         <v>0</v>
       </c>
-      <c r="P361" s="11">
+      <c r="P361" s="4">
         <v>20000</v>
       </c>
       <c r="Q361" s="11"/>
@@ -25994,7 +25994,7 @@
       <c r="O362" s="4">
         <v>0</v>
       </c>
-      <c r="P362" s="11">
+      <c r="P362" s="4">
         <v>200000</v>
       </c>
       <c r="Q362" s="11"/>
@@ -26057,7 +26057,7 @@
       <c r="O363" s="4">
         <v>0</v>
       </c>
-      <c r="P363" s="11">
+      <c r="P363" s="4">
         <v>400000</v>
       </c>
       <c r="Q363" s="11"/>
@@ -26122,7 +26122,7 @@
       <c r="O364" s="4">
         <v>0</v>
       </c>
-      <c r="P364" s="11">
+      <c r="P364" s="4">
         <v>400000</v>
       </c>
       <c r="Q364" s="11"/>
@@ -26179,7 +26179,7 @@
       <c r="O365" s="4">
         <v>0</v>
       </c>
-      <c r="P365" s="11"/>
+      <c r="P365" s="4"/>
       <c r="Q365" s="11"/>
       <c r="R365" s="4"/>
       <c r="S365" s="4"/>
@@ -26234,7 +26234,7 @@
       <c r="O366" s="4">
         <v>0</v>
       </c>
-      <c r="P366" s="11"/>
+      <c r="P366" s="4"/>
       <c r="Q366" s="11"/>
       <c r="R366" s="4"/>
       <c r="S366" s="4"/>
@@ -26289,7 +26289,7 @@
       <c r="O367" s="4">
         <v>0</v>
       </c>
-      <c r="P367" s="11"/>
+      <c r="P367" s="4"/>
       <c r="Q367" s="11"/>
       <c r="R367" s="4"/>
       <c r="S367" s="4"/>
@@ -26344,7 +26344,7 @@
       <c r="O368" s="4">
         <v>0</v>
       </c>
-      <c r="P368" s="11"/>
+      <c r="P368" s="4"/>
       <c r="Q368" s="11"/>
       <c r="R368" s="4"/>
       <c r="S368" s="4"/>
@@ -26399,7 +26399,7 @@
       <c r="O369" s="4">
         <v>0</v>
       </c>
-      <c r="P369" s="11"/>
+      <c r="P369" s="4"/>
       <c r="Q369" s="11"/>
       <c r="R369" s="4"/>
       <c r="S369" s="4"/>
@@ -26454,7 +26454,7 @@
       <c r="O370" s="4">
         <v>0</v>
       </c>
-      <c r="P370" s="11"/>
+      <c r="P370" s="4"/>
       <c r="Q370" s="11"/>
       <c r="R370" s="4"/>
       <c r="S370" s="4"/>

--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA52D3B2-7233-414F-A47D-AE9E18E9BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2781119F-A8A5-4AAE-8ACD-FFB0C22F551F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
   <sheets>
     <sheet name="Base Inversionistas 26" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="598">
   <si>
     <t>NO.</t>
   </si>
@@ -281,9 +281,6 @@
     <t xml:space="preserve">IG. EN CORDOBA </t>
   </si>
   <si>
-    <t>Cordoba</t>
-  </si>
-  <si>
     <t>IG. EN CUCUTA GUSTAVO LEON</t>
   </si>
   <si>
@@ -404,9 +401,6 @@
     <t xml:space="preserve">IG. EN UBATE </t>
   </si>
   <si>
-    <t>Ubate</t>
-  </si>
-  <si>
     <t xml:space="preserve">IG. EN VALLEDUPAR </t>
   </si>
   <si>
@@ -1772,9 +1766,6 @@
     <t>IG. EN CHIQUINQUIRA</t>
   </si>
   <si>
-    <t>MONTERIA</t>
-  </si>
-  <si>
     <t>ABREGO</t>
   </si>
   <si>
@@ -1808,9 +1799,6 @@
     <t>MARLENY DEL SOCORRO MONSALVE</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>MAURICIO ALEJANDRO MERCHAN</t>
   </si>
   <si>
@@ -1836,6 +1824,15 @@
   </si>
   <si>
     <t>EMANUEL FLORES VALENCIA APOYO</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>MONTERÍA</t>
+  </si>
+  <si>
+    <t>SANTA LUCÍA</t>
   </si>
 </sst>
 </file>
@@ -2531,13 +2528,13 @@
         <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>5</v>
@@ -2552,7 +2549,7 @@
         <v>8</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>10</v>
@@ -2596,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C5" s="2">
         <v>9289920</v>
@@ -2666,14 +2663,14 @@
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="45">
         <v>200000</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>23</v>
@@ -2738,7 +2735,7 @@
         <v>100000</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>23</v>
@@ -2803,7 +2800,7 @@
         <v>2000000</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>23</v>
@@ -2872,7 +2869,7 @@
         <v>1100000</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>23</v>
@@ -3064,7 +3061,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="43">
@@ -3134,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>36</v>
@@ -3192,7 +3189,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F14" s="8">
         <v>3</v>
@@ -3201,7 +3198,7 @@
         <v>1600000</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>23</v>
@@ -3259,14 +3256,14 @@
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="45">
         <v>1500000</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>23</v>
@@ -3324,14 +3321,14 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="43">
         <v>2820000</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>23</v>
@@ -3398,7 +3395,7 @@
         <v>1000000</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>23</v>
@@ -3469,7 +3466,7 @@
         <v>6219000</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>23</v>
@@ -3536,7 +3533,7 @@
         <v>4800000</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>23</v>
@@ -3601,7 +3598,7 @@
         <v>5200000</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>23</v>
@@ -3663,14 +3660,14 @@
         <v>3160438302</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="43">
         <v>100000</v>
       </c>
       <c r="H21" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>23</v>
@@ -3737,7 +3734,7 @@
         <v>22900000</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>23</v>
@@ -3806,7 +3803,7 @@
         <v>800000</v>
       </c>
       <c r="H23" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>23</v>
@@ -3830,7 +3827,7 @@
         <v>4000000</v>
       </c>
       <c r="P23" s="4">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
@@ -3839,19 +3836,19 @@
       <c r="U23" s="4"/>
       <c r="V23" s="5">
         <f t="shared" si="0"/>
-        <v>12000000</v>
+        <v>13100000</v>
       </c>
       <c r="W23" s="6">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>32.75</v>
       </c>
       <c r="X23" s="6">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
@@ -3873,7 +3870,7 @@
         <v>1200000</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>23</v>
@@ -3931,14 +3928,14 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="43">
         <v>200000</v>
       </c>
       <c r="H25" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>23</v>
@@ -3996,14 +3993,14 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="43">
         <v>2400000</v>
       </c>
       <c r="H26" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>23</v>
@@ -4061,7 +4058,7 @@
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
@@ -4070,7 +4067,7 @@
         <v>4400000</v>
       </c>
       <c r="H27" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>23</v>
@@ -4137,7 +4134,7 @@
         <v>240000</v>
       </c>
       <c r="H28" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>23</v>
@@ -4204,7 +4201,7 @@
         <v>1000000</v>
       </c>
       <c r="H29" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>23</v>
@@ -4273,7 +4270,7 @@
         <v>100000</v>
       </c>
       <c r="H30" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>23</v>
@@ -4340,7 +4337,7 @@
         <v>10045000</v>
       </c>
       <c r="H31" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>23</v>
@@ -4409,7 +4406,7 @@
         <v>450000</v>
       </c>
       <c r="H32" s="43" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>23</v>
@@ -4433,7 +4430,7 @@
         <v>1200000</v>
       </c>
       <c r="P32" s="4">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
@@ -4442,19 +4439,19 @@
       <c r="U32" s="4"/>
       <c r="V32" s="5">
         <f t="shared" si="0"/>
-        <v>8200000</v>
+        <v>9400000</v>
       </c>
       <c r="W32" s="6">
         <f t="shared" si="1"/>
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="X32" s="6">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
@@ -4476,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="44" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>23</v>
@@ -4534,14 +4531,14 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="43">
         <v>400000</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>23</v>
@@ -4608,7 +4605,7 @@
         <v>21600000</v>
       </c>
       <c r="H35" s="46" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>23</v>
@@ -4677,7 +4674,7 @@
         <v>2200000</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>23</v>
@@ -4701,7 +4698,7 @@
         <v>3600000</v>
       </c>
       <c r="P36" s="4">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
@@ -4710,19 +4707,19 @@
       <c r="U36" s="4"/>
       <c r="V36" s="5">
         <f t="shared" si="0"/>
-        <v>23600000</v>
+        <v>27200000</v>
       </c>
       <c r="W36" s="6">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="X36" s="6">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
@@ -4744,7 +4741,7 @@
         <v>800000</v>
       </c>
       <c r="H37" s="46" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>23</v>
@@ -4813,7 +4810,7 @@
         <v>1200000</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>23</v>
@@ -4871,14 +4868,14 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="45">
         <v>4400000</v>
       </c>
       <c r="H39" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>23</v>
@@ -4947,7 +4944,7 @@
         <v>6000000</v>
       </c>
       <c r="H40" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>23</v>
@@ -5016,7 +5013,7 @@
         <v>4400000</v>
       </c>
       <c r="H41" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>23</v>
@@ -5085,7 +5082,7 @@
         <v>6522000</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>23</v>
@@ -5150,7 +5147,7 @@
         <v>20208000</v>
       </c>
       <c r="H43" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>23</v>
@@ -5219,7 +5216,7 @@
         <v>600000</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>23</v>
@@ -5277,7 +5274,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="43">
@@ -5344,7 +5341,7 @@
         <v>31844096518</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F46" s="2">
         <v>1</v>
@@ -5353,7 +5350,7 @@
         <v>4095000</v>
       </c>
       <c r="H46" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>23</v>
@@ -5420,7 +5417,7 @@
         <v>12937600</v>
       </c>
       <c r="H47" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>23</v>
@@ -5478,7 +5475,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="2" t="s">
-        <v>80</v>
+        <v>595</v>
       </c>
       <c r="F48" s="8">
         <v>1</v>
@@ -5487,7 +5484,7 @@
         <v>16940000</v>
       </c>
       <c r="H48" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>23</v>
@@ -5540,7 +5537,7 @@
         <v>46</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C49" s="8">
         <v>16354014</v>
@@ -5556,7 +5553,7 @@
         <v>2700000</v>
       </c>
       <c r="H49" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>23</v>
@@ -5609,19 +5606,19 @@
         <v>47</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="45">
         <v>16800000</v>
       </c>
       <c r="H50" s="44" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>23</v>
@@ -5674,7 +5671,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C51" s="8">
         <v>900299699</v>
@@ -5690,7 +5687,7 @@
         <v>220000</v>
       </c>
       <c r="H51" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>23</v>
@@ -5714,7 +5711,7 @@
         <v>800000</v>
       </c>
       <c r="P51" s="4">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
@@ -5723,19 +5720,19 @@
       <c r="U51" s="4"/>
       <c r="V51" s="5">
         <f t="shared" si="0"/>
-        <v>4800000</v>
+        <v>5600000</v>
       </c>
       <c r="W51" s="6">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X51" s="6">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y51" s="6">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
@@ -5743,19 +5740,19 @@
         <v>49</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="45">
         <v>13600000</v>
       </c>
       <c r="H52" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>23</v>
@@ -5808,7 +5805,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -5820,7 +5817,7 @@
         <v>3050000</v>
       </c>
       <c r="H53" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>23</v>
@@ -5873,19 +5870,19 @@
         <v>51</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="45">
         <v>9745000</v>
       </c>
       <c r="H54" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>23</v>
@@ -5938,7 +5935,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C55" s="2">
         <v>11809146</v>
@@ -5947,14 +5944,14 @@
         <v>3136811706</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="43">
         <v>1600000</v>
       </c>
       <c r="H55" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>23</v>
@@ -6007,12 +6004,12 @@
         <v>53</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F56" s="8">
         <v>1</v>
@@ -6021,7 +6018,7 @@
         <v>2285000</v>
       </c>
       <c r="H56" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>23</v>
@@ -6074,19 +6071,19 @@
         <v>54</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F57" s="8"/>
       <c r="G57" s="45">
         <v>2800000</v>
       </c>
       <c r="H57" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>23</v>
@@ -6139,7 +6136,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -6151,7 +6148,7 @@
         <v>9200000</v>
       </c>
       <c r="H58" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>23</v>
@@ -6204,19 +6201,19 @@
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="43">
         <v>11200000</v>
       </c>
       <c r="H59" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>23</v>
@@ -6240,7 +6237,7 @@
         <v>600000</v>
       </c>
       <c r="P59" s="4">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
@@ -6249,19 +6246,19 @@
       <c r="U59" s="4"/>
       <c r="V59" s="5">
         <f t="shared" si="0"/>
-        <v>3800000</v>
+        <v>7400000</v>
       </c>
       <c r="W59" s="6">
         <f t="shared" si="1"/>
-        <v>9.5</v>
+        <v>18.5</v>
       </c>
       <c r="X59" s="6">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y59" s="6">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
@@ -6269,14 +6266,14 @@
         <v>57</v>
       </c>
       <c r="B60" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F60" s="2">
         <v>2</v>
@@ -6285,7 +6282,7 @@
         <v>14800000</v>
       </c>
       <c r="H60" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>23</v>
@@ -6338,19 +6335,19 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="43">
         <v>2400000</v>
       </c>
       <c r="H61" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I61" s="3" t="s">
         <v>23</v>
@@ -6403,7 +6400,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C62" s="8">
         <v>900371129</v>
@@ -6412,14 +6409,14 @@
         <v>3216464514</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F62" s="8"/>
       <c r="G62" s="45">
         <v>440000</v>
       </c>
       <c r="H62" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>23</v>
@@ -6472,19 +6469,19 @@
         <v>60</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
       <c r="E63" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="45">
         <v>1250000</v>
       </c>
       <c r="H63" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>23</v>
@@ -6537,19 +6534,19 @@
         <v>61</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="45">
         <v>1400000</v>
       </c>
       <c r="H64" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>23</v>
@@ -6602,19 +6599,19 @@
         <v>62</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="45">
         <v>9524000</v>
       </c>
       <c r="H65" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>23</v>
@@ -6667,19 +6664,19 @@
         <v>63</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
       <c r="E66" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="45">
         <v>7266250</v>
       </c>
       <c r="H66" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>23</v>
@@ -6732,23 +6729,23 @@
         <v>64</v>
       </c>
       <c r="B67" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>114</v>
       </c>
       <c r="D67" s="8">
         <v>3233712038</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="45">
         <v>3645000</v>
       </c>
       <c r="H67" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>23</v>
@@ -6801,19 +6798,19 @@
         <v>65</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="45">
         <v>5704059</v>
       </c>
       <c r="H68" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>23</v>
@@ -6866,19 +6863,19 @@
         <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="43">
         <v>18700000</v>
       </c>
       <c r="H69" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>23</v>
@@ -6931,7 +6928,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C70" s="2">
         <v>900384157</v>
@@ -6940,14 +6937,14 @@
         <v>3103160465</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>121</v>
+        <v>304</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="43">
         <v>62180000</v>
       </c>
       <c r="H70" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>23</v>
@@ -7000,21 +6997,21 @@
         <v>68</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C71" s="2">
         <v>900406774</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="43">
         <v>2110000</v>
       </c>
       <c r="H71" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I71" s="3" t="s">
         <v>23</v>
@@ -7067,19 +7064,19 @@
         <v>69</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="45">
         <v>7580000</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>23</v>
@@ -7132,19 +7129,19 @@
         <v>70</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="43">
         <v>2800000</v>
       </c>
       <c r="H73" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>23</v>
@@ -7197,12 +7194,12 @@
         <v>71</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="43">
@@ -7260,12 +7257,12 @@
         <v>72</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="43">
@@ -7323,12 +7320,12 @@
         <v>73</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="43">
@@ -7357,7 +7354,7 @@
         <v>2400000</v>
       </c>
       <c r="P76" s="4">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="Q76" s="4"/>
       <c r="R76" s="4"/>
@@ -7366,19 +7363,19 @@
       <c r="U76" s="4"/>
       <c r="V76" s="5">
         <f t="shared" si="4"/>
-        <v>7200000</v>
+        <v>9600000</v>
       </c>
       <c r="W76" s="6">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="X76" s="6">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y76" s="6">
         <f t="shared" si="7"/>
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
@@ -7386,10 +7383,10 @@
         <v>74</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D77" s="2">
         <v>3222616473</v>
@@ -7404,7 +7401,7 @@
         <v>14000000</v>
       </c>
       <c r="H77" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>23</v>
@@ -7457,19 +7454,19 @@
         <v>75</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="43">
         <v>200000</v>
       </c>
       <c r="H78" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>23</v>
@@ -7522,7 +7519,7 @@
         <v>76</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -7536,7 +7533,7 @@
         <v>50000</v>
       </c>
       <c r="H79" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>23</v>
@@ -7589,7 +7586,7 @@
         <v>77</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -7601,7 +7598,7 @@
         <v>1762000</v>
       </c>
       <c r="H80" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>23</v>
@@ -7654,7 +7651,7 @@
         <v>78</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="8"/>
@@ -7666,7 +7663,7 @@
         <v>800000</v>
       </c>
       <c r="H81" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>23</v>
@@ -7719,7 +7716,7 @@
         <v>79</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
@@ -7731,7 +7728,7 @@
         <v>6000000</v>
       </c>
       <c r="H82" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>23</v>
@@ -7784,7 +7781,7 @@
         <v>80</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C83" s="2">
         <v>1093783625</v>
@@ -7800,7 +7797,7 @@
         <v>4240000</v>
       </c>
       <c r="H83" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>23</v>
@@ -7853,7 +7850,7 @@
         <v>81</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C84" s="8">
         <v>79477468</v>
@@ -7862,14 +7859,14 @@
         <v>3185861284</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F84" s="8"/>
       <c r="G84" s="45">
         <v>1300000</v>
       </c>
       <c r="H84" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>23</v>
@@ -7922,21 +7919,21 @@
         <v>82</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C85" s="2">
         <v>12135690</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="43">
         <v>420000</v>
       </c>
       <c r="H85" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>23</v>
@@ -7989,7 +7986,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -8001,7 +7998,7 @@
         <v>2000000</v>
       </c>
       <c r="H86" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>23</v>
@@ -8054,7 +8051,7 @@
         <v>84</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C87" s="2">
         <v>1128400756</v>
@@ -8063,7 +8060,7 @@
         <v>3043640493</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="43">
@@ -8121,12 +8118,12 @@
         <v>85</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
       <c r="E88" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F88" s="8">
         <v>2</v>
@@ -8135,7 +8132,7 @@
         <v>4300000</v>
       </c>
       <c r="H88" s="46" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>23</v>
@@ -8188,7 +8185,7 @@
         <v>86</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C89" s="8">
         <v>13838106</v>
@@ -8197,14 +8194,14 @@
         <v>3158359949</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F89" s="8"/>
       <c r="G89" s="45">
         <v>3600000</v>
       </c>
       <c r="H89" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>23</v>
@@ -8257,21 +8254,21 @@
         <v>87</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C90" s="8">
         <v>91249777</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F90" s="8"/>
       <c r="G90" s="45">
         <v>400000</v>
       </c>
       <c r="H90" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>23</v>
@@ -8324,19 +8321,19 @@
         <v>88</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="45">
         <v>860000</v>
       </c>
       <c r="H91" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>23</v>
@@ -8389,19 +8386,19 @@
         <v>89</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="43">
         <v>4140000</v>
       </c>
       <c r="H92" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>23</v>
@@ -8454,14 +8451,14 @@
         <v>90</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C93" s="2">
         <v>15374739</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F93" s="2">
         <v>1</v>
@@ -8470,7 +8467,7 @@
         <v>400000</v>
       </c>
       <c r="H93" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I93" s="3" t="s">
         <v>23</v>
@@ -8523,19 +8520,19 @@
         <v>91</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="43">
         <v>1600000</v>
       </c>
       <c r="H94" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>23</v>
@@ -8588,12 +8585,12 @@
         <v>92</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="9"/>
       <c r="E95" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F95" s="2">
         <v>1</v>
@@ -8602,7 +8599,7 @@
         <v>1600000</v>
       </c>
       <c r="H95" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>23</v>
@@ -8655,7 +8652,7 @@
         <v>93</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C96" s="8">
         <v>1077426534</v>
@@ -8664,14 +8661,14 @@
         <v>3113654554</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="45">
         <v>1200000</v>
       </c>
       <c r="H96" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>23</v>
@@ -8724,7 +8721,7 @@
         <v>94</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C97" s="8">
         <v>70326161</v>
@@ -8791,19 +8788,19 @@
         <v>95</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
       <c r="E98" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F98" s="8"/>
       <c r="G98" s="45">
         <v>8000000</v>
       </c>
       <c r="H98" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>23</v>
@@ -8856,7 +8853,7 @@
         <v>96</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C99" s="8">
         <v>77037962</v>
@@ -8865,14 +8862,14 @@
         <v>3108469718</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="45">
         <v>10000000</v>
       </c>
       <c r="H99" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>23</v>
@@ -8925,19 +8922,19 @@
         <v>97</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="43">
         <v>800000</v>
       </c>
       <c r="H100" s="43" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>23</v>
@@ -8990,12 +8987,12 @@
         <v>98</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F101" s="2">
         <v>3</v>
@@ -9004,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="44" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>23</v>
@@ -9057,19 +9054,19 @@
         <v>99</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="43">
         <v>800000</v>
       </c>
       <c r="H102" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>23</v>
@@ -9122,19 +9119,19 @@
         <v>100</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="43">
         <v>4000000</v>
       </c>
       <c r="H103" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I103" s="3" t="s">
         <v>23</v>
@@ -9187,7 +9184,7 @@
         <v>101</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C104" s="8">
         <v>1077424658</v>
@@ -9196,7 +9193,7 @@
         <v>3216464514</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F104" s="2">
         <v>2</v>
@@ -9205,7 +9202,7 @@
         <v>12800000</v>
       </c>
       <c r="H104" s="44" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I104" s="3" t="s">
         <v>23</v>
@@ -9258,7 +9255,7 @@
         <v>102</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -9292,7 +9289,7 @@
         <v>800000</v>
       </c>
       <c r="P105" s="4">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
@@ -9301,19 +9298,19 @@
       <c r="U105" s="4"/>
       <c r="V105" s="5">
         <f t="shared" si="4"/>
-        <v>4800000</v>
+        <v>5600000</v>
       </c>
       <c r="W105" s="6">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X105" s="6">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y105" s="6">
         <f t="shared" si="7"/>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.25">
@@ -9321,7 +9318,7 @@
         <v>103</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -9333,7 +9330,7 @@
         <v>200000</v>
       </c>
       <c r="H106" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>23</v>
@@ -9386,7 +9383,7 @@
         <v>104</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
@@ -9400,7 +9397,7 @@
         <v>2800000</v>
       </c>
       <c r="H107" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>23</v>
@@ -9453,7 +9450,7 @@
         <v>105</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -9465,7 +9462,7 @@
         <v>500000</v>
       </c>
       <c r="H108" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>23</v>
@@ -9518,7 +9515,7 @@
         <v>106</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
@@ -9581,7 +9578,7 @@
         <v>107</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C110" s="2">
         <v>35601610</v>
@@ -9590,14 +9587,14 @@
         <v>3207593131</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="43">
         <v>12000000</v>
       </c>
       <c r="H110" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I110" s="3" t="s">
         <v>23</v>
@@ -9650,23 +9647,23 @@
         <v>108</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C111" s="2">
         <v>1032464597</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="43">
         <v>4800000</v>
       </c>
       <c r="H111" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I111" s="3" t="s">
         <v>23</v>
@@ -9719,19 +9716,19 @@
         <v>109</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
       <c r="E112" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F112" s="8"/>
       <c r="G112" s="45">
         <v>2400000</v>
       </c>
       <c r="H112" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>23</v>
@@ -9784,23 +9781,23 @@
         <v>110</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C113" s="2">
         <v>70067417</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="43">
         <v>2390000</v>
       </c>
       <c r="H113" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>23</v>
@@ -9853,7 +9850,7 @@
         <v>111</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C114" s="2">
         <v>13837081</v>
@@ -9862,14 +9859,14 @@
         <v>3208026783</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="43">
         <v>3700000</v>
       </c>
       <c r="H114" s="44" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>23</v>
@@ -9922,7 +9919,7 @@
         <v>112</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
@@ -9985,19 +9982,19 @@
         <v>113</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
       <c r="E116" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F116" s="8"/>
       <c r="G116" s="45">
         <v>1800000</v>
       </c>
       <c r="H116" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>23</v>
@@ -10050,7 +10047,7 @@
         <v>114</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C117" s="8">
         <v>1065587738</v>
@@ -10066,7 +10063,7 @@
         <v>100000</v>
       </c>
       <c r="H117" s="46" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>23</v>
@@ -10119,7 +10116,7 @@
         <v>115</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
@@ -10131,7 +10128,7 @@
         <v>400000</v>
       </c>
       <c r="H118" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I118" s="3" t="s">
         <v>23</v>
@@ -10184,7 +10181,7 @@
         <v>116</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -10196,7 +10193,7 @@
         <v>4000000</v>
       </c>
       <c r="H119" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>23</v>
@@ -10249,7 +10246,7 @@
         <v>117</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C120" s="8">
         <v>38230483</v>
@@ -10258,7 +10255,7 @@
         <v>3104869126</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F120" s="2">
         <v>1</v>
@@ -10267,7 +10264,7 @@
         <v>10670000</v>
       </c>
       <c r="H120" s="44" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>23</v>
@@ -10320,7 +10317,7 @@
         <v>118</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -10332,7 +10329,7 @@
         <v>1200000</v>
       </c>
       <c r="H121" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>23</v>
@@ -10385,14 +10382,14 @@
         <v>119</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C122" s="8">
         <v>22579381</v>
       </c>
       <c r="D122" s="8"/>
       <c r="E122" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="43">
@@ -10450,7 +10447,7 @@
         <v>120</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C123" s="2">
         <v>32936225</v>
@@ -10459,7 +10456,7 @@
         <v>3215254487</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="43">
@@ -10517,19 +10514,19 @@
         <v>121</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="43">
         <v>850000</v>
       </c>
       <c r="H124" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>23</v>
@@ -10582,19 +10579,19 @@
         <v>122</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
       <c r="E125" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F125" s="8"/>
       <c r="G125" s="45">
         <v>1600000</v>
       </c>
       <c r="H125" s="46" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>23</v>
@@ -10647,7 +10644,7 @@
         <v>123</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C126" s="2">
         <v>11809146</v>
@@ -10656,14 +10653,14 @@
         <v>3136811706</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="43">
         <v>3900000</v>
       </c>
       <c r="H126" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>23</v>
@@ -10716,12 +10713,12 @@
         <v>124</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="43">
@@ -10779,12 +10776,12 @@
         <v>125</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
       <c r="E128" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F128" s="8">
         <v>1</v>
@@ -10793,7 +10790,7 @@
         <v>400000</v>
       </c>
       <c r="H128" s="46" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>23</v>
@@ -10846,7 +10843,7 @@
         <v>126</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C129" s="2">
         <v>8694441</v>
@@ -10862,7 +10859,7 @@
         <v>3200000</v>
       </c>
       <c r="H129" s="43" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>23</v>
@@ -10915,7 +10912,7 @@
         <v>127</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C130" s="8">
         <v>60380993</v>
@@ -10933,7 +10930,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="44" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>23</v>
@@ -10986,12 +10983,12 @@
         <v>128</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F131" s="2"/>
       <c r="G131" s="43">
@@ -11049,7 +11046,7 @@
         <v>129</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C132" s="8">
         <v>860606</v>
@@ -11114,7 +11111,7 @@
         <v>130</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -11126,7 +11123,7 @@
         <v>100000</v>
       </c>
       <c r="H133" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>23</v>
@@ -11179,12 +11176,12 @@
         <v>131</v>
       </c>
       <c r="B134" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
       <c r="E134" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F134" s="8"/>
       <c r="G134" s="45">
@@ -11242,7 +11239,7 @@
         <v>132</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -11254,7 +11251,7 @@
         <v>100000</v>
       </c>
       <c r="H135" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>23</v>
@@ -11307,7 +11304,7 @@
         <v>133</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -11321,7 +11318,7 @@
         <v>11300000</v>
       </c>
       <c r="H136" s="43" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>23</v>
@@ -11374,7 +11371,7 @@
         <v>134</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C137" s="2">
         <v>77187578</v>
@@ -11392,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="44" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>23</v>
@@ -11445,19 +11442,19 @@
         <v>135</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c r="E138" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F138" s="8"/>
       <c r="G138" s="45">
         <v>4000000</v>
       </c>
       <c r="H138" s="46" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>23</v>
@@ -11510,23 +11507,23 @@
         <v>136</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C139" s="2">
         <v>41679611</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F139" s="2"/>
       <c r="G139" s="43">
         <v>3000000</v>
       </c>
       <c r="H139" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>23</v>
@@ -11579,12 +11576,12 @@
         <v>137</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
       <c r="E140" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F140" s="8"/>
       <c r="G140" s="45">
@@ -11642,19 +11639,19 @@
         <v>138</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
       <c r="E141" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="43">
         <v>3600000</v>
       </c>
       <c r="H141" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>23</v>
@@ -11707,7 +11704,7 @@
         <v>139</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
@@ -11770,21 +11767,21 @@
         <v>140</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C143" s="8">
         <v>4517739</v>
       </c>
       <c r="D143" s="8"/>
       <c r="E143" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="43">
         <v>400000</v>
       </c>
       <c r="H143" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>23</v>
@@ -11837,12 +11834,12 @@
         <v>141</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="43">
@@ -11900,12 +11897,12 @@
         <v>142</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="43">
@@ -11963,12 +11960,12 @@
         <v>143</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -11977,7 +11974,7 @@
         <v>400000</v>
       </c>
       <c r="H146" s="44" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I146" s="3" t="s">
         <v>23</v>
@@ -12030,12 +12027,12 @@
         <v>144</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
       <c r="E147" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="43">
@@ -12093,7 +12090,7 @@
         <v>145</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -12156,7 +12153,7 @@
         <v>146</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C149" s="2">
         <v>1067849185</v>
@@ -12165,7 +12162,7 @@
         <v>3043721442</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F149" s="2"/>
       <c r="G149" s="43">
@@ -12223,12 +12220,12 @@
         <v>147</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="43">
@@ -12286,12 +12283,12 @@
         <v>148</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
       <c r="E151" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="43">
@@ -12349,12 +12346,12 @@
         <v>149</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
       <c r="E152" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="43">
@@ -12412,12 +12409,12 @@
         <v>150</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
       <c r="E153" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F153" s="2"/>
       <c r="G153" s="43">
@@ -12475,7 +12472,7 @@
         <v>151</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C154" s="2">
         <v>1044429200</v>
@@ -12484,7 +12481,7 @@
         <v>3008202508</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F154" s="2"/>
       <c r="G154" s="43">
@@ -12542,14 +12539,14 @@
         <v>152</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C155" s="12">
         <v>1067594389</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" s="43">
@@ -12607,7 +12604,7 @@
         <v>153</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C156" s="12">
         <v>11705775</v>
@@ -12616,7 +12613,7 @@
         <v>3127559027</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="43">
@@ -12674,7 +12671,7 @@
         <v>154</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C157" s="8">
         <v>1077437902</v>
@@ -12683,7 +12680,7 @@
         <v>3127867720</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" s="43">
@@ -12741,7 +12738,7 @@
         <v>155</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C158" s="8">
         <v>1003932453</v>
@@ -12750,7 +12747,7 @@
         <v>3226546627</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F158" s="2"/>
       <c r="G158" s="43">
@@ -12808,7 +12805,7 @@
         <v>156</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C159" s="8"/>
       <c r="D159" s="8">
@@ -12873,12 +12870,12 @@
         <v>157</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="8"/>
       <c r="E160" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F160" s="2"/>
       <c r="G160" s="43">
@@ -12936,14 +12933,14 @@
         <v>158</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C161" s="8">
         <v>60267661</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="43">
@@ -13001,14 +12998,14 @@
         <v>159</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C162" s="8">
         <v>39105075</v>
       </c>
       <c r="D162" s="8"/>
       <c r="E162" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="43">
@@ -13066,7 +13063,7 @@
         <v>160</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C163" s="8">
         <v>11785866</v>
@@ -13075,7 +13072,7 @@
         <v>3106178104</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F163" s="2"/>
       <c r="G163" s="43">
@@ -13133,7 +13130,7 @@
         <v>161</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C164" s="8">
         <v>45591667</v>
@@ -13171,7 +13168,7 @@
         <v>400000</v>
       </c>
       <c r="P164" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q164" s="4"/>
       <c r="R164" s="4"/>
@@ -13180,19 +13177,19 @@
       <c r="U164" s="4"/>
       <c r="V164" s="5">
         <f t="shared" si="8"/>
-        <v>1200000</v>
+        <v>1600000</v>
       </c>
       <c r="W164" s="6">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X164" s="6">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y164" s="6">
         <f t="shared" si="11"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:25" x14ac:dyDescent="0.25">
@@ -13200,12 +13197,12 @@
         <v>162</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F165" s="2"/>
       <c r="G165" s="2">
@@ -13263,7 +13260,7 @@
         <v>163</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C166" s="2">
         <v>88311237</v>
@@ -13330,14 +13327,14 @@
         <v>164</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C167" s="2">
         <v>109042290</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="2">
@@ -13395,14 +13392,14 @@
         <v>165</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C168" s="2">
         <v>10937503</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F168" s="2"/>
       <c r="G168" s="2">
@@ -13460,14 +13457,14 @@
         <v>166</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C169" s="2">
         <v>60442867</v>
       </c>
       <c r="D169" s="8"/>
       <c r="E169" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F169" s="2"/>
       <c r="G169" s="43">
@@ -13525,7 +13522,7 @@
         <v>167</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C170" s="8">
         <v>1090397309</v>
@@ -13590,12 +13587,12 @@
         <v>168</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c r="E171" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F171" s="2"/>
       <c r="G171" s="43">
@@ -13653,7 +13650,7 @@
         <v>169</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C172" s="8">
         <v>1093786204</v>
@@ -13720,12 +13717,12 @@
         <v>170</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F173" s="2"/>
       <c r="G173" s="43">
@@ -13783,12 +13780,12 @@
         <v>171</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c r="E174" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" s="43">
@@ -13846,14 +13843,14 @@
         <v>172</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C175" s="8">
         <v>79772077</v>
       </c>
       <c r="D175" s="8"/>
       <c r="E175" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="43">
@@ -13911,14 +13908,14 @@
         <v>173</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C176" s="8">
         <v>1093775115</v>
       </c>
       <c r="D176" s="8"/>
       <c r="E176" s="2" t="s">
-        <v>571</v>
+        <v>28</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="43">
@@ -13976,7 +13973,7 @@
         <v>174</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C177" s="8">
         <v>1048020150</v>
@@ -14043,7 +14040,7 @@
         <v>175</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C178" s="8">
         <v>1042767190</v>
@@ -14052,7 +14049,7 @@
         <v>3146496028</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" s="43">
@@ -14110,16 +14107,16 @@
         <v>176</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C179" s="8">
         <v>54252099</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" s="43">
@@ -14177,7 +14174,7 @@
         <v>177</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C180" s="8">
         <v>64543061</v>
@@ -14244,14 +14241,14 @@
         <v>178</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C181" s="8">
         <v>1128051565</v>
       </c>
       <c r="D181" s="8"/>
       <c r="E181" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" s="43">
@@ -14309,7 +14306,7 @@
         <v>179</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C182" s="8">
         <v>98533404</v>
@@ -14318,7 +14315,7 @@
         <v>3016089190</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" s="43">
@@ -14376,12 +14373,12 @@
         <v>180</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C183" s="8"/>
       <c r="D183" s="8"/>
       <c r="E183" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" s="43">
@@ -14439,12 +14436,12 @@
         <v>181</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C184" s="8"/>
       <c r="D184" s="8"/>
       <c r="E184" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="43">
@@ -14502,7 +14499,7 @@
         <v>182</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
@@ -14565,12 +14562,12 @@
         <v>183</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
       <c r="E186" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="43">
@@ -14628,7 +14625,7 @@
         <v>184</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C187" s="2">
         <v>39302237</v>
@@ -14637,7 +14634,7 @@
         <v>3187333883</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" s="43">
@@ -14695,12 +14692,12 @@
         <v>185</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C188" s="8"/>
       <c r="D188" s="8"/>
       <c r="E188" s="2" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F188" s="2"/>
       <c r="G188" s="43">
@@ -14758,14 +14755,14 @@
         <v>186</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C189" s="8">
         <v>49741498</v>
       </c>
       <c r="D189" s="8"/>
       <c r="E189" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="43">
@@ -14823,7 +14820,7 @@
         <v>187</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C190" s="8">
         <v>92257868</v>
@@ -14832,7 +14829,7 @@
         <v>3014216556</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F190" s="2"/>
       <c r="G190" s="43">
@@ -14890,7 +14887,7 @@
         <v>188</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C191" s="8">
         <v>12610911</v>
@@ -14899,7 +14896,7 @@
         <v>3102029563</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F191" s="2"/>
       <c r="G191" s="43">
@@ -14957,12 +14954,12 @@
         <v>189</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
       <c r="E192" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="43">
@@ -15020,7 +15017,7 @@
         <v>190</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C193" s="8">
         <v>1093795671</v>
@@ -15087,7 +15084,7 @@
         <v>191</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C194" s="8">
         <v>11794402</v>
@@ -15096,7 +15093,7 @@
         <v>3107027375</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="43">
@@ -15154,12 +15151,12 @@
         <v>192</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C195" s="8"/>
       <c r="D195" s="8"/>
       <c r="E195" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="43">
@@ -15217,14 +15214,14 @@
         <v>193</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C196" s="8">
         <v>22528383</v>
       </c>
       <c r="D196" s="8"/>
       <c r="E196" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F196" s="2"/>
       <c r="G196" s="43">
@@ -15282,7 +15279,7 @@
         <v>194</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C197" s="8"/>
       <c r="D197" s="8"/>
@@ -15345,7 +15342,7 @@
         <v>195</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C198" s="8">
         <v>37315263</v>
@@ -15412,7 +15409,7 @@
         <v>196</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C199" s="8">
         <v>1067960477</v>
@@ -15479,7 +15476,7 @@
         <v>197</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C200" s="8">
         <v>1091669219</v>
@@ -15546,12 +15543,12 @@
         <v>198</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
       <c r="E201" s="2" t="s">
-        <v>104</v>
+        <v>569</v>
       </c>
       <c r="F201" s="2"/>
       <c r="G201" s="43">
@@ -15609,12 +15606,12 @@
         <v>199</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
       <c r="E202" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F202" s="2"/>
       <c r="G202" s="43">
@@ -15672,7 +15669,7 @@
         <v>200</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C203" s="8">
         <v>52809513</v>
@@ -15681,7 +15678,7 @@
         <v>3053034243</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F203" s="2"/>
       <c r="G203" s="43">
@@ -15739,7 +15736,7 @@
         <v>201</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C204" s="8">
         <v>1091681333</v>
@@ -15748,7 +15745,7 @@
         <v>3158769403</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F204" s="2"/>
       <c r="G204" s="43">
@@ -15806,12 +15803,12 @@
         <v>202</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
       <c r="E205" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="43">
@@ -15869,12 +15866,12 @@
         <v>203</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
       <c r="E206" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F206" s="2"/>
       <c r="G206" s="43">
@@ -15932,10 +15929,10 @@
         <v>204</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D207" s="8">
         <v>3170295457</v>
@@ -15999,12 +15996,12 @@
         <v>205</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C208" s="8"/>
       <c r="D208" s="8"/>
       <c r="E208" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F208" s="2"/>
       <c r="G208" s="43">
@@ -16062,7 +16059,7 @@
         <v>206</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C209" s="8">
         <v>91175909</v>
@@ -16071,14 +16068,14 @@
         <v>3188566515</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F209" s="2"/>
       <c r="G209" s="43">
         <v>800000</v>
       </c>
       <c r="H209" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I209" s="3" t="s">
         <v>23</v>
@@ -16131,7 +16128,7 @@
         <v>207</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C210" s="8">
         <v>15517784</v>
@@ -16140,7 +16137,7 @@
         <v>3206175921</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F210" s="2"/>
       <c r="G210" s="43">
@@ -16198,7 +16195,7 @@
         <v>208</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C211" s="8">
         <v>1114884317</v>
@@ -16207,7 +16204,7 @@
         <v>3128481002</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="43">
@@ -16265,7 +16262,7 @@
         <v>209</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C212" s="8">
         <v>49742240</v>
@@ -16274,7 +16271,7 @@
         <v>3207260191</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="43">
@@ -16332,7 +16329,7 @@
         <v>210</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C213" s="8">
         <v>1143355775</v>
@@ -16341,7 +16338,7 @@
         <v>3042425180</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="43">
@@ -16399,7 +16396,7 @@
         <v>211</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C214" s="8">
         <v>1015997321</v>
@@ -16466,10 +16463,10 @@
         <v>212</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D215" s="8">
         <v>3115871915</v>
@@ -16533,7 +16530,7 @@
         <v>213</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C216" s="8">
         <v>1045737100</v>
@@ -16542,7 +16539,7 @@
         <v>3015184734</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="43">
@@ -16600,7 +16597,7 @@
         <v>214</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C217" s="8">
         <v>26258801</v>
@@ -16609,7 +16606,7 @@
         <v>3206877280</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="43">
@@ -16667,7 +16664,7 @@
         <v>215</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C218" s="8">
         <v>88309418</v>
@@ -16734,7 +16731,7 @@
         <v>216</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C219" s="8">
         <v>9093848</v>
@@ -16743,7 +16740,7 @@
         <v>3184909196</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="43">
@@ -16801,7 +16798,7 @@
         <v>217</v>
       </c>
       <c r="B220" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C220" s="8">
         <v>1053798897</v>
@@ -16810,7 +16807,7 @@
         <v>3142872429</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="43">
@@ -16868,7 +16865,7 @@
         <v>218</v>
       </c>
       <c r="B221" s="8" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C221" s="8">
         <v>32556538</v>
@@ -16877,7 +16874,7 @@
         <v>3108936691</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="43">
@@ -16935,7 +16932,7 @@
         <v>219</v>
       </c>
       <c r="B222" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C222" s="8">
         <v>28967914</v>
@@ -16944,7 +16941,7 @@
         <v>336684935</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="43">
@@ -17002,7 +16999,7 @@
         <v>220</v>
       </c>
       <c r="B223" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C223" s="8">
         <v>1094228628</v>
@@ -17069,7 +17066,7 @@
         <v>221</v>
       </c>
       <c r="B224" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C224" s="8">
         <v>88237561</v>
@@ -17136,16 +17133,16 @@
         <v>222</v>
       </c>
       <c r="B225" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D225" s="8">
         <v>3102212862</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="43">
@@ -17203,16 +17200,16 @@
         <v>223</v>
       </c>
       <c r="B226" s="8" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D226" s="8">
         <v>3173802748</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F226" s="2"/>
       <c r="G226" s="43">
@@ -17270,16 +17267,16 @@
         <v>224</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D227" s="8">
         <v>3174007835</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="43">
@@ -17337,16 +17334,16 @@
         <v>225</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D228" s="8">
         <v>3008286649</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F228" s="2"/>
       <c r="G228" s="43">
@@ -17404,16 +17401,16 @@
         <v>226</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D229" s="8">
         <v>3212079648</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F229" s="2"/>
       <c r="G229" s="43">
@@ -17471,16 +17468,16 @@
         <v>227</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D230" s="8">
         <v>3212648565</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F230" s="2"/>
       <c r="G230" s="43">
@@ -17538,16 +17535,16 @@
         <v>228</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D231" s="8">
         <v>3156601344</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="43">
@@ -17605,16 +17602,16 @@
         <v>229</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D232" s="8">
         <v>3114967016</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="43">
@@ -17672,16 +17669,16 @@
         <v>230</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D233" s="8">
         <v>3214289394</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="43">
@@ -17739,16 +17736,16 @@
         <v>231</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C234" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D234" s="8">
         <v>3214411717</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" s="43">
@@ -17806,16 +17803,16 @@
         <v>232</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C235" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D235" s="8">
         <v>3204014480</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="43">
@@ -17873,16 +17870,16 @@
         <v>233</v>
       </c>
       <c r="B236" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C236" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D236" s="8">
         <v>3114612778</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="43">
@@ -17940,7 +17937,7 @@
         <v>234</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C237" s="8">
         <v>85203032</v>
@@ -17949,7 +17946,7 @@
         <v>3107315557</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="43">
@@ -18007,7 +18004,7 @@
         <v>235</v>
       </c>
       <c r="B238" s="8" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C238" s="8">
         <v>1067904102</v>
@@ -18016,7 +18013,7 @@
         <v>3137896402</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="43">
@@ -18074,7 +18071,7 @@
         <v>236</v>
       </c>
       <c r="B239" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C239" s="8">
         <v>50901037</v>
@@ -18083,7 +18080,7 @@
         <v>3205707487</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="43">
@@ -18141,7 +18138,7 @@
         <v>237</v>
       </c>
       <c r="B240" s="8" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C240" s="8">
         <v>1002371747</v>
@@ -18150,7 +18147,7 @@
         <v>3017076403</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="43">
@@ -18208,7 +18205,7 @@
         <v>238</v>
       </c>
       <c r="B241" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C241" s="8">
         <v>1066737038</v>
@@ -18217,7 +18214,7 @@
         <v>3122228619</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="43">
@@ -18275,7 +18272,7 @@
         <v>239</v>
       </c>
       <c r="B242" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C242" s="8">
         <v>1064996539</v>
@@ -18284,7 +18281,7 @@
         <v>3135513063</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="43">
@@ -18342,7 +18339,7 @@
         <v>240</v>
       </c>
       <c r="B243" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C243" s="8">
         <v>1067884505</v>
@@ -18351,7 +18348,7 @@
         <v>3215857733</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="43">
@@ -18409,7 +18406,7 @@
         <v>241</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C244" s="8">
         <v>30777006</v>
@@ -18418,7 +18415,7 @@
         <v>3186436044</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="43">
@@ -18476,7 +18473,7 @@
         <v>242</v>
       </c>
       <c r="B245" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C245" s="8">
         <v>34962463</v>
@@ -18485,7 +18482,7 @@
         <v>3205294049</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="43">
@@ -18543,7 +18540,7 @@
         <v>243</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C246" s="8">
         <v>1067922782</v>
@@ -18552,7 +18549,7 @@
         <v>3013999279</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="43">
@@ -18610,7 +18607,7 @@
         <v>244</v>
       </c>
       <c r="B247" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C247" s="8">
         <v>1133795577</v>
@@ -18619,7 +18616,7 @@
         <v>3013994780</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="43">
@@ -18677,7 +18674,7 @@
         <v>245</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C248" s="8">
         <v>78753440</v>
@@ -18686,7 +18683,7 @@
         <v>3217473284</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="43">
@@ -18744,7 +18741,7 @@
         <v>246</v>
       </c>
       <c r="B249" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C249" s="8">
         <v>34979435</v>
@@ -18753,7 +18750,7 @@
         <v>3205025275</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="43">
@@ -18811,7 +18808,7 @@
         <v>247</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C250" s="8">
         <v>78323723</v>
@@ -18820,7 +18817,7 @@
         <v>3136913916</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="43">
@@ -18878,7 +18875,7 @@
         <v>248</v>
       </c>
       <c r="B251" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C251" s="8">
         <v>1003404028</v>
@@ -18887,7 +18884,7 @@
         <v>3205172305</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>577</v>
+        <v>596</v>
       </c>
       <c r="F251" s="2"/>
       <c r="G251" s="43">
@@ -18945,7 +18942,7 @@
         <v>249</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C252" s="8">
         <v>30843113</v>
@@ -18954,7 +18951,7 @@
         <v>3135249664</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="43">
@@ -19012,7 +19009,7 @@
         <v>250</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C253" s="8">
         <v>15647945</v>
@@ -19021,7 +19018,7 @@
         <v>3105193541</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F253" s="2"/>
       <c r="G253" s="43">
@@ -19079,14 +19076,14 @@
         <v>251</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C254" s="8">
         <v>1088296001</v>
       </c>
       <c r="D254" s="8"/>
       <c r="E254" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="43">
@@ -19144,7 +19141,7 @@
         <v>252</v>
       </c>
       <c r="B255" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C255" s="8">
         <v>60319496</v>
@@ -19211,7 +19208,7 @@
         <v>253</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C256" s="8">
         <v>1121969843</v>
@@ -19220,14 +19217,14 @@
         <v>3026352060</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="43">
         <v>800000</v>
       </c>
       <c r="H256" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I256" s="3" t="s">
         <v>23</v>
@@ -19280,7 +19277,7 @@
         <v>254</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C257" s="8">
         <v>70322335</v>
@@ -19289,14 +19286,14 @@
         <v>3106907142</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F257" s="2"/>
       <c r="G257" s="43">
         <v>400000</v>
       </c>
       <c r="H257" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I257" s="3" t="s">
         <v>23</v>
@@ -19349,7 +19346,7 @@
         <v>255</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C258" s="8">
         <v>72049339</v>
@@ -19358,7 +19355,7 @@
         <v>3148093554</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F258" s="2"/>
       <c r="G258" s="43">
@@ -19416,7 +19413,7 @@
         <v>256</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C259" s="8">
         <v>71273662</v>
@@ -19425,7 +19422,7 @@
         <v>3103476233</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="43">
@@ -19454,7 +19451,7 @@
         <v>400000</v>
       </c>
       <c r="P259" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q259" s="11"/>
       <c r="R259" s="4"/>
@@ -19463,19 +19460,19 @@
       <c r="U259" s="4"/>
       <c r="V259" s="5">
         <f t="shared" si="12"/>
-        <v>2000000</v>
+        <v>2400000</v>
       </c>
       <c r="W259" s="6">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X259" s="6">
         <f t="shared" si="14"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y259" s="6">
         <f t="shared" si="15"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260" spans="1:25" x14ac:dyDescent="0.25">
@@ -19483,7 +19480,7 @@
         <v>257</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C260" s="8">
         <v>64556783</v>
@@ -19492,7 +19489,7 @@
         <v>3017981102</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F260" s="2"/>
       <c r="G260" s="43">
@@ -19550,16 +19547,16 @@
         <v>258</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C261" s="8">
         <v>30771251</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F261" s="2"/>
       <c r="G261" s="43">
@@ -19617,16 +19614,16 @@
         <v>259</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C262" s="8">
         <v>45758051</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F262" s="2"/>
       <c r="G262" s="43">
@@ -19684,7 +19681,7 @@
         <v>260</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C263" s="8">
         <v>88137146</v>
@@ -19722,7 +19719,7 @@
         <v>0</v>
       </c>
       <c r="P263" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q263" s="11"/>
       <c r="R263" s="4"/>
@@ -19731,19 +19728,19 @@
       <c r="U263" s="4"/>
       <c r="V263" s="5">
         <f t="shared" si="16"/>
-        <v>1200000</v>
+        <v>1600000</v>
       </c>
       <c r="W263" s="6">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X263" s="6">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y263" s="6">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264" spans="1:25" x14ac:dyDescent="0.25">
@@ -19751,7 +19748,7 @@
         <v>261</v>
       </c>
       <c r="B264" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C264" s="8">
         <v>88284263</v>
@@ -19818,7 +19815,7 @@
         <v>262</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C265" s="8">
         <v>77179718</v>
@@ -19885,7 +19882,7 @@
         <v>263</v>
       </c>
       <c r="B266" s="8" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C266" s="8">
         <v>16354014</v>
@@ -19950,16 +19947,16 @@
         <v>264</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C267" s="8">
         <v>26257532</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="43">
@@ -20017,12 +20014,12 @@
         <v>265</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C268" s="8"/>
       <c r="D268" s="8"/>
       <c r="E268" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="43">
@@ -20080,14 +20077,14 @@
         <v>266</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C269" s="8">
         <v>72295408</v>
       </c>
       <c r="D269" s="8"/>
       <c r="E269" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F269" s="2"/>
       <c r="G269" s="43">
@@ -20145,7 +20142,7 @@
         <v>267</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C270" s="8">
         <v>3770607</v>
@@ -20154,7 +20151,7 @@
         <v>3126624361</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F270" s="2"/>
       <c r="G270" s="43">
@@ -20212,16 +20209,16 @@
         <v>268</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C271" s="8">
         <v>1075271930</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="43">
@@ -20279,7 +20276,7 @@
         <v>269</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C272" s="8">
         <v>1093789365</v>
@@ -20315,7 +20312,7 @@
         <v>400000</v>
       </c>
       <c r="P272" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q272" s="11"/>
       <c r="R272" s="4"/>
@@ -20324,19 +20321,19 @@
       <c r="U272" s="4"/>
       <c r="V272" s="5">
         <f t="shared" si="16"/>
-        <v>2000000</v>
+        <v>2400000</v>
       </c>
       <c r="W272" s="6">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X272" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y272" s="6">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="273" spans="1:25" x14ac:dyDescent="0.25">
@@ -20344,7 +20341,7 @@
         <v>270</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C273" s="8">
         <v>98552933</v>
@@ -20353,7 +20350,7 @@
         <v>3184873565</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="43">
@@ -20411,14 +20408,14 @@
         <v>271</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C274" s="8">
         <v>45758051</v>
       </c>
       <c r="D274" s="8"/>
       <c r="E274" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="43">
@@ -20476,7 +20473,7 @@
         <v>272</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C275" s="8">
         <v>1091662369</v>
@@ -20543,7 +20540,7 @@
         <v>273</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C276" s="8">
         <v>16071816</v>
@@ -20552,7 +20549,7 @@
         <v>3176880448</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="43">
@@ -20610,7 +20607,7 @@
         <v>274</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C277" s="8">
         <v>1122403315</v>
@@ -20619,7 +20616,7 @@
         <v>3135707447</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F277" s="2"/>
       <c r="G277" s="43">
@@ -20677,7 +20674,7 @@
         <v>275</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C278" s="8">
         <v>1090405714</v>
@@ -20742,14 +20739,14 @@
         <v>276</v>
       </c>
       <c r="B279" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C279" s="8">
         <v>15274598</v>
       </c>
       <c r="D279" s="8"/>
       <c r="E279" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F279" s="2"/>
       <c r="G279" s="43">
@@ -20807,12 +20804,12 @@
         <v>277</v>
       </c>
       <c r="B280" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C280" s="8"/>
       <c r="D280" s="8"/>
       <c r="E280" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="43">
@@ -20870,7 +20867,7 @@
         <v>278</v>
       </c>
       <c r="B281" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C281" s="8"/>
       <c r="D281" s="8"/>
@@ -20902,7 +20899,7 @@
         <v>400000</v>
       </c>
       <c r="P281" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q281" s="11"/>
       <c r="R281" s="4"/>
@@ -20911,19 +20908,19 @@
       <c r="U281" s="4"/>
       <c r="V281" s="5">
         <f t="shared" si="16"/>
-        <v>2000000</v>
+        <v>2400000</v>
       </c>
       <c r="W281" s="6">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X281" s="6">
         <f t="shared" si="18"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y281" s="6">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:25" x14ac:dyDescent="0.25">
@@ -20931,12 +20928,12 @@
         <v>279</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C282" s="8"/>
       <c r="D282" s="8"/>
       <c r="E282" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="43"/>
@@ -20992,7 +20989,7 @@
         <v>280</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C283" s="8">
         <v>42027224</v>
@@ -21001,7 +20998,7 @@
         <v>3137328174</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="43"/>
@@ -21057,7 +21054,7 @@
         <v>281</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C284" s="8"/>
       <c r="D284" s="8"/>
@@ -21118,7 +21115,7 @@
         <v>282</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C285" s="8"/>
       <c r="D285" s="8"/>
@@ -21181,7 +21178,7 @@
         <v>283</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C286" s="8">
         <v>1090399128</v>
@@ -21244,14 +21241,14 @@
         <v>284</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C287" s="8">
         <v>13923806</v>
       </c>
       <c r="D287" s="8"/>
       <c r="E287" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F287" s="2"/>
       <c r="G287" s="43"/>
@@ -21307,7 +21304,7 @@
         <v>285</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C288" s="8">
         <v>60300203</v>
@@ -21341,7 +21338,7 @@
         <v>400000</v>
       </c>
       <c r="P288" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q288" s="11"/>
       <c r="R288" s="4"/>
@@ -21350,19 +21347,19 @@
       <c r="U288" s="4"/>
       <c r="V288" s="5">
         <f t="shared" si="20"/>
-        <v>2000000</v>
+        <v>2400000</v>
       </c>
       <c r="W288" s="6">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X288" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y288" s="6">
         <f t="shared" si="19"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:25" x14ac:dyDescent="0.25">
@@ -21370,14 +21367,14 @@
         <v>286</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C289" s="8"/>
       <c r="D289" s="8">
         <v>3188566515</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F289" s="2"/>
       <c r="G289" s="43"/>
@@ -21433,7 +21430,7 @@
         <v>287</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C290" s="8">
         <v>10667593528</v>
@@ -21496,7 +21493,7 @@
         <v>288</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C291" s="8">
         <v>71630690</v>
@@ -21505,12 +21502,12 @@
         <v>3012567771</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F291" s="2"/>
       <c r="G291" s="43"/>
       <c r="H291" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I291" s="3" t="s">
         <v>23</v>
@@ -21563,19 +21560,19 @@
         <v>289</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C292" s="8"/>
       <c r="D292" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>589</v>
+        <v>425</v>
       </c>
       <c r="F292" s="2"/>
       <c r="G292" s="43"/>
       <c r="H292" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I292" s="3" t="s">
         <v>23</v>
@@ -21628,14 +21625,14 @@
         <v>290</v>
       </c>
       <c r="B293" s="8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C293" s="8"/>
       <c r="D293" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>589</v>
+        <v>425</v>
       </c>
       <c r="F293" s="2"/>
       <c r="G293" s="43"/>
@@ -21691,7 +21688,7 @@
         <v>291</v>
       </c>
       <c r="B294" s="8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C294" s="8">
         <v>1090381261</v>
@@ -21754,12 +21751,12 @@
         <v>292</v>
       </c>
       <c r="B295" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C295" s="8"/>
       <c r="D295" s="8"/>
       <c r="E295" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F295" s="2"/>
       <c r="G295" s="43"/>
@@ -21815,7 +21812,7 @@
         <v>293</v>
       </c>
       <c r="B296" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C296" s="8">
         <v>26331372</v>
@@ -21824,7 +21821,7 @@
         <v>3216248917</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F296" s="2"/>
       <c r="G296" s="43"/>
@@ -21880,7 +21877,7 @@
         <v>294</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C297" s="8">
         <v>50995836</v>
@@ -21889,7 +21886,7 @@
         <v>3106115579</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F297" s="2"/>
       <c r="G297" s="43"/>
@@ -21945,7 +21942,7 @@
         <v>295</v>
       </c>
       <c r="B298" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C298" s="8"/>
       <c r="D298" s="8"/>
@@ -22006,12 +22003,12 @@
         <v>296</v>
       </c>
       <c r="B299" s="8" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C299" s="8"/>
       <c r="D299" s="8"/>
       <c r="E299" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F299" s="2"/>
       <c r="G299" s="43"/>
@@ -22067,7 +22064,7 @@
         <v>297</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C300" s="8"/>
       <c r="D300" s="8"/>
@@ -22128,12 +22125,12 @@
         <v>298</v>
       </c>
       <c r="B301" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C301" s="8"/>
       <c r="D301" s="8"/>
       <c r="E301" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F301" s="2"/>
       <c r="G301" s="43"/>
@@ -22189,14 +22186,14 @@
         <v>299</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C302" s="8">
         <v>32555373</v>
       </c>
       <c r="D302" s="8"/>
       <c r="E302" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="43"/>
@@ -22252,7 +22249,7 @@
         <v>300</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C303" s="8">
         <v>1143849172</v>
@@ -22261,7 +22258,7 @@
         <v>3182304776</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F303" s="2"/>
       <c r="G303" s="43"/>
@@ -22317,7 +22314,7 @@
         <v>301</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C304" s="8">
         <v>1003932454</v>
@@ -22382,14 +22379,14 @@
         <v>302</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C305" s="8">
         <v>1006365217</v>
       </c>
       <c r="D305" s="8"/>
       <c r="E305" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="43"/>
@@ -22445,7 +22442,7 @@
         <v>303</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C306" s="8">
         <v>1017157887</v>
@@ -22510,7 +22507,7 @@
         <v>304</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C307" s="8">
         <v>43679785</v>
@@ -22519,7 +22516,7 @@
         <v>3146218974</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F307" s="2"/>
       <c r="G307" s="43"/>
@@ -22575,7 +22572,7 @@
         <v>305</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C308" s="8">
         <v>11811323</v>
@@ -22584,7 +22581,7 @@
         <v>3202786408</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F308" s="2"/>
       <c r="G308" s="43"/>
@@ -22640,7 +22637,7 @@
         <v>306</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C309" s="8"/>
       <c r="D309" s="8"/>
@@ -22650,7 +22647,7 @@
       <c r="F309" s="2"/>
       <c r="G309" s="43"/>
       <c r="H309" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I309" s="3" t="s">
         <v>23</v>
@@ -22703,19 +22700,19 @@
         <v>307</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C310" s="8"/>
       <c r="D310" s="8" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F310" s="2"/>
       <c r="G310" s="43"/>
       <c r="H310" s="44" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I310" s="3" t="s">
         <v>23</v>
@@ -22768,14 +22765,14 @@
         <v>308</v>
       </c>
       <c r="B311" s="8" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C311" s="8"/>
       <c r="D311" s="8" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F311" s="2"/>
       <c r="G311" s="43"/>
@@ -22831,12 +22828,12 @@
         <v>309</v>
       </c>
       <c r="B312" s="8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C312" s="8"/>
       <c r="D312" s="8"/>
       <c r="E312" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F312" s="2"/>
       <c r="G312" s="43"/>
@@ -22892,7 +22889,7 @@
         <v>310</v>
       </c>
       <c r="B313" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C313" s="8"/>
       <c r="D313" s="8"/>
@@ -22953,7 +22950,7 @@
         <v>311</v>
       </c>
       <c r="B314" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C314" s="8"/>
       <c r="D314" s="8"/>
@@ -23014,7 +23011,7 @@
         <v>312</v>
       </c>
       <c r="B315" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C315" s="8"/>
       <c r="D315" s="8"/>
@@ -23075,7 +23072,7 @@
         <v>313</v>
       </c>
       <c r="B316" s="8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C316" s="8">
         <v>1092730946</v>
@@ -23140,12 +23137,12 @@
         <v>314</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C317" s="8"/>
       <c r="D317" s="8"/>
       <c r="E317" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F317" s="2"/>
       <c r="G317" s="43"/>
@@ -23201,12 +23198,12 @@
         <v>315</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C318" s="8"/>
       <c r="D318" s="8"/>
       <c r="E318" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F318" s="2"/>
       <c r="G318" s="43"/>
@@ -23262,12 +23259,12 @@
         <v>316</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C319" s="8"/>
       <c r="D319" s="8"/>
       <c r="E319" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F319" s="2"/>
       <c r="G319" s="43"/>
@@ -23323,7 +23320,7 @@
         <v>317</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C320" s="8">
         <v>1036943880</v>
@@ -23332,7 +23329,7 @@
         <v>3218969540</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F320" s="2"/>
       <c r="G320" s="43"/>
@@ -23388,7 +23385,7 @@
         <v>318</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C321" s="8"/>
       <c r="D321" s="8"/>
@@ -23449,14 +23446,14 @@
         <v>319</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C322" s="8">
         <v>1075304981</v>
       </c>
       <c r="D322" s="8"/>
       <c r="E322" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F322" s="2"/>
       <c r="G322" s="43"/>
@@ -23512,7 +23509,7 @@
         <v>320</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C323" s="8"/>
       <c r="D323" s="8"/>
@@ -23573,12 +23570,12 @@
         <v>321</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C324" s="8"/>
       <c r="D324" s="8"/>
       <c r="E324" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F324" s="2"/>
       <c r="G324" s="43"/>
@@ -23634,12 +23631,12 @@
         <v>322</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C325" s="8"/>
       <c r="D325" s="8"/>
       <c r="E325" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F325" s="2"/>
       <c r="G325" s="43"/>
@@ -23695,7 +23692,7 @@
         <v>323</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C326" s="8">
         <v>43868812</v>
@@ -23704,7 +23701,7 @@
         <v>3148927758</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F326" s="2"/>
       <c r="G326" s="43"/>
@@ -23760,7 +23757,7 @@
         <v>324</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C327" s="8">
         <v>19308428</v>
@@ -23769,7 +23766,7 @@
         <v>3113742824</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F327" s="2"/>
       <c r="G327" s="43"/>
@@ -23825,7 +23822,7 @@
         <v>325</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C328" s="8">
         <v>32491394</v>
@@ -23834,7 +23831,7 @@
         <v>3147816504</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F328" s="2"/>
       <c r="G328" s="43"/>
@@ -23890,14 +23887,14 @@
         <v>326</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C329" s="8">
         <v>72268623</v>
       </c>
       <c r="D329" s="8"/>
       <c r="E329" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F329" s="2"/>
       <c r="G329" s="43"/>
@@ -23953,14 +23950,14 @@
         <v>327</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C330" s="8">
         <v>72309365</v>
       </c>
       <c r="D330" s="8"/>
       <c r="E330" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="43"/>
@@ -24016,14 +24013,14 @@
         <v>328</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C331" s="8">
         <v>32686445</v>
       </c>
       <c r="D331" s="8"/>
       <c r="E331" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F331" s="2"/>
       <c r="G331" s="43"/>
@@ -24079,14 +24076,14 @@
         <v>329</v>
       </c>
       <c r="B332" s="8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C332" s="8">
         <v>72309256</v>
       </c>
       <c r="D332" s="8"/>
       <c r="E332" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F332" s="2"/>
       <c r="G332" s="43"/>
@@ -24142,14 +24139,14 @@
         <v>330</v>
       </c>
       <c r="B333" s="8" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C333" s="8">
         <v>1044427553</v>
       </c>
       <c r="D333" s="8"/>
       <c r="E333" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F333" s="2"/>
       <c r="G333" s="43"/>
@@ -24205,7 +24202,7 @@
         <v>331</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C334" s="8">
         <v>26030830</v>
@@ -24270,7 +24267,7 @@
         <v>332</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C335" s="8">
         <v>88269622</v>
@@ -24279,7 +24276,7 @@
         <v>3135768027</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F335" s="2"/>
       <c r="G335" s="43"/>
@@ -24335,12 +24332,12 @@
         <v>333</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C336" s="8"/>
       <c r="D336" s="8"/>
       <c r="E336" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F336" s="2"/>
       <c r="G336" s="43"/>
@@ -24396,7 +24393,7 @@
         <v>334</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C337" s="8">
         <v>27705490</v>
@@ -24461,14 +24458,14 @@
         <v>335</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C338" s="8">
         <v>72193575</v>
       </c>
       <c r="D338" s="8"/>
       <c r="E338" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F338" s="2"/>
       <c r="G338" s="43"/>
@@ -24524,7 +24521,7 @@
         <v>336</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C339" s="8">
         <v>1144057934</v>
@@ -24589,7 +24586,7 @@
         <v>337</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C340" s="8">
         <v>16784811</v>
@@ -24598,7 +24595,7 @@
         <v>3232388033</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F340" s="2"/>
       <c r="G340" s="43"/>
@@ -24654,7 +24651,7 @@
         <v>338</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C341" s="8">
         <v>34500768</v>
@@ -24663,7 +24660,7 @@
         <v>3136589048</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F341" s="2"/>
       <c r="G341" s="43"/>
@@ -24719,7 +24716,7 @@
         <v>339</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C342" s="8">
         <v>22579381</v>
@@ -24728,7 +24725,7 @@
         <v>3006140088</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="43"/>
@@ -24784,12 +24781,12 @@
         <v>340</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C343" s="8"/>
       <c r="D343" s="8"/>
       <c r="E343" s="2" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="F343" s="2"/>
       <c r="G343" s="43"/>
@@ -24845,7 +24842,7 @@
         <v>341</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C344" s="8"/>
       <c r="D344" s="8"/>
@@ -24906,7 +24903,7 @@
         <v>342</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C345" s="8">
         <v>10017038</v>
@@ -24915,7 +24912,7 @@
         <v>3154427396</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F345" s="2"/>
       <c r="G345" s="43"/>
@@ -24971,7 +24968,7 @@
         <v>343</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C346" s="8">
         <v>13873577</v>
@@ -24980,7 +24977,7 @@
         <v>3184381905</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F346" s="2"/>
       <c r="G346" s="43"/>
@@ -25036,14 +25033,14 @@
         <v>344</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C347" s="8">
         <v>13520281</v>
       </c>
       <c r="D347" s="8"/>
       <c r="E347" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F347" s="2"/>
       <c r="G347" s="43"/>
@@ -25099,7 +25096,7 @@
         <v>345</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C348" s="8">
         <v>1010132168</v>
@@ -25108,7 +25105,7 @@
         <v>3162491954</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" s="43"/>
@@ -25164,12 +25161,12 @@
         <v>348</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F349" s="2"/>
       <c r="G349" s="43"/>
@@ -25225,12 +25222,12 @@
         <v>349</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="2" t="s">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="F350" s="2"/>
       <c r="G350" s="43"/>
@@ -25286,14 +25283,14 @@
         <v>350</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C351" s="8">
         <v>7685262</v>
       </c>
       <c r="D351" s="8"/>
       <c r="E351" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F351" s="2"/>
       <c r="G351" s="43"/>
@@ -25349,7 +25346,7 @@
         <v>351</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C352" s="8"/>
       <c r="D352" s="8"/>
@@ -25410,12 +25407,12 @@
         <v>352</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C353" s="8"/>
       <c r="D353" s="8"/>
       <c r="E353" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F353" s="2"/>
       <c r="G353" s="43"/>
@@ -25471,12 +25468,12 @@
         <v>353</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C354" s="8"/>
       <c r="D354" s="8"/>
       <c r="E354" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F354" s="2"/>
       <c r="G354" s="43"/>
@@ -25532,12 +25529,12 @@
         <v>354</v>
       </c>
       <c r="B355" s="8" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C355" s="8"/>
       <c r="D355" s="8"/>
       <c r="E355" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F355" s="2"/>
       <c r="G355" s="43"/>
@@ -25593,12 +25590,12 @@
         <v>355</v>
       </c>
       <c r="B356" s="8" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C356" s="8"/>
       <c r="D356" s="8"/>
       <c r="E356" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F356" s="2"/>
       <c r="G356" s="43"/>
@@ -25654,14 +25651,14 @@
         <v>356</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C357" s="8">
         <v>39358951</v>
       </c>
       <c r="D357" s="8"/>
       <c r="E357" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F357" s="2"/>
       <c r="G357" s="43"/>
@@ -25717,12 +25714,12 @@
         <v>356</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C358" s="8"/>
       <c r="D358" s="8"/>
       <c r="E358" s="2" t="s">
-        <v>104</v>
+        <v>569</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="43"/>
@@ -25778,12 +25775,12 @@
         <v>357</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="C359" s="8"/>
       <c r="D359" s="8"/>
       <c r="E359" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F359" s="2"/>
       <c r="G359" s="43"/>
@@ -25839,12 +25836,12 @@
         <v>358</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C360" s="8"/>
       <c r="D360" s="8"/>
       <c r="E360" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F360" s="2"/>
       <c r="G360" s="43"/>
@@ -25900,12 +25897,12 @@
         <v>359</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C361" s="8"/>
       <c r="D361" s="8"/>
       <c r="E361" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F361" s="2"/>
       <c r="G361" s="43"/>
@@ -25961,14 +25958,14 @@
         <v>360</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C362" s="8">
         <v>1104013538</v>
       </c>
       <c r="D362" s="8"/>
       <c r="E362" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F362" s="2"/>
       <c r="G362" s="43"/>
@@ -26024,14 +26021,14 @@
         <v>361</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C363" s="8">
         <v>1143389598</v>
       </c>
       <c r="D363" s="8"/>
       <c r="E363" s="2" t="s">
-        <v>28</v>
+        <v>569</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="43"/>
@@ -26087,7 +26084,7 @@
         <v>362</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C364" s="8">
         <v>32832250</v>
@@ -26572,7 +26569,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -26587,13 +26584,13 @@
         <v>4</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>560</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>5</v>
@@ -26643,10 +26640,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -26677,10 +26674,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -26713,7 +26710,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>35</v>
@@ -26749,7 +26746,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>35</v>
@@ -26762,7 +26759,7 @@
         <v>-5231807</v>
       </c>
       <c r="I8" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J8" s="19" t="s">
         <v>36</v>
@@ -26787,7 +26784,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>35</v>
@@ -26800,7 +26797,7 @@
         <v>-3500000</v>
       </c>
       <c r="I9" s="54" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J9" s="19" t="s">
         <v>36</v>
@@ -26825,10 +26822,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
@@ -26838,7 +26835,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J10" s="19" t="s">
         <v>36</v>
@@ -26863,10 +26860,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
@@ -26876,7 +26873,7 @@
         <v>-20000000</v>
       </c>
       <c r="I11" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J11" s="19" t="s">
         <v>36</v>
@@ -26901,10 +26898,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -26935,10 +26932,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
@@ -26948,7 +26945,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="54" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J13" s="19" t="s">
         <v>36</v>
@@ -26973,10 +26970,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -27009,10 +27006,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -27022,7 +27019,7 @@
         <v>-6700000</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J15" s="19" t="s">
         <v>36</v>
@@ -27047,10 +27044,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -27081,10 +27078,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -27117,10 +27114,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
@@ -27151,10 +27148,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
@@ -27164,7 +27161,7 @@
         <v>-400000</v>
       </c>
       <c r="I19" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J19" s="19" t="s">
         <v>36</v>
@@ -27189,10 +27186,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
@@ -27202,7 +27199,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J20" s="19" t="s">
         <v>36</v>
@@ -27227,10 +27224,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
@@ -27238,7 +27235,7 @@
       <c r="G21" s="20"/>
       <c r="H21" s="53"/>
       <c r="I21" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J21" s="19" t="s">
         <v>36</v>
@@ -27263,10 +27260,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="20"/>
@@ -27299,10 +27296,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
@@ -27312,7 +27309,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="54" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J23" s="19" t="s">
         <v>36</v>
@@ -27337,10 +27334,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
@@ -27348,7 +27345,7 @@
       <c r="G24" s="20"/>
       <c r="H24" s="53"/>
       <c r="I24" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>36</v>
@@ -27373,10 +27370,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
@@ -27386,7 +27383,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="54" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J25" s="19" t="s">
         <v>36</v>
@@ -27411,10 +27408,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
@@ -27445,10 +27442,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D27" s="20"/>
       <c r="E27" s="20"/>
@@ -27479,10 +27476,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="20"/>
@@ -27513,10 +27510,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
@@ -27547,10 +27544,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="20"/>
@@ -27581,10 +27578,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="20"/>
@@ -27615,10 +27612,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D32" s="20"/>
       <c r="E32" s="20"/>
@@ -27649,10 +27646,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D33" s="20"/>
       <c r="E33" s="20"/>
@@ -27683,10 +27680,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D34" s="20"/>
       <c r="E34" s="20"/>
@@ -27717,10 +27714,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
@@ -27751,10 +27748,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D36" s="20"/>
       <c r="E36" s="20"/>
@@ -27785,10 +27782,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D37" s="20"/>
       <c r="E37" s="20"/>
@@ -27819,10 +27816,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="20"/>
@@ -27853,10 +27850,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D39" s="20"/>
       <c r="E39" s="20"/>
@@ -27887,10 +27884,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D40" s="20"/>
       <c r="E40" s="20"/>
@@ -27921,10 +27918,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
@@ -27955,10 +27952,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
@@ -27989,10 +27986,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D43" s="20"/>
       <c r="E43" s="20"/>
@@ -28023,10 +28020,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D44" s="20"/>
       <c r="E44" s="20"/>
@@ -28057,10 +28054,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D45" s="20"/>
       <c r="E45" s="20"/>
@@ -28091,10 +28088,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D46" s="20"/>
       <c r="E46" s="20"/>
@@ -28125,10 +28122,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D47" s="20"/>
       <c r="E47" s="20"/>
@@ -28159,10 +28156,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
@@ -28193,10 +28190,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
@@ -28227,10 +28224,10 @@
         <v>46</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D50" s="20"/>
       <c r="E50" s="20"/>
@@ -28261,10 +28258,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D51" s="21"/>
       <c r="E51" s="21"/>
@@ -28295,10 +28292,10 @@
         <v>48</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D52" s="21"/>
       <c r="E52" s="21"/>
@@ -28329,10 +28326,10 @@
         <v>49</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
@@ -28363,10 +28360,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
@@ -28396,10 +28393,10 @@
         <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
@@ -28429,10 +28426,10 @@
         <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
@@ -28462,10 +28459,10 @@
         <v>53</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
@@ -28495,10 +28492,10 @@
         <v>54</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D58" s="21"/>
       <c r="E58" s="21"/>
@@ -28530,10 +28527,10 @@
         <v>55</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D59" s="21"/>
       <c r="E59" s="21"/>
@@ -28563,10 +28560,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="24"/>
@@ -28596,10 +28593,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D61" s="30"/>
       <c r="E61" s="30"/>
@@ -28629,10 +28626,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D62" s="30"/>
       <c r="E62" s="30"/>
@@ -28662,10 +28659,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D63" s="30"/>
       <c r="E63" s="30"/>
@@ -28697,10 +28694,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D64" s="30"/>
       <c r="E64" s="30"/>
@@ -28732,10 +28729,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D65" s="30"/>
       <c r="E65" s="30"/>
@@ -28767,10 +28764,10 @@
         <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D66" s="30"/>
       <c r="E66" s="30"/>
@@ -28802,10 +28799,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D67" s="30"/>
       <c r="E67" s="30"/>
@@ -28837,10 +28834,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D68" s="30"/>
       <c r="E68" s="30"/>
@@ -28872,10 +28869,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D69" s="30"/>
       <c r="E69" s="30"/>
@@ -28907,10 +28904,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D70" s="30"/>
       <c r="E70" s="30"/>
@@ -28923,7 +28920,7 @@
       </c>
       <c r="K70" s="11"/>
       <c r="L70" s="11" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="M70" s="11"/>
       <c r="N70" s="11"/>
@@ -28942,10 +28939,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D71" s="30"/>
       <c r="E71" s="30"/>
@@ -28979,10 +28976,10 @@
         <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D72" s="30"/>
       <c r="E72" s="30"/>
@@ -29014,10 +29011,10 @@
         <v>69</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D73" s="21"/>
       <c r="E73" s="21"/>
@@ -29049,10 +29046,10 @@
         <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D74" s="21"/>
       <c r="E74" s="21"/>
@@ -29084,10 +29081,10 @@
         <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D75" s="21"/>
       <c r="E75" s="21"/>
@@ -29119,10 +29116,10 @@
         <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D76" s="21"/>
       <c r="E76" s="21"/>
@@ -29154,10 +29151,10 @@
         <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="23"/>
@@ -29189,10 +29186,10 @@
         <v>74</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="23"/>
@@ -29224,10 +29221,10 @@
         <v>75</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D79" s="23"/>
       <c r="E79" s="23"/>
@@ -29259,10 +29256,10 @@
         <v>76</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D80" s="23"/>
       <c r="E80" s="23"/>
@@ -29294,10 +29291,10 @@
         <v>77</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D81" s="23"/>
       <c r="E81" s="23"/>
@@ -29329,10 +29326,10 @@
         <v>78</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D82" s="23"/>
       <c r="E82" s="23"/>
@@ -29364,10 +29361,10 @@
         <v>79</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D83" s="23"/>
       <c r="E83" s="23"/>
@@ -29399,10 +29396,10 @@
         <v>80</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
@@ -29434,10 +29431,10 @@
         <v>81</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
@@ -29469,10 +29466,10 @@
         <v>82</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="23"/>
@@ -29504,10 +29501,10 @@
         <v>83</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D87" s="23"/>
       <c r="E87" s="23"/>
@@ -29539,10 +29536,10 @@
         <v>84</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D88" s="23"/>
       <c r="E88" s="23"/>
@@ -29574,10 +29571,10 @@
         <v>85</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D89" s="23"/>
       <c r="E89" s="23"/>
@@ -29609,10 +29606,10 @@
         <v>86</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D90" s="23"/>
       <c r="E90" s="23"/>
@@ -29644,10 +29641,10 @@
         <v>87</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D91" s="23"/>
       <c r="E91" s="23"/>
@@ -29679,10 +29676,10 @@
         <v>88</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D92" s="23"/>
       <c r="E92" s="23"/>
@@ -29714,10 +29711,10 @@
         <v>89</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C93" s="23" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D93" s="23"/>
       <c r="E93" s="23"/>
@@ -29747,10 +29744,10 @@
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="22"/>
       <c r="B94" s="22" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D94" s="23"/>
       <c r="E94" s="23"/>
@@ -29780,10 +29777,10 @@
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="22"/>
       <c r="B95" s="22" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D95" s="23"/>
       <c r="E95" s="23"/>
@@ -29813,10 +29810,10 @@
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="22"/>
       <c r="B96" s="22" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D96" s="23"/>
       <c r="E96" s="23"/>
@@ -29846,10 +29843,10 @@
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="22"/>
       <c r="B97" s="22" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D97" s="23"/>
       <c r="E97" s="23"/>
@@ -29879,10 +29876,10 @@
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="22"/>
       <c r="B98" s="22" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C98" s="23" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D98" s="23"/>
       <c r="E98" s="23"/>
@@ -29912,10 +29909,10 @@
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="22"/>
       <c r="B99" s="22" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="C99" s="23" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D99" s="23"/>
       <c r="E99" s="23"/>

--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51890AE9-349E-420B-B446-DB908FE596F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEEBEE5A-9BCF-407B-8E0D-9E715CB24C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Gastos 26" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base Inversionistas 26'!$A$4:$Y$370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Base Inversionistas 26'!$A$4:$Y$377</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gastos 26'!$A$4:$W$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="603">
   <si>
     <t>NO.</t>
   </si>
@@ -1836,6 +1836,18 @@
   </si>
   <si>
     <t>NOTA CONCILIATORIA FINAL JUNIO</t>
+  </si>
+  <si>
+    <t>Villa del Rosario</t>
+  </si>
+  <si>
+    <t>VILLAVICENCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO GUZMAN </t>
+  </si>
+  <si>
+    <t>IG. EN CALI</t>
   </si>
 </sst>
 </file>
@@ -2466,7 +2478,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:Y375"/>
+  <dimension ref="A1:Y382"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
@@ -2594,7 +2606,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>581</v>
@@ -2659,7 +2671,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>24</v>
@@ -2724,7 +2736,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>25</v>
@@ -2789,7 +2801,7 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>26</v>
@@ -2854,7 +2866,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>27</v>
@@ -2923,7 +2935,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>29</v>
@@ -2990,7 +3002,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -3057,7 +3069,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>33</v>
@@ -3120,7 +3132,7 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>34</v>
@@ -3185,7 +3197,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>35</v>
@@ -3252,7 +3264,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>37</v>
@@ -3317,7 +3329,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>38</v>
@@ -3382,7 +3394,7 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>39</v>
@@ -3449,7 +3461,7 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>41</v>
@@ -3520,7 +3532,7 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>42</v>
@@ -3587,7 +3599,7 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>43</v>
@@ -3652,7 +3664,7 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>44</v>
@@ -3721,7 +3733,7 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>45</v>
@@ -3788,7 +3800,7 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>46</v>
@@ -3831,7 +3843,7 @@
         <v>4000000</v>
       </c>
       <c r="P23" s="10">
-        <v>2700000</v>
+        <v>3500000</v>
       </c>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
@@ -3840,11 +3852,11 @@
       <c r="U23" s="4"/>
       <c r="V23" s="5">
         <f t="shared" si="3"/>
-        <v>14700000</v>
+        <v>15500000</v>
       </c>
       <c r="W23" s="6">
         <f t="shared" si="0"/>
-        <v>36.75</v>
+        <v>38.75</v>
       </c>
       <c r="X23" s="6">
         <f t="shared" si="1"/>
@@ -3852,12 +3864,12 @@
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>47</v>
@@ -3924,7 +3936,7 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>48</v>
@@ -3989,7 +4001,7 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>49</v>
@@ -4054,7 +4066,7 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>50</v>
@@ -4121,7 +4133,7 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>51</v>
@@ -4188,7 +4200,7 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>52</v>
@@ -4255,7 +4267,7 @@
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>53</v>
@@ -4324,7 +4336,7 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>55</v>
@@ -4391,7 +4403,7 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>56</v>
@@ -4460,7 +4472,7 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>58</v>
@@ -4527,7 +4539,7 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>59</v>
@@ -4592,7 +4604,7 @@
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>60</v>
@@ -4659,7 +4671,7 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>61</v>
@@ -4728,7 +4740,7 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>62</v>
@@ -4795,7 +4807,7 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>63</v>
@@ -4864,7 +4876,7 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>65</v>
@@ -4929,7 +4941,7 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>66</v>
@@ -4998,7 +5010,7 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>68</v>
@@ -5067,7 +5079,7 @@
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>69</v>
@@ -5136,7 +5148,7 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>71</v>
@@ -5201,7 +5213,7 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>73</v>
@@ -5270,7 +5282,7 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>75</v>
@@ -5333,7 +5345,7 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>76</v>
@@ -5378,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="10">
-        <v>0</v>
+        <v>5600000</v>
       </c>
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
@@ -5387,24 +5399,24 @@
       <c r="U46" s="4"/>
       <c r="V46" s="5">
         <f t="shared" si="3"/>
-        <v>44800000</v>
+        <v>50400000</v>
       </c>
       <c r="W46" s="6">
         <f t="shared" si="0"/>
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="X46" s="6">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y46" s="6">
         <f t="shared" si="2"/>
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>77</v>
@@ -5471,7 +5483,7 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>79</v>
@@ -5538,7 +5550,7 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>80</v>
@@ -5607,7 +5619,7 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>81</v>
@@ -5672,7 +5684,7 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>82</v>
@@ -5741,7 +5753,7 @@
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>83</v>
@@ -5806,7 +5818,7 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>85</v>
@@ -5845,7 +5857,7 @@
         <v>1500000</v>
       </c>
       <c r="P53" s="10">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
@@ -5854,24 +5866,24 @@
       <c r="U53" s="4"/>
       <c r="V53" s="5">
         <f t="shared" si="3"/>
-        <v>7650000</v>
+        <v>8850000</v>
       </c>
       <c r="W53" s="6">
         <f t="shared" si="0"/>
-        <v>19.125</v>
+        <v>22.125</v>
       </c>
       <c r="X53" s="6">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y53" s="6">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>86</v>
@@ -5936,7 +5948,7 @@
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>88</v>
@@ -6004,8 +6016,8 @@
       </c>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
-        <v>53</v>
+      <c r="A56" s="2">
+        <v>52</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>90</v>
@@ -6071,8 +6083,8 @@
       </c>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>54</v>
+      <c r="A57" s="8">
+        <v>53</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>92</v>
@@ -6137,7 +6149,7 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>94</v>
@@ -6202,7 +6214,7 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>95</v>
@@ -6267,7 +6279,7 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>97</v>
@@ -6336,7 +6348,7 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>100</v>
@@ -6401,7 +6413,7 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>102</v>
@@ -6444,7 +6456,7 @@
         <v>400000</v>
       </c>
       <c r="P62" s="10">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
@@ -6453,24 +6465,24 @@
       <c r="U62" s="4"/>
       <c r="V62" s="5">
         <f t="shared" si="3"/>
-        <v>8000000</v>
+        <v>8800000</v>
       </c>
       <c r="W62" s="6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X62" s="6">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y62" s="6">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>104</v>
@@ -6535,7 +6547,7 @@
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>106</v>
@@ -6600,7 +6612,7 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>108</v>
@@ -6665,7 +6677,7 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>110</v>
@@ -6730,7 +6742,7 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>112</v>
@@ -6799,7 +6811,7 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>115</v>
@@ -6864,7 +6876,7 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>117</v>
@@ -6929,7 +6941,7 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>119</v>
@@ -6972,7 +6984,7 @@
         <v>5060000</v>
       </c>
       <c r="P70" s="10">
-        <v>0</v>
+        <v>4300000</v>
       </c>
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
@@ -6981,24 +6993,24 @@
       <c r="U70" s="4"/>
       <c r="V70" s="5">
         <f t="shared" ref="V70:V133" si="7">SUM(J70:U70)</f>
-        <v>26300000</v>
+        <v>30600000</v>
       </c>
       <c r="W70" s="6">
         <f t="shared" si="4"/>
-        <v>65.75</v>
+        <v>76.5</v>
       </c>
       <c r="X70" s="6">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y70" s="6">
         <f t="shared" si="6"/>
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>120</v>
@@ -7065,7 +7077,7 @@
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>121</v>
@@ -7130,7 +7142,7 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>123</v>
@@ -7138,7 +7150,7 @@
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
       <c r="E73" s="2" t="s">
-        <v>424</v>
+        <v>599</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="43">
@@ -7195,7 +7207,7 @@
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>124</v>
@@ -7258,7 +7270,7 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>126</v>
@@ -7321,7 +7333,7 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>128</v>
@@ -7384,7 +7396,7 @@
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>130</v>
@@ -7455,7 +7467,7 @@
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>132</v>
@@ -7520,7 +7532,7 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>133</v>
@@ -7587,7 +7599,7 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>134</v>
@@ -7652,7 +7664,7 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>135</v>
@@ -7717,7 +7729,7 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>136</v>
@@ -7782,7 +7794,7 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>137</v>
@@ -7825,7 +7837,7 @@
         <v>1200000</v>
       </c>
       <c r="P83" s="10">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
@@ -7834,24 +7846,24 @@
       <c r="U83" s="4"/>
       <c r="V83" s="5">
         <f t="shared" si="7"/>
-        <v>6400000</v>
+        <v>7600000</v>
       </c>
       <c r="W83" s="6">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="X83" s="6">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y83" s="6">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>138</v>
@@ -7920,7 +7932,7 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>140</v>
@@ -7961,7 +7973,7 @@
         <v>400000</v>
       </c>
       <c r="P85" s="10">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
@@ -7970,11 +7982,11 @@
       <c r="U85" s="4"/>
       <c r="V85" s="5">
         <f t="shared" si="7"/>
-        <v>2201000</v>
+        <v>2601000</v>
       </c>
       <c r="W85" s="6">
         <f t="shared" si="4"/>
-        <v>5.5025000000000004</v>
+        <v>6.5025000000000004</v>
       </c>
       <c r="X85" s="6">
         <f t="shared" si="5"/>
@@ -7982,12 +7994,12 @@
       </c>
       <c r="Y85" s="6">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>141</v>
@@ -8052,7 +8064,7 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>142</v>
@@ -8119,7 +8131,7 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>144</v>
@@ -8186,7 +8198,7 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>145</v>
@@ -8255,7 +8267,7 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>146</v>
@@ -8322,7 +8334,7 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>147</v>
@@ -8387,7 +8399,7 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>148</v>
@@ -8452,7 +8464,7 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>149</v>
@@ -8521,7 +8533,7 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>150</v>
@@ -8586,7 +8598,7 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>151</v>
@@ -8653,7 +8665,7 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B96" s="9" t="s">
         <v>152</v>
@@ -8722,7 +8734,7 @@
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>153</v>
@@ -8789,7 +8801,7 @@
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>154</v>
@@ -8854,7 +8866,7 @@
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>155</v>
@@ -8923,7 +8935,7 @@
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>157</v>
@@ -8988,7 +9000,7 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>158</v>
@@ -9055,7 +9067,7 @@
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>159</v>
@@ -9120,7 +9132,7 @@
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>160</v>
@@ -9185,7 +9197,7 @@
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>161</v>
@@ -9256,7 +9268,7 @@
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>162</v>
@@ -9319,7 +9331,7 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>163</v>
@@ -9384,7 +9396,7 @@
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>164</v>
@@ -9451,7 +9463,7 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>165</v>
@@ -9516,7 +9528,7 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>166</v>
@@ -9579,7 +9591,7 @@
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>167</v>
@@ -9648,7 +9660,7 @@
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>168</v>
@@ -9717,7 +9729,7 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>171</v>
@@ -9782,7 +9794,7 @@
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B113" s="8" t="s">
         <v>172</v>
@@ -9851,7 +9863,7 @@
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>174</v>
@@ -9920,7 +9932,7 @@
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>176</v>
@@ -9983,7 +9995,7 @@
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>177</v>
@@ -10048,7 +10060,7 @@
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>178</v>
@@ -10117,7 +10129,7 @@
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>179</v>
@@ -10182,7 +10194,7 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>180</v>
@@ -10247,7 +10259,7 @@
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>181</v>
@@ -10318,7 +10330,7 @@
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B121" s="8" t="s">
         <v>183</v>
@@ -10383,7 +10395,7 @@
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>184</v>
@@ -10422,7 +10434,7 @@
         <v>400000</v>
       </c>
       <c r="P122" s="10">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="Q122" s="4"/>
       <c r="R122" s="4"/>
@@ -10431,11 +10443,11 @@
       <c r="U122" s="4"/>
       <c r="V122" s="5">
         <f t="shared" si="7"/>
-        <v>1700000</v>
+        <v>2100000</v>
       </c>
       <c r="W122" s="6">
         <f t="shared" si="4"/>
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="X122" s="6">
         <f t="shared" si="5"/>
@@ -10443,12 +10455,12 @@
       </c>
       <c r="Y122" s="6">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>185</v>
@@ -10515,7 +10527,7 @@
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>186</v>
@@ -10580,7 +10592,7 @@
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>187</v>
@@ -10645,7 +10657,7 @@
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B126" s="8" t="s">
         <v>188</v>
@@ -10714,7 +10726,7 @@
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>189</v>
@@ -10777,7 +10789,7 @@
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>190</v>
@@ -10844,7 +10856,7 @@
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B129" s="8" t="s">
         <v>191</v>
@@ -10913,7 +10925,7 @@
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>192</v>
@@ -10984,7 +10996,7 @@
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>193</v>
@@ -11047,7 +11059,7 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>194</v>
@@ -11112,7 +11124,7 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B133" s="8" t="s">
         <v>195</v>
@@ -11177,7 +11189,7 @@
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>196</v>
@@ -11240,7 +11252,7 @@
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>197</v>
@@ -11305,7 +11317,7 @@
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>198</v>
@@ -11372,7 +11384,7 @@
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>199</v>
@@ -11443,7 +11455,7 @@
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>200</v>
@@ -11508,7 +11520,7 @@
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B139" s="8" t="s">
         <v>201</v>
@@ -11577,7 +11589,7 @@
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>204</v>
@@ -11640,7 +11652,7 @@
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B141" s="8" t="s">
         <v>205</v>
@@ -11705,7 +11717,7 @@
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B142" s="8" t="s">
         <v>206</v>
@@ -11768,7 +11780,7 @@
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B143" s="8" t="s">
         <v>207</v>
@@ -11835,7 +11847,7 @@
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B144" s="8" t="s">
         <v>208</v>
@@ -11898,7 +11910,7 @@
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>209</v>
@@ -11961,7 +11973,7 @@
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>210</v>
@@ -12028,7 +12040,7 @@
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>212</v>
@@ -12091,7 +12103,7 @@
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>213</v>
@@ -12154,7 +12166,7 @@
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>214</v>
@@ -12221,7 +12233,7 @@
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>216</v>
@@ -12284,7 +12296,7 @@
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>217</v>
@@ -12347,7 +12359,7 @@
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B152" s="8" t="s">
         <v>218</v>
@@ -12410,7 +12422,7 @@
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B153" s="8" t="s">
         <v>219</v>
@@ -12473,7 +12485,7 @@
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B154" s="8" t="s">
         <v>220</v>
@@ -12514,7 +12526,7 @@
         <v>100000</v>
       </c>
       <c r="P154" s="10">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="Q154" s="4"/>
       <c r="R154" s="4"/>
@@ -12523,11 +12535,11 @@
       <c r="U154" s="4"/>
       <c r="V154" s="5">
         <f t="shared" si="11"/>
-        <v>700000</v>
+        <v>800000</v>
       </c>
       <c r="W154" s="6">
         <f t="shared" si="8"/>
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="X154" s="6">
         <f t="shared" si="9"/>
@@ -12540,7 +12552,7 @@
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B155" s="8" t="s">
         <v>221</v>
@@ -12605,7 +12617,7 @@
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B156" s="8" t="s">
         <v>222</v>
@@ -12672,7 +12684,7 @@
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>223</v>
@@ -12739,7 +12751,7 @@
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B158" s="8" t="s">
         <v>224</v>
@@ -12806,7 +12818,7 @@
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B159" s="8" t="s">
         <v>225</v>
@@ -12871,7 +12883,7 @@
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B160" s="8" t="s">
         <v>226</v>
@@ -12934,7 +12946,7 @@
     </row>
     <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B161" s="8" t="s">
         <v>227</v>
@@ -12999,7 +13011,7 @@
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B162" s="8" t="s">
         <v>228</v>
@@ -13064,7 +13076,7 @@
     </row>
     <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B163" s="8" t="s">
         <v>229</v>
@@ -13131,7 +13143,7 @@
     </row>
     <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B164" s="8" t="s">
         <v>230</v>
@@ -13198,7 +13210,7 @@
     </row>
     <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B165" s="8" t="s">
         <v>231</v>
@@ -13261,7 +13273,7 @@
     </row>
     <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>232</v>
@@ -13328,7 +13340,7 @@
     </row>
     <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>233</v>
@@ -13393,7 +13405,7 @@
     </row>
     <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>234</v>
@@ -13458,7 +13470,7 @@
     </row>
     <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>235</v>
@@ -13523,7 +13535,7 @@
     </row>
     <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B170" s="8" t="s">
         <v>236</v>
@@ -13588,7 +13600,7 @@
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B171" s="8" t="s">
         <v>237</v>
@@ -13651,7 +13663,7 @@
     </row>
     <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B172" s="8" t="s">
         <v>238</v>
@@ -13692,7 +13704,7 @@
         <v>2000000</v>
       </c>
       <c r="P172" s="10">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="Q172" s="4"/>
       <c r="R172" s="4"/>
@@ -13701,24 +13713,24 @@
       <c r="U172" s="4"/>
       <c r="V172" s="5">
         <f t="shared" si="11"/>
-        <v>3200000</v>
+        <v>4400000</v>
       </c>
       <c r="W172" s="6">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X172" s="6">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y172" s="6">
         <f t="shared" si="10"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B173" s="8" t="s">
         <v>239</v>
@@ -13781,7 +13793,7 @@
     </row>
     <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B174" s="8" t="s">
         <v>240</v>
@@ -13818,7 +13830,7 @@
         <v>800000</v>
       </c>
       <c r="P174" s="10">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="Q174" s="4"/>
       <c r="R174" s="4"/>
@@ -13827,24 +13839,24 @@
       <c r="U174" s="4"/>
       <c r="V174" s="5">
         <f t="shared" si="11"/>
-        <v>4400000</v>
+        <v>5200000</v>
       </c>
       <c r="W174" s="6">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X174" s="6">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y174" s="6">
         <f t="shared" si="10"/>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B175" s="8" t="s">
         <v>241</v>
@@ -13909,7 +13921,7 @@
     </row>
     <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B176" s="8" t="s">
         <v>242</v>
@@ -13919,7 +13931,7 @@
       </c>
       <c r="D176" s="8"/>
       <c r="E176" s="2" t="s">
-        <v>28</v>
+        <v>568</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" s="43">
@@ -13974,7 +13986,7 @@
     </row>
     <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B177" s="8" t="s">
         <v>243</v>
@@ -14041,7 +14053,7 @@
     </row>
     <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B178" s="8" t="s">
         <v>244</v>
@@ -14108,7 +14120,7 @@
     </row>
     <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>246</v>
@@ -14175,7 +14187,7 @@
     </row>
     <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B180" s="8" t="s">
         <v>248</v>
@@ -14242,7 +14254,7 @@
     </row>
     <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B181" s="8" t="s">
         <v>249</v>
@@ -14307,7 +14319,7 @@
     </row>
     <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>250</v>
@@ -14374,7 +14386,7 @@
     </row>
     <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>251</v>
@@ -14437,7 +14449,7 @@
     </row>
     <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B184" s="8" t="s">
         <v>252</v>
@@ -14500,7 +14512,7 @@
     </row>
     <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B185" s="8" t="s">
         <v>253</v>
@@ -14563,7 +14575,7 @@
     </row>
     <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B186" s="8" t="s">
         <v>254</v>
@@ -14571,7 +14583,7 @@
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
       <c r="E186" s="2" t="s">
-        <v>122</v>
+        <v>600</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" s="43">
@@ -14626,7 +14638,7 @@
     </row>
     <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B187" s="8" t="s">
         <v>255</v>
@@ -14693,7 +14705,7 @@
     </row>
     <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B188" s="8" t="s">
         <v>256</v>
@@ -14756,7 +14768,7 @@
     </row>
     <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>257</v>
@@ -14821,7 +14833,7 @@
     </row>
     <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>258</v>
@@ -14888,7 +14900,7 @@
     </row>
     <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>260</v>
@@ -14955,7 +14967,7 @@
     </row>
     <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>261</v>
@@ -15018,7 +15030,7 @@
     </row>
     <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>262</v>
@@ -15085,7 +15097,7 @@
     </row>
     <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>263</v>
@@ -15152,7 +15164,7 @@
     </row>
     <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>264</v>
@@ -15215,7 +15227,7 @@
     </row>
     <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B196" s="8" t="s">
         <v>265</v>
@@ -15280,7 +15292,7 @@
     </row>
     <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B197" s="8" t="s">
         <v>267</v>
@@ -15343,7 +15355,7 @@
     </row>
     <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>268</v>
@@ -15410,7 +15422,7 @@
     </row>
     <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B199" s="8" t="s">
         <v>269</v>
@@ -15477,7 +15489,7 @@
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>270</v>
@@ -15544,7 +15556,7 @@
     </row>
     <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B201" s="8" t="s">
         <v>271</v>
@@ -15607,7 +15619,7 @@
     </row>
     <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>272</v>
@@ -15670,7 +15682,7 @@
     </row>
     <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>273</v>
@@ -15737,7 +15749,7 @@
     </row>
     <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>275</v>
@@ -15804,7 +15816,7 @@
     </row>
     <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>276</v>
@@ -15867,7 +15879,7 @@
     </row>
     <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>277</v>
@@ -15930,7 +15942,7 @@
     </row>
     <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>278</v>
@@ -15997,7 +16009,7 @@
     </row>
     <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>280</v>
@@ -16060,7 +16072,7 @@
     </row>
     <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>281</v>
@@ -16129,7 +16141,7 @@
     </row>
     <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B210" s="8" t="s">
         <v>282</v>
@@ -16170,7 +16182,7 @@
         <v>400000</v>
       </c>
       <c r="P210" s="10">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q210" s="11"/>
       <c r="R210" s="4"/>
@@ -16179,24 +16191,24 @@
       <c r="U210" s="4"/>
       <c r="V210" s="5">
         <f t="shared" si="15"/>
-        <v>1200000</v>
+        <v>1600000</v>
       </c>
       <c r="W210" s="6">
         <f t="shared" si="12"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X210" s="6">
         <f t="shared" si="13"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y210" s="6">
         <f t="shared" si="14"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B211" s="8" t="s">
         <v>284</v>
@@ -16263,7 +16275,7 @@
     </row>
     <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B212" s="8" t="s">
         <v>286</v>
@@ -16304,7 +16316,7 @@
         <v>0</v>
       </c>
       <c r="P212" s="10">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="Q212" s="11"/>
       <c r="R212" s="4"/>
@@ -16313,15 +16325,15 @@
       <c r="U212" s="4"/>
       <c r="V212" s="5">
         <f t="shared" si="15"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="W212" s="6">
         <f t="shared" si="12"/>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="X212" s="6">
         <f t="shared" si="13"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y212" s="6">
         <f t="shared" si="14"/>
@@ -16330,7 +16342,7 @@
     </row>
     <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B213" s="8" t="s">
         <v>287</v>
@@ -16397,7 +16409,7 @@
     </row>
     <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B214" s="8" t="s">
         <v>288</v>
@@ -16464,7 +16476,7 @@
     </row>
     <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B215" s="8" t="s">
         <v>289</v>
@@ -16531,7 +16543,7 @@
     </row>
     <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B216" s="8" t="s">
         <v>291</v>
@@ -16598,7 +16610,7 @@
     </row>
     <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B217" s="8" t="s">
         <v>292</v>
@@ -16665,7 +16677,7 @@
     </row>
     <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B218" s="8" t="s">
         <v>293</v>
@@ -16732,7 +16744,7 @@
     </row>
     <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B219" s="8" t="s">
         <v>294</v>
@@ -16799,7 +16811,7 @@
     </row>
     <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B220" s="8" t="s">
         <v>296</v>
@@ -16866,7 +16878,7 @@
     </row>
     <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B221" s="8" t="s">
         <v>584</v>
@@ -16933,7 +16945,7 @@
     </row>
     <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B222" s="8" t="s">
         <v>298</v>
@@ -17000,7 +17012,7 @@
     </row>
     <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B223" s="8" t="s">
         <v>300</v>
@@ -17067,7 +17079,7 @@
     </row>
     <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B224" s="8" t="s">
         <v>301</v>
@@ -17134,7 +17146,7 @@
     </row>
     <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B225" s="8" t="s">
         <v>302</v>
@@ -17201,7 +17213,7 @@
     </row>
     <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>305</v>
@@ -17268,7 +17280,7 @@
     </row>
     <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B227" s="8" t="s">
         <v>307</v>
@@ -17335,7 +17347,7 @@
     </row>
     <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B228" s="8" t="s">
         <v>309</v>
@@ -17402,7 +17414,7 @@
     </row>
     <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B229" s="8" t="s">
         <v>311</v>
@@ -17469,7 +17481,7 @@
     </row>
     <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B230" s="8" t="s">
         <v>313</v>
@@ -17536,7 +17548,7 @@
     </row>
     <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B231" s="8" t="s">
         <v>316</v>
@@ -17603,7 +17615,7 @@
     </row>
     <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B232" s="8" t="s">
         <v>319</v>
@@ -17670,7 +17682,7 @@
     </row>
     <row r="233" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B233" s="8" t="s">
         <v>322</v>
@@ -17737,7 +17749,7 @@
     </row>
     <row r="234" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B234" s="8" t="s">
         <v>324</v>
@@ -17804,7 +17816,7 @@
     </row>
     <row r="235" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B235" s="8" t="s">
         <v>327</v>
@@ -17871,7 +17883,7 @@
     </row>
     <row r="236" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B236" s="8" t="s">
         <v>330</v>
@@ -17938,7 +17950,7 @@
     </row>
     <row r="237" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B237" s="8" t="s">
         <v>332</v>
@@ -18005,7 +18017,7 @@
     </row>
     <row r="238" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B238" s="8" t="s">
         <v>333</v>
@@ -18072,7 +18084,7 @@
     </row>
     <row r="239" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B239" s="8" t="s">
         <v>334</v>
@@ -18139,7 +18151,7 @@
     </row>
     <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B240" s="8" t="s">
         <v>335</v>
@@ -18206,7 +18218,7 @@
     </row>
     <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B241" s="8" t="s">
         <v>337</v>
@@ -18273,7 +18285,7 @@
     </row>
     <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B242" s="8" t="s">
         <v>339</v>
@@ -18340,7 +18352,7 @@
     </row>
     <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B243" s="8" t="s">
         <v>340</v>
@@ -18407,7 +18419,7 @@
     </row>
     <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B244" s="8" t="s">
         <v>341</v>
@@ -18474,7 +18486,7 @@
     </row>
     <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B245" s="8" t="s">
         <v>342</v>
@@ -18541,7 +18553,7 @@
     </row>
     <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B246" s="8" t="s">
         <v>343</v>
@@ -18608,7 +18620,7 @@
     </row>
     <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B247" s="8" t="s">
         <v>344</v>
@@ -18675,7 +18687,7 @@
     </row>
     <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B248" s="8" t="s">
         <v>345</v>
@@ -18742,7 +18754,7 @@
     </row>
     <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B249" s="8" t="s">
         <v>346</v>
@@ -18809,7 +18821,7 @@
     </row>
     <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B250" s="8" t="s">
         <v>347</v>
@@ -18876,7 +18888,7 @@
     </row>
     <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B251" s="8" t="s">
         <v>348</v>
@@ -18943,7 +18955,7 @@
     </row>
     <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B252" s="8" t="s">
         <v>349</v>
@@ -19010,7 +19022,7 @@
     </row>
     <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B253" s="8" t="s">
         <v>350</v>
@@ -19077,7 +19089,7 @@
     </row>
     <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B254" s="8" t="s">
         <v>351</v>
@@ -19142,7 +19154,7 @@
     </row>
     <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B255" s="8" t="s">
         <v>352</v>
@@ -19209,7 +19221,7 @@
     </row>
     <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B256" s="8" t="s">
         <v>353</v>
@@ -19278,7 +19290,7 @@
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B257" s="8" t="s">
         <v>355</v>
@@ -19347,7 +19359,7 @@
     </row>
     <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B258" s="8" t="s">
         <v>356</v>
@@ -19414,7 +19426,7 @@
     </row>
     <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B259" s="8" t="s">
         <v>357</v>
@@ -19481,7 +19493,7 @@
     </row>
     <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B260" s="8" t="s">
         <v>359</v>
@@ -19548,7 +19560,7 @@
     </row>
     <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B261" s="8" t="s">
         <v>360</v>
@@ -19615,7 +19627,7 @@
     </row>
     <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B262" s="8" t="s">
         <v>362</v>
@@ -19682,7 +19694,7 @@
     </row>
     <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B263" s="8" t="s">
         <v>364</v>
@@ -19749,7 +19761,7 @@
     </row>
     <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B264" s="8" t="s">
         <v>365</v>
@@ -19816,7 +19828,7 @@
     </row>
     <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B265" s="8" t="s">
         <v>366</v>
@@ -19883,7 +19895,7 @@
     </row>
     <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B266" s="8" t="s">
         <v>367</v>
@@ -19948,7 +19960,7 @@
     </row>
     <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B267" s="8" t="s">
         <v>368</v>
@@ -20015,7 +20027,7 @@
     </row>
     <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B268" s="8" t="s">
         <v>370</v>
@@ -20078,7 +20090,7 @@
     </row>
     <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B269" s="8" t="s">
         <v>371</v>
@@ -20143,7 +20155,7 @@
     </row>
     <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B270" s="8" t="s">
         <v>373</v>
@@ -20210,7 +20222,7 @@
     </row>
     <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B271" s="8" t="s">
         <v>374</v>
@@ -20277,7 +20289,7 @@
     </row>
     <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B272" s="8" t="s">
         <v>377</v>
@@ -20342,7 +20354,7 @@
     </row>
     <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B273" s="8" t="s">
         <v>378</v>
@@ -20409,7 +20421,7 @@
     </row>
     <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B274" s="8" t="s">
         <v>379</v>
@@ -20474,7 +20486,7 @@
     </row>
     <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B275" s="8" t="s">
         <v>380</v>
@@ -20541,7 +20553,7 @@
     </row>
     <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B276" s="8" t="s">
         <v>381</v>
@@ -20608,7 +20620,7 @@
     </row>
     <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B277" s="8" t="s">
         <v>382</v>
@@ -20675,7 +20687,7 @@
     </row>
     <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B278" s="8" t="s">
         <v>384</v>
@@ -20740,7 +20752,7 @@
     </row>
     <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B279" s="8" t="s">
         <v>385</v>
@@ -20805,7 +20817,7 @@
     </row>
     <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B280" s="8" t="s">
         <v>386</v>
@@ -20868,7 +20880,7 @@
     </row>
     <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B281" s="8" t="s">
         <v>387</v>
@@ -20929,7 +20941,7 @@
     </row>
     <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B282" s="8" t="s">
         <v>388</v>
@@ -20990,7 +21002,7 @@
     </row>
     <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B283" s="8" t="s">
         <v>390</v>
@@ -21055,7 +21067,7 @@
     </row>
     <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B284" s="8" t="s">
         <v>391</v>
@@ -21116,7 +21128,7 @@
     </row>
     <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B285" s="8" t="s">
         <v>392</v>
@@ -21179,7 +21191,7 @@
     </row>
     <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B286" s="8" t="s">
         <v>393</v>
@@ -21242,7 +21254,7 @@
     </row>
     <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B287" s="8" t="s">
         <v>394</v>
@@ -21305,7 +21317,7 @@
     </row>
     <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B288" s="8" t="s">
         <v>395</v>
@@ -21368,7 +21380,7 @@
     </row>
     <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B289" s="8" t="s">
         <v>396</v>
@@ -21405,7 +21417,7 @@
         <v>400000</v>
       </c>
       <c r="P289" s="10">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="Q289" s="11"/>
       <c r="R289" s="4"/>
@@ -21414,11 +21426,11 @@
       <c r="U289" s="4"/>
       <c r="V289" s="5">
         <f t="shared" si="20"/>
-        <v>1600000</v>
+        <v>2000000</v>
       </c>
       <c r="W289" s="6">
         <f t="shared" si="16"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X289" s="6">
         <f t="shared" si="17"/>
@@ -21426,12 +21438,12 @@
       </c>
       <c r="Y289" s="6">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B290" s="8" t="s">
         <v>397</v>
@@ -21494,7 +21506,7 @@
     </row>
     <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B291" s="8" t="s">
         <v>398</v>
@@ -21561,7 +21573,7 @@
     </row>
     <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B292" s="8" t="s">
         <v>400</v>
@@ -21626,7 +21638,7 @@
     </row>
     <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B293" s="8" t="s">
         <v>402</v>
@@ -21689,7 +21701,7 @@
     </row>
     <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B294" s="8" t="s">
         <v>404</v>
@@ -21752,7 +21764,7 @@
     </row>
     <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B295" s="8" t="s">
         <v>405</v>
@@ -21813,7 +21825,7 @@
     </row>
     <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B296" s="8" t="s">
         <v>407</v>
@@ -21878,7 +21890,7 @@
     </row>
     <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B297" s="8" t="s">
         <v>409</v>
@@ -21943,7 +21955,7 @@
     </row>
     <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B298" s="8" t="s">
         <v>596</v>
@@ -22004,7 +22016,7 @@
     </row>
     <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B299" s="8" t="s">
         <v>410</v>
@@ -22065,7 +22077,7 @@
     </row>
     <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B300" s="8" t="s">
         <v>411</v>
@@ -22126,7 +22138,7 @@
     </row>
     <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B301" s="8" t="s">
         <v>254</v>
@@ -22187,7 +22199,7 @@
     </row>
     <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B302" s="8" t="s">
         <v>413</v>
@@ -22250,7 +22262,7 @@
     </row>
     <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B303" s="8" t="s">
         <v>414</v>
@@ -22315,7 +22327,7 @@
     </row>
     <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B304" s="8" t="s">
         <v>415</v>
@@ -22380,7 +22392,7 @@
     </row>
     <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B305" s="8" t="s">
         <v>416</v>
@@ -22390,7 +22402,7 @@
       </c>
       <c r="D305" s="8"/>
       <c r="E305" s="2" t="s">
-        <v>568</v>
+        <v>466</v>
       </c>
       <c r="F305" s="2"/>
       <c r="G305" s="43"/>
@@ -22443,7 +22455,7 @@
     </row>
     <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B306" s="8" t="s">
         <v>417</v>
@@ -22508,7 +22520,7 @@
     </row>
     <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B307" s="8" t="s">
         <v>418</v>
@@ -22573,7 +22585,7 @@
     </row>
     <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B308" s="8" t="s">
         <v>419</v>
@@ -22638,7 +22650,7 @@
     </row>
     <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B309" s="8" t="s">
         <v>421</v>
@@ -22701,7 +22713,7 @@
     </row>
     <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B310" s="8" t="s">
         <v>422</v>
@@ -22766,7 +22778,7 @@
     </row>
     <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B311" s="8" t="s">
         <v>425</v>
@@ -22829,7 +22841,7 @@
     </row>
     <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B312" s="8" t="s">
         <v>427</v>
@@ -22890,7 +22902,7 @@
     </row>
     <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B313" s="8" t="s">
         <v>428</v>
@@ -22951,7 +22963,7 @@
     </row>
     <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B314" s="8" t="s">
         <v>429</v>
@@ -23012,7 +23024,7 @@
     </row>
     <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B315" s="8" t="s">
         <v>430</v>
@@ -23073,7 +23085,7 @@
     </row>
     <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B316" s="8" t="s">
         <v>431</v>
@@ -23138,7 +23150,7 @@
     </row>
     <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B317" s="8" t="s">
         <v>432</v>
@@ -23199,7 +23211,7 @@
     </row>
     <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B318" s="8" t="s">
         <v>433</v>
@@ -23260,7 +23272,7 @@
     </row>
     <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B319" s="8" t="s">
         <v>434</v>
@@ -23321,7 +23333,7 @@
     </row>
     <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B320" s="8" t="s">
         <v>435</v>
@@ -23386,7 +23398,7 @@
     </row>
     <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B321" s="8" t="s">
         <v>436</v>
@@ -23447,7 +23459,7 @@
     </row>
     <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B322" s="8" t="s">
         <v>437</v>
@@ -23510,7 +23522,7 @@
     </row>
     <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B323" s="8" t="s">
         <v>438</v>
@@ -23571,7 +23583,7 @@
     </row>
     <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B324" s="8" t="s">
         <v>439</v>
@@ -23632,7 +23644,7 @@
     </row>
     <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B325" s="8" t="s">
         <v>441</v>
@@ -23679,21 +23691,21 @@
         <v>400000</v>
       </c>
       <c r="W325" s="6">
-        <f t="shared" ref="W325:W369" si="21">V325/400000</f>
+        <f t="shared" ref="W325:W376" si="21">V325/400000</f>
         <v>1</v>
       </c>
       <c r="X325" s="6">
-        <f t="shared" ref="X325:X369" si="22">COUNTIF(J325:U325,"&gt;0")</f>
+        <f t="shared" ref="X325:X376" si="22">COUNTIF(J325:U325,"&gt;0")</f>
         <v>1</v>
       </c>
       <c r="Y325" s="6">
-        <f t="shared" ref="Y325:Y369" si="23">ROUNDUP(W325,0)</f>
+        <f t="shared" ref="Y325:Y376" si="23">ROUNDUP(W325,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B326" s="8" t="s">
         <v>442</v>
@@ -23732,7 +23744,7 @@
         <v>0</v>
       </c>
       <c r="P326" s="10">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q326" s="11"/>
       <c r="R326" s="4"/>
@@ -23740,25 +23752,25 @@
       <c r="T326" s="4"/>
       <c r="U326" s="4"/>
       <c r="V326" s="5">
-        <f t="shared" ref="V326:V369" si="24">SUM(J326:U326)</f>
-        <v>1200000</v>
+        <f t="shared" ref="V326:V376" si="24">SUM(J326:U326)</f>
+        <v>1600000</v>
       </c>
       <c r="W326" s="6">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X326" s="6">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y326" s="6">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B327" s="8" t="s">
         <v>443</v>
@@ -23823,7 +23835,7 @@
     </row>
     <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B328" s="8" t="s">
         <v>444</v>
@@ -23888,7 +23900,7 @@
     </row>
     <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B329" s="8" t="s">
         <v>445</v>
@@ -23951,7 +23963,7 @@
     </row>
     <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B330" s="8" t="s">
         <v>446</v>
@@ -24014,7 +24026,7 @@
     </row>
     <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B331" s="8" t="s">
         <v>447</v>
@@ -24077,7 +24089,7 @@
     </row>
     <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B332" s="8" t="s">
         <v>448</v>
@@ -24140,7 +24152,7 @@
     </row>
     <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B333" s="8" t="s">
         <v>449</v>
@@ -24203,7 +24215,7 @@
     </row>
     <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B334" s="8" t="s">
         <v>450</v>
@@ -24268,7 +24280,7 @@
     </row>
     <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B335" s="8" t="s">
         <v>451</v>
@@ -24307,7 +24319,7 @@
         <v>400000</v>
       </c>
       <c r="P335" s="10">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q335" s="11"/>
       <c r="R335" s="4"/>
@@ -24316,24 +24328,24 @@
       <c r="U335" s="4"/>
       <c r="V335" s="5">
         <f t="shared" si="24"/>
-        <v>1200000</v>
+        <v>1600000</v>
       </c>
       <c r="W335" s="6">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X335" s="6">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y335" s="6">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B336" s="8" t="s">
         <v>452</v>
@@ -24394,7 +24406,7 @@
     </row>
     <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B337" s="8" t="s">
         <v>454</v>
@@ -24459,7 +24471,7 @@
     </row>
     <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B338" s="8" t="s">
         <v>455</v>
@@ -24522,7 +24534,7 @@
     </row>
     <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B339" s="8" t="s">
         <v>456</v>
@@ -24587,7 +24599,7 @@
     </row>
     <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B340" s="8" t="s">
         <v>457</v>
@@ -24652,7 +24664,7 @@
     </row>
     <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B341" s="8" t="s">
         <v>459</v>
@@ -24717,7 +24729,7 @@
     </row>
     <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B342" s="8" t="s">
         <v>461</v>
@@ -24782,7 +24794,7 @@
     </row>
     <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B343" s="8" t="s">
         <v>462</v>
@@ -24845,7 +24857,7 @@
     </row>
     <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B344" s="8" t="s">
         <v>463</v>
@@ -24906,7 +24918,7 @@
     </row>
     <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B345" s="8" t="s">
         <v>464</v>
@@ -24971,7 +24983,7 @@
     </row>
     <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B346" s="8" t="s">
         <v>465</v>
@@ -25036,7 +25048,7 @@
     </row>
     <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B347" s="8" t="s">
         <v>467</v>
@@ -25099,7 +25111,7 @@
     </row>
     <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B348" s="8" t="s">
         <v>468</v>
@@ -25164,7 +25176,7 @@
     </row>
     <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B349" s="8" t="s">
         <v>469</v>
@@ -25225,7 +25237,7 @@
     </row>
     <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B350" s="8" t="s">
         <v>470</v>
@@ -25286,7 +25298,7 @@
     </row>
     <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B351" s="8" t="s">
         <v>471</v>
@@ -25349,7 +25361,7 @@
     </row>
     <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B352" s="8" t="s">
         <v>551</v>
@@ -25410,7 +25422,7 @@
     </row>
     <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B353" s="8" t="s">
         <v>552</v>
@@ -25471,7 +25483,7 @@
     </row>
     <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B354" s="8" t="s">
         <v>571</v>
@@ -25532,7 +25544,7 @@
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B355" s="8" t="s">
         <v>572</v>
@@ -25593,7 +25605,7 @@
     </row>
     <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B356" s="8" t="s">
         <v>573</v>
@@ -25654,7 +25666,7 @@
     </row>
     <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B357" s="8" t="s">
         <v>576</v>
@@ -26034,7 +26046,7 @@
       </c>
       <c r="D363" s="8"/>
       <c r="E363" s="2" t="s">
-        <v>568</v>
+        <v>28</v>
       </c>
       <c r="F363" s="2"/>
       <c r="G363" s="43"/>
@@ -26276,11 +26288,13 @@
       <c r="A367" s="2">
         <v>365</v>
       </c>
-      <c r="B367" s="8"/>
+      <c r="B367" s="8" t="s">
+        <v>601</v>
+      </c>
       <c r="C367" s="8"/>
       <c r="D367" s="8"/>
       <c r="E367" s="2" t="s">
-        <v>568</v>
+        <v>285</v>
       </c>
       <c r="F367" s="2"/>
       <c r="G367" s="43"/>
@@ -26307,7 +26321,7 @@
         <v>0</v>
       </c>
       <c r="P367" s="10">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q367" s="11"/>
       <c r="R367" s="4"/>
@@ -26316,30 +26330,32 @@
       <c r="U367" s="4"/>
       <c r="V367" s="5">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="W367" s="6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X367" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y367" s="6">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>366</v>
       </c>
-      <c r="B368" s="8"/>
+      <c r="B368" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="C368" s="8"/>
       <c r="D368" s="8"/>
       <c r="E368" s="2" t="s">
-        <v>568</v>
+        <v>285</v>
       </c>
       <c r="F368" s="2"/>
       <c r="G368" s="43"/>
@@ -26366,7 +26382,7 @@
         <v>0</v>
       </c>
       <c r="P368" s="10">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="Q368" s="11"/>
       <c r="R368" s="4"/>
@@ -26375,19 +26391,19 @@
       <c r="U368" s="4"/>
       <c r="V368" s="5">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="W368" s="6">
         <f t="shared" si="21"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X368" s="6">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y368" s="6">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369" spans="1:25" x14ac:dyDescent="0.25">
@@ -26433,72 +26449,522 @@
       <c r="T369" s="4"/>
       <c r="U369" s="4"/>
       <c r="V369" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="V369" si="25">SUM(J369:U369)</f>
         <v>0</v>
       </c>
       <c r="W369" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="W369" si="26">V369/400000</f>
         <v>0</v>
       </c>
       <c r="X369" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="X369" si="27">COUNTIF(J369:U369,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="Y369" s="6">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:25" s="47" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B370" s="48"/>
-      <c r="C370" s="48"/>
-      <c r="D370" s="48"/>
-      <c r="E370" s="48"/>
-      <c r="F370" s="48"/>
-      <c r="G370" s="49"/>
-      <c r="H370" s="50"/>
-      <c r="I370" s="51"/>
-      <c r="J370" s="52"/>
-      <c r="K370" s="52"/>
-      <c r="L370" s="52"/>
-      <c r="M370" s="52"/>
-      <c r="N370" s="52"/>
-      <c r="O370" s="52"/>
-      <c r="P370" s="52"/>
-      <c r="Q370" s="52"/>
-      <c r="R370" s="52"/>
-      <c r="S370" s="52"/>
-      <c r="T370" s="52"/>
-      <c r="U370" s="52"/>
+        <f t="shared" ref="Y369" si="28">ROUNDUP(W369,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A370" s="2">
+        <v>368</v>
+      </c>
+      <c r="B370" s="8"/>
+      <c r="C370" s="8"/>
+      <c r="D370" s="8"/>
+      <c r="E370" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F370" s="2"/>
+      <c r="G370" s="43"/>
+      <c r="H370" s="44"/>
+      <c r="I370" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J370" s="4">
+        <v>0</v>
+      </c>
+      <c r="K370" s="4">
+        <v>0</v>
+      </c>
+      <c r="L370" s="4">
+        <v>0</v>
+      </c>
+      <c r="M370" s="4">
+        <v>0</v>
+      </c>
+      <c r="N370" s="10">
+        <v>0</v>
+      </c>
+      <c r="O370" s="4">
+        <v>0</v>
+      </c>
+      <c r="P370" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q370" s="11"/>
+      <c r="R370" s="4"/>
+      <c r="S370" s="4"/>
+      <c r="T370" s="4"/>
+      <c r="U370" s="4"/>
+      <c r="V370" s="5">
+        <f t="shared" ref="V370:V376" si="29">SUM(J370:U370)</f>
+        <v>0</v>
+      </c>
+      <c r="W370" s="6">
+        <f t="shared" ref="W370:W376" si="30">V370/400000</f>
+        <v>0</v>
+      </c>
+      <c r="X370" s="6">
+        <f t="shared" ref="X370:X376" si="31">COUNTIF(J370:U370,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="Y370" s="6">
+        <f t="shared" ref="Y370:Y376" si="32">ROUNDUP(W370,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="371" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A371" s="13"/>
-      <c r="B371" s="13"/>
-      <c r="C371" s="13"/>
-      <c r="D371" s="13"/>
-      <c r="E371" s="13"/>
-      <c r="F371" s="13"/>
-      <c r="G371" s="13"/>
-      <c r="H371" s="13"/>
-      <c r="I371" s="13"/>
-      <c r="J371" s="14"/>
-      <c r="K371" s="14"/>
-      <c r="L371" s="14"/>
-      <c r="M371" s="14"/>
-      <c r="N371" s="14"/>
-      <c r="O371" s="14"/>
-      <c r="P371" s="15"/>
-      <c r="Q371" s="15"/>
-      <c r="R371" s="15"/>
-      <c r="S371" s="14"/>
-      <c r="T371" s="14"/>
-      <c r="U371" s="14"/>
+      <c r="A371" s="2">
+        <v>369</v>
+      </c>
+      <c r="B371" s="8"/>
+      <c r="C371" s="8"/>
+      <c r="D371" s="8"/>
+      <c r="E371" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F371" s="2"/>
+      <c r="G371" s="43"/>
+      <c r="H371" s="44"/>
+      <c r="I371" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J371" s="4">
+        <v>0</v>
+      </c>
+      <c r="K371" s="4">
+        <v>0</v>
+      </c>
+      <c r="L371" s="4">
+        <v>0</v>
+      </c>
+      <c r="M371" s="4">
+        <v>0</v>
+      </c>
+      <c r="N371" s="10">
+        <v>0</v>
+      </c>
+      <c r="O371" s="4">
+        <v>0</v>
+      </c>
+      <c r="P371" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q371" s="11"/>
+      <c r="R371" s="4"/>
+      <c r="S371" s="4"/>
+      <c r="T371" s="4"/>
+      <c r="U371" s="4"/>
+      <c r="V371" s="5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="W371" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X371" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y371" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A372" s="2">
+        <v>370</v>
+      </c>
+      <c r="B372" s="8"/>
+      <c r="C372" s="8"/>
+      <c r="D372" s="8"/>
+      <c r="E372" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F372" s="2"/>
+      <c r="G372" s="43"/>
+      <c r="H372" s="44"/>
+      <c r="I372" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J372" s="4">
+        <v>0</v>
+      </c>
+      <c r="K372" s="4">
+        <v>0</v>
+      </c>
+      <c r="L372" s="4">
+        <v>0</v>
+      </c>
+      <c r="M372" s="4">
+        <v>0</v>
+      </c>
+      <c r="N372" s="10">
+        <v>0</v>
+      </c>
+      <c r="O372" s="4">
+        <v>0</v>
+      </c>
+      <c r="P372" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q372" s="11"/>
+      <c r="R372" s="4"/>
+      <c r="S372" s="4"/>
+      <c r="T372" s="4"/>
+      <c r="U372" s="4"/>
+      <c r="V372" s="5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="W372" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X372" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y372" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A373" s="2">
+        <v>371</v>
+      </c>
+      <c r="B373" s="8"/>
+      <c r="C373" s="8"/>
+      <c r="D373" s="8"/>
+      <c r="E373" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F373" s="2"/>
+      <c r="G373" s="43"/>
+      <c r="H373" s="44"/>
+      <c r="I373" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J373" s="4">
+        <v>0</v>
+      </c>
+      <c r="K373" s="4">
+        <v>0</v>
+      </c>
+      <c r="L373" s="4">
+        <v>0</v>
+      </c>
+      <c r="M373" s="4">
+        <v>0</v>
+      </c>
+      <c r="N373" s="10">
+        <v>0</v>
+      </c>
+      <c r="O373" s="4">
+        <v>0</v>
+      </c>
+      <c r="P373" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q373" s="11"/>
+      <c r="R373" s="4"/>
+      <c r="S373" s="4"/>
+      <c r="T373" s="4"/>
+      <c r="U373" s="4"/>
+      <c r="V373" s="5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="W373" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X373" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y373" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A374" s="2">
+        <v>372</v>
+      </c>
+      <c r="B374" s="8"/>
+      <c r="C374" s="8"/>
+      <c r="D374" s="8"/>
+      <c r="E374" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F374" s="2"/>
+      <c r="G374" s="43"/>
+      <c r="H374" s="44"/>
+      <c r="I374" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J374" s="4">
+        <v>0</v>
+      </c>
+      <c r="K374" s="4">
+        <v>0</v>
+      </c>
+      <c r="L374" s="4">
+        <v>0</v>
+      </c>
+      <c r="M374" s="4">
+        <v>0</v>
+      </c>
+      <c r="N374" s="10">
+        <v>0</v>
+      </c>
+      <c r="O374" s="4">
+        <v>0</v>
+      </c>
+      <c r="P374" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q374" s="11"/>
+      <c r="R374" s="4"/>
+      <c r="S374" s="4"/>
+      <c r="T374" s="4"/>
+      <c r="U374" s="4"/>
+      <c r="V374" s="5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="W374" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X374" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y374" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="375" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="J375" s="16"/>
+      <c r="A375" s="2">
+        <v>373</v>
+      </c>
+      <c r="B375" s="8"/>
+      <c r="C375" s="8"/>
+      <c r="D375" s="8"/>
+      <c r="E375" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F375" s="2"/>
+      <c r="G375" s="43"/>
+      <c r="H375" s="44"/>
+      <c r="I375" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J375" s="4">
+        <v>0</v>
+      </c>
+      <c r="K375" s="4">
+        <v>0</v>
+      </c>
+      <c r="L375" s="4">
+        <v>0</v>
+      </c>
+      <c r="M375" s="4">
+        <v>0</v>
+      </c>
+      <c r="N375" s="10">
+        <v>0</v>
+      </c>
+      <c r="O375" s="4">
+        <v>0</v>
+      </c>
+      <c r="P375" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q375" s="11"/>
+      <c r="R375" s="4"/>
+      <c r="S375" s="4"/>
+      <c r="T375" s="4"/>
+      <c r="U375" s="4"/>
+      <c r="V375" s="5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="W375" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X375" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y375" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A376" s="2">
+        <v>374</v>
+      </c>
+      <c r="B376" s="8"/>
+      <c r="C376" s="8"/>
+      <c r="D376" s="8"/>
+      <c r="E376" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F376" s="2"/>
+      <c r="G376" s="43"/>
+      <c r="H376" s="44"/>
+      <c r="I376" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J376" s="4">
+        <v>0</v>
+      </c>
+      <c r="K376" s="4">
+        <v>0</v>
+      </c>
+      <c r="L376" s="4">
+        <v>0</v>
+      </c>
+      <c r="M376" s="4">
+        <v>0</v>
+      </c>
+      <c r="N376" s="10">
+        <v>0</v>
+      </c>
+      <c r="O376" s="4">
+        <v>0</v>
+      </c>
+      <c r="P376" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q376" s="11"/>
+      <c r="R376" s="4"/>
+      <c r="S376" s="4"/>
+      <c r="T376" s="4"/>
+      <c r="U376" s="4"/>
+      <c r="V376" s="5">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="W376" s="6">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="X376" s="6">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y376" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:25" s="47" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A377" s="2">
+        <v>375</v>
+      </c>
+      <c r="B377" s="8"/>
+      <c r="C377" s="8"/>
+      <c r="D377" s="8"/>
+      <c r="E377" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F377" s="2"/>
+      <c r="G377" s="43"/>
+      <c r="H377" s="44"/>
+      <c r="I377" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J377" s="4">
+        <v>0</v>
+      </c>
+      <c r="K377" s="4">
+        <v>0</v>
+      </c>
+      <c r="L377" s="4">
+        <v>0</v>
+      </c>
+      <c r="M377" s="4">
+        <v>0</v>
+      </c>
+      <c r="N377" s="10">
+        <v>0</v>
+      </c>
+      <c r="O377" s="4">
+        <v>0</v>
+      </c>
+      <c r="P377" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q377" s="11"/>
+      <c r="R377" s="4"/>
+      <c r="S377" s="4"/>
+      <c r="T377" s="4"/>
+      <c r="U377" s="4"/>
+      <c r="V377" s="5">
+        <f t="shared" ref="V377" si="33">SUM(J377:U377)</f>
+        <v>0</v>
+      </c>
+      <c r="W377" s="6">
+        <f t="shared" ref="W377" si="34">V377/400000</f>
+        <v>0</v>
+      </c>
+      <c r="X377" s="6">
+        <f t="shared" ref="X377" si="35">COUNTIF(J377:U377,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="Y377" s="6">
+        <f t="shared" ref="Y377" si="36">ROUNDUP(W377,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A378" s="13"/>
+      <c r="B378" s="13"/>
+      <c r="C378" s="13"/>
+      <c r="D378" s="13"/>
+      <c r="E378" s="13"/>
+      <c r="F378" s="13"/>
+      <c r="G378" s="13"/>
+      <c r="H378" s="13"/>
+      <c r="I378" s="13"/>
+      <c r="J378" s="14"/>
+      <c r="K378" s="14"/>
+      <c r="L378" s="14"/>
+      <c r="M378" s="14"/>
+      <c r="N378" s="14"/>
+      <c r="O378" s="14"/>
+      <c r="P378" s="15"/>
+      <c r="Q378" s="15"/>
+      <c r="R378" s="15"/>
+      <c r="S378" s="14"/>
+      <c r="T378" s="14"/>
+      <c r="U378" s="14"/>
+    </row>
+    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="J382" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y370" xr:uid="{C6945147-255D-4DEE-A923-83C03D92F174}"/>
+  <autoFilter ref="A4:Y377" xr:uid="{C6945147-255D-4DEE-A923-83C03D92F174}"/>
   <mergeCells count="1">
     <mergeCell ref="J3:U3"/>
   </mergeCells>

--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47072F2-B6E4-4533-BDF7-26B044DE00B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7C670E-BF4B-4102-AB3B-6D1EDE067425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
@@ -2562,7 +2562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4685470C-085C-48D5-B824-F806273A25BF}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:Y386"/>
@@ -2691,7 +2691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>3</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>4</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>5</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>6</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>7</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>8</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>9</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -3495,7 +3495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>36</v>
       </c>
@@ -5151,7 +5151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>37</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>38</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>39</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>40</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>41</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>42</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>43</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>44</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>45</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>46</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>47</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>48</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>49</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>50</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>51</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>52</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>53</v>
       </c>
@@ -6320,7 +6320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>54</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>55</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>56</v>
       </c>
@@ -6525,7 +6525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>57</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>58</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>59</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>60</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>61</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>63</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>64</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>65</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>66</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>67</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>68</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>69</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>70</v>
       </c>
@@ -7475,7 +7475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>71</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>72</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>73</v>
       </c>
@@ -7678,7 +7678,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>74</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>75</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>76</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>77</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>78</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>79</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>80</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>81</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>82</v>
       </c>
@@ -8297,7 +8297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>83</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>84</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>85</v>
       </c>
@@ -8500,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>86</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>87</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>88</v>
       </c>
@@ -8699,7 +8699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>89</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>90</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>91</v>
       </c>
@@ -8904,7 +8904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>92</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>93</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>94</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>95</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>96</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>97</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>98</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>99</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>100</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>101</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>102</v>
       </c>
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>103</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>104</v>
       </c>
@@ -9781,7 +9781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>105</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>106</v>
       </c>
@@ -9921,7 +9921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>107</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>108</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>109</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>110</v>
       </c>
@@ -10195,7 +10195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>111</v>
       </c>
@@ -10258,7 +10258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>112</v>
       </c>
@@ -10329,7 +10329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>113</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>114</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>115</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>116</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>117</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>118</v>
       </c>
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>119</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>120</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>121</v>
       </c>
@@ -10938,7 +10938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>122</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>123</v>
       </c>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>124</v>
       </c>
@@ -11139,7 +11139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>125</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>126</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>127</v>
       </c>
@@ -11344,7 +11344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>128</v>
       </c>
@@ -11409,7 +11409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>129</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>130</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>131</v>
       </c>
@@ -11606,7 +11606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>132</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>133</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>134</v>
       </c>
@@ -11817,7 +11817,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>135</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>136</v>
       </c>
@@ -11945,7 +11945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>137</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>138</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>139</v>
       </c>
@@ -12144,7 +12144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>140</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>141</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>142</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>143</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>144</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>145</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>146</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>147</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>148</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>149</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>150</v>
       </c>
@@ -12859,7 +12859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>151</v>
       </c>
@@ -12928,7 +12928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>152</v>
       </c>
@@ -12997,7 +12997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>153</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>154</v>
       </c>
@@ -13133,7 +13133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>155</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>156</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>157</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>158</v>
       </c>
@@ -13397,7 +13397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>159</v>
       </c>
@@ -13466,7 +13466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>160</v>
       </c>
@@ -13529,7 +13529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>161</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>162</v>
       </c>
@@ -13663,7 +13663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>163</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>164</v>
       </c>
@@ -13793,7 +13793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>165</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>166</v>
       </c>
@@ -13923,7 +13923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>167</v>
       </c>
@@ -13992,7 +13992,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>168</v>
       </c>
@@ -14057,7 +14057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>169</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>170</v>
       </c>
@@ -14187,7 +14187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>171</v>
       </c>
@@ -14254,7 +14254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>172</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>173</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>174</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>175</v>
       </c>
@@ -14530,7 +14530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>176</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>177</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>178</v>
       </c>
@@ -14729,7 +14729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>179</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>180</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>181</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>182</v>
       </c>
@@ -14991,7 +14991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>183</v>
       </c>
@@ -15056,7 +15056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>184</v>
       </c>
@@ -15121,7 +15121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>185</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>186</v>
       </c>
@@ -15259,7 +15259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>187</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>188</v>
       </c>
@@ -15391,7 +15391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>189</v>
       </c>
@@ -15460,7 +15460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>190</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>191</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>192</v>
       </c>
@@ -15657,7 +15657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>193</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>194</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>195</v>
       </c>
@@ -15864,7 +15864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>196</v>
       </c>
@@ -15933,7 +15933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>197</v>
       </c>
@@ -15996,7 +15996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>198</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>199</v>
       </c>
@@ -16134,7 +16134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>200</v>
       </c>
@@ -16197,7 +16197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>201</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>202</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>203</v>
       </c>
@@ -16394,7 +16394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>204</v>
       </c>
@@ -16463,7 +16463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>205</v>
       </c>
@@ -16534,7 +16534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>206</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>207</v>
       </c>
@@ -16672,7 +16672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>208</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>209</v>
       </c>
@@ -16810,7 +16810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>210</v>
       </c>
@@ -16879,7 +16879,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>211</v>
       </c>
@@ -16948,7 +16948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>212</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>213</v>
       </c>
@@ -17086,7 +17086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>214</v>
       </c>
@@ -17155,7 +17155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>215</v>
       </c>
@@ -17224,7 +17224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>216</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>217</v>
       </c>
@@ -17362,7 +17362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>218</v>
       </c>
@@ -17431,7 +17431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>219</v>
       </c>
@@ -17500,7 +17500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>220</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>221</v>
       </c>
@@ -17638,7 +17638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>222</v>
       </c>
@@ -17707,7 +17707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>223</v>
       </c>
@@ -17776,7 +17776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>224</v>
       </c>
@@ -17845,7 +17845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>225</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>226</v>
       </c>
@@ -17983,7 +17983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>227</v>
       </c>
@@ -18052,7 +18052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>228</v>
       </c>
@@ -18121,7 +18121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>229</v>
       </c>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>230</v>
       </c>
@@ -18259,7 +18259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>231</v>
       </c>
@@ -18328,7 +18328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>232</v>
       </c>
@@ -18397,7 +18397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>233</v>
       </c>
@@ -18466,7 +18466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>234</v>
       </c>
@@ -18533,7 +18533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>235</v>
       </c>
@@ -18602,7 +18602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>236</v>
       </c>
@@ -18671,7 +18671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>237</v>
       </c>
@@ -18740,7 +18740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>238</v>
       </c>
@@ -18809,7 +18809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>239</v>
       </c>
@@ -18878,7 +18878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>240</v>
       </c>
@@ -18947,7 +18947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>241</v>
       </c>
@@ -19016,7 +19016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>242</v>
       </c>
@@ -19085,7 +19085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>243</v>
       </c>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>244</v>
       </c>
@@ -19223,7 +19223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>245</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>246</v>
       </c>
@@ -19361,7 +19361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>247</v>
       </c>
@@ -19430,7 +19430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>248</v>
       </c>
@@ -19499,7 +19499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>249</v>
       </c>
@@ -19566,7 +19566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>250</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>251</v>
       </c>
@@ -19704,7 +19704,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>252</v>
       </c>
@@ -19775,7 +19775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>253</v>
       </c>
@@ -19846,7 +19846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>254</v>
       </c>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>255</v>
       </c>
@@ -19984,7 +19984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>256</v>
       </c>
@@ -20053,7 +20053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>257</v>
       </c>
@@ -20122,7 +20122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>258</v>
       </c>
@@ -20191,7 +20191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>259</v>
       </c>
@@ -20260,7 +20260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>260</v>
       </c>
@@ -20329,7 +20329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>261</v>
       </c>
@@ -20396,7 +20396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>262</v>
       </c>
@@ -20465,7 +20465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>263</v>
       </c>
@@ -20530,7 +20530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>264</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>265</v>
       </c>
@@ -20666,7 +20666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>266</v>
       </c>
@@ -20735,7 +20735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>267</v>
       </c>
@@ -20802,7 +20802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>268</v>
       </c>
@@ -20871,7 +20871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>269</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>270</v>
       </c>
@@ -21007,7 +21007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>271</v>
       </c>
@@ -21076,7 +21076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>272</v>
       </c>
@@ -21145,7 +21145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>273</v>
       </c>
@@ -21212,7 +21212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>274</v>
       </c>
@@ -21279,7 +21279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>275</v>
       </c>
@@ -21344,7 +21344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>276</v>
       </c>
@@ -21409,7 +21409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>277</v>
       </c>
@@ -21474,7 +21474,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>278</v>
       </c>
@@ -21541,7 +21541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>279</v>
       </c>
@@ -21604,7 +21604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>280</v>
       </c>
@@ -21667,7 +21667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>281</v>
       </c>
@@ -21734,7 +21734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>282</v>
       </c>
@@ -21799,7 +21799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>283</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>284</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>285</v>
       </c>
@@ -21994,7 +21994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>286</v>
       </c>
@@ -22061,7 +22061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>287</v>
       </c>
@@ -22128,7 +22128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>288</v>
       </c>
@@ -22195,7 +22195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>289</v>
       </c>
@@ -22260,7 +22260,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>290</v>
       </c>
@@ -22323,7 +22323,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>291</v>
       </c>
@@ -22390,7 +22390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>292</v>
       </c>
@@ -22457,7 +22457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>293</v>
       </c>
@@ -22520,7 +22520,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>294</v>
       </c>
@@ -22583,7 +22583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>295</v>
       </c>
@@ -22646,7 +22646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>296</v>
       </c>
@@ -22709,7 +22709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>297</v>
       </c>
@@ -22774,7 +22774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>298</v>
       </c>
@@ -22841,7 +22841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>299</v>
       </c>
@@ -22908,7 +22908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>300</v>
       </c>
@@ -22973,7 +22973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>301</v>
       </c>
@@ -23040,7 +23040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>302</v>
       </c>
@@ -23107,7 +23107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>303</v>
       </c>
@@ -23174,7 +23174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>304</v>
       </c>
@@ -23237,7 +23237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>305</v>
       </c>
@@ -23304,7 +23304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>306</v>
       </c>
@@ -23371,7 +23371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>307</v>
       </c>
@@ -23434,7 +23434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>308</v>
       </c>
@@ -23497,7 +23497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>309</v>
       </c>
@@ -23560,7 +23560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>310</v>
       </c>
@@ -23623,7 +23623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>311</v>
       </c>
@@ -23690,7 +23690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>312</v>
       </c>
@@ -23753,7 +23753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>313</v>
       </c>
@@ -23816,7 +23816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>314</v>
       </c>
@@ -23879,7 +23879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>315</v>
       </c>
@@ -23946,7 +23946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>316</v>
       </c>
@@ -24009,7 +24009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>317</v>
       </c>
@@ -24074,7 +24074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>318</v>
       </c>
@@ -24137,7 +24137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>319</v>
       </c>
@@ -24200,7 +24200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>320</v>
       </c>
@@ -24263,7 +24263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>321</v>
       </c>
@@ -24330,7 +24330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>322</v>
       </c>
@@ -24397,7 +24397,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>323</v>
       </c>
@@ -24464,7 +24464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>324</v>
       </c>
@@ -24529,7 +24529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>325</v>
       </c>
@@ -24594,7 +24594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>326</v>
       </c>
@@ -24659,7 +24659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>327</v>
       </c>
@@ -24724,7 +24724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>328</v>
       </c>
@@ -24789,7 +24789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>329</v>
       </c>
@@ -24854,7 +24854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>330</v>
       </c>
@@ -24919,7 +24919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>331</v>
       </c>
@@ -24980,7 +24980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>332</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>333</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>334</v>
       </c>
@@ -25173,7 +25173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>335</v>
       </c>
@@ -25238,7 +25238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>336</v>
       </c>
@@ -25303,7 +25303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>337</v>
       </c>
@@ -25368,7 +25368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>338</v>
       </c>
@@ -25431,7 +25431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>339</v>
       </c>
@@ -25492,7 +25492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>340</v>
       </c>
@@ -25557,7 +25557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>341</v>
       </c>
@@ -25622,7 +25622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>342</v>
       </c>
@@ -25685,7 +25685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>343</v>
       </c>
@@ -25750,7 +25750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>344</v>
       </c>
@@ -25811,7 +25811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>345</v>
       </c>
@@ -25872,7 +25872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>348</v>
       </c>
@@ -25935,7 +25935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>349</v>
       </c>
@@ -25996,7 +25996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>350</v>
       </c>
@@ -26057,7 +26057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>351</v>
       </c>
@@ -26118,7 +26118,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>352</v>
       </c>
@@ -26179,7 +26179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>353</v>
       </c>
@@ -26240,7 +26240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>354</v>
       </c>
@@ -26303,7 +26303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>355</v>
       </c>
@@ -26364,7 +26364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>356</v>
       </c>
@@ -26425,7 +26425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>357</v>
       </c>
@@ -26486,7 +26486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>358</v>
       </c>
@@ -26547,7 +26547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>359</v>
       </c>
@@ -26610,7 +26610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>360</v>
       </c>
@@ -26673,7 +26673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>361</v>
       </c>
@@ -26738,7 +26738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>362</v>
       </c>
@@ -26799,7 +26799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>363</v>
       </c>
@@ -26860,7 +26860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>364</v>
       </c>
@@ -26921,7 +26921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>365</v>
       </c>
@@ -26982,7 +26982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>366</v>
       </c>
@@ -27043,7 +27043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>367</v>
       </c>
@@ -27104,7 +27104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>368</v>
       </c>
@@ -27169,7 +27169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>369</v>
       </c>
@@ -27234,7 +27234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <v>370</v>
       </c>
@@ -27299,7 +27299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>371</v>
       </c>
@@ -27360,7 +27360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>372</v>
       </c>
@@ -27423,7 +27423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <v>373</v>
       </c>
@@ -27486,7 +27486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>374</v>
       </c>
@@ -27549,7 +27549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:25" s="46" customFormat="1" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:25" s="46" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>375</v>
       </c>
@@ -27612,7 +27612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:25" s="46" customFormat="1" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:25" s="46" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A378" s="2"/>
       <c r="B378" s="8" t="s">
         <v>620</v>
@@ -27661,7 +27661,7 @@
       <c r="X378" s="6"/>
       <c r="Y378" s="6"/>
     </row>
-    <row r="379" spans="1:25" s="46" customFormat="1" ht="12.75" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:25" s="46" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A379" s="2"/>
       <c r="B379" s="8" t="s">
         <v>621</v>
@@ -27900,13 +27900,7 @@
       <c r="Y386" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y379" xr:uid="{C6945147-255D-4DEE-A923-83C03D92F174}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Sta marta"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:Y379" xr:uid="{C6945147-255D-4DEE-A923-83C03D92F174}"/>
   <mergeCells count="1">
     <mergeCell ref="J3:U3"/>
   </mergeCells>

--- a/inversionistas-del-reino-colombia/data/dashboard.xlsx
+++ b/inversionistas-del-reino-colombia/data/dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Iglesia\INVERSIONISTAS DEL REINO\2026\1. ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30204F4-DE68-4A27-83B0-082E8B4B4F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA25622-E337-4B59-8F99-47BC58D492B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A90E9E2-D95C-4E11-9440-BC96C0602631}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1565" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="627">
   <si>
     <t>NO.</t>
   </si>
@@ -24808,7 +24808,9 @@
       <c r="F333" s="2"/>
       <c r="G333" s="42"/>
       <c r="H333" s="43"/>
-      <c r="I333" s="3"/>
+      <c r="I333" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J333" s="4">
         <v>0</v>
       </c>
@@ -24873,7 +24875,9 @@
       <c r="F334" s="2"/>
       <c r="G334" s="42"/>
       <c r="H334" s="43"/>
-      <c r="I334" s="3"/>
+      <c r="I334" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J334" s="4">
         <v>0</v>
       </c>
@@ -24934,7 +24938,9 @@
       <c r="F335" s="2"/>
       <c r="G335" s="42"/>
       <c r="H335" s="43"/>
-      <c r="I335" s="3"/>
+      <c r="I335" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J335" s="4">
         <v>0</v>
       </c>
@@ -24999,7 +25005,9 @@
       <c r="F336" s="2"/>
       <c r="G336" s="42"/>
       <c r="H336" s="43"/>
-      <c r="I336" s="3"/>
+      <c r="I336" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J336" s="4">
         <v>0</v>
       </c>
@@ -25062,7 +25070,9 @@
       <c r="F337" s="2"/>
       <c r="G337" s="42"/>
       <c r="H337" s="43"/>
-      <c r="I337" s="3"/>
+      <c r="I337" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J337" s="4">
         <v>0</v>
       </c>
@@ -25127,7 +25137,9 @@
       <c r="F338" s="2"/>
       <c r="G338" s="42"/>
       <c r="H338" s="43"/>
-      <c r="I338" s="3"/>
+      <c r="I338" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J338" s="4">
         <v>0</v>
       </c>
@@ -25192,7 +25204,9 @@
       <c r="F339" s="2"/>
       <c r="G339" s="42"/>
       <c r="H339" s="43"/>
-      <c r="I339" s="3"/>
+      <c r="I339" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J339" s="4">
         <v>0</v>
       </c>
@@ -25257,7 +25271,9 @@
       <c r="F340" s="2"/>
       <c r="G340" s="42"/>
       <c r="H340" s="43"/>
-      <c r="I340" s="3"/>
+      <c r="I340" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J340" s="4">
         <v>0</v>
       </c>
@@ -25322,7 +25338,9 @@
       <c r="F341" s="2"/>
       <c r="G341" s="42"/>
       <c r="H341" s="43"/>
-      <c r="I341" s="3"/>
+      <c r="I341" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J341" s="4">
         <v>0</v>
       </c>
@@ -25385,7 +25403,9 @@
       <c r="F342" s="2"/>
       <c r="G342" s="42"/>
       <c r="H342" s="43"/>
-      <c r="I342" s="3"/>
+      <c r="I342" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J342" s="4">
         <v>0</v>
       </c>
@@ -25446,7 +25466,9 @@
       <c r="F343" s="2"/>
       <c r="G343" s="42"/>
       <c r="H343" s="43"/>
-      <c r="I343" s="3"/>
+      <c r="I343" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J343" s="4">
         <v>0</v>
       </c>
@@ -25511,7 +25533,9 @@
       <c r="F344" s="2"/>
       <c r="G344" s="42"/>
       <c r="H344" s="43"/>
-      <c r="I344" s="3"/>
+      <c r="I344" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J344" s="4">
         <v>0</v>
       </c>
@@ -25576,7 +25600,9 @@
       <c r="F345" s="2"/>
       <c r="G345" s="42"/>
       <c r="H345" s="43"/>
-      <c r="I345" s="3"/>
+      <c r="I345" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J345" s="4">
         <v>0</v>
       </c>
@@ -25639,7 +25665,9 @@
       <c r="F346" s="2"/>
       <c r="G346" s="42"/>
       <c r="H346" s="43"/>
-      <c r="I346" s="3"/>
+      <c r="I346" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J346" s="4">
         <v>0</v>
       </c>
@@ -25704,7 +25732,9 @@
       <c r="F347" s="2"/>
       <c r="G347" s="42"/>
       <c r="H347" s="43"/>
-      <c r="I347" s="3"/>
+      <c r="I347" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J347" s="4">
         <v>0</v>
       </c>
@@ -25765,7 +25795,9 @@
       <c r="F348" s="2"/>
       <c r="G348" s="42"/>
       <c r="H348" s="43"/>
-      <c r="I348" s="3"/>
+      <c r="I348" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J348" s="4">
         <v>0</v>
       </c>
@@ -25826,7 +25858,9 @@
       <c r="F349" s="2"/>
       <c r="G349" s="42"/>
       <c r="H349" s="43"/>
-      <c r="I349" s="3"/>
+      <c r="I349" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J349" s="4">
         <v>0</v>
       </c>
@@ -25889,7 +25923,9 @@
       <c r="F350" s="2"/>
       <c r="G350" s="42"/>
       <c r="H350" s="43"/>
-      <c r="I350" s="3"/>
+      <c r="I350" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J350" s="4">
         <v>0</v>
       </c>
@@ -25950,7 +25986,9 @@
       <c r="F351" s="2"/>
       <c r="G351" s="42"/>
       <c r="H351" s="43"/>
-      <c r="I351" s="3"/>
+      <c r="I351" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J351" s="4">
         <v>0</v>
       </c>
@@ -26011,7 +26049,9 @@
       <c r="F352" s="2"/>
       <c r="G352" s="42"/>
       <c r="H352" s="43"/>
-      <c r="I352" s="3"/>
+      <c r="I352" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J352" s="4">
         <v>0</v>
       </c>
@@ -26072,7 +26112,9 @@
       <c r="F353" s="2"/>
       <c r="G353" s="42"/>
       <c r="H353" s="43"/>
-      <c r="I353" s="3"/>
+      <c r="I353" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J353" s="4">
         <v>0</v>
       </c>
@@ -26133,7 +26175,9 @@
       <c r="F354" s="2"/>
       <c r="G354" s="42"/>
       <c r="H354" s="43"/>
-      <c r="I354" s="3"/>
+      <c r="I354" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J354" s="4">
         <v>0</v>
       </c>
@@ -26194,7 +26238,9 @@
       <c r="F355" s="2"/>
       <c r="G355" s="42"/>
       <c r="H355" s="43"/>
-      <c r="I355" s="3"/>
+      <c r="I355" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J355" s="4">
         <v>0</v>
       </c>
@@ -26257,7 +26303,9 @@
       <c r="F356" s="2"/>
       <c r="G356" s="42"/>
       <c r="H356" s="43"/>
-      <c r="I356" s="3"/>
+      <c r="I356" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J356" s="4">
         <v>0</v>
       </c>
@@ -26318,7 +26366,9 @@
       <c r="F357" s="2"/>
       <c r="G357" s="42"/>
       <c r="H357" s="43"/>
-      <c r="I357" s="3"/>
+      <c r="I357" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J357" s="4">
         <v>0</v>
       </c>
@@ -26379,7 +26429,9 @@
       <c r="F358" s="2"/>
       <c r="G358" s="42"/>
       <c r="H358" s="43"/>
-      <c r="I358" s="3"/>
+      <c r="I358" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J358" s="4">
         <v>0</v>
       </c>
@@ -26440,7 +26492,9 @@
       <c r="F359" s="2"/>
       <c r="G359" s="42"/>
       <c r="H359" s="43"/>
-      <c r="I359" s="3"/>
+      <c r="I359" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J359" s="4">
         <v>0</v>
       </c>
@@ -26501,7 +26555,9 @@
       <c r="F360" s="2"/>
       <c r="G360" s="42"/>
       <c r="H360" s="43"/>
-      <c r="I360" s="3"/>
+      <c r="I360" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J360" s="4">
         <v>0</v>
       </c>
@@ -26564,7 +26620,9 @@
       <c r="F361" s="2"/>
       <c r="G361" s="42"/>
       <c r="H361" s="43"/>
-      <c r="I361" s="3"/>
+      <c r="I361" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J361" s="4">
         <v>0</v>
       </c>
@@ -26627,7 +26685,9 @@
       <c r="F362" s="2"/>
       <c r="G362" s="42"/>
       <c r="H362" s="43"/>
-      <c r="I362" s="3"/>
+      <c r="I362" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J362" s="4">
         <v>0</v>
       </c>
@@ -26692,7 +26752,9 @@
       <c r="F363" s="2"/>
       <c r="G363" s="42"/>
       <c r="H363" s="43"/>
-      <c r="I363" s="3"/>
+      <c r="I363" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J363" s="4">
         <v>0</v>
       </c>
@@ -26753,7 +26815,9 @@
       <c r="F364" s="2"/>
       <c r="G364" s="42"/>
       <c r="H364" s="43"/>
-      <c r="I364" s="3"/>
+      <c r="I364" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J364" s="4">
         <v>0</v>
       </c>
@@ -26814,7 +26878,9 @@
       <c r="F365" s="2"/>
       <c r="G365" s="42"/>
       <c r="H365" s="43"/>
-      <c r="I365" s="3"/>
+      <c r="I365" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J365" s="4">
         <v>0</v>
       </c>
@@ -26875,7 +26941,9 @@
       <c r="F366" s="2"/>
       <c r="G366" s="42"/>
       <c r="H366" s="43"/>
-      <c r="I366" s="3"/>
+      <c r="I366" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J366" s="4">
         <v>0</v>
       </c>
@@ -26936,7 +27004,9 @@
       <c r="F367" s="2"/>
       <c r="G367" s="42"/>
       <c r="H367" s="43"/>
-      <c r="I367" s="3"/>
+      <c r="I367" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J367" s="4">
         <v>0</v>
       </c>
@@ -26997,7 +27067,9 @@
       <c r="F368" s="2"/>
       <c r="G368" s="42"/>
       <c r="H368" s="43"/>
-      <c r="I368" s="3"/>
+      <c r="I368" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J368" s="4">
         <v>0</v>
       </c>
@@ -27058,7 +27130,9 @@
       <c r="F369" s="2"/>
       <c r="G369" s="42"/>
       <c r="H369" s="43"/>
-      <c r="I369" s="3"/>
+      <c r="I369" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J369" s="4">
         <v>0</v>
       </c>
@@ -27123,7 +27197,9 @@
       <c r="F370" s="2"/>
       <c r="G370" s="42"/>
       <c r="H370" s="43"/>
-      <c r="I370" s="3"/>
+      <c r="I370" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J370" s="4">
         <v>0</v>
       </c>
@@ -27188,7 +27264,9 @@
       <c r="F371" s="2"/>
       <c r="G371" s="42"/>
       <c r="H371" s="43"/>
-      <c r="I371" s="3"/>
+      <c r="I371" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J371" s="4">
         <v>0</v>
       </c>
@@ -27253,7 +27331,9 @@
       <c r="F372" s="2"/>
       <c r="G372" s="42"/>
       <c r="H372" s="43"/>
-      <c r="I372" s="3"/>
+      <c r="I372" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J372" s="4">
         <v>0</v>
       </c>
@@ -27314,7 +27394,9 @@
       <c r="F373" s="2"/>
       <c r="G373" s="42"/>
       <c r="H373" s="43"/>
-      <c r="I373" s="3"/>
+      <c r="I373" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J373" s="4">
         <v>0</v>
       </c>
@@ -27377,7 +27459,9 @@
       <c r="F374" s="2"/>
       <c r="G374" s="42"/>
       <c r="H374" s="43"/>
-      <c r="I374" s="3"/>
+      <c r="I374" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J374" s="4">
         <v>0</v>
       </c>
@@ -27440,7 +27524,9 @@
       <c r="F375" s="2"/>
       <c r="G375" s="42"/>
       <c r="H375" s="43"/>
-      <c r="I375" s="3"/>
+      <c r="I375" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J375" s="4">
         <v>0</v>
       </c>
@@ -27503,7 +27589,9 @@
       <c r="F376" s="2"/>
       <c r="G376" s="42"/>
       <c r="H376" s="43"/>
-      <c r="I376" s="3"/>
+      <c r="I376" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J376" s="4">
         <v>0</v>
       </c>
@@ -27566,7 +27654,9 @@
       <c r="F377" s="2"/>
       <c r="G377" s="42"/>
       <c r="H377" s="43"/>
-      <c r="I377" s="3"/>
+      <c r="I377" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J377" s="4">
         <v>0</v>
       </c>
@@ -27613,7 +27703,9 @@
       </c>
     </row>
     <row r="378" spans="1:25" s="46" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A378" s="2"/>
+      <c r="A378" s="2">
+        <v>376</v>
+      </c>
       <c r="B378" s="8" t="s">
         <v>620</v>
       </c>
@@ -27627,7 +27719,9 @@
       <c r="F378" s="2"/>
       <c r="G378" s="42"/>
       <c r="H378" s="43"/>
-      <c r="I378" s="3"/>
+      <c r="I378" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J378" s="4">
         <v>0</v>
       </c>
@@ -27662,7 +27756,9 @@
       <c r="Y378" s="6"/>
     </row>
     <row r="379" spans="1:25" s="46" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A379" s="2"/>
+      <c r="A379" s="2">
+        <v>377</v>
+      </c>
       <c r="B379" s="8" t="s">
         <v>621</v>
       </c>
@@ -27676,7 +27772,9 @@
       <c r="F379" s="2"/>
       <c r="G379" s="42"/>
       <c r="H379" s="43"/>
-      <c r="I379" s="3"/>
+      <c r="I379" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="J379" s="4">
         <v>0</v>
       </c>
